--- a/data/base_creditas.xlsx
+++ b/data/base_creditas.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C34709F1-C32F-4B25-ABFB-2679C6FC5D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="27">
   <si>
     <t>Data</t>
   </si>
@@ -83,13 +89,25 @@
   </si>
   <si>
     <t>Custo</t>
+  </si>
+  <si>
+    <t>Creditas_Locator</t>
+  </si>
+  <si>
+    <t>::</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>Locator_Creditas_benef</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,24 +159,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -196,7 +226,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -230,6 +260,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -264,9 +295,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -439,11 +471,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:W11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -512,6 +544,695 @@
       </c>
       <c r="W1" s="1" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B2">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>81</v>
+      </c>
+      <c r="D2">
+        <v>85</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2">
+        <v>34</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>0</v>
+      </c>
+      <c r="R2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B3">
+        <v>11</v>
+      </c>
+      <c r="C3">
+        <v>81</v>
+      </c>
+      <c r="D3">
+        <v>85</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3">
+        <v>34</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>9</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>0</v>
+      </c>
+      <c r="R3" t="s">
+        <v>25</v>
+      </c>
+      <c r="S3" t="s">
+        <v>25</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B4">
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>84</v>
+      </c>
+      <c r="D4">
+        <v>86</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>6</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4">
+        <v>2.3148148148148147E-5</v>
+      </c>
+      <c r="P4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="R4" s="3">
+        <v>0</v>
+      </c>
+      <c r="S4" t="s">
+        <v>25</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4" t="s">
+        <v>25</v>
+      </c>
+      <c r="W4">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B5">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>81</v>
+      </c>
+      <c r="D5">
+        <v>85</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5">
+        <v>34</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>26</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="P5" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>0.15379999999999999</v>
+      </c>
+      <c r="R5" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="S5" s="3">
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5" t="s">
+        <v>25</v>
+      </c>
+      <c r="W5">
+        <v>0.192</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B6">
+        <v>14</v>
+      </c>
+      <c r="C6">
+        <v>81</v>
+      </c>
+      <c r="D6">
+        <v>85</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6">
+        <v>34</v>
+      </c>
+      <c r="G6">
+        <v>10</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>44</v>
+      </c>
+      <c r="J6">
+        <v>21</v>
+      </c>
+      <c r="K6">
+        <v>14</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4">
+        <v>2.3148148148148147E-5</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1.7939814814814815E-3</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>0.4773</v>
+      </c>
+      <c r="R6" s="5">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0.35709999999999997</v>
+      </c>
+      <c r="T6">
+        <v>3</v>
+      </c>
+      <c r="U6" s="5">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="V6" s="5">
+        <v>0.42859999999999998</v>
+      </c>
+      <c r="W6">
+        <v>1.968</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B7">
+        <v>16</v>
+      </c>
+      <c r="C7">
+        <v>81</v>
+      </c>
+      <c r="D7">
+        <v>85</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7">
+        <v>34</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4">
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="P7" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>0.28570000000000001</v>
+      </c>
+      <c r="R7" s="3">
+        <v>0</v>
+      </c>
+      <c r="S7" t="s">
+        <v>25</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7" t="s">
+        <v>25</v>
+      </c>
+      <c r="W7">
+        <v>0.192</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B8">
+        <v>11</v>
+      </c>
+      <c r="C8">
+        <v>81</v>
+      </c>
+      <c r="D8">
+        <v>85</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8">
+        <v>33365</v>
+      </c>
+      <c r="G8">
+        <v>50</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>3681</v>
+      </c>
+      <c r="J8">
+        <v>70</v>
+      </c>
+      <c r="K8">
+        <v>12</v>
+      </c>
+      <c r="L8">
+        <v>12</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4">
+        <v>6.018518518518519E-4</v>
+      </c>
+      <c r="P8" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>1.9E-2</v>
+      </c>
+      <c r="R8" s="5">
+        <v>0.1714</v>
+      </c>
+      <c r="S8" s="3">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8" t="s">
+        <v>25</v>
+      </c>
+      <c r="V8" t="s">
+        <v>25</v>
+      </c>
+      <c r="W8">
+        <v>11.808</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B9">
+        <v>12</v>
+      </c>
+      <c r="C9">
+        <v>81</v>
+      </c>
+      <c r="D9">
+        <v>85</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9">
+        <v>33365</v>
+      </c>
+      <c r="G9">
+        <v>50</v>
+      </c>
+      <c r="H9">
+        <v>5</v>
+      </c>
+      <c r="I9">
+        <v>10368</v>
+      </c>
+      <c r="J9">
+        <v>154</v>
+      </c>
+      <c r="K9">
+        <v>35</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>19</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4">
+        <v>7.7546296296296293E-4</v>
+      </c>
+      <c r="P9" s="4">
+        <v>6.018518518518519E-4</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>1.49E-2</v>
+      </c>
+      <c r="R9" s="5">
+        <v>0.2273</v>
+      </c>
+      <c r="S9" s="5">
+        <v>2.86E-2</v>
+      </c>
+      <c r="T9">
+        <v>15</v>
+      </c>
+      <c r="U9" s="5">
+        <v>0.44119999999999998</v>
+      </c>
+      <c r="V9" s="5">
+        <v>0.87880000000000003</v>
+      </c>
+      <c r="W9">
+        <v>28.332000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B10">
+        <v>17</v>
+      </c>
+      <c r="C10">
+        <v>81</v>
+      </c>
+      <c r="D10">
+        <v>85</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10">
+        <v>33365</v>
+      </c>
+      <c r="G10">
+        <v>50</v>
+      </c>
+      <c r="H10">
+        <v>3</v>
+      </c>
+      <c r="I10">
+        <v>3214</v>
+      </c>
+      <c r="J10">
+        <v>52</v>
+      </c>
+      <c r="K10">
+        <v>13</v>
+      </c>
+      <c r="L10">
+        <v>2</v>
+      </c>
+      <c r="M10">
+        <v>5</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10" s="4">
+        <v>7.0601851851851847E-4</v>
+      </c>
+      <c r="P10" s="4">
+        <v>1.5972222222222223E-3</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>1.6199999999999999E-2</v>
+      </c>
+      <c r="R10" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="S10" s="5">
+        <v>0.15379999999999999</v>
+      </c>
+      <c r="T10">
+        <v>6</v>
+      </c>
+      <c r="U10" s="5">
+        <v>0.54549999999999998</v>
+      </c>
+      <c r="V10" s="5">
+        <v>0.72729999999999995</v>
+      </c>
+      <c r="W10">
+        <v>10.542</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B11">
+        <v>18</v>
+      </c>
+      <c r="C11">
+        <v>81</v>
+      </c>
+      <c r="D11">
+        <v>85</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11">
+        <v>33365</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11" s="4">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="P11" s="4">
+        <v>9.6064814814814819E-4</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>1</v>
+      </c>
+      <c r="R11" s="3">
+        <v>1</v>
+      </c>
+      <c r="S11" s="3">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11" s="3">
+        <v>0</v>
+      </c>
+      <c r="V11" s="5">
+        <v>1</v>
+      </c>
+      <c r="W11">
+        <v>0.114</v>
       </c>
     </row>
   </sheetData>

--- a/data/base_creditas.xlsx
+++ b/data/base_creditas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C34709F1-C32F-4B25-ABFB-2679C6FC5D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47BCE17A-FBDD-448C-9376-68FFEA5013E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="27">
   <si>
     <t>Data</t>
   </si>
@@ -472,8 +472,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W11"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -1233,6 +1236,819 @@
       </c>
       <c r="W11">
         <v>0.114</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B12">
+        <v>9</v>
+      </c>
+      <c r="C12">
+        <v>81</v>
+      </c>
+      <c r="D12">
+        <v>85</v>
+      </c>
+      <c r="E12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12">
+        <v>7533</v>
+      </c>
+      <c r="G12">
+        <v>25</v>
+      </c>
+      <c r="H12">
+        <v>4</v>
+      </c>
+      <c r="I12">
+        <v>18719</v>
+      </c>
+      <c r="J12">
+        <v>232</v>
+      </c>
+      <c r="K12">
+        <v>37</v>
+      </c>
+      <c r="L12">
+        <v>16</v>
+      </c>
+      <c r="M12">
+        <v>18</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12" s="4">
+        <v>8.9120370370370373E-4</v>
+      </c>
+      <c r="P12" s="4">
+        <v>1.2037037037037038E-3</v>
+      </c>
+      <c r="Q12" s="5">
+        <v>1.24E-2</v>
+      </c>
+      <c r="R12" s="5">
+        <v>0.1595</v>
+      </c>
+      <c r="S12" s="5">
+        <v>0.43240000000000001</v>
+      </c>
+      <c r="T12">
+        <v>3</v>
+      </c>
+      <c r="U12" s="5">
+        <v>0.1429</v>
+      </c>
+      <c r="V12" s="5">
+        <v>0.95240000000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B13">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>81</v>
+      </c>
+      <c r="D13">
+        <v>85</v>
+      </c>
+      <c r="E13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13">
+        <v>7533</v>
+      </c>
+      <c r="G13">
+        <v>25</v>
+      </c>
+      <c r="H13">
+        <v>9</v>
+      </c>
+      <c r="I13">
+        <v>20163</v>
+      </c>
+      <c r="J13">
+        <v>250</v>
+      </c>
+      <c r="K13">
+        <v>54</v>
+      </c>
+      <c r="L13">
+        <v>20</v>
+      </c>
+      <c r="M13">
+        <v>26</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13" s="4">
+        <v>8.9120370370370373E-4</v>
+      </c>
+      <c r="P13" s="4">
+        <v>9.3749999999999997E-4</v>
+      </c>
+      <c r="Q13" s="5">
+        <v>1.24E-2</v>
+      </c>
+      <c r="R13" s="5">
+        <v>0.216</v>
+      </c>
+      <c r="S13" s="5">
+        <v>0.37040000000000001</v>
+      </c>
+      <c r="T13">
+        <v>8</v>
+      </c>
+      <c r="U13" s="5">
+        <v>0.23530000000000001</v>
+      </c>
+      <c r="V13" s="5">
+        <v>0.85289999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B14">
+        <v>11</v>
+      </c>
+      <c r="C14">
+        <v>81</v>
+      </c>
+      <c r="D14">
+        <v>85</v>
+      </c>
+      <c r="E14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14">
+        <v>7533</v>
+      </c>
+      <c r="G14">
+        <v>25</v>
+      </c>
+      <c r="H14">
+        <v>8</v>
+      </c>
+      <c r="I14">
+        <v>12067</v>
+      </c>
+      <c r="J14">
+        <v>121</v>
+      </c>
+      <c r="K14">
+        <v>18</v>
+      </c>
+      <c r="L14">
+        <v>5</v>
+      </c>
+      <c r="M14">
+        <v>13</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14" s="4">
+        <v>1.1226851851851851E-3</v>
+      </c>
+      <c r="P14" s="4">
+        <v>1.7824074074074075E-3</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="R14" s="5">
+        <v>0.14879999999999999</v>
+      </c>
+      <c r="S14" s="5">
+        <v>0.27779999999999999</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B15">
+        <v>12</v>
+      </c>
+      <c r="C15">
+        <v>81</v>
+      </c>
+      <c r="D15">
+        <v>85</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15">
+        <v>7533</v>
+      </c>
+      <c r="G15">
+        <v>25</v>
+      </c>
+      <c r="H15">
+        <v>7</v>
+      </c>
+      <c r="I15">
+        <v>9021</v>
+      </c>
+      <c r="J15">
+        <v>85</v>
+      </c>
+      <c r="K15">
+        <v>17</v>
+      </c>
+      <c r="L15">
+        <v>7</v>
+      </c>
+      <c r="M15">
+        <v>10</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15" s="4">
+        <v>1.1574074074074073E-3</v>
+      </c>
+      <c r="P15" s="4">
+        <v>1.4004629629629629E-3</v>
+      </c>
+      <c r="Q15" s="5">
+        <v>9.4000000000000004E-3</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="S15" s="5">
+        <v>0.4118</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B16">
+        <v>13</v>
+      </c>
+      <c r="C16">
+        <v>81</v>
+      </c>
+      <c r="D16">
+        <v>85</v>
+      </c>
+      <c r="E16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16">
+        <v>7533</v>
+      </c>
+      <c r="G16">
+        <v>25</v>
+      </c>
+      <c r="H16">
+        <v>6</v>
+      </c>
+      <c r="I16">
+        <v>14219</v>
+      </c>
+      <c r="J16">
+        <v>182</v>
+      </c>
+      <c r="K16">
+        <v>26</v>
+      </c>
+      <c r="L16">
+        <v>11</v>
+      </c>
+      <c r="M16">
+        <v>14</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16" s="4">
+        <v>8.4490740740740739E-4</v>
+      </c>
+      <c r="P16" s="4">
+        <v>1.736111111111111E-3</v>
+      </c>
+      <c r="Q16" s="5">
+        <v>1.2800000000000001E-2</v>
+      </c>
+      <c r="R16" s="5">
+        <v>0.1429</v>
+      </c>
+      <c r="S16" s="5">
+        <v>0.42309999999999998</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
+      </c>
+      <c r="U16" s="5">
+        <v>6.6699999999999995E-2</v>
+      </c>
+      <c r="V16" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B17">
+        <v>14</v>
+      </c>
+      <c r="C17">
+        <v>81</v>
+      </c>
+      <c r="D17">
+        <v>85</v>
+      </c>
+      <c r="E17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17">
+        <v>7533</v>
+      </c>
+      <c r="G17">
+        <v>25</v>
+      </c>
+      <c r="H17">
+        <v>6</v>
+      </c>
+      <c r="I17">
+        <v>6219</v>
+      </c>
+      <c r="J17">
+        <v>72</v>
+      </c>
+      <c r="K17">
+        <v>13</v>
+      </c>
+      <c r="L17">
+        <v>6</v>
+      </c>
+      <c r="M17">
+        <v>7</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17" s="4">
+        <v>9.1435185185185185E-4</v>
+      </c>
+      <c r="P17" s="4">
+        <v>9.0277777777777774E-4</v>
+      </c>
+      <c r="Q17" s="5">
+        <v>1.1599999999999999E-2</v>
+      </c>
+      <c r="R17" s="5">
+        <v>0.18060000000000001</v>
+      </c>
+      <c r="S17" s="5">
+        <v>0.46150000000000002</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17" s="3">
+        <v>0</v>
+      </c>
+      <c r="V17" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B18">
+        <v>15</v>
+      </c>
+      <c r="C18">
+        <v>81</v>
+      </c>
+      <c r="D18">
+        <v>85</v>
+      </c>
+      <c r="E18" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18">
+        <v>7533</v>
+      </c>
+      <c r="G18">
+        <v>25</v>
+      </c>
+      <c r="H18">
+        <v>8</v>
+      </c>
+      <c r="I18">
+        <v>11882</v>
+      </c>
+      <c r="J18">
+        <v>153</v>
+      </c>
+      <c r="K18">
+        <v>30</v>
+      </c>
+      <c r="L18">
+        <v>14</v>
+      </c>
+      <c r="M18">
+        <v>16</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18" s="4">
+        <v>7.9861111111111116E-4</v>
+      </c>
+      <c r="P18" s="4">
+        <v>1.9791666666666668E-3</v>
+      </c>
+      <c r="Q18" s="5">
+        <v>1.29E-2</v>
+      </c>
+      <c r="R18" s="5">
+        <v>0.1961</v>
+      </c>
+      <c r="S18" s="5">
+        <v>0.4667</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18" s="3">
+        <v>0</v>
+      </c>
+      <c r="V18" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B19">
+        <v>16</v>
+      </c>
+      <c r="C19">
+        <v>81</v>
+      </c>
+      <c r="D19">
+        <v>85</v>
+      </c>
+      <c r="E19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19">
+        <v>7533</v>
+      </c>
+      <c r="G19">
+        <v>25</v>
+      </c>
+      <c r="H19">
+        <v>9</v>
+      </c>
+      <c r="I19">
+        <v>16923</v>
+      </c>
+      <c r="J19">
+        <v>262</v>
+      </c>
+      <c r="K19">
+        <v>42</v>
+      </c>
+      <c r="L19">
+        <v>13</v>
+      </c>
+      <c r="M19">
+        <v>29</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19" s="4">
+        <v>6.7129629629629625E-4</v>
+      </c>
+      <c r="P19" s="4">
+        <v>1.4467592592592592E-3</v>
+      </c>
+      <c r="Q19" s="5">
+        <v>1.55E-2</v>
+      </c>
+      <c r="R19" s="5">
+        <v>0.1603</v>
+      </c>
+      <c r="S19" s="5">
+        <v>0.3095</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19" s="3">
+        <v>0</v>
+      </c>
+      <c r="V19" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B20">
+        <v>17</v>
+      </c>
+      <c r="C20">
+        <v>81</v>
+      </c>
+      <c r="D20">
+        <v>85</v>
+      </c>
+      <c r="E20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20">
+        <v>7533</v>
+      </c>
+      <c r="G20">
+        <v>25</v>
+      </c>
+      <c r="H20">
+        <v>7</v>
+      </c>
+      <c r="I20">
+        <v>17295</v>
+      </c>
+      <c r="J20">
+        <v>282</v>
+      </c>
+      <c r="K20">
+        <v>45</v>
+      </c>
+      <c r="L20">
+        <v>18</v>
+      </c>
+      <c r="M20">
+        <v>27</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20" s="4">
+        <v>6.5972222222222224E-4</v>
+      </c>
+      <c r="P20" s="4">
+        <v>9.1435185185185185E-4</v>
+      </c>
+      <c r="Q20" s="5">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="R20" s="5">
+        <v>0.15959999999999999</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B21">
+        <v>18</v>
+      </c>
+      <c r="C21">
+        <v>81</v>
+      </c>
+      <c r="D21">
+        <v>85</v>
+      </c>
+      <c r="E21" t="s">
+        <v>23</v>
+      </c>
+      <c r="F21">
+        <v>7533</v>
+      </c>
+      <c r="G21">
+        <v>25</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>24262</v>
+      </c>
+      <c r="J21">
+        <v>261</v>
+      </c>
+      <c r="K21">
+        <v>63</v>
+      </c>
+      <c r="L21">
+        <v>32</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21" s="4">
+        <v>1.0532407407407407E-3</v>
+      </c>
+      <c r="P21" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q21" s="5">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="R21" s="5">
+        <v>0.2414</v>
+      </c>
+      <c r="S21" s="5">
+        <v>0.50790000000000002</v>
+      </c>
+      <c r="T21">
+        <v>31</v>
+      </c>
+      <c r="U21" s="3">
+        <v>1</v>
+      </c>
+      <c r="V21" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B22">
+        <v>19</v>
+      </c>
+      <c r="C22">
+        <v>81</v>
+      </c>
+      <c r="D22">
+        <v>85</v>
+      </c>
+      <c r="E22" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22">
+        <v>7533</v>
+      </c>
+      <c r="G22">
+        <v>25</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>28325</v>
+      </c>
+      <c r="J22">
+        <v>277</v>
+      </c>
+      <c r="K22">
+        <v>42</v>
+      </c>
+      <c r="L22">
+        <v>15</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22" s="4">
+        <v>1.1458333333333333E-3</v>
+      </c>
+      <c r="P22" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q22" s="5">
+        <v>9.7999999999999997E-3</v>
+      </c>
+      <c r="R22" s="5">
+        <v>0.15160000000000001</v>
+      </c>
+      <c r="S22" s="5">
+        <v>0.35709999999999997</v>
+      </c>
+      <c r="T22">
+        <v>27</v>
+      </c>
+      <c r="U22" s="3">
+        <v>1</v>
+      </c>
+      <c r="V22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B23">
+        <v>20</v>
+      </c>
+      <c r="C23">
+        <v>81</v>
+      </c>
+      <c r="D23">
+        <v>85</v>
+      </c>
+      <c r="E23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23">
+        <v>7533</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>246</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23" s="4">
+        <v>2.8240740740740739E-3</v>
+      </c>
+      <c r="P23" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q23" s="5">
+        <v>4.1000000000000003E-3</v>
+      </c>
+      <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" t="s">
+        <v>25</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/data/base_creditas.xlsx
+++ b/data/base_creditas.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47BCE17A-FBDD-448C-9376-68FFEA5013E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{076BA2AC-4894-4D6D-86DA-5CB69BB7EBC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Funil_2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
@@ -2054,4 +2055,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A581A0A1-DC33-4936-9515-37E0B3821B5E}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/data/base_creditas.xlsx
+++ b/data/base_creditas.xlsx
@@ -5,23 +5,36 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gersou\Downloads\OSPDataCommandCenter_MULTI_CLIENTES_v8_COMPARATIVO_EXECUTIVO_DATAS\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{076BA2AC-4894-4D6D-86DA-5CB69BB7EBC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF4FEEFE-1F07-465D-A6B2-AAB21F8FE4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28665" yWindow="-135" windowWidth="29070" windowHeight="15750" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Funil_2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="35">
   <si>
     <t>Data</t>
   </si>
@@ -102,13 +115,41 @@
   </si>
   <si>
     <t>Locator_Creditas_benef</t>
+  </si>
+  <si>
+    <t>DATA</t>
+  </si>
+  <si>
+    <t>Logados</t>
+  </si>
+  <si>
+    <t>Cpc</t>
+  </si>
+  <si>
+    <t>Loc</t>
+  </si>
+  <si>
+    <t>Conver</t>
+  </si>
+  <si>
+    <t>WAY_Cobranca</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>WAY_Cobranca_Rescindidos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -118,6 +159,13 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -157,10 +205,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -169,9 +218,21 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -477,6 +538,28 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
@@ -2059,9 +2142,1243 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A581A0A1-DC33-4936-9515-37E0B3821B5E}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="A1:K33"/>
+  <sheetFormatPr defaultColWidth="11.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.109375" customWidth="1"/>
+    <col min="11" max="11" width="11.77734375" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>46157</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+      <c r="D2" s="6">
+        <v>13411</v>
+      </c>
+      <c r="E2" s="6">
+        <v>618</v>
+      </c>
+      <c r="F2">
+        <v>26</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="7">
+        <f>IFERROR(E2/D2,)</f>
+        <v>4.6081574826634851E-2</v>
+      </c>
+      <c r="I2" s="7">
+        <f>IFERROR(F2/E2,)</f>
+        <v>4.2071197411003236E-2</v>
+      </c>
+      <c r="J2" s="7">
+        <f>IFERROR(G2/F2,)</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="9">
+        <v>1.0185185185185184E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>46158</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="6">
+        <v>9304</v>
+      </c>
+      <c r="E3" s="6">
+        <v>490</v>
+      </c>
+      <c r="F3">
+        <v>9</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="7">
+        <f t="shared" ref="H3:J33" si="0">IFERROR(E3/D3,)</f>
+        <v>5.2665520206362858E-2</v>
+      </c>
+      <c r="I3" s="7">
+        <f t="shared" si="0"/>
+        <v>1.8367346938775512E-2</v>
+      </c>
+      <c r="J3" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K3" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>46160</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4" s="6">
+        <v>13285</v>
+      </c>
+      <c r="E4" s="6">
+        <v>652</v>
+      </c>
+      <c r="F4">
+        <v>31</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4" s="7">
+        <f t="shared" si="0"/>
+        <v>4.907790741437712E-2</v>
+      </c>
+      <c r="I4" s="7">
+        <f t="shared" si="0"/>
+        <v>4.7546012269938653E-2</v>
+      </c>
+      <c r="J4" s="7">
+        <f t="shared" si="0"/>
+        <v>6.4516129032258063E-2</v>
+      </c>
+      <c r="K4" s="9">
+        <v>1.8287037037037037E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>46161</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5" s="6">
+        <v>12417</v>
+      </c>
+      <c r="E5" s="6">
+        <v>728</v>
+      </c>
+      <c r="F5">
+        <v>28</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="7">
+        <f t="shared" si="0"/>
+        <v>5.8629298542321011E-2</v>
+      </c>
+      <c r="I5" s="7">
+        <f t="shared" si="0"/>
+        <v>3.8461538461538464E-2</v>
+      </c>
+      <c r="J5" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K5" s="9">
+        <v>1.8865740740740742E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6" s="6">
+        <v>12507</v>
+      </c>
+      <c r="E6" s="6">
+        <v>708</v>
+      </c>
+      <c r="F6">
+        <v>30</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6" s="7">
+        <f t="shared" si="0"/>
+        <v>5.6608299352362675E-2</v>
+      </c>
+      <c r="I6" s="7">
+        <f t="shared" si="0"/>
+        <v>4.2372881355932202E-2</v>
+      </c>
+      <c r="J6" s="7">
+        <f t="shared" si="0"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="K6" s="9">
+        <v>2.3032407407407407E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7" s="6">
+        <v>12650</v>
+      </c>
+      <c r="E7" s="6">
+        <v>664</v>
+      </c>
+      <c r="F7">
+        <v>24</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7" s="7">
+        <f t="shared" si="0"/>
+        <v>5.2490118577075098E-2</v>
+      </c>
+      <c r="I7" s="7">
+        <f t="shared" si="0"/>
+        <v>3.614457831325301E-2</v>
+      </c>
+      <c r="J7" s="7">
+        <f t="shared" si="0"/>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="K7" s="9">
+        <v>1.8749999999999999E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+      <c r="D8" s="6">
+        <v>13055</v>
+      </c>
+      <c r="E8" s="6">
+        <v>627</v>
+      </c>
+      <c r="F8">
+        <v>23</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" s="7">
+        <f t="shared" si="0"/>
+        <v>4.8027575641516662E-2</v>
+      </c>
+      <c r="I8" s="7">
+        <f t="shared" si="0"/>
+        <v>3.6682615629984053E-2</v>
+      </c>
+      <c r="J8" s="7">
+        <f t="shared" si="0"/>
+        <v>4.3478260869565216E-2</v>
+      </c>
+      <c r="K8" s="9">
+        <v>2.1759259259259258E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="6">
+        <v>9087</v>
+      </c>
+      <c r="E9" s="6">
+        <v>487</v>
+      </c>
+      <c r="F9">
+        <v>11</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7">
+        <f t="shared" si="0"/>
+        <v>5.3593045009354023E-2</v>
+      </c>
+      <c r="I9" s="7">
+        <f t="shared" si="0"/>
+        <v>2.2587268993839837E-2</v>
+      </c>
+      <c r="J9" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+      <c r="D10">
+        <v>12443</v>
+      </c>
+      <c r="E10">
+        <v>671</v>
+      </c>
+      <c r="F10">
+        <v>31</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" s="7">
+        <f t="shared" si="0"/>
+        <v>5.3925902113638187E-2</v>
+      </c>
+      <c r="I10" s="7">
+        <f t="shared" si="0"/>
+        <v>4.6199701937406856E-2</v>
+      </c>
+      <c r="J10" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="9">
+        <v>1.4236111111111112E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11">
+        <v>6</v>
+      </c>
+      <c r="D11">
+        <v>13026</v>
+      </c>
+      <c r="E11">
+        <v>615</v>
+      </c>
+      <c r="F11">
+        <v>25</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7">
+        <f t="shared" si="0"/>
+        <v>4.7213265776140025E-2</v>
+      </c>
+      <c r="I11" s="7">
+        <f t="shared" si="0"/>
+        <v>4.065040650406504E-2</v>
+      </c>
+      <c r="J11" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="9">
+        <v>1.1458333333333333E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>46169</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12">
+        <v>6</v>
+      </c>
+      <c r="D12" s="6">
+        <v>12685</v>
+      </c>
+      <c r="E12" s="6">
+        <v>678</v>
+      </c>
+      <c r="F12">
+        <v>15</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" s="7">
+        <f t="shared" si="0"/>
+        <v>5.3448955459203785E-2</v>
+      </c>
+      <c r="I12" s="7">
+        <f t="shared" si="0"/>
+        <v>2.2123893805309734E-2</v>
+      </c>
+      <c r="J12" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="9">
+        <v>2.3379629629629631E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>46170</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13">
+        <v>6</v>
+      </c>
+      <c r="D13" s="6">
+        <v>3257</v>
+      </c>
+      <c r="E13" s="6">
+        <v>218</v>
+      </c>
+      <c r="F13">
+        <v>11</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13" s="7">
+        <f t="shared" si="0"/>
+        <v>6.6932760208781084E-2</v>
+      </c>
+      <c r="I13" s="7">
+        <f t="shared" si="0"/>
+        <v>5.0458715596330278E-2</v>
+      </c>
+      <c r="J13" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K13" s="9">
+        <v>1.9212962962962964E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>46171</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14">
+        <v>5</v>
+      </c>
+      <c r="D14" s="6">
+        <v>0</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>46172</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" s="6">
+        <v>0</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I15" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16">
+        <v>5</v>
+      </c>
+      <c r="D16" s="6">
+        <v>10635</v>
+      </c>
+      <c r="E16" s="6">
+        <v>573</v>
+      </c>
+      <c r="F16">
+        <v>39</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+      <c r="H16" s="7">
+        <f t="shared" si="0"/>
+        <v>5.3878702397743297E-2</v>
+      </c>
+      <c r="I16" s="7">
+        <f t="shared" si="0"/>
+        <v>6.8062827225130892E-2</v>
+      </c>
+      <c r="J16" s="7">
+        <f t="shared" si="0"/>
+        <v>5.128205128205128E-2</v>
+      </c>
+      <c r="K16" s="9">
+        <v>2.3842592592592591E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17">
+        <v>7</v>
+      </c>
+      <c r="D17" s="6">
+        <v>12034</v>
+      </c>
+      <c r="E17" s="6">
+        <v>637</v>
+      </c>
+      <c r="F17">
+        <v>24</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17" s="7">
+        <f t="shared" si="0"/>
+        <v>5.2933355492770486E-2</v>
+      </c>
+      <c r="I17" s="7">
+        <f t="shared" si="0"/>
+        <v>3.7676609105180531E-2</v>
+      </c>
+      <c r="J17" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="9">
+        <v>1.5277777777777779E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>46157</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="10">
+        <v>0</v>
+      </c>
+      <c r="D18" s="6">
+        <v>47</v>
+      </c>
+      <c r="E18" s="6">
+        <v>15</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18" s="7">
+        <f t="shared" si="0"/>
+        <v>0.31914893617021278</v>
+      </c>
+      <c r="I18" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>46158</v>
+      </c>
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="10"/>
+      <c r="D19" s="6">
+        <v>11</v>
+      </c>
+      <c r="E19" s="6">
+        <v>2</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19" s="7">
+        <f t="shared" si="0"/>
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="I19" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="9"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>46160</v>
+      </c>
+      <c r="B20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="10">
+        <v>0</v>
+      </c>
+      <c r="D20" s="6">
+        <v>2</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>46161</v>
+      </c>
+      <c r="B21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="D21" s="6">
+        <v>550</v>
+      </c>
+      <c r="E21" s="6">
+        <v>9</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21" s="7">
+        <f t="shared" si="0"/>
+        <v>1.6363636363636365E-2</v>
+      </c>
+      <c r="I21" s="7">
+        <f t="shared" si="0"/>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="J21" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="10">
+        <v>7.75</v>
+      </c>
+      <c r="D22" s="6">
+        <v>5475</v>
+      </c>
+      <c r="E22" s="6">
+        <v>233</v>
+      </c>
+      <c r="F22">
+        <v>31</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22" s="7">
+        <f t="shared" si="0"/>
+        <v>4.2557077625570774E-2</v>
+      </c>
+      <c r="I22" s="7">
+        <f t="shared" si="0"/>
+        <v>0.13304721030042918</v>
+      </c>
+      <c r="J22" s="7">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="K22" s="9">
+        <v>8.7962962962962962E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="10">
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="D23" s="6">
+        <v>4427</v>
+      </c>
+      <c r="E23" s="6">
+        <v>163</v>
+      </c>
+      <c r="F23">
+        <v>11</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23" s="7">
+        <f t="shared" si="0"/>
+        <v>3.6819516602665463E-2</v>
+      </c>
+      <c r="I23" s="7">
+        <f t="shared" si="0"/>
+        <v>6.7484662576687116E-2</v>
+      </c>
+      <c r="J23" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="9">
+        <v>8.4490740740740739E-4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="10">
+        <v>5</v>
+      </c>
+      <c r="D24" s="6">
+        <v>4060</v>
+      </c>
+      <c r="E24" s="6">
+        <v>114</v>
+      </c>
+      <c r="F24">
+        <v>10</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24" s="7">
+        <f t="shared" si="0"/>
+        <v>2.8078817733990149E-2</v>
+      </c>
+      <c r="I24" s="7">
+        <f t="shared" si="0"/>
+        <v>8.771929824561403E-2</v>
+      </c>
+      <c r="J24" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="9">
+        <v>1.3425925925925925E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B25" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="10"/>
+      <c r="D25" s="6">
+        <v>429</v>
+      </c>
+      <c r="E25" s="6">
+        <v>9</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25" s="7">
+        <f t="shared" si="0"/>
+        <v>2.097902097902098E-2</v>
+      </c>
+      <c r="I25" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="9"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="10">
+        <v>3</v>
+      </c>
+      <c r="D26" s="6">
+        <v>3607</v>
+      </c>
+      <c r="E26" s="6">
+        <v>97</v>
+      </c>
+      <c r="F26">
+        <v>9</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26" s="7">
+        <f t="shared" si="0"/>
+        <v>2.6892154144718603E-2</v>
+      </c>
+      <c r="I26" s="7">
+        <f t="shared" si="0"/>
+        <v>9.2783505154639179E-2</v>
+      </c>
+      <c r="J26" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B27" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="D27" s="6">
+        <v>3982</v>
+      </c>
+      <c r="E27" s="6">
+        <v>92</v>
+      </c>
+      <c r="F27">
+        <v>9</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27" s="7">
+        <f t="shared" si="0"/>
+        <v>2.3103967855349072E-2</v>
+      </c>
+      <c r="I27" s="7">
+        <f t="shared" si="0"/>
+        <v>9.7826086956521743E-2</v>
+      </c>
+      <c r="J27" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="9">
+        <v>4.5138888888888887E-4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>46169</v>
+      </c>
+      <c r="B28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="10">
+        <v>2.25</v>
+      </c>
+      <c r="D28" s="6">
+        <v>3939</v>
+      </c>
+      <c r="E28" s="6">
+        <v>75</v>
+      </c>
+      <c r="F28">
+        <v>9</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28" s="7">
+        <f t="shared" si="0"/>
+        <v>1.9040365575019039E-2</v>
+      </c>
+      <c r="I28" s="7">
+        <f t="shared" si="0"/>
+        <v>0.12</v>
+      </c>
+      <c r="J28" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="9">
+        <v>6.3657407407407413E-4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>46170</v>
+      </c>
+      <c r="B29" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="D29" s="6">
+        <v>1379</v>
+      </c>
+      <c r="E29" s="6">
+        <v>24</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29" s="7">
+        <f t="shared" si="0"/>
+        <v>1.7403915881073241E-2</v>
+      </c>
+      <c r="I29" s="7">
+        <f t="shared" si="0"/>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="J29" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="9">
+        <v>2.3611111111111111E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>46171</v>
+      </c>
+      <c r="B30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="10">
+        <v>0</v>
+      </c>
+      <c r="D30" s="6">
+        <v>0</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30" t="s">
+        <v>33</v>
+      </c>
+      <c r="H30" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I30" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="9"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>46172</v>
+      </c>
+      <c r="B31" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" s="10"/>
+      <c r="D31" s="6">
+        <v>0</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31" t="s">
+        <v>33</v>
+      </c>
+      <c r="H31" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I31" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="9"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" s="10">
+        <v>0</v>
+      </c>
+      <c r="D32" s="6">
+        <v>0</v>
+      </c>
+      <c r="E32" s="6">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="H32" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I32" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="9"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" s="10">
+        <v>0</v>
+      </c>
+      <c r="D33" s="6">
+        <v>0</v>
+      </c>
+      <c r="E33" s="6">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="H33" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I33" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="9"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/data/base_creditas.xlsx
+++ b/data/base_creditas.xlsx
@@ -5,36 +5,23 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gersou\Downloads\OSPDataCommandCenter_MULTI_CLIENTES_v8_COMPARATIVO_EXECUTIVO_DATAS\OSPDataCommandCenter\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF4FEEFE-1F07-465D-A6B2-AAB21F8FE4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{076BA2AC-4894-4D6D-86DA-5CB69BB7EBC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28665" yWindow="-135" windowWidth="29070" windowHeight="15750" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Funil_2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="27">
   <si>
     <t>Data</t>
   </si>
@@ -115,41 +102,13 @@
   </si>
   <si>
     <t>Locator_Creditas_benef</t>
-  </si>
-  <si>
-    <t>DATA</t>
-  </si>
-  <si>
-    <t>Logados</t>
-  </si>
-  <si>
-    <t>Cpc</t>
-  </si>
-  <si>
-    <t>Loc</t>
-  </si>
-  <si>
-    <t>Conver</t>
-  </si>
-  <si>
-    <t>WAY_Cobranca</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>WAY_Cobranca_Rescindidos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-  </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,13 +118,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -205,11 +157,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -218,21 +169,9 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -538,28 +477,6 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
@@ -2142,1243 +2059,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A581A0A1-DC33-4936-9515-37E0B3821B5E}">
-  <dimension ref="A1:K33"/>
-  <sheetFormatPr defaultColWidth="11.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.109375" customWidth="1"/>
-    <col min="11" max="11" width="11.77734375" style="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I1" t="s">
-        <v>30</v>
-      </c>
-      <c r="J1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>46157</v>
-      </c>
-      <c r="B2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2">
-        <v>5</v>
-      </c>
-      <c r="D2" s="6">
-        <v>13411</v>
-      </c>
-      <c r="E2" s="6">
-        <v>618</v>
-      </c>
-      <c r="F2">
-        <v>26</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2" s="7">
-        <f>IFERROR(E2/D2,)</f>
-        <v>4.6081574826634851E-2</v>
-      </c>
-      <c r="I2" s="7">
-        <f>IFERROR(F2/E2,)</f>
-        <v>4.2071197411003236E-2</v>
-      </c>
-      <c r="J2" s="7">
-        <f>IFERROR(G2/F2,)</f>
-        <v>0</v>
-      </c>
-      <c r="K2" s="9">
-        <v>1.0185185185185184E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>46158</v>
-      </c>
-      <c r="B3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="6">
-        <v>9304</v>
-      </c>
-      <c r="E3" s="6">
-        <v>490</v>
-      </c>
-      <c r="F3">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3" s="7">
-        <f t="shared" ref="H3:J33" si="0">IFERROR(E3/D3,)</f>
-        <v>5.2665520206362858E-2</v>
-      </c>
-      <c r="I3" s="7">
-        <f t="shared" si="0"/>
-        <v>1.8367346938775512E-2</v>
-      </c>
-      <c r="J3" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K3" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>46160</v>
-      </c>
-      <c r="B4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-      <c r="D4" s="6">
-        <v>13285</v>
-      </c>
-      <c r="E4" s="6">
-        <v>652</v>
-      </c>
-      <c r="F4">
-        <v>31</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4" s="7">
-        <f t="shared" si="0"/>
-        <v>4.907790741437712E-2</v>
-      </c>
-      <c r="I4" s="7">
-        <f t="shared" si="0"/>
-        <v>4.7546012269938653E-2</v>
-      </c>
-      <c r="J4" s="7">
-        <f t="shared" si="0"/>
-        <v>6.4516129032258063E-2</v>
-      </c>
-      <c r="K4" s="9">
-        <v>1.8287037037037037E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>46161</v>
-      </c>
-      <c r="B5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5" s="6">
-        <v>12417</v>
-      </c>
-      <c r="E5" s="6">
-        <v>728</v>
-      </c>
-      <c r="F5">
-        <v>28</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5" s="7">
-        <f t="shared" si="0"/>
-        <v>5.8629298542321011E-2</v>
-      </c>
-      <c r="I5" s="7">
-        <f t="shared" si="0"/>
-        <v>3.8461538461538464E-2</v>
-      </c>
-      <c r="J5" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K5" s="9">
-        <v>1.8865740740740742E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>46162</v>
-      </c>
-      <c r="B6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6" s="6">
-        <v>12507</v>
-      </c>
-      <c r="E6" s="6">
-        <v>708</v>
-      </c>
-      <c r="F6">
-        <v>30</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6" s="7">
-        <f t="shared" si="0"/>
-        <v>5.6608299352362675E-2</v>
-      </c>
-      <c r="I6" s="7">
-        <f t="shared" si="0"/>
-        <v>4.2372881355932202E-2</v>
-      </c>
-      <c r="J6" s="7">
-        <f t="shared" si="0"/>
-        <v>6.6666666666666666E-2</v>
-      </c>
-      <c r="K6" s="9">
-        <v>2.3032407407407407E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>46163</v>
-      </c>
-      <c r="B7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7" s="6">
-        <v>12650</v>
-      </c>
-      <c r="E7" s="6">
-        <v>664</v>
-      </c>
-      <c r="F7">
-        <v>24</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="H7" s="7">
-        <f t="shared" si="0"/>
-        <v>5.2490118577075098E-2</v>
-      </c>
-      <c r="I7" s="7">
-        <f t="shared" si="0"/>
-        <v>3.614457831325301E-2</v>
-      </c>
-      <c r="J7" s="7">
-        <f t="shared" si="0"/>
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="K7" s="9">
-        <v>1.8749999999999999E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>46164</v>
-      </c>
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-      <c r="D8" s="6">
-        <v>13055</v>
-      </c>
-      <c r="E8" s="6">
-        <v>627</v>
-      </c>
-      <c r="F8">
-        <v>23</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8" s="7">
-        <f t="shared" si="0"/>
-        <v>4.8027575641516662E-2</v>
-      </c>
-      <c r="I8" s="7">
-        <f t="shared" si="0"/>
-        <v>3.6682615629984053E-2</v>
-      </c>
-      <c r="J8" s="7">
-        <f t="shared" si="0"/>
-        <v>4.3478260869565216E-2</v>
-      </c>
-      <c r="K8" s="9">
-        <v>2.1759259259259258E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
-        <v>46165</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="6">
-        <v>9087</v>
-      </c>
-      <c r="E9" s="6">
-        <v>487</v>
-      </c>
-      <c r="F9">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9" s="7">
-        <f t="shared" si="0"/>
-        <v>5.3593045009354023E-2</v>
-      </c>
-      <c r="I9" s="7">
-        <f t="shared" si="0"/>
-        <v>2.2587268993839837E-2</v>
-      </c>
-      <c r="J9" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K9" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <v>46167</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-      <c r="D10">
-        <v>12443</v>
-      </c>
-      <c r="E10">
-        <v>671</v>
-      </c>
-      <c r="F10">
-        <v>31</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10" s="7">
-        <f t="shared" si="0"/>
-        <v>5.3925902113638187E-2</v>
-      </c>
-      <c r="I10" s="7">
-        <f t="shared" si="0"/>
-        <v>4.6199701937406856E-2</v>
-      </c>
-      <c r="J10" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="9">
-        <v>1.4236111111111112E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>46168</v>
-      </c>
-      <c r="B11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11">
-        <v>6</v>
-      </c>
-      <c r="D11">
-        <v>13026</v>
-      </c>
-      <c r="E11">
-        <v>615</v>
-      </c>
-      <c r="F11">
-        <v>25</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11" s="7">
-        <f t="shared" si="0"/>
-        <v>4.7213265776140025E-2</v>
-      </c>
-      <c r="I11" s="7">
-        <f t="shared" si="0"/>
-        <v>4.065040650406504E-2</v>
-      </c>
-      <c r="J11" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="9">
-        <v>1.1458333333333333E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <v>46169</v>
-      </c>
-      <c r="B12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12">
-        <v>6</v>
-      </c>
-      <c r="D12" s="6">
-        <v>12685</v>
-      </c>
-      <c r="E12" s="6">
-        <v>678</v>
-      </c>
-      <c r="F12">
-        <v>15</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12" s="7">
-        <f t="shared" si="0"/>
-        <v>5.3448955459203785E-2</v>
-      </c>
-      <c r="I12" s="7">
-        <f t="shared" si="0"/>
-        <v>2.2123893805309734E-2</v>
-      </c>
-      <c r="J12" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="9">
-        <v>2.3379629629629631E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>46170</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13">
-        <v>6</v>
-      </c>
-      <c r="D13" s="6">
-        <v>3257</v>
-      </c>
-      <c r="E13" s="6">
-        <v>218</v>
-      </c>
-      <c r="F13">
-        <v>11</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13" s="7">
-        <f t="shared" si="0"/>
-        <v>6.6932760208781084E-2</v>
-      </c>
-      <c r="I13" s="7">
-        <f t="shared" si="0"/>
-        <v>5.0458715596330278E-2</v>
-      </c>
-      <c r="J13" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="9">
-        <v>1.9212962962962964E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
-        <v>46171</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14">
-        <v>5</v>
-      </c>
-      <c r="D14" s="6">
-        <v>0</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F14" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" t="s">
-        <v>33</v>
-      </c>
-      <c r="H14" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
-        <v>46172</v>
-      </c>
-      <c r="B15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15" s="6">
-        <v>0</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15" t="s">
-        <v>33</v>
-      </c>
-      <c r="H15" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
-        <v>46174</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16">
-        <v>5</v>
-      </c>
-      <c r="D16" s="6">
-        <v>10635</v>
-      </c>
-      <c r="E16" s="6">
-        <v>573</v>
-      </c>
-      <c r="F16">
-        <v>39</v>
-      </c>
-      <c r="G16">
-        <v>2</v>
-      </c>
-      <c r="H16" s="7">
-        <f t="shared" si="0"/>
-        <v>5.3878702397743297E-2</v>
-      </c>
-      <c r="I16" s="7">
-        <f t="shared" si="0"/>
-        <v>6.8062827225130892E-2</v>
-      </c>
-      <c r="J16" s="7">
-        <f t="shared" si="0"/>
-        <v>5.128205128205128E-2</v>
-      </c>
-      <c r="K16" s="9">
-        <v>2.3842592592592591E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
-        <v>46175</v>
-      </c>
-      <c r="B17" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17">
-        <v>7</v>
-      </c>
-      <c r="D17" s="6">
-        <v>12034</v>
-      </c>
-      <c r="E17" s="6">
-        <v>637</v>
-      </c>
-      <c r="F17">
-        <v>24</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17" s="7">
-        <f t="shared" si="0"/>
-        <v>5.2933355492770486E-2</v>
-      </c>
-      <c r="I17" s="7">
-        <f t="shared" si="0"/>
-        <v>3.7676609105180531E-2</v>
-      </c>
-      <c r="J17" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K17" s="9">
-        <v>1.5277777777777779E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
-        <v>46157</v>
-      </c>
-      <c r="B18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" s="10">
-        <v>0</v>
-      </c>
-      <c r="D18" s="6">
-        <v>47</v>
-      </c>
-      <c r="E18" s="6">
-        <v>15</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18" s="7">
-        <f t="shared" si="0"/>
-        <v>0.31914893617021278</v>
-      </c>
-      <c r="I18" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J18" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K18" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
-        <v>46158</v>
-      </c>
-      <c r="B19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="6">
-        <v>11</v>
-      </c>
-      <c r="E19" s="6">
-        <v>2</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19" s="7">
-        <f t="shared" si="0"/>
-        <v>0.18181818181818182</v>
-      </c>
-      <c r="I19" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K19" s="9"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
-        <v>46160</v>
-      </c>
-      <c r="B20" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" s="10">
-        <v>0</v>
-      </c>
-      <c r="D20" s="6">
-        <v>2</v>
-      </c>
-      <c r="E20" s="6">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I20" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
-        <v>46161</v>
-      </c>
-      <c r="B21" t="s">
-        <v>34</v>
-      </c>
-      <c r="C21" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="D21" s="6">
-        <v>550</v>
-      </c>
-      <c r="E21" s="6">
-        <v>9</v>
-      </c>
-      <c r="F21">
-        <v>2</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21" s="7">
-        <f t="shared" si="0"/>
-        <v>1.6363636363636365E-2</v>
-      </c>
-      <c r="I21" s="7">
-        <f t="shared" si="0"/>
-        <v>0.22222222222222221</v>
-      </c>
-      <c r="J21" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K21" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
-        <v>46162</v>
-      </c>
-      <c r="B22" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="10">
-        <v>7.75</v>
-      </c>
-      <c r="D22" s="6">
-        <v>5475</v>
-      </c>
-      <c r="E22" s="6">
-        <v>233</v>
-      </c>
-      <c r="F22">
-        <v>31</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-      <c r="H22" s="7">
-        <f t="shared" si="0"/>
-        <v>4.2557077625570774E-2</v>
-      </c>
-      <c r="I22" s="7">
-        <f t="shared" si="0"/>
-        <v>0.13304721030042918</v>
-      </c>
-      <c r="J22" s="7">
-        <f t="shared" si="0"/>
-        <v>3.2258064516129031E-2</v>
-      </c>
-      <c r="K22" s="9">
-        <v>8.7962962962962962E-4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
-        <v>46163</v>
-      </c>
-      <c r="B23" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" s="10">
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="D23" s="6">
-        <v>4427</v>
-      </c>
-      <c r="E23" s="6">
-        <v>163</v>
-      </c>
-      <c r="F23">
-        <v>11</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23" s="7">
-        <f t="shared" si="0"/>
-        <v>3.6819516602665463E-2</v>
-      </c>
-      <c r="I23" s="7">
-        <f t="shared" si="0"/>
-        <v>6.7484662576687116E-2</v>
-      </c>
-      <c r="J23" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K23" s="9">
-        <v>8.4490740740740739E-4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
-        <v>46164</v>
-      </c>
-      <c r="B24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" s="10">
-        <v>5</v>
-      </c>
-      <c r="D24" s="6">
-        <v>4060</v>
-      </c>
-      <c r="E24" s="6">
-        <v>114</v>
-      </c>
-      <c r="F24">
-        <v>10</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24" s="7">
-        <f t="shared" si="0"/>
-        <v>2.8078817733990149E-2</v>
-      </c>
-      <c r="I24" s="7">
-        <f t="shared" si="0"/>
-        <v>8.771929824561403E-2</v>
-      </c>
-      <c r="J24" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K24" s="9">
-        <v>1.3425925925925925E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
-        <v>46165</v>
-      </c>
-      <c r="B25" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="6">
-        <v>429</v>
-      </c>
-      <c r="E25" s="6">
-        <v>9</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25" s="7">
-        <f t="shared" si="0"/>
-        <v>2.097902097902098E-2</v>
-      </c>
-      <c r="I25" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J25" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K25" s="9"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
-        <v>46167</v>
-      </c>
-      <c r="B26" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="10">
-        <v>3</v>
-      </c>
-      <c r="D26" s="6">
-        <v>3607</v>
-      </c>
-      <c r="E26" s="6">
-        <v>97</v>
-      </c>
-      <c r="F26">
-        <v>9</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26" s="7">
-        <f t="shared" si="0"/>
-        <v>2.6892154144718603E-2</v>
-      </c>
-      <c r="I26" s="7">
-        <f t="shared" si="0"/>
-        <v>9.2783505154639179E-2</v>
-      </c>
-      <c r="J26" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K26" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="2">
-        <v>46168</v>
-      </c>
-      <c r="B27" t="s">
-        <v>34</v>
-      </c>
-      <c r="C27" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="D27" s="6">
-        <v>3982</v>
-      </c>
-      <c r="E27" s="6">
-        <v>92</v>
-      </c>
-      <c r="F27">
-        <v>9</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27" s="7">
-        <f t="shared" si="0"/>
-        <v>2.3103967855349072E-2</v>
-      </c>
-      <c r="I27" s="7">
-        <f t="shared" si="0"/>
-        <v>9.7826086956521743E-2</v>
-      </c>
-      <c r="J27" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K27" s="9">
-        <v>4.5138888888888887E-4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
-        <v>46169</v>
-      </c>
-      <c r="B28" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="10">
-        <v>2.25</v>
-      </c>
-      <c r="D28" s="6">
-        <v>3939</v>
-      </c>
-      <c r="E28" s="6">
-        <v>75</v>
-      </c>
-      <c r="F28">
-        <v>9</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28" s="7">
-        <f t="shared" si="0"/>
-        <v>1.9040365575019039E-2</v>
-      </c>
-      <c r="I28" s="7">
-        <f t="shared" si="0"/>
-        <v>0.12</v>
-      </c>
-      <c r="J28" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K28" s="9">
-        <v>6.3657407407407413E-4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="2">
-        <v>46170</v>
-      </c>
-      <c r="B29" t="s">
-        <v>34</v>
-      </c>
-      <c r="C29" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="D29" s="6">
-        <v>1379</v>
-      </c>
-      <c r="E29" s="6">
-        <v>24</v>
-      </c>
-      <c r="F29">
-        <v>2</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29" s="7">
-        <f t="shared" si="0"/>
-        <v>1.7403915881073241E-2</v>
-      </c>
-      <c r="I29" s="7">
-        <f t="shared" si="0"/>
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="J29" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K29" s="9">
-        <v>2.3611111111111111E-3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="2">
-        <v>46171</v>
-      </c>
-      <c r="B30" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" s="10">
-        <v>0</v>
-      </c>
-      <c r="D30" s="6">
-        <v>0</v>
-      </c>
-      <c r="E30" s="6">
-        <v>0</v>
-      </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30" t="s">
-        <v>33</v>
-      </c>
-      <c r="H30" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I30" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J30" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K30" s="9"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="2">
-        <v>46172</v>
-      </c>
-      <c r="B31" t="s">
-        <v>34</v>
-      </c>
-      <c r="C31" s="10"/>
-      <c r="D31" s="6">
-        <v>0</v>
-      </c>
-      <c r="E31" s="6">
-        <v>0</v>
-      </c>
-      <c r="F31">
-        <v>0</v>
-      </c>
-      <c r="G31" t="s">
-        <v>33</v>
-      </c>
-      <c r="H31" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I31" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J31" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K31" s="9"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="2">
-        <v>46174</v>
-      </c>
-      <c r="B32" t="s">
-        <v>34</v>
-      </c>
-      <c r="C32" s="10">
-        <v>0</v>
-      </c>
-      <c r="D32" s="6">
-        <v>0</v>
-      </c>
-      <c r="E32" s="6">
-        <v>0</v>
-      </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
-      <c r="H32" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I32" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J32" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K32" s="9"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33" s="2">
-        <v>46175</v>
-      </c>
-      <c r="B33" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" s="10">
-        <v>0</v>
-      </c>
-      <c r="D33" s="6">
-        <v>0</v>
-      </c>
-      <c r="E33" s="6">
-        <v>0</v>
-      </c>
-      <c r="F33">
-        <v>0</v>
-      </c>
-      <c r="H33" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I33" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J33" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K33" s="9"/>
-    </row>
-  </sheetData>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/data/base_creditas.xlsx
+++ b/data/base_creditas.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{076BA2AC-4894-4D6D-86DA-5CB69BB7EBC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{629A76BA-11EA-4A54-9C1F-9518636F2B20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Funil_2" sheetId="2" r:id="rId2"/>
+    <sheet name="Funil_3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="30">
   <si>
     <t>Data</t>
   </si>
@@ -102,6 +103,15 @@
   </si>
   <si>
     <t>Locator_Creditas_benef</t>
+  </si>
+  <si>
+    <t>Creditas_Locator Auto</t>
+  </si>
+  <si>
+    <t>WAY_Cobranca</t>
+  </si>
+  <si>
+    <t>NULL</t>
   </si>
 </sst>
 </file>
@@ -473,7 +483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:W63"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -2050,6 +2060,2726 @@
       </c>
       <c r="U23" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B24">
+        <v>8</v>
+      </c>
+      <c r="C24">
+        <v>81</v>
+      </c>
+      <c r="D24">
+        <v>85</v>
+      </c>
+      <c r="E24" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24">
+        <v>7468</v>
+      </c>
+      <c r="G24">
+        <v>25</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>11322</v>
+      </c>
+      <c r="J24">
+        <v>189</v>
+      </c>
+      <c r="K24">
+        <v>212</v>
+      </c>
+      <c r="L24">
+        <v>12</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24" s="4">
+        <v>6.8287037037037036E-4</v>
+      </c>
+      <c r="P24" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q24" s="5">
+        <v>1.67E-2</v>
+      </c>
+      <c r="R24" s="5">
+        <v>1.121</v>
+      </c>
+      <c r="S24" s="5">
+        <v>5.6599999999999998E-2</v>
+      </c>
+      <c r="T24">
+        <v>200</v>
+      </c>
+      <c r="U24" s="3">
+        <v>1</v>
+      </c>
+      <c r="V24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+      <c r="C25">
+        <v>84</v>
+      </c>
+      <c r="D25">
+        <v>86</v>
+      </c>
+      <c r="E25" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25">
+        <v>15993</v>
+      </c>
+      <c r="G25">
+        <v>25</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>4604</v>
+      </c>
+      <c r="J25">
+        <v>139</v>
+      </c>
+      <c r="K25">
+        <v>104</v>
+      </c>
+      <c r="L25">
+        <v>7</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25" s="4">
+        <v>3.7037037037037035E-4</v>
+      </c>
+      <c r="P25" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q25" s="5">
+        <v>3.0200000000000001E-2</v>
+      </c>
+      <c r="R25" s="5">
+        <v>0.74819999999999998</v>
+      </c>
+      <c r="S25" s="5">
+        <v>6.7299999999999999E-2</v>
+      </c>
+      <c r="T25">
+        <v>97</v>
+      </c>
+      <c r="U25" s="3">
+        <v>1</v>
+      </c>
+      <c r="V25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B26">
+        <v>9</v>
+      </c>
+      <c r="C26">
+        <v>81</v>
+      </c>
+      <c r="D26">
+        <v>85</v>
+      </c>
+      <c r="E26" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26">
+        <v>7468</v>
+      </c>
+      <c r="G26">
+        <v>25</v>
+      </c>
+      <c r="H26">
+        <v>5</v>
+      </c>
+      <c r="I26">
+        <v>7174</v>
+      </c>
+      <c r="J26">
+        <v>91</v>
+      </c>
+      <c r="K26">
+        <v>30</v>
+      </c>
+      <c r="L26">
+        <v>11</v>
+      </c>
+      <c r="M26">
+        <v>18</v>
+      </c>
+      <c r="N26">
+        <v>1</v>
+      </c>
+      <c r="O26" s="4">
+        <v>9.0277777777777774E-4</v>
+      </c>
+      <c r="P26" s="4">
+        <v>1.1111111111111111E-3</v>
+      </c>
+      <c r="Q26" s="5">
+        <v>1.2699999999999999E-2</v>
+      </c>
+      <c r="R26" s="5">
+        <v>0.32969999999999999</v>
+      </c>
+      <c r="S26" s="5">
+        <v>0.36670000000000003</v>
+      </c>
+      <c r="T26">
+        <v>1</v>
+      </c>
+      <c r="U26" s="5">
+        <v>5.2600000000000001E-2</v>
+      </c>
+      <c r="V26" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B27">
+        <v>9</v>
+      </c>
+      <c r="C27">
+        <v>84</v>
+      </c>
+      <c r="D27">
+        <v>86</v>
+      </c>
+      <c r="E27" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27">
+        <v>15993</v>
+      </c>
+      <c r="G27">
+        <v>25</v>
+      </c>
+      <c r="H27">
+        <v>8</v>
+      </c>
+      <c r="I27">
+        <v>7018</v>
+      </c>
+      <c r="J27">
+        <v>183</v>
+      </c>
+      <c r="K27">
+        <v>47</v>
+      </c>
+      <c r="L27">
+        <v>5</v>
+      </c>
+      <c r="M27">
+        <v>41</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27" s="4">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="P27" s="4">
+        <v>6.018518518518519E-4</v>
+      </c>
+      <c r="Q27" s="5">
+        <v>2.6100000000000002E-2</v>
+      </c>
+      <c r="R27" s="5">
+        <v>0.25679999999999997</v>
+      </c>
+      <c r="S27" s="5">
+        <v>0.10639999999999999</v>
+      </c>
+      <c r="T27">
+        <v>1</v>
+      </c>
+      <c r="U27" s="5">
+        <v>2.3800000000000002E-2</v>
+      </c>
+      <c r="V27" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B28">
+        <v>10</v>
+      </c>
+      <c r="C28">
+        <v>81</v>
+      </c>
+      <c r="D28">
+        <v>85</v>
+      </c>
+      <c r="E28" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28">
+        <v>7468</v>
+      </c>
+      <c r="G28">
+        <v>25</v>
+      </c>
+      <c r="H28">
+        <v>7</v>
+      </c>
+      <c r="I28">
+        <v>14655</v>
+      </c>
+      <c r="J28">
+        <v>161</v>
+      </c>
+      <c r="K28">
+        <v>3436</v>
+      </c>
+      <c r="L28">
+        <v>17</v>
+      </c>
+      <c r="M28">
+        <v>19</v>
+      </c>
+      <c r="N28">
+        <v>2</v>
+      </c>
+      <c r="O28" s="4">
+        <v>9.837962962962962E-4</v>
+      </c>
+      <c r="P28" s="4">
+        <v>1.5740740740740741E-3</v>
+      </c>
+      <c r="Q28" s="5">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="R28" s="5">
+        <v>21.34</v>
+      </c>
+      <c r="S28" s="5">
+        <v>4.8999999999999998E-3</v>
+      </c>
+      <c r="T28">
+        <v>3400</v>
+      </c>
+      <c r="U28" s="5">
+        <v>0.99439999999999995</v>
+      </c>
+      <c r="V28" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B29">
+        <v>10</v>
+      </c>
+      <c r="C29">
+        <v>84</v>
+      </c>
+      <c r="D29">
+        <v>86</v>
+      </c>
+      <c r="E29" t="s">
+        <v>26</v>
+      </c>
+      <c r="F29">
+        <v>15993</v>
+      </c>
+      <c r="G29">
+        <v>25</v>
+      </c>
+      <c r="H29">
+        <v>8</v>
+      </c>
+      <c r="I29">
+        <v>5338</v>
+      </c>
+      <c r="J29">
+        <v>127</v>
+      </c>
+      <c r="K29">
+        <v>1262</v>
+      </c>
+      <c r="L29">
+        <v>9</v>
+      </c>
+      <c r="M29">
+        <v>25</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29" s="4">
+        <v>4.5138888888888887E-4</v>
+      </c>
+      <c r="P29" s="4">
+        <v>6.5972222222222224E-4</v>
+      </c>
+      <c r="Q29" s="5">
+        <v>2.3800000000000002E-2</v>
+      </c>
+      <c r="R29" s="5">
+        <v>9.9369999999999994</v>
+      </c>
+      <c r="S29" s="5">
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="T29">
+        <v>1228</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0.98</v>
+      </c>
+      <c r="V29" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B30">
+        <v>11</v>
+      </c>
+      <c r="C30">
+        <v>81</v>
+      </c>
+      <c r="D30">
+        <v>85</v>
+      </c>
+      <c r="E30" t="s">
+        <v>27</v>
+      </c>
+      <c r="F30">
+        <v>7468</v>
+      </c>
+      <c r="G30">
+        <v>25</v>
+      </c>
+      <c r="H30">
+        <v>6</v>
+      </c>
+      <c r="I30">
+        <v>16328</v>
+      </c>
+      <c r="J30">
+        <v>181</v>
+      </c>
+      <c r="K30">
+        <v>3683</v>
+      </c>
+      <c r="L30">
+        <v>18</v>
+      </c>
+      <c r="M30">
+        <v>24</v>
+      </c>
+      <c r="N30">
+        <v>2</v>
+      </c>
+      <c r="O30" s="4">
+        <v>9.7222222222222219E-4</v>
+      </c>
+      <c r="P30" s="4">
+        <v>1.2962962962962963E-3</v>
+      </c>
+      <c r="Q30" s="5">
+        <v>1.11E-2</v>
+      </c>
+      <c r="R30" s="5">
+        <v>20.34</v>
+      </c>
+      <c r="S30" s="5">
+        <v>4.8999999999999998E-3</v>
+      </c>
+      <c r="T30">
+        <v>3641</v>
+      </c>
+      <c r="U30" s="5">
+        <v>0.99350000000000005</v>
+      </c>
+      <c r="V30" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B31">
+        <v>11</v>
+      </c>
+      <c r="C31">
+        <v>84</v>
+      </c>
+      <c r="D31">
+        <v>86</v>
+      </c>
+      <c r="E31" t="s">
+        <v>26</v>
+      </c>
+      <c r="F31">
+        <v>15993</v>
+      </c>
+      <c r="G31">
+        <v>25</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31">
+        <v>2369</v>
+      </c>
+      <c r="J31">
+        <v>52</v>
+      </c>
+      <c r="K31">
+        <v>521</v>
+      </c>
+      <c r="L31">
+        <v>2</v>
+      </c>
+      <c r="M31">
+        <v>3</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31" s="4">
+        <v>4.9768518518518521E-4</v>
+      </c>
+      <c r="P31" s="4">
+        <v>7.291666666666667E-4</v>
+      </c>
+      <c r="Q31" s="5">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="R31" s="5">
+        <v>10.01</v>
+      </c>
+      <c r="S31" s="5">
+        <v>3.8E-3</v>
+      </c>
+      <c r="T31">
+        <v>516</v>
+      </c>
+      <c r="U31" s="5">
+        <v>0.99419999999999997</v>
+      </c>
+      <c r="V31" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B32">
+        <v>12</v>
+      </c>
+      <c r="C32">
+        <v>81</v>
+      </c>
+      <c r="D32">
+        <v>85</v>
+      </c>
+      <c r="E32" t="s">
+        <v>27</v>
+      </c>
+      <c r="F32">
+        <v>7468</v>
+      </c>
+      <c r="G32">
+        <v>25</v>
+      </c>
+      <c r="H32">
+        <v>9</v>
+      </c>
+      <c r="I32">
+        <v>17098</v>
+      </c>
+      <c r="J32">
+        <v>157</v>
+      </c>
+      <c r="K32">
+        <v>3426</v>
+      </c>
+      <c r="L32">
+        <v>22</v>
+      </c>
+      <c r="M32">
+        <v>17</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32" s="4">
+        <v>1.1805555555555556E-3</v>
+      </c>
+      <c r="P32" s="4">
+        <v>1.5625000000000001E-3</v>
+      </c>
+      <c r="Q32" s="5">
+        <v>9.1999999999999998E-3</v>
+      </c>
+      <c r="R32" s="5">
+        <v>21.82</v>
+      </c>
+      <c r="S32" s="5">
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="T32">
+        <v>3387</v>
+      </c>
+      <c r="U32" s="5">
+        <v>0.995</v>
+      </c>
+      <c r="V32" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B33">
+        <v>12</v>
+      </c>
+      <c r="C33">
+        <v>84</v>
+      </c>
+      <c r="D33">
+        <v>86</v>
+      </c>
+      <c r="E33" t="s">
+        <v>26</v>
+      </c>
+      <c r="F33">
+        <v>15993</v>
+      </c>
+      <c r="G33">
+        <v>25</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>2068</v>
+      </c>
+      <c r="J33">
+        <v>49</v>
+      </c>
+      <c r="K33">
+        <v>441</v>
+      </c>
+      <c r="L33">
+        <v>5</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33" s="4">
+        <v>4.5138888888888887E-4</v>
+      </c>
+      <c r="P33" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q33" s="5">
+        <v>2.3699999999999999E-2</v>
+      </c>
+      <c r="R33" s="3">
+        <v>9</v>
+      </c>
+      <c r="S33" s="5">
+        <v>1.1299999999999999E-2</v>
+      </c>
+      <c r="T33">
+        <v>436</v>
+      </c>
+      <c r="U33" s="3">
+        <v>1</v>
+      </c>
+      <c r="V33" s="5">
+        <v>0.72729999999999995</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B34">
+        <v>13</v>
+      </c>
+      <c r="C34">
+        <v>81</v>
+      </c>
+      <c r="D34">
+        <v>85</v>
+      </c>
+      <c r="E34" t="s">
+        <v>27</v>
+      </c>
+      <c r="F34">
+        <v>7468</v>
+      </c>
+      <c r="G34">
+        <v>25</v>
+      </c>
+      <c r="H34">
+        <v>5</v>
+      </c>
+      <c r="I34">
+        <v>18676</v>
+      </c>
+      <c r="J34">
+        <v>157</v>
+      </c>
+      <c r="K34">
+        <v>2905</v>
+      </c>
+      <c r="L34">
+        <v>21</v>
+      </c>
+      <c r="M34">
+        <v>19</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34" s="4">
+        <v>1.2962962962962963E-3</v>
+      </c>
+      <c r="P34" s="4">
+        <v>1.0532407407407407E-3</v>
+      </c>
+      <c r="Q34" s="5">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="R34" s="5">
+        <v>18.5</v>
+      </c>
+      <c r="S34" s="5">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="T34">
+        <v>2865</v>
+      </c>
+      <c r="U34" s="5">
+        <v>0.99339999999999995</v>
+      </c>
+      <c r="V34" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B35">
+        <v>13</v>
+      </c>
+      <c r="C35">
+        <v>84</v>
+      </c>
+      <c r="D35">
+        <v>86</v>
+      </c>
+      <c r="E35" t="s">
+        <v>26</v>
+      </c>
+      <c r="F35">
+        <v>15993</v>
+      </c>
+      <c r="G35">
+        <v>16</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>922</v>
+      </c>
+      <c r="J35">
+        <v>16</v>
+      </c>
+      <c r="K35">
+        <v>137</v>
+      </c>
+      <c r="L35">
+        <v>1</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35" s="4">
+        <v>6.2500000000000001E-4</v>
+      </c>
+      <c r="P35" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q35" s="5">
+        <v>1.7399999999999999E-2</v>
+      </c>
+      <c r="R35" s="5">
+        <v>8.5619999999999994</v>
+      </c>
+      <c r="S35" s="5">
+        <v>7.3000000000000001E-3</v>
+      </c>
+      <c r="T35">
+        <v>136</v>
+      </c>
+      <c r="U35" s="3">
+        <v>1</v>
+      </c>
+      <c r="V35" s="5">
+        <v>0.33329999999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A36" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B36">
+        <v>14</v>
+      </c>
+      <c r="C36">
+        <v>81</v>
+      </c>
+      <c r="D36">
+        <v>85</v>
+      </c>
+      <c r="E36" t="s">
+        <v>27</v>
+      </c>
+      <c r="F36">
+        <v>7468</v>
+      </c>
+      <c r="G36">
+        <v>25</v>
+      </c>
+      <c r="H36">
+        <v>5</v>
+      </c>
+      <c r="I36">
+        <v>18370</v>
+      </c>
+      <c r="J36">
+        <v>182</v>
+      </c>
+      <c r="K36">
+        <v>1112</v>
+      </c>
+      <c r="L36">
+        <v>11</v>
+      </c>
+      <c r="M36">
+        <v>15</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36" s="4">
+        <v>1.1342592592592593E-3</v>
+      </c>
+      <c r="P36" s="4">
+        <v>1.1111111111111111E-3</v>
+      </c>
+      <c r="Q36" s="5">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="R36" s="5">
+        <v>6.109</v>
+      </c>
+      <c r="S36" s="5">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="T36">
+        <v>1086</v>
+      </c>
+      <c r="U36" s="5">
+        <v>0.98640000000000005</v>
+      </c>
+      <c r="V36" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A37" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B37">
+        <v>14</v>
+      </c>
+      <c r="C37">
+        <v>84</v>
+      </c>
+      <c r="D37">
+        <v>86</v>
+      </c>
+      <c r="E37" t="s">
+        <v>26</v>
+      </c>
+      <c r="F37">
+        <v>15993</v>
+      </c>
+      <c r="G37">
+        <v>25</v>
+      </c>
+      <c r="H37">
+        <v>3</v>
+      </c>
+      <c r="I37">
+        <v>2302</v>
+      </c>
+      <c r="J37">
+        <v>94</v>
+      </c>
+      <c r="K37">
+        <v>150</v>
+      </c>
+      <c r="L37">
+        <v>4</v>
+      </c>
+      <c r="M37">
+        <v>15</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37" s="4">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="P37" s="4">
+        <v>8.4490740740740739E-4</v>
+      </c>
+      <c r="Q37" s="5">
+        <v>4.0800000000000003E-2</v>
+      </c>
+      <c r="R37" s="5">
+        <v>1.595</v>
+      </c>
+      <c r="S37" s="5">
+        <v>2.6700000000000002E-2</v>
+      </c>
+      <c r="T37">
+        <v>131</v>
+      </c>
+      <c r="U37" s="5">
+        <v>0.89729999999999999</v>
+      </c>
+      <c r="V37" s="5">
+        <v>0.88239999999999996</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B38">
+        <v>15</v>
+      </c>
+      <c r="C38">
+        <v>81</v>
+      </c>
+      <c r="D38">
+        <v>85</v>
+      </c>
+      <c r="E38" t="s">
+        <v>27</v>
+      </c>
+      <c r="F38">
+        <v>7468</v>
+      </c>
+      <c r="G38">
+        <v>25</v>
+      </c>
+      <c r="H38">
+        <v>8</v>
+      </c>
+      <c r="I38">
+        <v>14762</v>
+      </c>
+      <c r="J38">
+        <v>171</v>
+      </c>
+      <c r="K38">
+        <v>32</v>
+      </c>
+      <c r="L38">
+        <v>13</v>
+      </c>
+      <c r="M38">
+        <v>18</v>
+      </c>
+      <c r="N38">
+        <v>1</v>
+      </c>
+      <c r="O38" s="4">
+        <v>9.837962962962962E-4</v>
+      </c>
+      <c r="P38" s="4">
+        <v>1.4930555555555556E-3</v>
+      </c>
+      <c r="Q38" s="5">
+        <v>1.1599999999999999E-2</v>
+      </c>
+      <c r="R38" s="5">
+        <v>0.18709999999999999</v>
+      </c>
+      <c r="S38" s="5">
+        <v>0.40629999999999999</v>
+      </c>
+      <c r="T38">
+        <v>1</v>
+      </c>
+      <c r="U38" s="5">
+        <v>5.2600000000000001E-2</v>
+      </c>
+      <c r="V38" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A39" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B39">
+        <v>15</v>
+      </c>
+      <c r="C39">
+        <v>84</v>
+      </c>
+      <c r="D39">
+        <v>86</v>
+      </c>
+      <c r="E39" t="s">
+        <v>26</v>
+      </c>
+      <c r="F39">
+        <v>15993</v>
+      </c>
+      <c r="G39">
+        <v>25</v>
+      </c>
+      <c r="H39">
+        <v>4</v>
+      </c>
+      <c r="I39">
+        <v>5623</v>
+      </c>
+      <c r="J39">
+        <v>163</v>
+      </c>
+      <c r="K39">
+        <v>37</v>
+      </c>
+      <c r="L39">
+        <v>7</v>
+      </c>
+      <c r="M39">
+        <v>30</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39" s="4">
+        <v>3.9351851851851852E-4</v>
+      </c>
+      <c r="P39" s="4">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="Q39" s="5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="R39" s="5">
+        <v>0.22700000000000001</v>
+      </c>
+      <c r="S39" s="5">
+        <v>0.18920000000000001</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39" s="3">
+        <v>0</v>
+      </c>
+      <c r="V39" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B40">
+        <v>16</v>
+      </c>
+      <c r="C40">
+        <v>81</v>
+      </c>
+      <c r="D40">
+        <v>85</v>
+      </c>
+      <c r="E40" t="s">
+        <v>27</v>
+      </c>
+      <c r="F40">
+        <v>7468</v>
+      </c>
+      <c r="G40">
+        <v>25</v>
+      </c>
+      <c r="H40">
+        <v>4</v>
+      </c>
+      <c r="I40">
+        <v>16376</v>
+      </c>
+      <c r="J40">
+        <v>157</v>
+      </c>
+      <c r="K40">
+        <v>57</v>
+      </c>
+      <c r="L40">
+        <v>30</v>
+      </c>
+      <c r="M40">
+        <v>11</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40" s="4">
+        <v>1.1921296296296296E-3</v>
+      </c>
+      <c r="P40" s="4">
+        <v>3.2407407407407406E-4</v>
+      </c>
+      <c r="Q40" s="5">
+        <v>9.5999999999999992E-3</v>
+      </c>
+      <c r="R40" s="5">
+        <v>0.36309999999999998</v>
+      </c>
+      <c r="S40" s="5">
+        <v>0.52629999999999999</v>
+      </c>
+      <c r="T40">
+        <v>16</v>
+      </c>
+      <c r="U40" s="5">
+        <v>0.59260000000000002</v>
+      </c>
+      <c r="V40" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A41" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B41">
+        <v>16</v>
+      </c>
+      <c r="C41">
+        <v>84</v>
+      </c>
+      <c r="D41">
+        <v>86</v>
+      </c>
+      <c r="E41" t="s">
+        <v>26</v>
+      </c>
+      <c r="F41">
+        <v>15993</v>
+      </c>
+      <c r="G41">
+        <v>25</v>
+      </c>
+      <c r="H41">
+        <v>4</v>
+      </c>
+      <c r="I41">
+        <v>8943</v>
+      </c>
+      <c r="J41">
+        <v>253</v>
+      </c>
+      <c r="K41">
+        <v>75</v>
+      </c>
+      <c r="L41">
+        <v>25</v>
+      </c>
+      <c r="M41">
+        <v>40</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41" s="4">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="P41" s="4">
+        <v>4.5138888888888887E-4</v>
+      </c>
+      <c r="Q41" s="5">
+        <v>2.8299999999999999E-2</v>
+      </c>
+      <c r="R41" s="5">
+        <v>0.2964</v>
+      </c>
+      <c r="S41" s="5">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="T41">
+        <v>10</v>
+      </c>
+      <c r="U41" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="V41" s="5">
+        <v>0.95240000000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B42">
+        <v>17</v>
+      </c>
+      <c r="C42">
+        <v>81</v>
+      </c>
+      <c r="D42">
+        <v>85</v>
+      </c>
+      <c r="E42" t="s">
+        <v>27</v>
+      </c>
+      <c r="F42">
+        <v>7468</v>
+      </c>
+      <c r="G42">
+        <v>25</v>
+      </c>
+      <c r="H42">
+        <v>6</v>
+      </c>
+      <c r="I42">
+        <v>17303</v>
+      </c>
+      <c r="J42">
+        <v>114</v>
+      </c>
+      <c r="K42">
+        <v>36</v>
+      </c>
+      <c r="L42">
+        <v>19</v>
+      </c>
+      <c r="M42">
+        <v>11</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42" s="4">
+        <v>1.7476851851851852E-3</v>
+      </c>
+      <c r="P42" s="4">
+        <v>7.291666666666667E-4</v>
+      </c>
+      <c r="Q42" s="5">
+        <v>6.6E-3</v>
+      </c>
+      <c r="R42" s="5">
+        <v>0.31580000000000003</v>
+      </c>
+      <c r="S42" s="5">
+        <v>0.52780000000000005</v>
+      </c>
+      <c r="T42">
+        <v>6</v>
+      </c>
+      <c r="U42" s="5">
+        <v>0.35289999999999999</v>
+      </c>
+      <c r="V42" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B43">
+        <v>17</v>
+      </c>
+      <c r="C43">
+        <v>84</v>
+      </c>
+      <c r="D43">
+        <v>86</v>
+      </c>
+      <c r="E43" t="s">
+        <v>26</v>
+      </c>
+      <c r="F43">
+        <v>15993</v>
+      </c>
+      <c r="G43">
+        <v>25</v>
+      </c>
+      <c r="H43">
+        <v>2</v>
+      </c>
+      <c r="I43">
+        <v>6584</v>
+      </c>
+      <c r="J43">
+        <v>158</v>
+      </c>
+      <c r="K43">
+        <v>39</v>
+      </c>
+      <c r="L43">
+        <v>11</v>
+      </c>
+      <c r="M43">
+        <v>13</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43" s="4">
+        <v>4.7453703703703704E-4</v>
+      </c>
+      <c r="P43" s="4">
+        <v>6.134259259259259E-4</v>
+      </c>
+      <c r="Q43" s="5">
+        <v>2.4E-2</v>
+      </c>
+      <c r="R43" s="5">
+        <v>0.24679999999999999</v>
+      </c>
+      <c r="S43" s="5">
+        <v>0.28210000000000002</v>
+      </c>
+      <c r="T43">
+        <v>15</v>
+      </c>
+      <c r="U43" s="5">
+        <v>0.53569999999999995</v>
+      </c>
+      <c r="V43" s="5">
+        <v>0.79410000000000003</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B44">
+        <v>18</v>
+      </c>
+      <c r="C44">
+        <v>81</v>
+      </c>
+      <c r="D44">
+        <v>85</v>
+      </c>
+      <c r="E44" t="s">
+        <v>27</v>
+      </c>
+      <c r="F44">
+        <v>7468</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>133</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44" t="s">
+        <v>24</v>
+      </c>
+      <c r="P44" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" t="s">
+        <v>25</v>
+      </c>
+      <c r="S44" t="s">
+        <v>25</v>
+      </c>
+      <c r="T44">
+        <v>0</v>
+      </c>
+      <c r="U44" t="s">
+        <v>25</v>
+      </c>
+      <c r="V44" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A45" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B45">
+        <v>18</v>
+      </c>
+      <c r="C45">
+        <v>84</v>
+      </c>
+      <c r="D45">
+        <v>86</v>
+      </c>
+      <c r="E45" t="s">
+        <v>26</v>
+      </c>
+      <c r="F45">
+        <v>15993</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>18</v>
+      </c>
+      <c r="J45">
+        <v>1</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45" s="4">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="P45" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q45" s="5">
+        <v>5.5599999999999997E-2</v>
+      </c>
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" t="s">
+        <v>25</v>
+      </c>
+      <c r="T45">
+        <v>0</v>
+      </c>
+      <c r="U45" t="s">
+        <v>25</v>
+      </c>
+      <c r="V45" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B46">
+        <v>8</v>
+      </c>
+      <c r="C46">
+        <v>81</v>
+      </c>
+      <c r="D46">
+        <v>85</v>
+      </c>
+      <c r="E46" t="s">
+        <v>27</v>
+      </c>
+      <c r="F46">
+        <v>7407</v>
+      </c>
+      <c r="G46">
+        <v>25</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>17156</v>
+      </c>
+      <c r="J46">
+        <v>138</v>
+      </c>
+      <c r="K46">
+        <v>40</v>
+      </c>
+      <c r="L46">
+        <v>18</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46" s="4">
+        <v>1.4236111111111112E-3</v>
+      </c>
+      <c r="P46" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q46" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="R46" s="5">
+        <v>0.28989999999999999</v>
+      </c>
+      <c r="S46" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="T46">
+        <v>22</v>
+      </c>
+      <c r="U46" s="3">
+        <v>1</v>
+      </c>
+      <c r="V46" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B47">
+        <v>8</v>
+      </c>
+      <c r="C47">
+        <v>84</v>
+      </c>
+      <c r="D47">
+        <v>86</v>
+      </c>
+      <c r="E47" t="s">
+        <v>26</v>
+      </c>
+      <c r="F47">
+        <v>36058</v>
+      </c>
+      <c r="G47">
+        <v>25</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>7848</v>
+      </c>
+      <c r="J47">
+        <v>143</v>
+      </c>
+      <c r="K47">
+        <v>32</v>
+      </c>
+      <c r="L47">
+        <v>9</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47" s="4">
+        <v>6.2500000000000001E-4</v>
+      </c>
+      <c r="P47" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q47" s="5">
+        <v>1.8200000000000001E-2</v>
+      </c>
+      <c r="R47" s="5">
+        <v>0.2238</v>
+      </c>
+      <c r="S47" s="5">
+        <v>0.28129999999999999</v>
+      </c>
+      <c r="T47">
+        <v>23</v>
+      </c>
+      <c r="U47" s="3">
+        <v>1</v>
+      </c>
+      <c r="V47" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B48">
+        <v>9</v>
+      </c>
+      <c r="C48">
+        <v>81</v>
+      </c>
+      <c r="D48">
+        <v>85</v>
+      </c>
+      <c r="E48" t="s">
+        <v>27</v>
+      </c>
+      <c r="F48">
+        <v>7407</v>
+      </c>
+      <c r="G48">
+        <v>25</v>
+      </c>
+      <c r="H48">
+        <v>5</v>
+      </c>
+      <c r="I48">
+        <v>17669</v>
+      </c>
+      <c r="J48">
+        <v>163</v>
+      </c>
+      <c r="K48">
+        <v>1068</v>
+      </c>
+      <c r="L48">
+        <v>31</v>
+      </c>
+      <c r="M48">
+        <v>20</v>
+      </c>
+      <c r="N48">
+        <v>1</v>
+      </c>
+      <c r="O48" s="4">
+        <v>1.2268518518518518E-3</v>
+      </c>
+      <c r="P48" s="4">
+        <v>1.5740740740740741E-3</v>
+      </c>
+      <c r="Q48" s="5">
+        <v>9.1999999999999998E-3</v>
+      </c>
+      <c r="R48" s="5">
+        <v>6.5519999999999996</v>
+      </c>
+      <c r="S48" s="5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="T48">
+        <v>1017</v>
+      </c>
+      <c r="U48" s="5">
+        <v>0.98070000000000002</v>
+      </c>
+      <c r="V48" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B49">
+        <v>9</v>
+      </c>
+      <c r="C49">
+        <v>84</v>
+      </c>
+      <c r="D49">
+        <v>86</v>
+      </c>
+      <c r="E49" t="s">
+        <v>26</v>
+      </c>
+      <c r="F49">
+        <v>36058</v>
+      </c>
+      <c r="G49">
+        <v>25</v>
+      </c>
+      <c r="H49">
+        <v>3</v>
+      </c>
+      <c r="I49">
+        <v>6190</v>
+      </c>
+      <c r="J49">
+        <v>93</v>
+      </c>
+      <c r="K49">
+        <v>280</v>
+      </c>
+      <c r="L49">
+        <v>9</v>
+      </c>
+      <c r="M49">
+        <v>14</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49" s="4">
+        <v>7.5231481481481482E-4</v>
+      </c>
+      <c r="P49" s="4">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="Q49" s="5">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="R49" s="5">
+        <v>3.01</v>
+      </c>
+      <c r="S49" s="5">
+        <v>3.2099999999999997E-2</v>
+      </c>
+      <c r="T49">
+        <v>257</v>
+      </c>
+      <c r="U49" s="5">
+        <v>0.94830000000000003</v>
+      </c>
+      <c r="V49" s="5">
+        <v>0.86360000000000003</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B50">
+        <v>10</v>
+      </c>
+      <c r="C50">
+        <v>81</v>
+      </c>
+      <c r="D50">
+        <v>85</v>
+      </c>
+      <c r="E50" t="s">
+        <v>27</v>
+      </c>
+      <c r="F50">
+        <v>7407</v>
+      </c>
+      <c r="G50">
+        <v>25</v>
+      </c>
+      <c r="H50">
+        <v>8</v>
+      </c>
+      <c r="I50">
+        <v>21673</v>
+      </c>
+      <c r="J50">
+        <v>165</v>
+      </c>
+      <c r="K50">
+        <v>1685</v>
+      </c>
+      <c r="L50">
+        <v>23</v>
+      </c>
+      <c r="M50">
+        <v>25</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50" s="4">
+        <v>1.4699074074074074E-3</v>
+      </c>
+      <c r="P50" s="4">
+        <v>1.1921296296296296E-3</v>
+      </c>
+      <c r="Q50" s="5">
+        <v>7.6E-3</v>
+      </c>
+      <c r="R50" s="5">
+        <v>10.210000000000001</v>
+      </c>
+      <c r="S50" s="5">
+        <v>1.3599999999999999E-2</v>
+      </c>
+      <c r="T50">
+        <v>1637</v>
+      </c>
+      <c r="U50" s="5">
+        <v>0.98499999999999999</v>
+      </c>
+      <c r="V50" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A51" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B51">
+        <v>10</v>
+      </c>
+      <c r="C51">
+        <v>84</v>
+      </c>
+      <c r="D51">
+        <v>86</v>
+      </c>
+      <c r="E51" t="s">
+        <v>26</v>
+      </c>
+      <c r="F51">
+        <v>36058</v>
+      </c>
+      <c r="G51">
+        <v>25</v>
+      </c>
+      <c r="H51">
+        <v>3</v>
+      </c>
+      <c r="I51">
+        <v>2538</v>
+      </c>
+      <c r="J51">
+        <v>75</v>
+      </c>
+      <c r="K51">
+        <v>76</v>
+      </c>
+      <c r="L51">
+        <v>4</v>
+      </c>
+      <c r="M51">
+        <v>8</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51" s="4">
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="P51" s="4">
+        <v>4.861111111111111E-4</v>
+      </c>
+      <c r="Q51" s="5">
+        <v>2.9600000000000001E-2</v>
+      </c>
+      <c r="R51" s="5">
+        <v>1.0129999999999999</v>
+      </c>
+      <c r="S51" s="5">
+        <v>5.2600000000000001E-2</v>
+      </c>
+      <c r="T51">
+        <v>64</v>
+      </c>
+      <c r="U51" s="5">
+        <v>0.88890000000000002</v>
+      </c>
+      <c r="V51" s="5">
+        <v>0.90910000000000002</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A52" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B52">
+        <v>11</v>
+      </c>
+      <c r="C52">
+        <v>81</v>
+      </c>
+      <c r="D52">
+        <v>85</v>
+      </c>
+      <c r="E52" t="s">
+        <v>27</v>
+      </c>
+      <c r="F52">
+        <v>7407</v>
+      </c>
+      <c r="G52">
+        <v>25</v>
+      </c>
+      <c r="H52">
+        <v>8</v>
+      </c>
+      <c r="I52">
+        <v>17931</v>
+      </c>
+      <c r="J52">
+        <v>141</v>
+      </c>
+      <c r="K52">
+        <v>2061</v>
+      </c>
+      <c r="L52">
+        <v>28</v>
+      </c>
+      <c r="M52">
+        <v>15</v>
+      </c>
+      <c r="N52">
+        <v>1</v>
+      </c>
+      <c r="O52" s="4">
+        <v>1.4120370370370369E-3</v>
+      </c>
+      <c r="P52" s="4">
+        <v>1.4120370370370369E-3</v>
+      </c>
+      <c r="Q52" s="5">
+        <v>7.9000000000000008E-3</v>
+      </c>
+      <c r="R52" s="5">
+        <v>14.61</v>
+      </c>
+      <c r="S52" s="5">
+        <v>1.3599999999999999E-2</v>
+      </c>
+      <c r="T52">
+        <v>2018</v>
+      </c>
+      <c r="U52" s="5">
+        <v>0.99260000000000004</v>
+      </c>
+      <c r="V52" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A53" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B53">
+        <v>11</v>
+      </c>
+      <c r="C53">
+        <v>84</v>
+      </c>
+      <c r="D53">
+        <v>86</v>
+      </c>
+      <c r="E53" t="s">
+        <v>26</v>
+      </c>
+      <c r="F53">
+        <v>36058</v>
+      </c>
+      <c r="G53">
+        <v>25</v>
+      </c>
+      <c r="H53">
+        <v>3</v>
+      </c>
+      <c r="I53">
+        <v>2818</v>
+      </c>
+      <c r="J53">
+        <v>119</v>
+      </c>
+      <c r="K53">
+        <v>231</v>
+      </c>
+      <c r="L53">
+        <v>4</v>
+      </c>
+      <c r="M53">
+        <v>17</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53" s="4">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="P53" s="4">
+        <v>1.5162037037037036E-3</v>
+      </c>
+      <c r="Q53" s="5">
+        <v>4.2200000000000001E-2</v>
+      </c>
+      <c r="R53" s="5">
+        <v>1.9410000000000001</v>
+      </c>
+      <c r="S53" s="5">
+        <v>1.7299999999999999E-2</v>
+      </c>
+      <c r="T53">
+        <v>210</v>
+      </c>
+      <c r="U53" s="5">
+        <v>0.92510000000000003</v>
+      </c>
+      <c r="V53" s="5">
+        <v>0.95450000000000002</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A54" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B54">
+        <v>12</v>
+      </c>
+      <c r="C54">
+        <v>81</v>
+      </c>
+      <c r="D54">
+        <v>85</v>
+      </c>
+      <c r="E54" t="s">
+        <v>27</v>
+      </c>
+      <c r="F54">
+        <v>7407</v>
+      </c>
+      <c r="G54">
+        <v>25</v>
+      </c>
+      <c r="H54">
+        <v>8</v>
+      </c>
+      <c r="I54">
+        <v>31421</v>
+      </c>
+      <c r="J54">
+        <v>209</v>
+      </c>
+      <c r="K54">
+        <v>4079</v>
+      </c>
+      <c r="L54">
+        <v>26</v>
+      </c>
+      <c r="M54">
+        <v>16</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54" s="4">
+        <v>1.6666666666666668E-3</v>
+      </c>
+      <c r="P54" s="4">
+        <v>1.2152777777777778E-3</v>
+      </c>
+      <c r="Q54" s="5">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="R54" s="5">
+        <v>19.510000000000002</v>
+      </c>
+      <c r="S54" s="5">
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="T54">
+        <v>4037</v>
+      </c>
+      <c r="U54" s="5">
+        <v>0.99609999999999999</v>
+      </c>
+      <c r="V54" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A55" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B55">
+        <v>12</v>
+      </c>
+      <c r="C55">
+        <v>84</v>
+      </c>
+      <c r="D55">
+        <v>86</v>
+      </c>
+      <c r="E55" t="s">
+        <v>26</v>
+      </c>
+      <c r="F55">
+        <v>36058</v>
+      </c>
+      <c r="G55">
+        <v>25</v>
+      </c>
+      <c r="H55">
+        <v>3</v>
+      </c>
+      <c r="I55">
+        <v>1295</v>
+      </c>
+      <c r="J55">
+        <v>51</v>
+      </c>
+      <c r="K55">
+        <v>208</v>
+      </c>
+      <c r="L55">
+        <v>3</v>
+      </c>
+      <c r="M55">
+        <v>12</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55" s="4">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="P55" s="4">
+        <v>7.8703703703703705E-4</v>
+      </c>
+      <c r="Q55" s="5">
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="R55" s="5">
+        <v>4.0780000000000003</v>
+      </c>
+      <c r="S55" s="5">
+        <v>1.44E-2</v>
+      </c>
+      <c r="T55">
+        <v>193</v>
+      </c>
+      <c r="U55" s="5">
+        <v>0.9415</v>
+      </c>
+      <c r="V55" s="5">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A56" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B56">
+        <v>13</v>
+      </c>
+      <c r="C56">
+        <v>81</v>
+      </c>
+      <c r="D56">
+        <v>85</v>
+      </c>
+      <c r="E56" t="s">
+        <v>27</v>
+      </c>
+      <c r="F56">
+        <v>7407</v>
+      </c>
+      <c r="G56">
+        <v>25</v>
+      </c>
+      <c r="H56">
+        <v>6</v>
+      </c>
+      <c r="I56">
+        <v>32181</v>
+      </c>
+      <c r="J56">
+        <v>227</v>
+      </c>
+      <c r="K56">
+        <v>4284</v>
+      </c>
+      <c r="L56">
+        <v>26</v>
+      </c>
+      <c r="M56">
+        <v>21</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56" s="4">
+        <v>1.5393518518518519E-3</v>
+      </c>
+      <c r="P56" s="4">
+        <v>1.5740740740740741E-3</v>
+      </c>
+      <c r="Q56" s="5">
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="R56" s="5">
+        <v>18.87</v>
+      </c>
+      <c r="S56" s="5">
+        <v>6.1000000000000004E-3</v>
+      </c>
+      <c r="T56">
+        <v>4237</v>
+      </c>
+      <c r="U56" s="5">
+        <v>0.99509999999999998</v>
+      </c>
+      <c r="V56" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A57" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B57">
+        <v>14</v>
+      </c>
+      <c r="C57">
+        <v>81</v>
+      </c>
+      <c r="D57">
+        <v>85</v>
+      </c>
+      <c r="E57" t="s">
+        <v>27</v>
+      </c>
+      <c r="F57">
+        <v>7407</v>
+      </c>
+      <c r="G57">
+        <v>25</v>
+      </c>
+      <c r="H57">
+        <v>6</v>
+      </c>
+      <c r="I57">
+        <v>12598</v>
+      </c>
+      <c r="J57">
+        <v>72</v>
+      </c>
+      <c r="K57">
+        <v>1575</v>
+      </c>
+      <c r="L57">
+        <v>13</v>
+      </c>
+      <c r="M57">
+        <v>7</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57" s="4">
+        <v>1.9560185185185184E-3</v>
+      </c>
+      <c r="P57" s="4">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="Q57" s="5">
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="R57" s="5">
+        <v>21.87</v>
+      </c>
+      <c r="S57" s="5">
+        <v>8.3000000000000001E-3</v>
+      </c>
+      <c r="T57">
+        <v>1555</v>
+      </c>
+      <c r="U57" s="5">
+        <v>0.99550000000000005</v>
+      </c>
+      <c r="V57" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A58" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B58">
+        <v>15</v>
+      </c>
+      <c r="C58">
+        <v>81</v>
+      </c>
+      <c r="D58">
+        <v>85</v>
+      </c>
+      <c r="E58" t="s">
+        <v>27</v>
+      </c>
+      <c r="F58">
+        <v>7407</v>
+      </c>
+      <c r="G58">
+        <v>25</v>
+      </c>
+      <c r="H58">
+        <v>6</v>
+      </c>
+      <c r="I58">
+        <v>19843</v>
+      </c>
+      <c r="J58">
+        <v>140</v>
+      </c>
+      <c r="K58">
+        <v>1634</v>
+      </c>
+      <c r="L58">
+        <v>16</v>
+      </c>
+      <c r="M58">
+        <v>10</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58" s="4">
+        <v>1.5625000000000001E-3</v>
+      </c>
+      <c r="P58" s="4">
+        <v>9.3749999999999997E-4</v>
+      </c>
+      <c r="Q58" s="5">
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="R58" s="5">
+        <v>11.67</v>
+      </c>
+      <c r="S58" s="5">
+        <v>9.7999999999999997E-3</v>
+      </c>
+      <c r="T58">
+        <v>1608</v>
+      </c>
+      <c r="U58" s="5">
+        <v>0.99380000000000002</v>
+      </c>
+      <c r="V58" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A59" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B59">
+        <v>16</v>
+      </c>
+      <c r="C59">
+        <v>81</v>
+      </c>
+      <c r="D59">
+        <v>85</v>
+      </c>
+      <c r="E59" t="s">
+        <v>27</v>
+      </c>
+      <c r="F59">
+        <v>7407</v>
+      </c>
+      <c r="G59">
+        <v>25</v>
+      </c>
+      <c r="H59">
+        <v>8</v>
+      </c>
+      <c r="I59">
+        <v>31658</v>
+      </c>
+      <c r="J59">
+        <v>240</v>
+      </c>
+      <c r="K59">
+        <v>1300</v>
+      </c>
+      <c r="L59">
+        <v>57</v>
+      </c>
+      <c r="M59">
+        <v>16</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59" s="4">
+        <v>1.4930555555555556E-3</v>
+      </c>
+      <c r="P59" s="4">
+        <v>1.0648148148148149E-3</v>
+      </c>
+      <c r="Q59" s="5">
+        <v>7.6E-3</v>
+      </c>
+      <c r="R59" s="5">
+        <v>5.4160000000000004</v>
+      </c>
+      <c r="S59" s="5">
+        <v>4.3799999999999999E-2</v>
+      </c>
+      <c r="T59">
+        <v>1227</v>
+      </c>
+      <c r="U59" s="5">
+        <v>0.98709999999999998</v>
+      </c>
+      <c r="V59" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A60" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B60">
+        <v>17</v>
+      </c>
+      <c r="C60">
+        <v>81</v>
+      </c>
+      <c r="D60">
+        <v>85</v>
+      </c>
+      <c r="E60" t="s">
+        <v>27</v>
+      </c>
+      <c r="F60">
+        <v>7407</v>
+      </c>
+      <c r="G60">
+        <v>25</v>
+      </c>
+      <c r="H60">
+        <v>5</v>
+      </c>
+      <c r="I60">
+        <v>28922</v>
+      </c>
+      <c r="J60">
+        <v>139</v>
+      </c>
+      <c r="K60">
+        <v>1897</v>
+      </c>
+      <c r="L60">
+        <v>31</v>
+      </c>
+      <c r="M60">
+        <v>10</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60" s="4">
+        <v>2.3495370370370371E-3</v>
+      </c>
+      <c r="P60" s="4">
+        <v>1.5856481481481481E-3</v>
+      </c>
+      <c r="Q60" s="5">
+        <v>4.7999999999999996E-3</v>
+      </c>
+      <c r="R60" s="5">
+        <v>13.64</v>
+      </c>
+      <c r="S60" s="5">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="T60">
+        <v>1856</v>
+      </c>
+      <c r="U60" s="5">
+        <v>0.99460000000000004</v>
+      </c>
+      <c r="V60" s="5">
+        <v>0.92310000000000003</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A61" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B61">
+        <v>18</v>
+      </c>
+      <c r="C61">
+        <v>81</v>
+      </c>
+      <c r="D61">
+        <v>85</v>
+      </c>
+      <c r="E61" t="s">
+        <v>27</v>
+      </c>
+      <c r="F61">
+        <v>7407</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>278</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>73</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61" t="s">
+        <v>24</v>
+      </c>
+      <c r="P61" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" t="s">
+        <v>25</v>
+      </c>
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61">
+        <v>73</v>
+      </c>
+      <c r="U61" s="3">
+        <v>1</v>
+      </c>
+      <c r="V61" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A62" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B62">
+        <v>9</v>
+      </c>
+      <c r="C62">
+        <v>81</v>
+      </c>
+      <c r="D62">
+        <v>85</v>
+      </c>
+      <c r="E62" t="s">
+        <v>27</v>
+      </c>
+      <c r="F62">
+        <v>7392</v>
+      </c>
+      <c r="G62">
+        <v>25</v>
+      </c>
+      <c r="H62">
+        <v>5</v>
+      </c>
+      <c r="I62">
+        <v>18853</v>
+      </c>
+      <c r="J62">
+        <v>112</v>
+      </c>
+      <c r="K62">
+        <v>28</v>
+      </c>
+      <c r="L62">
+        <v>20</v>
+      </c>
+      <c r="M62">
+        <v>7</v>
+      </c>
+      <c r="N62">
+        <v>1</v>
+      </c>
+      <c r="O62" s="4">
+        <v>1.8634259259259259E-3</v>
+      </c>
+      <c r="P62" s="4">
+        <v>1.4467592592592592E-3</v>
+      </c>
+      <c r="Q62" s="5">
+        <v>5.8999999999999999E-3</v>
+      </c>
+      <c r="R62" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="S62" s="5">
+        <v>0.71430000000000005</v>
+      </c>
+      <c r="T62">
+        <v>1</v>
+      </c>
+      <c r="U62" s="5">
+        <v>0.125</v>
+      </c>
+      <c r="V62" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A63" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B63">
+        <v>10</v>
+      </c>
+      <c r="C63">
+        <v>81</v>
+      </c>
+      <c r="D63">
+        <v>85</v>
+      </c>
+      <c r="E63" t="s">
+        <v>27</v>
+      </c>
+      <c r="F63">
+        <v>7392</v>
+      </c>
+      <c r="G63">
+        <v>25</v>
+      </c>
+      <c r="H63">
+        <v>5</v>
+      </c>
+      <c r="I63">
+        <v>31047</v>
+      </c>
+      <c r="J63">
+        <v>228</v>
+      </c>
+      <c r="K63">
+        <v>72</v>
+      </c>
+      <c r="L63">
+        <v>60</v>
+      </c>
+      <c r="M63">
+        <v>12</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63" s="4">
+        <v>1.5046296296296296E-3</v>
+      </c>
+      <c r="P63" s="4">
+        <v>5.7870370370370367E-4</v>
+      </c>
+      <c r="Q63" s="5">
+        <v>7.3000000000000001E-3</v>
+      </c>
+      <c r="R63" s="5">
+        <v>0.31580000000000003</v>
+      </c>
+      <c r="S63" s="5">
+        <v>0.83330000000000004</v>
+      </c>
+      <c r="T63">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2064,4 +4794,1277 @@
   <sheetData/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95E31587-C25C-4BF6-8E90-7B26C43A25CA}">
+  <dimension ref="A1:U20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="3.88671875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O1" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>18</v>
+      </c>
+      <c r="R1" t="s">
+        <v>19</v>
+      </c>
+      <c r="S1" t="s">
+        <v>20</v>
+      </c>
+      <c r="T1" t="s">
+        <v>21</v>
+      </c>
+      <c r="U1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B2">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1210</v>
+      </c>
+      <c r="H2">
+        <v>78</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2" s="4">
+        <v>1.7361111111111112E-4</v>
+      </c>
+      <c r="M2" s="4">
+        <v>9.3749999999999997E-4</v>
+      </c>
+      <c r="N2" s="5">
+        <v>6.4500000000000002E-2</v>
+      </c>
+      <c r="O2" s="5">
+        <v>3.85E-2</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>0</v>
+      </c>
+      <c r="R2" s="5">
+        <v>2</v>
+      </c>
+      <c r="S2" s="5">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="T2" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>1363</v>
+      </c>
+      <c r="H3">
+        <v>75</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="M3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="5">
+        <v>5.5E-2</v>
+      </c>
+      <c r="O3" s="3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>25</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3" t="s">
+        <v>25</v>
+      </c>
+      <c r="T3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B4">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>1226</v>
+      </c>
+      <c r="H4">
+        <v>100</v>
+      </c>
+      <c r="I4">
+        <v>4</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="M4" s="4">
+        <v>1.7361111111111112E-4</v>
+      </c>
+      <c r="N4" s="5">
+        <v>8.1600000000000006E-2</v>
+      </c>
+      <c r="O4" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>0</v>
+      </c>
+      <c r="R4" s="3">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="T4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B5">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1520</v>
+      </c>
+      <c r="H5">
+        <v>69</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4">
+        <v>2.5462962962962961E-4</v>
+      </c>
+      <c r="M5" s="4">
+        <v>3.9351851851851852E-4</v>
+      </c>
+      <c r="N5" s="5">
+        <v>4.5400000000000003E-2</v>
+      </c>
+      <c r="O5" s="5">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>0</v>
+      </c>
+      <c r="R5" s="3">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="T5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B6">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1476</v>
+      </c>
+      <c r="H6">
+        <v>73</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="M6" s="4">
+        <v>4.7800925925925927E-3</v>
+      </c>
+      <c r="N6" s="5">
+        <v>4.9500000000000002E-2</v>
+      </c>
+      <c r="O6" s="5">
+        <v>4.1099999999999998E-2</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>0</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="T6" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B7">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>671</v>
+      </c>
+      <c r="H7">
+        <v>32</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7" s="4">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="M7" s="4">
+        <v>1.8287037037037037E-3</v>
+      </c>
+      <c r="N7" s="5">
+        <v>4.7699999999999999E-2</v>
+      </c>
+      <c r="O7" s="5">
+        <v>3.1300000000000001E-2</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>0</v>
+      </c>
+      <c r="R7" s="3">
+        <v>0</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+      <c r="T7" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B8">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>1542</v>
+      </c>
+      <c r="H8">
+        <v>61</v>
+      </c>
+      <c r="I8">
+        <v>5</v>
+      </c>
+      <c r="J8">
+        <v>5</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="M8" s="4">
+        <v>8.564814814814815E-4</v>
+      </c>
+      <c r="N8" s="5">
+        <v>3.9600000000000003E-2</v>
+      </c>
+      <c r="O8" s="5">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+      <c r="T8" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B9">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1537</v>
+      </c>
+      <c r="H9">
+        <v>75</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9">
+        <v>2</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9" s="4">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="M9" s="4">
+        <v>3.3564814814814812E-4</v>
+      </c>
+      <c r="N9" s="5">
+        <v>4.8800000000000003E-2</v>
+      </c>
+      <c r="O9" s="5">
+        <v>2.6700000000000002E-2</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>0</v>
+      </c>
+      <c r="R9" s="3">
+        <v>0</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
+      <c r="T9" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B10">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1488</v>
+      </c>
+      <c r="H10">
+        <v>74</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="M10" s="4">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="N10" s="5">
+        <v>4.9700000000000001E-2</v>
+      </c>
+      <c r="O10" s="5">
+        <v>2.7E-2</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>0</v>
+      </c>
+      <c r="R10" s="3">
+        <v>1</v>
+      </c>
+      <c r="S10" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="T10" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B11">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11" t="s">
+        <v>24</v>
+      </c>
+      <c r="M11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N11" s="3">
+        <v>0</v>
+      </c>
+      <c r="O11" t="s">
+        <v>25</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>25</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B12">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12">
+        <v>1418</v>
+      </c>
+      <c r="H12">
+        <v>71</v>
+      </c>
+      <c r="I12">
+        <v>5</v>
+      </c>
+      <c r="J12">
+        <v>5</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12" s="4">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="M12" s="4">
+        <v>1.2847222222222223E-3</v>
+      </c>
+      <c r="N12" s="5">
+        <v>5.0099999999999999E-2</v>
+      </c>
+      <c r="O12" s="5">
+        <v>7.0400000000000004E-2</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>0</v>
+      </c>
+      <c r="R12" s="3">
+        <v>0</v>
+      </c>
+      <c r="S12" s="5">
+        <v>0</v>
+      </c>
+      <c r="T12" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B13">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>1672</v>
+      </c>
+      <c r="H13">
+        <v>55</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4">
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="M13" t="s">
+        <v>24</v>
+      </c>
+      <c r="N13" s="5">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>25</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13" t="s">
+        <v>25</v>
+      </c>
+      <c r="T13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B14">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14">
+        <v>867</v>
+      </c>
+      <c r="H14">
+        <v>39</v>
+      </c>
+      <c r="I14">
+        <v>3</v>
+      </c>
+      <c r="J14">
+        <v>3</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4">
+        <v>2.5462962962962961E-4</v>
+      </c>
+      <c r="M14" s="4">
+        <v>1.0069444444444444E-3</v>
+      </c>
+      <c r="N14" s="5">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="O14" s="5">
+        <v>7.6899999999999996E-2</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="5">
+        <v>0</v>
+      </c>
+      <c r="T14" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B15">
+        <v>10</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15">
+        <v>1794</v>
+      </c>
+      <c r="H15">
+        <v>57</v>
+      </c>
+      <c r="I15">
+        <v>4</v>
+      </c>
+      <c r="J15">
+        <v>4</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15" s="4">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="M15" s="4">
+        <v>1.8055555555555555E-3</v>
+      </c>
+      <c r="N15" s="5">
+        <v>3.1800000000000002E-2</v>
+      </c>
+      <c r="O15" s="5">
+        <v>7.0199999999999999E-2</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="5">
+        <v>0</v>
+      </c>
+      <c r="T15" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B16">
+        <v>11</v>
+      </c>
+      <c r="C16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+      <c r="G16">
+        <v>532</v>
+      </c>
+      <c r="H16">
+        <v>28</v>
+      </c>
+      <c r="I16">
+        <v>5</v>
+      </c>
+      <c r="J16">
+        <v>5</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16" s="4">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="M16" s="4">
+        <v>2.3726851851851851E-3</v>
+      </c>
+      <c r="N16" s="5">
+        <v>5.2600000000000001E-2</v>
+      </c>
+      <c r="O16" s="5">
+        <v>0.17860000000000001</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>0</v>
+      </c>
+      <c r="R16" s="3">
+        <v>0</v>
+      </c>
+      <c r="S16" s="5">
+        <v>0</v>
+      </c>
+      <c r="T16" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B17">
+        <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>46</v>
+      </c>
+      <c r="H17">
+        <v>4</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17" s="4">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="M17" t="s">
+        <v>24</v>
+      </c>
+      <c r="N17" s="5">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="O17" s="3">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>25</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17" t="s">
+        <v>25</v>
+      </c>
+      <c r="T17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B18">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>466</v>
+      </c>
+      <c r="H18">
+        <v>15</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18" s="4">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="M18" s="4">
+        <v>2.3148148148148147E-3</v>
+      </c>
+      <c r="N18" s="5">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="O18" s="5">
+        <v>6.6699999999999995E-2</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>0</v>
+      </c>
+      <c r="R18" s="3">
+        <v>0</v>
+      </c>
+      <c r="S18" s="5">
+        <v>0</v>
+      </c>
+      <c r="T18" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B19">
+        <v>14</v>
+      </c>
+      <c r="C19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>260</v>
+      </c>
+      <c r="H19">
+        <v>12</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19" s="4">
+        <v>2.4305555555555555E-4</v>
+      </c>
+      <c r="M19" t="s">
+        <v>24</v>
+      </c>
+      <c r="N19" s="5">
+        <v>4.6199999999999998E-2</v>
+      </c>
+      <c r="O19" s="3">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>25</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19" t="s">
+        <v>25</v>
+      </c>
+      <c r="T19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B20">
+        <v>15</v>
+      </c>
+      <c r="C20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>1184</v>
+      </c>
+      <c r="H20">
+        <v>28</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20" s="4">
+        <v>4.861111111111111E-4</v>
+      </c>
+      <c r="M20" s="4">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="N20" s="5">
+        <v>2.3599999999999999E-2</v>
+      </c>
+      <c r="O20" s="5">
+        <v>3.5700000000000003E-2</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="5">
+        <v>0</v>
+      </c>
+      <c r="T20" s="5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/data/base_creditas.xlsx
+++ b/data/base_creditas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{629A76BA-11EA-4A54-9C1F-9518636F2B20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB7EA03-FC73-4515-A80C-AF94A85DB08D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="30">
   <si>
     <t>Data</t>
   </si>
@@ -111,7 +111,7 @@
     <t>WAY_Cobranca</t>
   </si>
   <si>
-    <t>NULL</t>
+    <t>WAY_Cobranca_Rescindidos</t>
   </si>
 </sst>
 </file>
@@ -170,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -179,6 +179,7 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4798,1270 +4799,2245 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95E31587-C25C-4BF6-8E90-7B26C43A25CA}">
-  <dimension ref="A1:U20"/>
+  <dimension ref="A1:T49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="3.88671875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" customWidth="1"/>
+    <col min="4" max="4" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R1" t="s">
+        <v>20</v>
+      </c>
+      <c r="S1" t="s">
+        <v>21</v>
+      </c>
+      <c r="T1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>46143</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="6">
+        <v>13034</v>
+      </c>
+      <c r="G2" s="6">
+        <v>715</v>
+      </c>
+      <c r="H2">
+        <v>31</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" s="5">
+        <v>5.4899999999999997E-2</v>
+      </c>
+      <c r="N2" s="5">
+        <v>4.3400000000000001E-2</v>
+      </c>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>46143</v>
+      </c>
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="6">
+        <v>2844</v>
+      </c>
+      <c r="G3" s="6">
+        <v>65</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4">
+        <v>1.6203703703703703E-4</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="5">
+        <v>2.29E-2</v>
+      </c>
+      <c r="N3" s="3">
+        <v>3.0800000000000001E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>46144</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
+        <v>563</v>
+      </c>
+      <c r="G4" s="6">
+        <v>14</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4">
+        <v>1.5046296296296297E-4</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" s="5">
+        <v>2.4899999999999999E-2</v>
+      </c>
+      <c r="N4" s="3">
+        <v>7.1400000000000005E-2</v>
+      </c>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>46144</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6">
+        <v>9493</v>
+      </c>
+      <c r="G5" s="6">
+        <v>545</v>
+      </c>
+      <c r="H5">
+        <v>14</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" s="5">
+        <v>5.74E-2</v>
+      </c>
+      <c r="N5" s="5">
+        <v>2.5700000000000001E-2</v>
+      </c>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>46146</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F6" s="6">
+        <v>10921</v>
+      </c>
+      <c r="G6" s="6">
+        <v>670</v>
+      </c>
+      <c r="H6">
+        <v>27</v>
+      </c>
+      <c r="I6">
+        <v>17</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="L6" s="4">
+        <v>6.5972222222222224E-4</v>
+      </c>
+      <c r="M6" s="5">
+        <v>6.13E-2</v>
+      </c>
+      <c r="N6" s="5">
+        <v>4.0300000000000002E-2</v>
+      </c>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>46146</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7" s="6">
+        <v>2841</v>
+      </c>
+      <c r="G7" s="6">
+        <v>55</v>
+      </c>
+      <c r="H7">
         <v>5</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="L7" s="4">
+        <v>7.407407407407407E-4</v>
+      </c>
+      <c r="M7" s="5">
+        <v>1.9400000000000001E-2</v>
+      </c>
+      <c r="N7" s="5">
+        <v>9.0899999999999995E-2</v>
+      </c>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>46147</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8" s="6">
+        <v>5996</v>
+      </c>
+      <c r="G8" s="6">
+        <v>205</v>
+      </c>
+      <c r="H8">
+        <v>34</v>
+      </c>
+      <c r="I8">
+        <v>21</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="L8" s="4">
+        <v>9.9537037037037042E-4</v>
+      </c>
+      <c r="M8" s="5">
+        <v>3.4200000000000001E-2</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0.16589999999999999</v>
+      </c>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>46147</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9" s="6">
+        <v>11875</v>
+      </c>
+      <c r="G9" s="6">
+        <v>562</v>
+      </c>
+      <c r="H9">
+        <v>28</v>
+      </c>
+      <c r="I9">
+        <v>26</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9" s="4">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="L9" s="4">
+        <v>1.1574074074074073E-3</v>
+      </c>
+      <c r="M9" s="5">
+        <v>4.7300000000000002E-2</v>
+      </c>
+      <c r="N9" s="5">
+        <v>4.9799999999999997E-2</v>
+      </c>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+      <c r="F10">
+        <v>13292</v>
+      </c>
+      <c r="G10">
+        <v>677</v>
+      </c>
+      <c r="H10">
+        <v>18</v>
+      </c>
+      <c r="I10">
+        <v>17</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10" s="4">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="L10" s="4">
+        <v>1.6550925925925926E-3</v>
+      </c>
+      <c r="M10" s="5">
+        <v>5.0900000000000001E-2</v>
+      </c>
+      <c r="N10" s="5">
+        <v>2.6599999999999999E-2</v>
+      </c>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11">
+        <v>2351</v>
+      </c>
+      <c r="G11">
+        <v>73</v>
+      </c>
+      <c r="H11">
+        <v>10</v>
+      </c>
+      <c r="I11">
+        <v>4</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11" s="4">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="L11" s="4">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="M11" s="3">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0.13700000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>46149</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6">
+        <v>5</v>
+      </c>
+      <c r="G12" s="6">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="4"/>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>46149</v>
+      </c>
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>5</v>
+      </c>
+      <c r="F13" s="6">
+        <v>13270</v>
+      </c>
+      <c r="G13" s="6">
+        <v>682</v>
+      </c>
+      <c r="H13">
+        <v>30</v>
+      </c>
+      <c r="I13">
+        <v>26</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13" s="4">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="L13" s="4">
+        <v>1.5509259259259259E-3</v>
+      </c>
+      <c r="M13" s="5">
+        <v>5.1400000000000001E-2</v>
+      </c>
+      <c r="N13" s="3">
+        <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>46150</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
         <v>6</v>
       </c>
-      <c r="F1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" t="s">
-        <v>15</v>
-      </c>
-      <c r="N1" t="s">
-        <v>16</v>
-      </c>
-      <c r="O1" t="s">
-        <v>17</v>
-      </c>
-      <c r="P1" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>18</v>
-      </c>
-      <c r="R1" t="s">
-        <v>19</v>
-      </c>
-      <c r="S1" t="s">
-        <v>20</v>
-      </c>
-      <c r="T1" t="s">
-        <v>21</v>
-      </c>
-      <c r="U1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>46175</v>
-      </c>
-      <c r="B2">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="F14" s="6">
+        <v>13450</v>
+      </c>
+      <c r="G14" s="6">
+        <v>664</v>
+      </c>
+      <c r="H14">
+        <v>29</v>
+      </c>
+      <c r="I14">
+        <v>25</v>
+      </c>
+      <c r="J14">
+        <v>2</v>
+      </c>
+      <c r="K14" s="4">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="L14" s="4">
+        <v>2.1412037037037038E-3</v>
+      </c>
+      <c r="M14" s="5">
+        <v>4.9399999999999999E-2</v>
+      </c>
+      <c r="N14" s="5">
+        <v>4.3700000000000003E-2</v>
+      </c>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>46150</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>5</v>
+      </c>
+      <c r="F15" s="6">
+        <v>4331</v>
+      </c>
+      <c r="G15" s="6">
+        <v>250</v>
+      </c>
+      <c r="H15">
+        <v>46</v>
+      </c>
+      <c r="I15">
+        <v>32</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15" s="4">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="L15" s="4">
+        <v>7.5231481481481482E-4</v>
+      </c>
+      <c r="M15" s="5">
+        <v>5.7700000000000001E-2</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0.184</v>
+      </c>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>46151</v>
+      </c>
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6">
+        <v>3075</v>
+      </c>
+      <c r="G16" s="6">
+        <v>182</v>
+      </c>
+      <c r="H16">
+        <v>40</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" s="4">
+        <v>2.4305555555555555E-4</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M16" s="5">
+        <v>5.9200000000000003E-2</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0.2198</v>
+      </c>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="5"/>
+      <c r="S16" s="5"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>46151</v>
+      </c>
+      <c r="B17" t="s">
         <v>28</v>
       </c>
-      <c r="D2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1210</v>
-      </c>
-      <c r="H2">
-        <v>78</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2" s="4">
-        <v>1.7361111111111112E-4</v>
-      </c>
-      <c r="M2" s="4">
-        <v>9.3749999999999997E-4</v>
-      </c>
-      <c r="N2" s="5">
-        <v>6.4500000000000002E-2</v>
-      </c>
-      <c r="O2" s="5">
-        <v>3.85E-2</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>0</v>
-      </c>
-      <c r="R2" s="5">
-        <v>2</v>
-      </c>
-      <c r="S2" s="5">
-        <v>0.66669999999999996</v>
-      </c>
-      <c r="T2" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>46175</v>
-      </c>
-      <c r="B3">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>1363</v>
-      </c>
-      <c r="H3">
-        <v>75</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3" s="4">
-        <v>2.0833333333333335E-4</v>
-      </c>
-      <c r="M3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" s="5">
-        <v>5.5E-2</v>
-      </c>
-      <c r="O3" s="3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>25</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3" t="s">
-        <v>25</v>
-      </c>
-      <c r="T3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>46175</v>
-      </c>
-      <c r="B4">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>1226</v>
-      </c>
-      <c r="H4">
-        <v>100</v>
-      </c>
-      <c r="I4">
-        <v>4</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4" s="4">
-        <v>1.3888888888888889E-4</v>
-      </c>
-      <c r="M4" s="4">
-        <v>1.7361111111111112E-4</v>
-      </c>
-      <c r="N4" s="5">
-        <v>8.1600000000000006E-2</v>
-      </c>
-      <c r="O4" s="3">
-        <v>0.04</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="3">
-        <v>0</v>
-      </c>
-      <c r="R4" s="3">
-        <v>2</v>
-      </c>
-      <c r="S4" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="T4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>46175</v>
-      </c>
-      <c r="B5">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1520</v>
-      </c>
-      <c r="H5">
-        <v>69</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="4">
-        <v>2.5462962962962961E-4</v>
-      </c>
-      <c r="M5" s="4">
-        <v>3.9351851851851852E-4</v>
-      </c>
-      <c r="N5" s="5">
-        <v>4.5400000000000003E-2</v>
-      </c>
-      <c r="O5" s="5">
-        <v>5.8000000000000003E-2</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="3">
-        <v>0</v>
-      </c>
-      <c r="R5" s="3">
-        <v>1</v>
-      </c>
-      <c r="S5" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="T5" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>46175</v>
-      </c>
-      <c r="B6">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1476</v>
-      </c>
-      <c r="H6">
-        <v>73</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6" s="4">
-        <v>2.3148148148148149E-4</v>
-      </c>
-      <c r="M6" s="4">
-        <v>4.7800925925925927E-3</v>
-      </c>
-      <c r="N6" s="5">
-        <v>4.9500000000000002E-2</v>
-      </c>
-      <c r="O6" s="5">
-        <v>4.1099999999999998E-2</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="3">
-        <v>0</v>
-      </c>
-      <c r="R6" s="5">
-        <v>1</v>
-      </c>
-      <c r="S6" s="5">
-        <v>0.33329999999999999</v>
-      </c>
-      <c r="T6" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>46175</v>
-      </c>
-      <c r="B7">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>671</v>
-      </c>
-      <c r="H7">
-        <v>32</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7" s="4">
-        <v>2.3148148148148149E-4</v>
-      </c>
-      <c r="M7" s="4">
-        <v>1.8287037037037037E-3</v>
-      </c>
-      <c r="N7" s="5">
-        <v>4.7699999999999999E-2</v>
-      </c>
-      <c r="O7" s="5">
-        <v>3.1300000000000001E-2</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="3">
-        <v>0</v>
-      </c>
-      <c r="R7" s="3">
-        <v>0</v>
-      </c>
-      <c r="S7" s="5">
-        <v>0</v>
-      </c>
-      <c r="T7" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>46175</v>
-      </c>
-      <c r="B8">
-        <v>15</v>
-      </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>2</v>
-      </c>
-      <c r="G8">
-        <v>1542</v>
-      </c>
-      <c r="H8">
-        <v>61</v>
-      </c>
-      <c r="I8">
-        <v>5</v>
-      </c>
-      <c r="J8">
-        <v>5</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8" s="4">
-        <v>2.8935185185185184E-4</v>
-      </c>
-      <c r="M8" s="4">
-        <v>8.564814814814815E-4</v>
-      </c>
-      <c r="N8" s="5">
-        <v>3.9600000000000003E-2</v>
-      </c>
-      <c r="O8" s="5">
-        <v>8.2000000000000003E-2</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
-      <c r="R8" s="3">
-        <v>0</v>
-      </c>
-      <c r="S8" s="5">
-        <v>0</v>
-      </c>
-      <c r="T8" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
-        <v>46175</v>
-      </c>
-      <c r="B9">
-        <v>16</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>1537</v>
-      </c>
-      <c r="H9">
-        <v>75</v>
-      </c>
-      <c r="I9">
-        <v>2</v>
-      </c>
-      <c r="J9">
-        <v>2</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9" s="4">
-        <v>2.3148148148148149E-4</v>
-      </c>
-      <c r="M9" s="4">
-        <v>3.3564814814814812E-4</v>
-      </c>
-      <c r="N9" s="5">
-        <v>4.8800000000000003E-2</v>
-      </c>
-      <c r="O9" s="5">
-        <v>2.6700000000000002E-2</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>0</v>
-      </c>
-      <c r="R9" s="3">
-        <v>0</v>
-      </c>
-      <c r="S9" s="5">
-        <v>0</v>
-      </c>
-      <c r="T9" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <v>46175</v>
-      </c>
-      <c r="B10">
-        <v>17</v>
-      </c>
-      <c r="C10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10">
-        <v>1488</v>
-      </c>
-      <c r="H10">
-        <v>74</v>
-      </c>
-      <c r="I10">
-        <v>2</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10" s="4">
-        <v>2.3148148148148149E-4</v>
-      </c>
-      <c r="M10" s="4">
-        <v>1.1574074074074075E-4</v>
-      </c>
-      <c r="N10" s="5">
-        <v>4.9700000000000001E-2</v>
-      </c>
-      <c r="O10" s="5">
-        <v>2.7E-2</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>0</v>
-      </c>
-      <c r="R10" s="3">
-        <v>1</v>
-      </c>
-      <c r="S10" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="T10" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>46175</v>
-      </c>
-      <c r="B11">
-        <v>18</v>
-      </c>
-      <c r="C11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11" t="s">
-        <v>24</v>
-      </c>
-      <c r="M11" t="s">
-        <v>24</v>
-      </c>
-      <c r="N11" s="3">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
-        <v>25</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>25</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <v>46176</v>
-      </c>
-      <c r="B12">
-        <v>9</v>
-      </c>
-      <c r="C12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>2</v>
-      </c>
-      <c r="G12">
-        <v>1418</v>
-      </c>
-      <c r="H12">
-        <v>71</v>
-      </c>
-      <c r="I12">
-        <v>5</v>
-      </c>
-      <c r="J12">
-        <v>5</v>
-      </c>
-      <c r="K12">
-        <v>1</v>
-      </c>
-      <c r="L12" s="4">
-        <v>2.199074074074074E-4</v>
-      </c>
-      <c r="M12" s="4">
-        <v>1.2847222222222223E-3</v>
-      </c>
-      <c r="N12" s="5">
-        <v>5.0099999999999999E-2</v>
-      </c>
-      <c r="O12" s="5">
-        <v>7.0400000000000004E-2</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>0</v>
-      </c>
-      <c r="R12" s="3">
-        <v>0</v>
-      </c>
-      <c r="S12" s="5">
-        <v>0</v>
-      </c>
-      <c r="T12" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>46176</v>
-      </c>
-      <c r="B13">
-        <v>10</v>
-      </c>
-      <c r="C13" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>1672</v>
-      </c>
-      <c r="H13">
-        <v>55</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13" s="4">
-        <v>3.4722222222222224E-4</v>
-      </c>
-      <c r="M13" t="s">
-        <v>24</v>
-      </c>
-      <c r="N13" s="5">
-        <v>3.2899999999999999E-2</v>
-      </c>
-      <c r="O13" s="3">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>25</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13" t="s">
-        <v>25</v>
-      </c>
-      <c r="T13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
-        <v>46176</v>
-      </c>
-      <c r="B14">
-        <v>11</v>
-      </c>
-      <c r="C14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" t="s">
-        <v>29</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14">
-        <v>2</v>
-      </c>
-      <c r="G14">
-        <v>867</v>
-      </c>
-      <c r="H14">
-        <v>39</v>
-      </c>
-      <c r="I14">
-        <v>3</v>
-      </c>
-      <c r="J14">
-        <v>3</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14" s="4">
-        <v>2.5462962962962961E-4</v>
-      </c>
-      <c r="M14" s="4">
-        <v>1.0069444444444444E-3</v>
-      </c>
-      <c r="N14" s="5">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="O14" s="5">
-        <v>7.6899999999999996E-2</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="5">
-        <v>0</v>
-      </c>
-      <c r="T14" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
-        <v>46178</v>
-      </c>
-      <c r="B15">
-        <v>10</v>
-      </c>
-      <c r="C15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="F15">
-        <v>2</v>
-      </c>
-      <c r="G15">
-        <v>1794</v>
-      </c>
-      <c r="H15">
-        <v>57</v>
-      </c>
-      <c r="I15">
-        <v>4</v>
-      </c>
-      <c r="J15">
-        <v>4</v>
-      </c>
-      <c r="K15">
-        <v>1</v>
-      </c>
-      <c r="L15" s="4">
-        <v>3.5879629629629629E-4</v>
-      </c>
-      <c r="M15" s="4">
-        <v>1.8055555555555555E-3</v>
-      </c>
-      <c r="N15" s="5">
-        <v>3.1800000000000002E-2</v>
-      </c>
-      <c r="O15" s="5">
-        <v>7.0199999999999999E-2</v>
-      </c>
-      <c r="P15">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
-      </c>
-      <c r="S15" s="5">
-        <v>0</v>
-      </c>
-      <c r="T15" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
-        <v>46178</v>
-      </c>
-      <c r="B16">
-        <v>11</v>
-      </c>
-      <c r="C16" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" t="s">
-        <v>29</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="F16">
-        <v>3</v>
-      </c>
-      <c r="G16">
-        <v>532</v>
-      </c>
-      <c r="H16">
-        <v>28</v>
-      </c>
-      <c r="I16">
-        <v>5</v>
-      </c>
-      <c r="J16">
-        <v>5</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16" s="4">
-        <v>2.0833333333333335E-4</v>
-      </c>
-      <c r="M16" s="4">
-        <v>2.3726851851851851E-3</v>
-      </c>
-      <c r="N16" s="5">
-        <v>5.2600000000000001E-2</v>
-      </c>
-      <c r="O16" s="5">
-        <v>0.17860000000000001</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="3">
-        <v>0</v>
-      </c>
-      <c r="R16" s="3">
-        <v>0</v>
-      </c>
-      <c r="S16" s="5">
-        <v>0</v>
-      </c>
-      <c r="T16" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
-        <v>46178</v>
-      </c>
-      <c r="B17">
-        <v>12</v>
-      </c>
-      <c r="C17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" t="s">
-        <v>29</v>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>46</v>
+      <c r="F17" s="6">
+        <v>2066</v>
+      </c>
+      <c r="G17" s="6">
+        <v>122</v>
       </c>
       <c r="H17">
         <v>4</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
-      <c r="K17">
-        <v>0</v>
+      <c r="K17" s="4">
+        <v>1.3888888888888889E-4</v>
       </c>
       <c r="L17" s="4">
+        <v>9.6064814814814819E-4</v>
+      </c>
+      <c r="M17" s="5">
+        <v>5.91E-2</v>
+      </c>
+      <c r="N17" s="3">
+        <v>3.2800000000000003E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>46153</v>
+      </c>
+      <c r="B18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>5</v>
+      </c>
+      <c r="F18" s="6">
+        <v>12986</v>
+      </c>
+      <c r="G18" s="6">
+        <v>662</v>
+      </c>
+      <c r="H18">
+        <v>34</v>
+      </c>
+      <c r="I18">
+        <v>33</v>
+      </c>
+      <c r="J18">
+        <v>3</v>
+      </c>
+      <c r="K18" s="4">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="L18" s="4">
+        <v>1.9444444444444444E-3</v>
+      </c>
+      <c r="M18" s="5">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="N18" s="5">
+        <v>5.1400000000000001E-2</v>
+      </c>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>46153</v>
+      </c>
+      <c r="B19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19" s="6">
+        <v>2286</v>
+      </c>
+      <c r="G19" s="6">
+        <v>123</v>
+      </c>
+      <c r="H19">
+        <v>21</v>
+      </c>
+      <c r="I19">
+        <v>9</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="L19" s="4">
+        <v>9.9537037037037042E-4</v>
+      </c>
+      <c r="M19" s="5">
+        <v>5.3800000000000001E-2</v>
+      </c>
+      <c r="N19" s="3">
+        <v>0.17069999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>46154</v>
+      </c>
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20" s="6">
+        <v>1267</v>
+      </c>
+      <c r="G20" s="6">
+        <v>39</v>
+      </c>
+      <c r="H20">
+        <v>3</v>
+      </c>
+      <c r="I20">
+        <v>3</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" s="4">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="L20" s="4">
+        <v>3.3564814814814812E-4</v>
+      </c>
+      <c r="M20" s="5">
+        <v>3.0800000000000001E-2</v>
+      </c>
+      <c r="N20" s="5">
+        <v>7.6899999999999996E-2</v>
+      </c>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="5"/>
+      <c r="S20" s="5"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>46154</v>
+      </c>
+      <c r="B21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>5</v>
+      </c>
+      <c r="F21" s="6">
+        <v>12521</v>
+      </c>
+      <c r="G21" s="6">
+        <v>688</v>
+      </c>
+      <c r="H21">
+        <v>44</v>
+      </c>
+      <c r="I21">
+        <v>40</v>
+      </c>
+      <c r="J21">
+        <v>3</v>
+      </c>
+      <c r="K21" s="4">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="L21" s="4">
+        <v>1.4467592592592592E-3</v>
+      </c>
+      <c r="M21" s="5">
+        <v>5.4899999999999997E-2</v>
+      </c>
+      <c r="N21" s="5">
+        <v>6.4000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>46155</v>
+      </c>
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>4</v>
+      </c>
+      <c r="F22" s="6">
+        <v>13487</v>
+      </c>
+      <c r="G22" s="6">
+        <v>631</v>
+      </c>
+      <c r="H22">
+        <v>22</v>
+      </c>
+      <c r="I22">
+        <v>15</v>
+      </c>
+      <c r="J22">
+        <v>2</v>
+      </c>
+      <c r="K22" s="4">
         <v>1.273148148148148E-4</v>
       </c>
-      <c r="M17" t="s">
+      <c r="L22" s="4">
+        <v>1.4699074074074074E-3</v>
+      </c>
+      <c r="M22" s="5">
+        <v>4.6800000000000001E-2</v>
+      </c>
+      <c r="N22" s="5">
+        <v>3.49E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>46155</v>
+      </c>
+      <c r="B23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>4</v>
+      </c>
+      <c r="F23" s="6">
+        <v>5226</v>
+      </c>
+      <c r="G23" s="6">
+        <v>193</v>
+      </c>
+      <c r="H23">
+        <v>25</v>
+      </c>
+      <c r="I23">
+        <v>9</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23" s="4">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="L23" s="4">
+        <v>1.0648148148148149E-3</v>
+      </c>
+      <c r="M23" s="5">
+        <v>3.6900000000000002E-2</v>
+      </c>
+      <c r="N23" s="5">
+        <v>0.1295</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>46156</v>
+      </c>
+      <c r="B24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24" s="6">
+        <v>533</v>
+      </c>
+      <c r="G24" s="6">
+        <v>50</v>
+      </c>
+      <c r="H24">
+        <v>2</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24" s="4">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="L24" t="s">
         <v>24</v>
       </c>
-      <c r="N17" s="5">
-        <v>8.6999999999999994E-2</v>
-      </c>
-      <c r="O17" s="3">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>25</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17" t="s">
-        <v>25</v>
-      </c>
-      <c r="T17" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
-        <v>46178</v>
-      </c>
-      <c r="B18">
-        <v>13</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="M24" s="5">
+        <v>9.3799999999999994E-2</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>46156</v>
+      </c>
+      <c r="B25" t="s">
         <v>28</v>
       </c>
-      <c r="D18" t="s">
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>5</v>
+      </c>
+      <c r="F25" s="6">
+        <v>13160</v>
+      </c>
+      <c r="G25" s="6">
+        <v>716</v>
+      </c>
+      <c r="H25">
+        <v>26</v>
+      </c>
+      <c r="I25">
+        <v>23</v>
+      </c>
+      <c r="J25">
+        <v>4</v>
+      </c>
+      <c r="K25" s="4">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="L25" s="4">
+        <v>2.5578703703703705E-3</v>
+      </c>
+      <c r="M25" s="5">
+        <v>5.4399999999999997E-2</v>
+      </c>
+      <c r="N25" s="5">
+        <v>3.6299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>46157</v>
+      </c>
+      <c r="B26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>5</v>
+      </c>
+      <c r="F26" s="6">
+        <v>13411</v>
+      </c>
+      <c r="G26" s="6">
+        <v>618</v>
+      </c>
+      <c r="H26">
+        <v>26</v>
+      </c>
+      <c r="I26">
+        <v>19</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26" s="4">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="L26" s="4">
+        <v>6.8287037037037036E-4</v>
+      </c>
+      <c r="M26" s="5">
+        <v>4.6100000000000002E-2</v>
+      </c>
+      <c r="N26" s="5">
+        <v>4.2099999999999999E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>46157</v>
+      </c>
+      <c r="B27" t="s">
         <v>29</v>
       </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18">
-        <v>466</v>
-      </c>
-      <c r="H18">
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27" s="6">
+        <v>47</v>
+      </c>
+      <c r="G27" s="6">
         <v>15</v>
       </c>
-      <c r="I18">
-        <v>1</v>
-      </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18" s="4">
-        <v>3.5879629629629629E-4</v>
-      </c>
-      <c r="M18" s="4">
-        <v>2.3148148148148147E-3</v>
-      </c>
-      <c r="N18" s="5">
-        <v>3.2199999999999999E-2</v>
-      </c>
-      <c r="O18" s="5">
-        <v>6.6699999999999995E-2</v>
-      </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>0</v>
-      </c>
-      <c r="R18" s="3">
-        <v>0</v>
-      </c>
-      <c r="S18" s="5">
-        <v>0</v>
-      </c>
-      <c r="T18" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
-        <v>46178</v>
-      </c>
-      <c r="B19">
-        <v>14</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27" s="4">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="M27" s="5">
+        <v>0.31909999999999999</v>
+      </c>
+      <c r="N27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>46158</v>
+      </c>
+      <c r="B28" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28" s="6">
+        <v>11</v>
+      </c>
+      <c r="G28" s="6">
+        <v>2</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28" s="4">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="M28" s="5">
+        <v>0.18179999999999999</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>46158</v>
+      </c>
+      <c r="B29" t="s">
         <v>28</v>
       </c>
-      <c r="D19" t="s">
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29" s="6">
+        <v>9304</v>
+      </c>
+      <c r="G29" s="6">
+        <v>490</v>
+      </c>
+      <c r="H29">
+        <v>9</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29" s="4">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="L29" t="s">
+        <v>24</v>
+      </c>
+      <c r="M29" s="5">
+        <v>5.2699999999999997E-2</v>
+      </c>
+      <c r="N29" s="5">
+        <v>1.84E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>46160</v>
+      </c>
+      <c r="B30" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>5</v>
+      </c>
+      <c r="F30">
+        <v>13285</v>
+      </c>
+      <c r="G30">
+        <v>651</v>
+      </c>
+      <c r="H30">
+        <v>31</v>
+      </c>
+      <c r="I30">
+        <v>26</v>
+      </c>
+      <c r="J30">
+        <v>2</v>
+      </c>
+      <c r="K30" s="4">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="L30" s="4">
+        <v>1.3773148148148147E-3</v>
+      </c>
+      <c r="M30" s="5">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="N30" s="5">
+        <v>4.7600000000000003E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>46160</v>
+      </c>
+      <c r="B31" t="s">
         <v>29</v>
       </c>
-      <c r="E19">
-        <v>1</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>260</v>
-      </c>
-      <c r="H19">
-        <v>12</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19" s="4">
-        <v>2.4305555555555555E-4</v>
-      </c>
-      <c r="M19" t="s">
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>2</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31" t="s">
         <v>24</v>
       </c>
-      <c r="N19" s="5">
-        <v>4.6199999999999998E-2</v>
-      </c>
-      <c r="O19" s="3">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>25</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19" t="s">
-        <v>25</v>
-      </c>
-      <c r="T19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
-        <v>46178</v>
-      </c>
-      <c r="B20">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
+        <v>46161</v>
+      </c>
+      <c r="B32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>550</v>
+      </c>
+      <c r="G32">
+        <v>9</v>
+      </c>
+      <c r="H32">
+        <v>2</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32" s="4">
+        <v>2.5462962962962961E-4</v>
+      </c>
+      <c r="L32" t="s">
+        <v>24</v>
+      </c>
+      <c r="M32" s="5">
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="N32" s="5">
+        <v>0.22220000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
+        <v>46161</v>
+      </c>
+      <c r="B33" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>4</v>
+      </c>
+      <c r="F33">
+        <v>12417</v>
+      </c>
+      <c r="G33">
+        <v>727</v>
+      </c>
+      <c r="H33">
+        <v>28</v>
+      </c>
+      <c r="I33">
+        <v>23</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33" s="4">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="L33" s="4">
+        <v>1.2962962962962963E-3</v>
+      </c>
+      <c r="M33" s="5">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="N33" s="5">
+        <v>3.85E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B34" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>5</v>
+      </c>
+      <c r="F34">
+        <v>12507</v>
+      </c>
+      <c r="G34">
+        <v>708</v>
+      </c>
+      <c r="H34">
+        <v>30</v>
+      </c>
+      <c r="I34">
+        <v>27</v>
+      </c>
+      <c r="J34">
+        <v>2</v>
+      </c>
+      <c r="K34" s="4">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="L34" s="4">
+        <v>1.9444444444444444E-3</v>
+      </c>
+      <c r="M34" s="5">
+        <v>5.6599999999999998E-2</v>
+      </c>
+      <c r="N34" s="5">
+        <v>4.24E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B35" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>4</v>
+      </c>
+      <c r="F35">
+        <v>5475</v>
+      </c>
+      <c r="G35">
+        <v>233</v>
+      </c>
+      <c r="H35">
+        <v>31</v>
+      </c>
+      <c r="I35">
         <v>15</v>
       </c>
-      <c r="C20" t="s">
+      <c r="J35">
+        <v>1</v>
+      </c>
+      <c r="K35" s="4">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="L35" s="4">
+        <v>5.7870370370370367E-4</v>
+      </c>
+      <c r="M35" s="5">
+        <v>4.2599999999999999E-2</v>
+      </c>
+      <c r="N35" s="5">
+        <v>0.13300000000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B36" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <v>3</v>
+      </c>
+      <c r="F36">
+        <v>4427</v>
+      </c>
+      <c r="G36">
+        <v>163</v>
+      </c>
+      <c r="H36">
+        <v>11</v>
+      </c>
+      <c r="I36">
+        <v>8</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36" s="4">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="L36" s="4">
+        <v>3.1250000000000001E-4</v>
+      </c>
+      <c r="M36" s="5">
+        <v>3.6799999999999999E-2</v>
+      </c>
+      <c r="N36" s="5">
+        <v>6.7500000000000004E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B37" t="s">
         <v>28</v>
       </c>
-      <c r="D20" t="s">
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>4</v>
+      </c>
+      <c r="F37">
+        <v>12650</v>
+      </c>
+      <c r="G37">
+        <v>664</v>
+      </c>
+      <c r="H37">
+        <v>24</v>
+      </c>
+      <c r="I37">
+        <v>20</v>
+      </c>
+      <c r="J37">
+        <v>2</v>
+      </c>
+      <c r="K37" s="4">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="L37" s="4">
+        <v>1.5625000000000001E-3</v>
+      </c>
+      <c r="M37" s="5">
+        <v>5.2499999999999998E-2</v>
+      </c>
+      <c r="N37" s="5">
+        <v>3.61E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B38" t="s">
+        <v>28</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <v>4</v>
+      </c>
+      <c r="F38">
+        <v>13055</v>
+      </c>
+      <c r="G38">
+        <v>627</v>
+      </c>
+      <c r="H38">
+        <v>23</v>
+      </c>
+      <c r="I38">
+        <v>21</v>
+      </c>
+      <c r="J38">
+        <v>1</v>
+      </c>
+      <c r="K38" s="4">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="L38" s="4">
+        <v>1.6087962962962963E-3</v>
+      </c>
+      <c r="M38" s="5">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="N38" s="5">
+        <v>3.6700000000000003E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B39" t="s">
         <v>29</v>
       </c>
-      <c r="E20">
-        <v>1</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20">
-        <v>1184</v>
-      </c>
-      <c r="H20">
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="F39">
+        <v>4060</v>
+      </c>
+      <c r="G39">
+        <v>114</v>
+      </c>
+      <c r="H39">
+        <v>10</v>
+      </c>
+      <c r="I39">
+        <v>7</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39" s="4">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="L39" s="4">
+        <v>9.6064814814814819E-4</v>
+      </c>
+      <c r="M39" s="5">
+        <v>2.81E-2</v>
+      </c>
+      <c r="N39" s="5">
+        <v>8.77E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B40" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>429</v>
+      </c>
+      <c r="G40">
+        <v>9</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40" s="4">
+        <v>1.7361111111111112E-4</v>
+      </c>
+      <c r="M40" s="5">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="N40" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A41" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B41" t="s">
         <v>28</v>
       </c>
-      <c r="I20">
-        <v>1</v>
-      </c>
-      <c r="J20">
-        <v>1</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20" s="4">
-        <v>4.861111111111111E-4</v>
-      </c>
-      <c r="M20" s="4">
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>1</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>9087</v>
+      </c>
+      <c r="G41">
+        <v>486</v>
+      </c>
+      <c r="H41">
+        <v>11</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41" s="4">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="L41" t="s">
+        <v>24</v>
+      </c>
+      <c r="M41" s="5">
+        <v>5.3499999999999999E-2</v>
+      </c>
+      <c r="N41" s="5">
+        <v>2.2599999999999999E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B42" t="s">
+        <v>28</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42">
+        <v>5</v>
+      </c>
+      <c r="F42">
+        <v>12443</v>
+      </c>
+      <c r="G42">
+        <v>670</v>
+      </c>
+      <c r="H42">
+        <v>31</v>
+      </c>
+      <c r="I42">
+        <v>33</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42" s="4">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="L42" s="4">
+        <v>9.4907407407407408E-4</v>
+      </c>
+      <c r="M42" s="5">
+        <v>5.3800000000000001E-2</v>
+      </c>
+      <c r="N42" s="5">
+        <v>4.6300000000000001E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B43" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>3607</v>
+      </c>
+      <c r="G43">
+        <v>97</v>
+      </c>
+      <c r="H43">
+        <v>9</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43" s="4">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="L43" t="s">
+        <v>24</v>
+      </c>
+      <c r="M43" s="5">
+        <v>2.69E-2</v>
+      </c>
+      <c r="N43" s="5">
+        <v>9.2799999999999994E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44">
+        <v>2</v>
+      </c>
+      <c r="F44">
+        <v>3982</v>
+      </c>
+      <c r="G44">
+        <v>92</v>
+      </c>
+      <c r="H44">
+        <v>9</v>
+      </c>
+      <c r="I44">
+        <v>6</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44" s="4">
         <v>1.9675925925925926E-4</v>
       </c>
-      <c r="N20" s="5">
-        <v>2.3599999999999999E-2</v>
-      </c>
-      <c r="O20" s="5">
-        <v>3.5700000000000003E-2</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="5">
-        <v>0</v>
-      </c>
-      <c r="T20" s="5">
-        <v>1</v>
+      <c r="L44" s="4">
+        <v>1.5046296296296297E-4</v>
+      </c>
+      <c r="M44" s="5">
+        <v>2.3099999999999999E-2</v>
+      </c>
+      <c r="N44" s="5">
+        <v>9.7799999999999998E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A45" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B45" t="s">
+        <v>28</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45">
+        <v>5</v>
+      </c>
+      <c r="F45">
+        <v>13026</v>
+      </c>
+      <c r="G45">
+        <v>615</v>
+      </c>
+      <c r="H45">
+        <v>25</v>
+      </c>
+      <c r="I45">
+        <v>21</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45" s="4">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="L45" s="4">
+        <v>9.4907407407407408E-4</v>
+      </c>
+      <c r="M45" s="5">
+        <v>4.7199999999999999E-2</v>
+      </c>
+      <c r="N45" s="5">
+        <v>4.07E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
+        <v>46169</v>
+      </c>
+      <c r="B46" t="s">
+        <v>28</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46">
+        <v>5</v>
+      </c>
+      <c r="F46">
+        <v>12685</v>
+      </c>
+      <c r="G46">
+        <v>678</v>
+      </c>
+      <c r="H46">
+        <v>15</v>
+      </c>
+      <c r="I46">
+        <v>15</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46" s="4">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="L46" s="4">
+        <v>1.6435185185185185E-3</v>
+      </c>
+      <c r="M46" s="5">
+        <v>5.3400000000000003E-2</v>
+      </c>
+      <c r="N46" s="5">
+        <v>2.2100000000000002E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
+        <v>46169</v>
+      </c>
+      <c r="B47" t="s">
+        <v>29</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+      <c r="F47">
+        <v>3939</v>
+      </c>
+      <c r="G47">
+        <v>75</v>
+      </c>
+      <c r="H47">
+        <v>9</v>
+      </c>
+      <c r="I47">
+        <v>6</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47" s="4">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="L47" s="4">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="M47" s="5">
+        <v>1.9E-2</v>
+      </c>
+      <c r="N47" s="3">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <v>46170</v>
+      </c>
+      <c r="B48" t="s">
+        <v>29</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+      <c r="F48">
+        <v>1379</v>
+      </c>
+      <c r="G48">
+        <v>24</v>
+      </c>
+      <c r="H48">
+        <v>2</v>
+      </c>
+      <c r="I48">
+        <v>2</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48" s="4">
+        <v>1.7361111111111112E-4</v>
+      </c>
+      <c r="L48" s="4">
+        <v>1.4699074074074074E-3</v>
+      </c>
+      <c r="M48" s="5">
+        <v>1.7399999999999999E-2</v>
+      </c>
+      <c r="N48" s="5">
+        <v>8.3299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
+        <v>46170</v>
+      </c>
+      <c r="B49" t="s">
+        <v>28</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>1</v>
+      </c>
+      <c r="E49">
+        <v>5</v>
+      </c>
+      <c r="F49">
+        <v>3257</v>
+      </c>
+      <c r="G49">
+        <v>218</v>
+      </c>
+      <c r="H49">
+        <v>11</v>
+      </c>
+      <c r="I49">
+        <v>11</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49" s="4">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="L49" s="4">
+        <v>1.4814814814814814E-3</v>
+      </c>
+      <c r="M49" s="5">
+        <v>6.6900000000000001E-2</v>
+      </c>
+      <c r="N49" s="5">
+        <v>5.0500000000000003E-2</v>
       </c>
     </row>
   </sheetData>

--- a/data/base_creditas.xlsx
+++ b/data/base_creditas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB7EA03-FC73-4515-A80C-AF94A85DB08D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EADFEA4-AC21-4972-8B55-47325C18A365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="30">
   <si>
     <t>Data</t>
   </si>
@@ -484,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W63"/>
+  <dimension ref="A1:W71"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -4664,7 +4664,7 @@
         <v>27</v>
       </c>
       <c r="F62">
-        <v>7392</v>
+        <v>7442</v>
       </c>
       <c r="G62">
         <v>25</v>
@@ -4732,7 +4732,7 @@
         <v>27</v>
       </c>
       <c r="F63">
-        <v>7392</v>
+        <v>7442</v>
       </c>
       <c r="G63">
         <v>25</v>
@@ -4741,46 +4741,590 @@
         <v>5</v>
       </c>
       <c r="I63">
-        <v>31047</v>
+        <v>31100</v>
       </c>
       <c r="J63">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="K63">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L63">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M63">
+        <v>14</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63" s="4">
+        <v>1.4699074074074074E-3</v>
+      </c>
+      <c r="P63" s="4">
+        <v>6.7129629629629625E-4</v>
+      </c>
+      <c r="Q63" s="5">
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="R63" s="5">
+        <v>0.312</v>
+      </c>
+      <c r="S63" s="5">
+        <v>0.80820000000000003</v>
+      </c>
+      <c r="T63">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A64" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B64">
+        <v>11</v>
+      </c>
+      <c r="C64">
+        <v>81</v>
+      </c>
+      <c r="D64">
+        <v>85</v>
+      </c>
+      <c r="E64" t="s">
+        <v>27</v>
+      </c>
+      <c r="F64">
+        <v>7442</v>
+      </c>
+      <c r="G64">
+        <v>25</v>
+      </c>
+      <c r="H64">
+        <v>8</v>
+      </c>
+      <c r="I64">
+        <v>29093</v>
+      </c>
+      <c r="J64">
+        <v>138</v>
+      </c>
+      <c r="K64">
+        <v>41</v>
+      </c>
+      <c r="L64">
+        <v>29</v>
+      </c>
+      <c r="M64">
         <v>12</v>
       </c>
-      <c r="N63">
-        <v>0</v>
-      </c>
-      <c r="O63" s="4">
-        <v>1.5046296296296296E-3</v>
-      </c>
-      <c r="P63" s="4">
-        <v>5.7870370370370367E-4</v>
-      </c>
-      <c r="Q63" s="5">
-        <v>7.3000000000000001E-3</v>
-      </c>
-      <c r="R63" s="5">
-        <v>0.31580000000000003</v>
-      </c>
-      <c r="S63" s="5">
-        <v>0.83330000000000004</v>
-      </c>
-      <c r="T63">
-        <v>0</v>
-      </c>
-      <c r="U63" s="3">
-        <v>0</v>
-      </c>
-      <c r="V63" s="5">
-        <v>1</v>
+      <c r="N64">
+        <v>1</v>
+      </c>
+      <c r="O64" s="4">
+        <v>2.3611111111111111E-3</v>
+      </c>
+      <c r="P64" s="4">
+        <v>1.2268518518518518E-3</v>
+      </c>
+      <c r="Q64" s="5">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="R64" s="5">
+        <v>0.29709999999999998</v>
+      </c>
+      <c r="S64" s="5">
+        <v>0.70730000000000004</v>
+      </c>
+      <c r="T64">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+      <c r="V64" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A65" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B65">
+        <v>12</v>
+      </c>
+      <c r="C65">
+        <v>81</v>
+      </c>
+      <c r="D65">
+        <v>85</v>
+      </c>
+      <c r="E65" t="s">
+        <v>27</v>
+      </c>
+      <c r="F65">
+        <v>7442</v>
+      </c>
+      <c r="G65">
+        <v>25</v>
+      </c>
+      <c r="H65">
+        <v>8</v>
+      </c>
+      <c r="I65">
+        <v>21877</v>
+      </c>
+      <c r="J65">
+        <v>107</v>
+      </c>
+      <c r="K65">
+        <v>31</v>
+      </c>
+      <c r="L65">
+        <v>15</v>
+      </c>
+      <c r="M65">
+        <v>16</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65" s="4">
+        <v>2.2916666666666667E-3</v>
+      </c>
+      <c r="P65" s="4">
+        <v>7.6388888888888893E-4</v>
+      </c>
+      <c r="Q65" s="5">
+        <v>4.8999999999999998E-3</v>
+      </c>
+      <c r="R65" s="5">
+        <v>0.28970000000000001</v>
+      </c>
+      <c r="S65" s="5">
+        <v>0.4839</v>
+      </c>
+      <c r="T65">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A66" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B66">
+        <v>13</v>
+      </c>
+      <c r="C66">
+        <v>81</v>
+      </c>
+      <c r="D66">
+        <v>85</v>
+      </c>
+      <c r="E66" t="s">
+        <v>27</v>
+      </c>
+      <c r="F66">
+        <v>7442</v>
+      </c>
+      <c r="G66">
+        <v>25</v>
+      </c>
+      <c r="H66">
+        <v>5</v>
+      </c>
+      <c r="I66">
+        <v>14372</v>
+      </c>
+      <c r="J66">
+        <v>85</v>
+      </c>
+      <c r="K66">
+        <v>23</v>
+      </c>
+      <c r="L66">
+        <v>16</v>
+      </c>
+      <c r="M66">
+        <v>7</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66" s="4">
+        <v>1.9444444444444444E-3</v>
+      </c>
+      <c r="P66" s="4">
+        <v>1.4930555555555556E-3</v>
+      </c>
+      <c r="Q66" s="5">
+        <v>5.8999999999999999E-3</v>
+      </c>
+      <c r="R66" s="5">
+        <v>0.27060000000000001</v>
+      </c>
+      <c r="S66" s="5">
+        <v>0.69569999999999999</v>
+      </c>
+      <c r="T66">
+        <v>0</v>
+      </c>
+      <c r="U66" s="3">
+        <v>0</v>
+      </c>
+      <c r="V66" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A67" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B67">
+        <v>14</v>
+      </c>
+      <c r="C67">
+        <v>81</v>
+      </c>
+      <c r="D67">
+        <v>85</v>
+      </c>
+      <c r="E67" t="s">
+        <v>27</v>
+      </c>
+      <c r="F67">
+        <v>7442</v>
+      </c>
+      <c r="G67">
+        <v>25</v>
+      </c>
+      <c r="H67">
+        <v>4</v>
+      </c>
+      <c r="I67">
+        <v>16434</v>
+      </c>
+      <c r="J67">
+        <v>126</v>
+      </c>
+      <c r="K67">
+        <v>19</v>
+      </c>
+      <c r="L67">
+        <v>14</v>
+      </c>
+      <c r="M67">
+        <v>5</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67" s="4">
+        <v>1.4814814814814814E-3</v>
+      </c>
+      <c r="P67" s="4">
+        <v>8.1018518518518516E-4</v>
+      </c>
+      <c r="Q67" s="5">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="R67" s="5">
+        <v>0.15079999999999999</v>
+      </c>
+      <c r="S67" s="5">
+        <v>0.73680000000000001</v>
+      </c>
+      <c r="T67">
+        <v>0</v>
+      </c>
+      <c r="U67" s="3">
+        <v>0</v>
+      </c>
+      <c r="V67" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A68" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B68">
+        <v>15</v>
+      </c>
+      <c r="C68">
+        <v>81</v>
+      </c>
+      <c r="D68">
+        <v>85</v>
+      </c>
+      <c r="E68" t="s">
+        <v>27</v>
+      </c>
+      <c r="F68">
+        <v>7442</v>
+      </c>
+      <c r="G68">
+        <v>25</v>
+      </c>
+      <c r="H68">
+        <v>3</v>
+      </c>
+      <c r="I68">
+        <v>16782</v>
+      </c>
+      <c r="J68">
+        <v>115</v>
+      </c>
+      <c r="K68">
+        <v>19</v>
+      </c>
+      <c r="L68">
+        <v>11</v>
+      </c>
+      <c r="M68">
+        <v>8</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68" s="4">
+        <v>1.6666666666666668E-3</v>
+      </c>
+      <c r="P68" s="4">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="Q68" s="5">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="R68" s="5">
+        <v>0.16520000000000001</v>
+      </c>
+      <c r="S68" s="5">
+        <v>0.57889999999999997</v>
+      </c>
+      <c r="T68">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A69" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B69">
+        <v>16</v>
+      </c>
+      <c r="C69">
+        <v>81</v>
+      </c>
+      <c r="D69">
+        <v>85</v>
+      </c>
+      <c r="E69" t="s">
+        <v>27</v>
+      </c>
+      <c r="F69">
+        <v>7442</v>
+      </c>
+      <c r="G69">
+        <v>25</v>
+      </c>
+      <c r="H69">
+        <v>5</v>
+      </c>
+      <c r="I69">
+        <v>15999</v>
+      </c>
+      <c r="J69">
+        <v>121</v>
+      </c>
+      <c r="K69">
+        <v>17</v>
+      </c>
+      <c r="L69">
+        <v>11</v>
+      </c>
+      <c r="M69">
+        <v>6</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69" s="4">
+        <v>1.4930555555555556E-3</v>
+      </c>
+      <c r="P69" s="4">
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="Q69" s="5">
+        <v>7.6E-3</v>
+      </c>
+      <c r="R69" s="5">
+        <v>0.14050000000000001</v>
+      </c>
+      <c r="S69" s="5">
+        <v>0.64710000000000001</v>
+      </c>
+      <c r="T69">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A70" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B70">
+        <v>17</v>
+      </c>
+      <c r="C70">
+        <v>81</v>
+      </c>
+      <c r="D70">
+        <v>85</v>
+      </c>
+      <c r="E70" t="s">
+        <v>27</v>
+      </c>
+      <c r="F70">
+        <v>7442</v>
+      </c>
+      <c r="G70">
+        <v>25</v>
+      </c>
+      <c r="H70">
+        <v>6</v>
+      </c>
+      <c r="I70">
+        <v>22243</v>
+      </c>
+      <c r="J70">
+        <v>197</v>
+      </c>
+      <c r="K70">
+        <v>58</v>
+      </c>
+      <c r="L70">
+        <v>48</v>
+      </c>
+      <c r="M70">
+        <v>10</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70" s="4">
+        <v>1.2847222222222223E-3</v>
+      </c>
+      <c r="P70" s="4">
+        <v>1.0995370370370371E-3</v>
+      </c>
+      <c r="Q70" s="5">
+        <v>8.8999999999999999E-3</v>
+      </c>
+      <c r="R70" s="5">
+        <v>0.2944</v>
+      </c>
+      <c r="S70" s="5">
+        <v>0.8276</v>
+      </c>
+      <c r="T70">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A71" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B71">
+        <v>18</v>
+      </c>
+      <c r="C71">
+        <v>81</v>
+      </c>
+      <c r="D71">
+        <v>85</v>
+      </c>
+      <c r="E71" t="s">
+        <v>27</v>
+      </c>
+      <c r="F71">
+        <v>7442</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>94</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71" t="s">
+        <v>24</v>
+      </c>
+      <c r="P71" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" t="s">
+        <v>25</v>
+      </c>
+      <c r="S71" t="s">
+        <v>25</v>
+      </c>
+      <c r="T71">
+        <v>0</v>
+      </c>
+      <c r="U71" t="s">
+        <v>25</v>
+      </c>
+      <c r="V71" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/data/base_creditas.xlsx
+++ b/data/base_creditas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EADFEA4-AC21-4972-8B55-47325C18A365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB7EA03-FC73-4515-A80C-AF94A85DB08D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="30">
   <si>
     <t>Data</t>
   </si>
@@ -484,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W71"/>
+  <dimension ref="A1:W63"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -4664,7 +4664,7 @@
         <v>27</v>
       </c>
       <c r="F62">
-        <v>7442</v>
+        <v>7392</v>
       </c>
       <c r="G62">
         <v>25</v>
@@ -4732,7 +4732,7 @@
         <v>27</v>
       </c>
       <c r="F63">
-        <v>7442</v>
+        <v>7392</v>
       </c>
       <c r="G63">
         <v>25</v>
@@ -4741,37 +4741,37 @@
         <v>5</v>
       </c>
       <c r="I63">
-        <v>31100</v>
+        <v>31047</v>
       </c>
       <c r="J63">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="K63">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L63">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M63">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N63">
         <v>0</v>
       </c>
       <c r="O63" s="4">
-        <v>1.4699074074074074E-3</v>
+        <v>1.5046296296296296E-3</v>
       </c>
       <c r="P63" s="4">
-        <v>6.7129629629629625E-4</v>
+        <v>5.7870370370370367E-4</v>
       </c>
       <c r="Q63" s="5">
-        <v>7.4999999999999997E-3</v>
+        <v>7.3000000000000001E-3</v>
       </c>
       <c r="R63" s="5">
-        <v>0.312</v>
+        <v>0.31580000000000003</v>
       </c>
       <c r="S63" s="5">
-        <v>0.80820000000000003</v>
+        <v>0.83330000000000004</v>
       </c>
       <c r="T63">
         <v>0</v>
@@ -4781,550 +4781,6 @@
       </c>
       <c r="V63" s="5">
         <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A64" s="2">
-        <v>46185</v>
-      </c>
-      <c r="B64">
-        <v>11</v>
-      </c>
-      <c r="C64">
-        <v>81</v>
-      </c>
-      <c r="D64">
-        <v>85</v>
-      </c>
-      <c r="E64" t="s">
-        <v>27</v>
-      </c>
-      <c r="F64">
-        <v>7442</v>
-      </c>
-      <c r="G64">
-        <v>25</v>
-      </c>
-      <c r="H64">
-        <v>8</v>
-      </c>
-      <c r="I64">
-        <v>29093</v>
-      </c>
-      <c r="J64">
-        <v>138</v>
-      </c>
-      <c r="K64">
-        <v>41</v>
-      </c>
-      <c r="L64">
-        <v>29</v>
-      </c>
-      <c r="M64">
-        <v>12</v>
-      </c>
-      <c r="N64">
-        <v>1</v>
-      </c>
-      <c r="O64" s="4">
-        <v>2.3611111111111111E-3</v>
-      </c>
-      <c r="P64" s="4">
-        <v>1.2268518518518518E-3</v>
-      </c>
-      <c r="Q64" s="5">
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="R64" s="5">
-        <v>0.29709999999999998</v>
-      </c>
-      <c r="S64" s="5">
-        <v>0.70730000000000004</v>
-      </c>
-      <c r="T64">
-        <v>0</v>
-      </c>
-      <c r="U64" s="3">
-        <v>0</v>
-      </c>
-      <c r="V64" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A65" s="2">
-        <v>46185</v>
-      </c>
-      <c r="B65">
-        <v>12</v>
-      </c>
-      <c r="C65">
-        <v>81</v>
-      </c>
-      <c r="D65">
-        <v>85</v>
-      </c>
-      <c r="E65" t="s">
-        <v>27</v>
-      </c>
-      <c r="F65">
-        <v>7442</v>
-      </c>
-      <c r="G65">
-        <v>25</v>
-      </c>
-      <c r="H65">
-        <v>8</v>
-      </c>
-      <c r="I65">
-        <v>21877</v>
-      </c>
-      <c r="J65">
-        <v>107</v>
-      </c>
-      <c r="K65">
-        <v>31</v>
-      </c>
-      <c r="L65">
-        <v>15</v>
-      </c>
-      <c r="M65">
-        <v>16</v>
-      </c>
-      <c r="N65">
-        <v>0</v>
-      </c>
-      <c r="O65" s="4">
-        <v>2.2916666666666667E-3</v>
-      </c>
-      <c r="P65" s="4">
-        <v>7.6388888888888893E-4</v>
-      </c>
-      <c r="Q65" s="5">
-        <v>4.8999999999999998E-3</v>
-      </c>
-      <c r="R65" s="5">
-        <v>0.28970000000000001</v>
-      </c>
-      <c r="S65" s="5">
-        <v>0.4839</v>
-      </c>
-      <c r="T65">
-        <v>0</v>
-      </c>
-      <c r="U65" s="3">
-        <v>0</v>
-      </c>
-      <c r="V65" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A66" s="2">
-        <v>46185</v>
-      </c>
-      <c r="B66">
-        <v>13</v>
-      </c>
-      <c r="C66">
-        <v>81</v>
-      </c>
-      <c r="D66">
-        <v>85</v>
-      </c>
-      <c r="E66" t="s">
-        <v>27</v>
-      </c>
-      <c r="F66">
-        <v>7442</v>
-      </c>
-      <c r="G66">
-        <v>25</v>
-      </c>
-      <c r="H66">
-        <v>5</v>
-      </c>
-      <c r="I66">
-        <v>14372</v>
-      </c>
-      <c r="J66">
-        <v>85</v>
-      </c>
-      <c r="K66">
-        <v>23</v>
-      </c>
-      <c r="L66">
-        <v>16</v>
-      </c>
-      <c r="M66">
-        <v>7</v>
-      </c>
-      <c r="N66">
-        <v>0</v>
-      </c>
-      <c r="O66" s="4">
-        <v>1.9444444444444444E-3</v>
-      </c>
-      <c r="P66" s="4">
-        <v>1.4930555555555556E-3</v>
-      </c>
-      <c r="Q66" s="5">
-        <v>5.8999999999999999E-3</v>
-      </c>
-      <c r="R66" s="5">
-        <v>0.27060000000000001</v>
-      </c>
-      <c r="S66" s="5">
-        <v>0.69569999999999999</v>
-      </c>
-      <c r="T66">
-        <v>0</v>
-      </c>
-      <c r="U66" s="3">
-        <v>0</v>
-      </c>
-      <c r="V66" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A67" s="2">
-        <v>46185</v>
-      </c>
-      <c r="B67">
-        <v>14</v>
-      </c>
-      <c r="C67">
-        <v>81</v>
-      </c>
-      <c r="D67">
-        <v>85</v>
-      </c>
-      <c r="E67" t="s">
-        <v>27</v>
-      </c>
-      <c r="F67">
-        <v>7442</v>
-      </c>
-      <c r="G67">
-        <v>25</v>
-      </c>
-      <c r="H67">
-        <v>4</v>
-      </c>
-      <c r="I67">
-        <v>16434</v>
-      </c>
-      <c r="J67">
-        <v>126</v>
-      </c>
-      <c r="K67">
-        <v>19</v>
-      </c>
-      <c r="L67">
-        <v>14</v>
-      </c>
-      <c r="M67">
-        <v>5</v>
-      </c>
-      <c r="N67">
-        <v>0</v>
-      </c>
-      <c r="O67" s="4">
-        <v>1.4814814814814814E-3</v>
-      </c>
-      <c r="P67" s="4">
-        <v>8.1018518518518516E-4</v>
-      </c>
-      <c r="Q67" s="5">
-        <v>7.7000000000000002E-3</v>
-      </c>
-      <c r="R67" s="5">
-        <v>0.15079999999999999</v>
-      </c>
-      <c r="S67" s="5">
-        <v>0.73680000000000001</v>
-      </c>
-      <c r="T67">
-        <v>0</v>
-      </c>
-      <c r="U67" s="3">
-        <v>0</v>
-      </c>
-      <c r="V67" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A68" s="2">
-        <v>46185</v>
-      </c>
-      <c r="B68">
-        <v>15</v>
-      </c>
-      <c r="C68">
-        <v>81</v>
-      </c>
-      <c r="D68">
-        <v>85</v>
-      </c>
-      <c r="E68" t="s">
-        <v>27</v>
-      </c>
-      <c r="F68">
-        <v>7442</v>
-      </c>
-      <c r="G68">
-        <v>25</v>
-      </c>
-      <c r="H68">
-        <v>3</v>
-      </c>
-      <c r="I68">
-        <v>16782</v>
-      </c>
-      <c r="J68">
-        <v>115</v>
-      </c>
-      <c r="K68">
-        <v>19</v>
-      </c>
-      <c r="L68">
-        <v>11</v>
-      </c>
-      <c r="M68">
-        <v>8</v>
-      </c>
-      <c r="N68">
-        <v>0</v>
-      </c>
-      <c r="O68" s="4">
-        <v>1.6666666666666668E-3</v>
-      </c>
-      <c r="P68" s="4">
-        <v>1.8518518518518518E-4</v>
-      </c>
-      <c r="Q68" s="5">
-        <v>6.8999999999999999E-3</v>
-      </c>
-      <c r="R68" s="5">
-        <v>0.16520000000000001</v>
-      </c>
-      <c r="S68" s="5">
-        <v>0.57889999999999997</v>
-      </c>
-      <c r="T68">
-        <v>0</v>
-      </c>
-      <c r="U68" s="3">
-        <v>0</v>
-      </c>
-      <c r="V68" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A69" s="2">
-        <v>46185</v>
-      </c>
-      <c r="B69">
-        <v>16</v>
-      </c>
-      <c r="C69">
-        <v>81</v>
-      </c>
-      <c r="D69">
-        <v>85</v>
-      </c>
-      <c r="E69" t="s">
-        <v>27</v>
-      </c>
-      <c r="F69">
-        <v>7442</v>
-      </c>
-      <c r="G69">
-        <v>25</v>
-      </c>
-      <c r="H69">
-        <v>5</v>
-      </c>
-      <c r="I69">
-        <v>15999</v>
-      </c>
-      <c r="J69">
-        <v>121</v>
-      </c>
-      <c r="K69">
-        <v>17</v>
-      </c>
-      <c r="L69">
-        <v>11</v>
-      </c>
-      <c r="M69">
-        <v>6</v>
-      </c>
-      <c r="N69">
-        <v>0</v>
-      </c>
-      <c r="O69" s="4">
-        <v>1.4930555555555556E-3</v>
-      </c>
-      <c r="P69" s="4">
-        <v>3.8194444444444446E-4</v>
-      </c>
-      <c r="Q69" s="5">
-        <v>7.6E-3</v>
-      </c>
-      <c r="R69" s="5">
-        <v>0.14050000000000001</v>
-      </c>
-      <c r="S69" s="5">
-        <v>0.64710000000000001</v>
-      </c>
-      <c r="T69">
-        <v>0</v>
-      </c>
-      <c r="U69" s="3">
-        <v>0</v>
-      </c>
-      <c r="V69" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A70" s="2">
-        <v>46185</v>
-      </c>
-      <c r="B70">
-        <v>17</v>
-      </c>
-      <c r="C70">
-        <v>81</v>
-      </c>
-      <c r="D70">
-        <v>85</v>
-      </c>
-      <c r="E70" t="s">
-        <v>27</v>
-      </c>
-      <c r="F70">
-        <v>7442</v>
-      </c>
-      <c r="G70">
-        <v>25</v>
-      </c>
-      <c r="H70">
-        <v>6</v>
-      </c>
-      <c r="I70">
-        <v>22243</v>
-      </c>
-      <c r="J70">
-        <v>197</v>
-      </c>
-      <c r="K70">
-        <v>58</v>
-      </c>
-      <c r="L70">
-        <v>48</v>
-      </c>
-      <c r="M70">
-        <v>10</v>
-      </c>
-      <c r="N70">
-        <v>0</v>
-      </c>
-      <c r="O70" s="4">
-        <v>1.2847222222222223E-3</v>
-      </c>
-      <c r="P70" s="4">
-        <v>1.0995370370370371E-3</v>
-      </c>
-      <c r="Q70" s="5">
-        <v>8.8999999999999999E-3</v>
-      </c>
-      <c r="R70" s="5">
-        <v>0.2944</v>
-      </c>
-      <c r="S70" s="5">
-        <v>0.8276</v>
-      </c>
-      <c r="T70">
-        <v>0</v>
-      </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
-      <c r="V70" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A71" s="2">
-        <v>46185</v>
-      </c>
-      <c r="B71">
-        <v>18</v>
-      </c>
-      <c r="C71">
-        <v>81</v>
-      </c>
-      <c r="D71">
-        <v>85</v>
-      </c>
-      <c r="E71" t="s">
-        <v>27</v>
-      </c>
-      <c r="F71">
-        <v>7442</v>
-      </c>
-      <c r="G71">
-        <v>0</v>
-      </c>
-      <c r="H71">
-        <v>0</v>
-      </c>
-      <c r="I71">
-        <v>94</v>
-      </c>
-      <c r="J71">
-        <v>0</v>
-      </c>
-      <c r="K71">
-        <v>0</v>
-      </c>
-      <c r="L71">
-        <v>0</v>
-      </c>
-      <c r="M71">
-        <v>0</v>
-      </c>
-      <c r="N71">
-        <v>0</v>
-      </c>
-      <c r="O71" t="s">
-        <v>24</v>
-      </c>
-      <c r="P71" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q71" s="3">
-        <v>0</v>
-      </c>
-      <c r="R71" t="s">
-        <v>25</v>
-      </c>
-      <c r="S71" t="s">
-        <v>25</v>
-      </c>
-      <c r="T71">
-        <v>0</v>
-      </c>
-      <c r="U71" t="s">
-        <v>25</v>
-      </c>
-      <c r="V71" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/data/base_creditas.xlsx
+++ b/data/base_creditas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB7EA03-FC73-4515-A80C-AF94A85DB08D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D5B45A5-3DEE-4916-96D6-84E2AFF26556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="30">
   <si>
     <t>Data</t>
   </si>
@@ -484,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W63"/>
+  <dimension ref="A1:W80"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -4664,7 +4664,7 @@
         <v>27</v>
       </c>
       <c r="F62">
-        <v>7392</v>
+        <v>7442</v>
       </c>
       <c r="G62">
         <v>25</v>
@@ -4732,7 +4732,7 @@
         <v>27</v>
       </c>
       <c r="F63">
-        <v>7392</v>
+        <v>7442</v>
       </c>
       <c r="G63">
         <v>25</v>
@@ -4741,46 +4741,1223 @@
         <v>5</v>
       </c>
       <c r="I63">
-        <v>31047</v>
+        <v>31100</v>
       </c>
       <c r="J63">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="K63">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L63">
+        <v>59</v>
+      </c>
+      <c r="M63">
+        <v>14</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63" s="4">
+        <v>1.4699074074074074E-3</v>
+      </c>
+      <c r="P63" s="4">
+        <v>6.7129629629629625E-4</v>
+      </c>
+      <c r="Q63" s="5">
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="R63" s="5">
+        <v>0.312</v>
+      </c>
+      <c r="S63" s="5">
+        <v>0.80820000000000003</v>
+      </c>
+      <c r="T63">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A64" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B64">
+        <v>11</v>
+      </c>
+      <c r="C64">
+        <v>81</v>
+      </c>
+      <c r="D64">
+        <v>85</v>
+      </c>
+      <c r="E64" t="s">
+        <v>27</v>
+      </c>
+      <c r="F64">
+        <v>7442</v>
+      </c>
+      <c r="G64">
+        <v>25</v>
+      </c>
+      <c r="H64">
+        <v>8</v>
+      </c>
+      <c r="I64">
+        <v>29093</v>
+      </c>
+      <c r="J64">
+        <v>138</v>
+      </c>
+      <c r="K64">
+        <v>41</v>
+      </c>
+      <c r="L64">
+        <v>29</v>
+      </c>
+      <c r="M64">
+        <v>12</v>
+      </c>
+      <c r="N64">
+        <v>1</v>
+      </c>
+      <c r="O64" s="4">
+        <v>2.3611111111111111E-3</v>
+      </c>
+      <c r="P64" s="4">
+        <v>1.2268518518518518E-3</v>
+      </c>
+      <c r="Q64" s="5">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="R64" s="5">
+        <v>0.29709999999999998</v>
+      </c>
+      <c r="S64" s="5">
+        <v>0.70730000000000004</v>
+      </c>
+      <c r="T64">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+      <c r="V64" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A65" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B65">
+        <v>12</v>
+      </c>
+      <c r="C65">
+        <v>81</v>
+      </c>
+      <c r="D65">
+        <v>85</v>
+      </c>
+      <c r="E65" t="s">
+        <v>27</v>
+      </c>
+      <c r="F65">
+        <v>7442</v>
+      </c>
+      <c r="G65">
+        <v>25</v>
+      </c>
+      <c r="H65">
+        <v>8</v>
+      </c>
+      <c r="I65">
+        <v>21877</v>
+      </c>
+      <c r="J65">
+        <v>107</v>
+      </c>
+      <c r="K65">
+        <v>31</v>
+      </c>
+      <c r="L65">
+        <v>15</v>
+      </c>
+      <c r="M65">
+        <v>16</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65" s="4">
+        <v>2.2916666666666667E-3</v>
+      </c>
+      <c r="P65" s="4">
+        <v>7.6388888888888893E-4</v>
+      </c>
+      <c r="Q65" s="5">
+        <v>4.8999999999999998E-3</v>
+      </c>
+      <c r="R65" s="5">
+        <v>0.28970000000000001</v>
+      </c>
+      <c r="S65" s="5">
+        <v>0.4839</v>
+      </c>
+      <c r="T65">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A66" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B66">
+        <v>13</v>
+      </c>
+      <c r="C66">
+        <v>81</v>
+      </c>
+      <c r="D66">
+        <v>85</v>
+      </c>
+      <c r="E66" t="s">
+        <v>27</v>
+      </c>
+      <c r="F66">
+        <v>7442</v>
+      </c>
+      <c r="G66">
+        <v>25</v>
+      </c>
+      <c r="H66">
+        <v>5</v>
+      </c>
+      <c r="I66">
+        <v>14372</v>
+      </c>
+      <c r="J66">
+        <v>85</v>
+      </c>
+      <c r="K66">
+        <v>23</v>
+      </c>
+      <c r="L66">
+        <v>16</v>
+      </c>
+      <c r="M66">
+        <v>7</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66" s="4">
+        <v>1.9444444444444444E-3</v>
+      </c>
+      <c r="P66" s="4">
+        <v>1.4930555555555556E-3</v>
+      </c>
+      <c r="Q66" s="5">
+        <v>5.8999999999999999E-3</v>
+      </c>
+      <c r="R66" s="5">
+        <v>0.27060000000000001</v>
+      </c>
+      <c r="S66" s="5">
+        <v>0.69569999999999999</v>
+      </c>
+      <c r="T66">
+        <v>0</v>
+      </c>
+      <c r="U66" s="3">
+        <v>0</v>
+      </c>
+      <c r="V66" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A67" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B67">
+        <v>14</v>
+      </c>
+      <c r="C67">
+        <v>81</v>
+      </c>
+      <c r="D67">
+        <v>85</v>
+      </c>
+      <c r="E67" t="s">
+        <v>27</v>
+      </c>
+      <c r="F67">
+        <v>7442</v>
+      </c>
+      <c r="G67">
+        <v>25</v>
+      </c>
+      <c r="H67">
+        <v>4</v>
+      </c>
+      <c r="I67">
+        <v>16434</v>
+      </c>
+      <c r="J67">
+        <v>126</v>
+      </c>
+      <c r="K67">
+        <v>19</v>
+      </c>
+      <c r="L67">
+        <v>14</v>
+      </c>
+      <c r="M67">
+        <v>5</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67" s="4">
+        <v>1.4814814814814814E-3</v>
+      </c>
+      <c r="P67" s="4">
+        <v>8.1018518518518516E-4</v>
+      </c>
+      <c r="Q67" s="5">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="R67" s="5">
+        <v>0.15079999999999999</v>
+      </c>
+      <c r="S67" s="5">
+        <v>0.73680000000000001</v>
+      </c>
+      <c r="T67">
+        <v>0</v>
+      </c>
+      <c r="U67" s="3">
+        <v>0</v>
+      </c>
+      <c r="V67" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A68" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B68">
+        <v>15</v>
+      </c>
+      <c r="C68">
+        <v>81</v>
+      </c>
+      <c r="D68">
+        <v>85</v>
+      </c>
+      <c r="E68" t="s">
+        <v>27</v>
+      </c>
+      <c r="F68">
+        <v>7442</v>
+      </c>
+      <c r="G68">
+        <v>25</v>
+      </c>
+      <c r="H68">
+        <v>3</v>
+      </c>
+      <c r="I68">
+        <v>16782</v>
+      </c>
+      <c r="J68">
+        <v>115</v>
+      </c>
+      <c r="K68">
+        <v>19</v>
+      </c>
+      <c r="L68">
+        <v>11</v>
+      </c>
+      <c r="M68">
+        <v>8</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68" s="4">
+        <v>1.6666666666666668E-3</v>
+      </c>
+      <c r="P68" s="4">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="Q68" s="5">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="R68" s="5">
+        <v>0.16520000000000001</v>
+      </c>
+      <c r="S68" s="5">
+        <v>0.57889999999999997</v>
+      </c>
+      <c r="T68">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A69" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B69">
+        <v>16</v>
+      </c>
+      <c r="C69">
+        <v>81</v>
+      </c>
+      <c r="D69">
+        <v>85</v>
+      </c>
+      <c r="E69" t="s">
+        <v>27</v>
+      </c>
+      <c r="F69">
+        <v>7442</v>
+      </c>
+      <c r="G69">
+        <v>25</v>
+      </c>
+      <c r="H69">
+        <v>5</v>
+      </c>
+      <c r="I69">
+        <v>15999</v>
+      </c>
+      <c r="J69">
+        <v>121</v>
+      </c>
+      <c r="K69">
+        <v>17</v>
+      </c>
+      <c r="L69">
+        <v>11</v>
+      </c>
+      <c r="M69">
+        <v>6</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69" s="4">
+        <v>1.4930555555555556E-3</v>
+      </c>
+      <c r="P69" s="4">
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="Q69" s="5">
+        <v>7.6E-3</v>
+      </c>
+      <c r="R69" s="5">
+        <v>0.14050000000000001</v>
+      </c>
+      <c r="S69" s="5">
+        <v>0.64710000000000001</v>
+      </c>
+      <c r="T69">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A70" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B70">
+        <v>17</v>
+      </c>
+      <c r="C70">
+        <v>81</v>
+      </c>
+      <c r="D70">
+        <v>85</v>
+      </c>
+      <c r="E70" t="s">
+        <v>27</v>
+      </c>
+      <c r="F70">
+        <v>7442</v>
+      </c>
+      <c r="G70">
+        <v>25</v>
+      </c>
+      <c r="H70">
+        <v>6</v>
+      </c>
+      <c r="I70">
+        <v>22243</v>
+      </c>
+      <c r="J70">
+        <v>197</v>
+      </c>
+      <c r="K70">
+        <v>58</v>
+      </c>
+      <c r="L70">
+        <v>48</v>
+      </c>
+      <c r="M70">
+        <v>10</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70" s="4">
+        <v>1.2847222222222223E-3</v>
+      </c>
+      <c r="P70" s="4">
+        <v>1.0995370370370371E-3</v>
+      </c>
+      <c r="Q70" s="5">
+        <v>8.8999999999999999E-3</v>
+      </c>
+      <c r="R70" s="5">
+        <v>0.2944</v>
+      </c>
+      <c r="S70" s="5">
+        <v>0.8276</v>
+      </c>
+      <c r="T70">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A71" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B71">
+        <v>18</v>
+      </c>
+      <c r="C71">
+        <v>81</v>
+      </c>
+      <c r="D71">
+        <v>85</v>
+      </c>
+      <c r="E71" t="s">
+        <v>27</v>
+      </c>
+      <c r="F71">
+        <v>7442</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>94</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71" t="s">
+        <v>24</v>
+      </c>
+      <c r="P71" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" t="s">
+        <v>25</v>
+      </c>
+      <c r="S71" t="s">
+        <v>25</v>
+      </c>
+      <c r="T71">
+        <v>0</v>
+      </c>
+      <c r="U71" t="s">
+        <v>25</v>
+      </c>
+      <c r="V71" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A72" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B72">
+        <v>10</v>
+      </c>
+      <c r="C72">
+        <v>81</v>
+      </c>
+      <c r="D72">
+        <v>85</v>
+      </c>
+      <c r="E72" t="s">
+        <v>27</v>
+      </c>
+      <c r="F72">
+        <v>8976</v>
+      </c>
+      <c r="G72">
+        <v>25</v>
+      </c>
+      <c r="H72">
+        <v>8</v>
+      </c>
+      <c r="I72">
+        <v>11497</v>
+      </c>
+      <c r="J72">
+        <v>132</v>
+      </c>
+      <c r="K72">
+        <v>51</v>
+      </c>
+      <c r="L72">
+        <v>38</v>
+      </c>
+      <c r="M72">
+        <v>13</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72" s="4">
+        <v>9.9537037037037042E-4</v>
+      </c>
+      <c r="P72" s="4">
+        <v>2.3379629629629631E-3</v>
+      </c>
+      <c r="Q72" s="5">
+        <v>1.15E-2</v>
+      </c>
+      <c r="R72" s="5">
+        <v>0.38640000000000002</v>
+      </c>
+      <c r="S72" s="5">
+        <v>0.74509999999999998</v>
+      </c>
+      <c r="T72">
+        <v>0</v>
+      </c>
+      <c r="U72" s="3">
+        <v>0</v>
+      </c>
+      <c r="V72" s="5">
+        <v>1</v>
+      </c>
+      <c r="W72">
+        <v>3.6659999999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A73" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B73">
+        <v>11</v>
+      </c>
+      <c r="C73">
+        <v>81</v>
+      </c>
+      <c r="D73">
+        <v>85</v>
+      </c>
+      <c r="E73" t="s">
+        <v>27</v>
+      </c>
+      <c r="F73">
+        <v>8976</v>
+      </c>
+      <c r="G73">
+        <v>25</v>
+      </c>
+      <c r="H73">
+        <v>8</v>
+      </c>
+      <c r="I73">
+        <v>30692</v>
+      </c>
+      <c r="J73">
+        <v>259</v>
+      </c>
+      <c r="K73">
+        <v>83</v>
+      </c>
+      <c r="L73">
+        <v>51</v>
+      </c>
+      <c r="M73">
+        <v>30</v>
+      </c>
+      <c r="N73">
+        <v>2</v>
+      </c>
+      <c r="O73" s="4">
+        <v>1.3541666666666667E-3</v>
+      </c>
+      <c r="P73" s="4">
+        <v>1.8055555555555555E-3</v>
+      </c>
+      <c r="Q73" s="5">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="R73" s="5">
+        <v>0.32050000000000001</v>
+      </c>
+      <c r="S73" s="5">
+        <v>0.61450000000000005</v>
+      </c>
+      <c r="T73">
+        <v>2</v>
+      </c>
+      <c r="U73" s="5">
+        <v>6.25E-2</v>
+      </c>
+      <c r="V73" s="5">
+        <v>0.9677</v>
+      </c>
+      <c r="W73">
+        <v>34.128</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A74" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B74">
+        <v>12</v>
+      </c>
+      <c r="C74">
+        <v>81</v>
+      </c>
+      <c r="D74">
+        <v>85</v>
+      </c>
+      <c r="E74" t="s">
+        <v>27</v>
+      </c>
+      <c r="F74">
+        <v>8976</v>
+      </c>
+      <c r="G74">
+        <v>25</v>
+      </c>
+      <c r="H74">
+        <v>1</v>
+      </c>
+      <c r="I74">
+        <v>33207</v>
+      </c>
+      <c r="J74">
+        <v>240</v>
+      </c>
+      <c r="K74">
         <v>60</v>
       </c>
-      <c r="M63">
-        <v>12</v>
-      </c>
-      <c r="N63">
-        <v>0</v>
-      </c>
-      <c r="O63" s="4">
-        <v>1.5046296296296296E-3</v>
-      </c>
-      <c r="P63" s="4">
-        <v>5.7870370370370367E-4</v>
-      </c>
-      <c r="Q63" s="5">
-        <v>7.3000000000000001E-3</v>
-      </c>
-      <c r="R63" s="5">
-        <v>0.31580000000000003</v>
-      </c>
-      <c r="S63" s="5">
-        <v>0.83330000000000004</v>
-      </c>
-      <c r="T63">
-        <v>0</v>
-      </c>
-      <c r="U63" s="3">
-        <v>0</v>
-      </c>
-      <c r="V63" s="5">
-        <v>1</v>
+      <c r="L74">
+        <v>59</v>
+      </c>
+      <c r="M74">
+        <v>1</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74" s="4">
+        <v>1.5856481481481481E-3</v>
+      </c>
+      <c r="P74" s="4">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="Q74" s="5">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="S74" s="5">
+        <v>0.98329999999999995</v>
+      </c>
+      <c r="T74">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+      <c r="V74" s="5">
+        <v>1</v>
+      </c>
+      <c r="W74">
+        <v>22.643999999999998</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A75" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B75">
+        <v>13</v>
+      </c>
+      <c r="C75">
+        <v>81</v>
+      </c>
+      <c r="D75">
+        <v>85</v>
+      </c>
+      <c r="E75" t="s">
+        <v>27</v>
+      </c>
+      <c r="F75">
+        <v>8976</v>
+      </c>
+      <c r="G75">
+        <v>44</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>23624</v>
+      </c>
+      <c r="J75">
+        <v>220</v>
+      </c>
+      <c r="K75">
+        <v>35</v>
+      </c>
+      <c r="L75">
+        <v>35</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75" s="4">
+        <v>1.2268518518518518E-3</v>
+      </c>
+      <c r="P75" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q75" s="5">
+        <v>9.2999999999999992E-3</v>
+      </c>
+      <c r="R75" s="5">
+        <v>0.15909999999999999</v>
+      </c>
+      <c r="S75" s="3">
+        <v>1</v>
+      </c>
+      <c r="T75">
+        <v>0</v>
+      </c>
+      <c r="U75" t="s">
+        <v>25</v>
+      </c>
+      <c r="V75" t="s">
+        <v>25</v>
+      </c>
+      <c r="W75">
+        <v>26.43</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A76" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B76">
+        <v>14</v>
+      </c>
+      <c r="C76">
+        <v>81</v>
+      </c>
+      <c r="D76">
+        <v>85</v>
+      </c>
+      <c r="E76" t="s">
+        <v>27</v>
+      </c>
+      <c r="F76">
+        <v>8976</v>
+      </c>
+      <c r="G76">
+        <v>25</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>22591</v>
+      </c>
+      <c r="J76">
+        <v>239</v>
+      </c>
+      <c r="K76">
+        <v>28</v>
+      </c>
+      <c r="L76">
+        <v>28</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76" s="4">
+        <v>1.0763888888888889E-3</v>
+      </c>
+      <c r="P76" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q76" s="5">
+        <v>1.06E-2</v>
+      </c>
+      <c r="R76" s="5">
+        <v>0.1172</v>
+      </c>
+      <c r="S76" s="3">
+        <v>1</v>
+      </c>
+      <c r="T76">
+        <v>0</v>
+      </c>
+      <c r="U76" t="s">
+        <v>25</v>
+      </c>
+      <c r="V76" t="s">
+        <v>25</v>
+      </c>
+      <c r="W76">
+        <v>24.654</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A77" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B77">
+        <v>15</v>
+      </c>
+      <c r="C77">
+        <v>81</v>
+      </c>
+      <c r="D77">
+        <v>85</v>
+      </c>
+      <c r="E77" t="s">
+        <v>27</v>
+      </c>
+      <c r="F77">
+        <v>8976</v>
+      </c>
+      <c r="G77">
+        <v>25</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>21702</v>
+      </c>
+      <c r="J77">
+        <v>216</v>
+      </c>
+      <c r="K77">
+        <v>51</v>
+      </c>
+      <c r="L77">
+        <v>51</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77" s="4">
+        <v>1.1458333333333333E-3</v>
+      </c>
+      <c r="P77" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="R77" s="5">
+        <v>0.2361</v>
+      </c>
+      <c r="S77" s="3">
+        <v>1</v>
+      </c>
+      <c r="T77">
+        <v>0</v>
+      </c>
+      <c r="U77" t="s">
+        <v>25</v>
+      </c>
+      <c r="V77" t="s">
+        <v>25</v>
+      </c>
+      <c r="W77">
+        <v>36.558</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A78" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B78">
+        <v>16</v>
+      </c>
+      <c r="C78">
+        <v>81</v>
+      </c>
+      <c r="D78">
+        <v>85</v>
+      </c>
+      <c r="E78" t="s">
+        <v>27</v>
+      </c>
+      <c r="F78">
+        <v>8976</v>
+      </c>
+      <c r="G78">
+        <v>25</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>46702</v>
+      </c>
+      <c r="J78">
+        <v>487</v>
+      </c>
+      <c r="K78">
+        <v>145</v>
+      </c>
+      <c r="L78">
+        <v>145</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78" s="4">
+        <v>1.0995370370370371E-3</v>
+      </c>
+      <c r="P78" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q78" s="5">
+        <v>1.04E-2</v>
+      </c>
+      <c r="R78" s="5">
+        <v>0.29770000000000002</v>
+      </c>
+      <c r="S78" s="3">
+        <v>1</v>
+      </c>
+      <c r="T78">
+        <v>0</v>
+      </c>
+      <c r="U78" t="s">
+        <v>25</v>
+      </c>
+      <c r="V78" t="s">
+        <v>25</v>
+      </c>
+      <c r="W78">
+        <v>50.658000000000001</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A79" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B79">
+        <v>17</v>
+      </c>
+      <c r="C79">
+        <v>81</v>
+      </c>
+      <c r="D79">
+        <v>85</v>
+      </c>
+      <c r="E79" t="s">
+        <v>27</v>
+      </c>
+      <c r="F79">
+        <v>8976</v>
+      </c>
+      <c r="G79">
+        <v>25</v>
+      </c>
+      <c r="H79">
+        <v>5</v>
+      </c>
+      <c r="I79">
+        <v>31351</v>
+      </c>
+      <c r="J79">
+        <v>262</v>
+      </c>
+      <c r="K79">
+        <v>79</v>
+      </c>
+      <c r="L79">
+        <v>37</v>
+      </c>
+      <c r="M79">
+        <v>29</v>
+      </c>
+      <c r="N79">
+        <v>2</v>
+      </c>
+      <c r="O79" s="4">
+        <v>1.3773148148148147E-3</v>
+      </c>
+      <c r="P79" s="4">
+        <v>1.7013888888888888E-3</v>
+      </c>
+      <c r="Q79" s="5">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="R79" s="5">
+        <v>0.30149999999999999</v>
+      </c>
+      <c r="S79" s="5">
+        <v>0.46839999999999998</v>
+      </c>
+      <c r="T79">
+        <v>13</v>
+      </c>
+      <c r="U79" s="5">
+        <v>0.3095</v>
+      </c>
+      <c r="V79" s="5">
+        <v>0.78569999999999995</v>
+      </c>
+      <c r="W79">
+        <v>22.295999999999999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A80" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B80">
+        <v>18</v>
+      </c>
+      <c r="C80">
+        <v>81</v>
+      </c>
+      <c r="D80">
+        <v>85</v>
+      </c>
+      <c r="E80" t="s">
+        <v>27</v>
+      </c>
+      <c r="F80">
+        <v>8976</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>70</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80" t="s">
+        <v>24</v>
+      </c>
+      <c r="P80" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q80" s="3">
+        <v>0</v>
+      </c>
+      <c r="R80" t="s">
+        <v>25</v>
+      </c>
+      <c r="S80" t="s">
+        <v>25</v>
+      </c>
+      <c r="T80">
+        <v>0</v>
+      </c>
+      <c r="U80" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/data/base_creditas.xlsx
+++ b/data/base_creditas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D5B45A5-3DEE-4916-96D6-84E2AFF26556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09AACF5-8504-4D54-8101-2FD8D426C7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="31">
   <si>
     <t>Data</t>
   </si>
@@ -112,6 +112,9 @@
   </si>
   <si>
     <t>WAY_Cobranca_Rescindidos</t>
+  </si>
+  <si>
+    <t>NULL</t>
   </si>
 </sst>
 </file>
@@ -484,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W80"/>
+  <dimension ref="A1:W110"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -1252,10 +1255,10 @@
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>46182</v>
+        <v>46178</v>
       </c>
       <c r="B12">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C12">
         <v>81</v>
@@ -1264,66 +1267,69 @@
         <v>85</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12">
-        <v>7533</v>
+        <v>27</v>
+      </c>
+      <c r="F12" t="s">
+        <v>30</v>
       </c>
       <c r="G12">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I12">
-        <v>18719</v>
+        <v>4818</v>
       </c>
       <c r="J12">
-        <v>232</v>
+        <v>64</v>
       </c>
       <c r="K12">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="M12">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>1</v>
       </c>
       <c r="O12" s="4">
-        <v>8.9120370370370373E-4</v>
+        <v>8.6805555555555551E-4</v>
       </c>
       <c r="P12" s="4">
-        <v>1.2037037037037038E-3</v>
+        <v>2.5347222222222221E-3</v>
       </c>
       <c r="Q12" s="5">
-        <v>1.24E-2</v>
+        <v>1.3299999999999999E-2</v>
       </c>
       <c r="R12" s="5">
-        <v>0.1595</v>
+        <v>0.15629999999999999</v>
       </c>
       <c r="S12" s="5">
-        <v>0.43240000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="T12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U12" s="5">
         <v>0.1429</v>
       </c>
       <c r="V12" s="5">
-        <v>0.95240000000000002</v>
+        <v>0.71430000000000005</v>
+      </c>
+      <c r="W12">
+        <v>14.513999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>46182</v>
+        <v>46178</v>
       </c>
       <c r="B13">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C13">
         <v>81</v>
@@ -1332,66 +1338,69 @@
         <v>85</v>
       </c>
       <c r="E13" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13">
-        <v>7533</v>
+        <v>27</v>
+      </c>
+      <c r="F13" t="s">
+        <v>30</v>
       </c>
       <c r="G13">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H13">
+        <v>3</v>
+      </c>
+      <c r="I13">
+        <v>5514</v>
+      </c>
+      <c r="J13">
+        <v>86</v>
+      </c>
+      <c r="K13">
+        <v>13</v>
+      </c>
+      <c r="L13">
+        <v>4</v>
+      </c>
+      <c r="M13">
         <v>9</v>
       </c>
-      <c r="I13">
-        <v>20163</v>
-      </c>
-      <c r="J13">
-        <v>250</v>
-      </c>
-      <c r="K13">
-        <v>54</v>
-      </c>
-      <c r="L13">
-        <v>20</v>
-      </c>
-      <c r="M13">
-        <v>26</v>
-      </c>
       <c r="N13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="4">
-        <v>8.9120370370370373E-4</v>
+        <v>7.407407407407407E-4</v>
       </c>
       <c r="P13" s="4">
-        <v>9.3749999999999997E-4</v>
+        <v>1.736111111111111E-3</v>
       </c>
       <c r="Q13" s="5">
-        <v>1.24E-2</v>
+        <v>1.5599999999999999E-2</v>
       </c>
       <c r="R13" s="5">
-        <v>0.216</v>
+        <v>0.1512</v>
       </c>
       <c r="S13" s="5">
-        <v>0.37040000000000001</v>
+        <v>0.30769999999999997</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="U13" s="5">
-        <v>0.23530000000000001</v>
+        <v>0</v>
       </c>
       <c r="V13" s="5">
-        <v>0.85289999999999999</v>
+        <v>1</v>
+      </c>
+      <c r="W13">
+        <v>17.928000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>46182</v>
+        <v>46178</v>
       </c>
       <c r="B14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C14">
         <v>81</v>
@@ -1400,66 +1409,69 @@
         <v>85</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14">
-        <v>7533</v>
+        <v>27</v>
+      </c>
+      <c r="F14" t="s">
+        <v>30</v>
       </c>
       <c r="G14">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="H14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I14">
-        <v>12067</v>
+        <v>2058</v>
       </c>
       <c r="J14">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="K14">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="L14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M14">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" s="4">
-        <v>1.1226851851851851E-3</v>
+        <v>6.018518518518519E-4</v>
       </c>
       <c r="P14" s="4">
-        <v>1.7824074074074075E-3</v>
+        <v>2.9513888888888888E-3</v>
       </c>
       <c r="Q14" s="3">
-        <v>0.01</v>
+        <v>1.9E-2</v>
       </c>
       <c r="R14" s="5">
-        <v>0.14879999999999999</v>
+        <v>0.23080000000000001</v>
       </c>
       <c r="S14" s="5">
-        <v>0.27779999999999999</v>
+        <v>0.22220000000000001</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U14" s="3">
-        <v>0</v>
+        <v>0.42859999999999998</v>
       </c>
       <c r="V14" s="5">
-        <v>1</v>
+        <v>0.71430000000000005</v>
+      </c>
+      <c r="W14">
+        <v>7.5060000000000002</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>46182</v>
+        <v>46178</v>
       </c>
       <c r="B15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C15">
         <v>81</v>
@@ -1468,66 +1480,69 @@
         <v>85</v>
       </c>
       <c r="E15" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15">
-        <v>7533</v>
+        <v>27</v>
+      </c>
+      <c r="F15" t="s">
+        <v>30</v>
       </c>
       <c r="G15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H15">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>9021</v>
+        <v>5147</v>
       </c>
       <c r="J15">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="K15">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L15">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M15">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N15">
         <v>1</v>
       </c>
       <c r="O15" s="4">
-        <v>1.1574074074074073E-3</v>
+        <v>9.2592592592592596E-4</v>
       </c>
       <c r="P15" s="4">
-        <v>1.4004629629629629E-3</v>
+        <v>3.9930555555555552E-3</v>
       </c>
       <c r="Q15" s="5">
-        <v>9.4000000000000004E-3</v>
+        <v>1.24E-2</v>
       </c>
       <c r="R15" s="3">
+        <v>0.15629999999999999</v>
+      </c>
+      <c r="S15" s="5">
         <v>0.2</v>
       </c>
-      <c r="S15" s="5">
-        <v>0.4118</v>
-      </c>
       <c r="T15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U15" s="3">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="V15" s="5">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="W15">
+        <v>13.476000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>46182</v>
+        <v>46178</v>
       </c>
       <c r="B16">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C16">
         <v>81</v>
@@ -1536,66 +1551,69 @@
         <v>85</v>
       </c>
       <c r="E16" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16">
-        <v>7533</v>
+        <v>27</v>
+      </c>
+      <c r="F16" t="s">
+        <v>30</v>
       </c>
       <c r="G16">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H16">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>14219</v>
+        <v>10780</v>
       </c>
       <c r="J16">
-        <v>182</v>
+        <v>86</v>
       </c>
       <c r="K16">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L16">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M16">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N16">
         <v>0</v>
       </c>
       <c r="O16" s="4">
-        <v>8.4490740740740739E-4</v>
-      </c>
-      <c r="P16" s="4">
-        <v>1.736111111111111E-3</v>
+        <v>1.4467592592592592E-3</v>
+      </c>
+      <c r="P16" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="Q16" s="5">
-        <v>1.2800000000000001E-2</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="R16" s="5">
-        <v>0.1429</v>
-      </c>
-      <c r="S16" s="5">
-        <v>0.42309999999999998</v>
+        <v>0</v>
+      </c>
+      <c r="S16" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="T16">
-        <v>1</v>
-      </c>
-      <c r="U16" s="5">
-        <v>6.6699999999999995E-2</v>
-      </c>
-      <c r="V16" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="U16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="V16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="W16">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>46182</v>
+        <v>46178</v>
       </c>
       <c r="B17">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C17">
         <v>81</v>
@@ -1604,134 +1622,138 @@
         <v>85</v>
       </c>
       <c r="E17" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17">
+        <v>50</v>
+      </c>
+      <c r="H17">
+        <v>3</v>
+      </c>
+      <c r="I17">
+        <v>12161</v>
+      </c>
+      <c r="J17">
+        <v>151</v>
+      </c>
+      <c r="K17">
+        <v>41</v>
+      </c>
+      <c r="L17">
+        <v>16</v>
+      </c>
+      <c r="M17">
         <v>23</v>
       </c>
-      <c r="F17">
-        <v>7533</v>
-      </c>
-      <c r="G17">
-        <v>25</v>
-      </c>
-      <c r="H17">
-        <v>6</v>
-      </c>
-      <c r="I17">
-        <v>6219</v>
-      </c>
-      <c r="J17">
-        <v>72</v>
-      </c>
-      <c r="K17">
-        <v>13</v>
-      </c>
-      <c r="L17">
-        <v>6</v>
-      </c>
-      <c r="M17">
-        <v>7</v>
-      </c>
       <c r="N17">
         <v>0</v>
       </c>
       <c r="O17" s="4">
-        <v>9.1435185185185185E-4</v>
+        <v>9.2592592592592596E-4</v>
       </c>
       <c r="P17" s="4">
-        <v>9.0277777777777774E-4</v>
+        <v>1.238425925925926E-3</v>
       </c>
       <c r="Q17" s="5">
-        <v>1.1599999999999999E-2</v>
+        <v>1.24E-2</v>
       </c>
       <c r="R17" s="5">
-        <v>0.18060000000000001</v>
+        <v>0.27150000000000002</v>
       </c>
       <c r="S17" s="5">
-        <v>0.46150000000000002</v>
+        <v>0.39019999999999999</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U17" s="3">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="V17" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+        <v>0.84</v>
+      </c>
+      <c r="W17">
+        <v>34.11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>46182</v>
+        <v>46178</v>
       </c>
       <c r="B18">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C18">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D18">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>23</v>
-      </c>
-      <c r="F18">
-        <v>7533</v>
+        <v>26</v>
+      </c>
+      <c r="F18" t="s">
+        <v>30</v>
       </c>
       <c r="G18">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>11882</v>
+        <v>2</v>
       </c>
       <c r="J18">
-        <v>153</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L18">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N18">
         <v>0</v>
       </c>
       <c r="O18" s="4">
-        <v>7.9861111111111116E-4</v>
-      </c>
-      <c r="P18" s="4">
-        <v>1.9791666666666668E-3</v>
+        <v>2.3148148148148147E-5</v>
+      </c>
+      <c r="P18" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="Q18" s="5">
-        <v>1.29E-2</v>
+        <v>0.5</v>
       </c>
       <c r="R18" s="5">
-        <v>0.1961</v>
-      </c>
-      <c r="S18" s="5">
-        <v>0.4667</v>
+        <v>0</v>
+      </c>
+      <c r="S18" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="T18">
         <v>0</v>
       </c>
-      <c r="U18" s="3">
-        <v>0</v>
-      </c>
-      <c r="V18" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="U18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="V18" s="5"/>
+      <c r="W18">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>46182</v>
+        <v>46178</v>
       </c>
       <c r="B19">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C19">
         <v>81</v>
@@ -1740,134 +1762,132 @@
         <v>85</v>
       </c>
       <c r="E19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F19">
-        <v>7533</v>
+        <v>27</v>
+      </c>
+      <c r="F19" t="s">
+        <v>30</v>
       </c>
       <c r="G19">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>16923</v>
+        <v>1</v>
       </c>
       <c r="J19">
-        <v>262</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L19">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M19">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="N19">
         <v>0</v>
       </c>
-      <c r="O19" s="4">
-        <v>6.7129629629629625E-4</v>
-      </c>
-      <c r="P19" s="4">
-        <v>1.4467592592592592E-3</v>
+      <c r="O19" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P19" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="Q19" s="5">
-        <v>1.55E-2</v>
-      </c>
-      <c r="R19" s="5">
-        <v>0.1603</v>
-      </c>
-      <c r="S19" s="5">
-        <v>0.3095</v>
+        <v>0</v>
+      </c>
+      <c r="R19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="S19" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="T19">
         <v>0</v>
       </c>
-      <c r="U19" s="3">
-        <v>0</v>
-      </c>
-      <c r="V19" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="U19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="V19" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>46182</v>
+        <v>46178</v>
       </c>
       <c r="B20">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C20">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D20">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>23</v>
-      </c>
-      <c r="F20">
-        <v>7533</v>
+        <v>26</v>
+      </c>
+      <c r="F20" t="s">
+        <v>30</v>
       </c>
       <c r="G20">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>17295</v>
+        <v>1</v>
       </c>
       <c r="J20">
-        <v>282</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M20">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="N20">
         <v>0</v>
       </c>
-      <c r="O20" s="4">
-        <v>6.5972222222222224E-4</v>
-      </c>
-      <c r="P20" s="4">
-        <v>9.1435185185185185E-4</v>
+      <c r="O20" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P20" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="Q20" s="5">
-        <v>1.6299999999999999E-2</v>
-      </c>
-      <c r="R20" s="5">
-        <v>0.15959999999999999</v>
-      </c>
-      <c r="S20" s="3">
-        <v>0.4</v>
+        <v>0</v>
+      </c>
+      <c r="R20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="T20">
         <v>0</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="U20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="V20" s="5"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>46182</v>
+        <v>46181</v>
       </c>
       <c r="B21">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C21">
         <v>81</v>
@@ -1876,66 +1896,69 @@
         <v>85</v>
       </c>
       <c r="E21" t="s">
-        <v>23</v>
-      </c>
-      <c r="F21">
-        <v>7533</v>
+        <v>27</v>
+      </c>
+      <c r="F21" t="s">
+        <v>30</v>
       </c>
       <c r="G21">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I21">
-        <v>24262</v>
+        <v>20711</v>
       </c>
       <c r="J21">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="K21">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="L21">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" s="4">
-        <v>1.0532407407407407E-3</v>
-      </c>
-      <c r="P21" t="s">
-        <v>24</v>
+        <v>8.7962962962962962E-4</v>
+      </c>
+      <c r="P21" s="4">
+        <v>1.5162037037037036E-3</v>
       </c>
       <c r="Q21" s="5">
-        <v>1.0800000000000001E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="R21" s="5">
-        <v>0.2414</v>
-      </c>
-      <c r="S21" s="5">
-        <v>0.50790000000000002</v>
+        <v>0.26300000000000001</v>
+      </c>
+      <c r="S21" s="3">
+        <v>1</v>
       </c>
       <c r="T21">
-        <v>31</v>
-      </c>
-      <c r="U21" s="3">
-        <v>1</v>
+        <v>-37</v>
+      </c>
+      <c r="U21" t="s">
+        <v>25</v>
       </c>
       <c r="V21" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+        <v>0.8679</v>
+      </c>
+      <c r="W21">
+        <v>56.67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>46182</v>
+        <v>46181</v>
       </c>
       <c r="B22">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C22">
         <v>81</v>
@@ -1944,66 +1967,69 @@
         <v>85</v>
       </c>
       <c r="E22" t="s">
-        <v>23</v>
-      </c>
-      <c r="F22">
-        <v>7533</v>
+        <v>27</v>
+      </c>
+      <c r="F22" t="s">
+        <v>30</v>
       </c>
       <c r="G22">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I22">
-        <v>28325</v>
+        <v>16842</v>
       </c>
       <c r="J22">
-        <v>277</v>
+        <v>147</v>
       </c>
       <c r="K22">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="L22">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" s="4">
-        <v>1.1458333333333333E-3</v>
-      </c>
-      <c r="P22" t="s">
-        <v>24</v>
+        <v>1.3194444444444445E-3</v>
+      </c>
+      <c r="P22" s="4">
+        <v>1.5393518518518519E-3</v>
       </c>
       <c r="Q22" s="5">
-        <v>9.7999999999999997E-3</v>
+        <v>8.6999999999999994E-3</v>
       </c>
       <c r="R22" s="5">
-        <v>0.15160000000000001</v>
-      </c>
-      <c r="S22" s="5">
-        <v>0.35709999999999997</v>
+        <v>0.1905</v>
+      </c>
+      <c r="S22" s="3">
+        <v>1</v>
       </c>
       <c r="T22">
-        <v>27</v>
-      </c>
-      <c r="U22" s="3">
-        <v>1</v>
-      </c>
-      <c r="V22" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+        <v>-21</v>
+      </c>
+      <c r="U22" t="s">
+        <v>25</v>
+      </c>
+      <c r="V22" s="5">
+        <v>1</v>
+      </c>
+      <c r="W22">
+        <v>14.574</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>46182</v>
+        <v>46181</v>
       </c>
       <c r="B23">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C23">
         <v>81</v>
@@ -2012,63 +2038,69 @@
         <v>85</v>
       </c>
       <c r="E23" t="s">
-        <v>23</v>
-      </c>
-      <c r="F23">
-        <v>7533</v>
+        <v>27</v>
+      </c>
+      <c r="F23" t="s">
+        <v>30</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I23">
-        <v>246</v>
+        <v>20557</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>135</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" s="4">
-        <v>2.8240740740740739E-3</v>
-      </c>
-      <c r="P23" t="s">
-        <v>24</v>
+        <v>1.7592592592592592E-3</v>
+      </c>
+      <c r="P23" s="4">
+        <v>1.4699074074074074E-3</v>
       </c>
       <c r="Q23" s="5">
-        <v>4.1000000000000003E-3</v>
-      </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
-      <c r="S23" t="s">
-        <v>25</v>
+        <v>6.6E-3</v>
+      </c>
+      <c r="R23" s="5">
+        <v>0.1852</v>
+      </c>
+      <c r="S23" s="3">
+        <v>1</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="U23" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="V23" s="5">
+        <v>0.88239999999999996</v>
+      </c>
+      <c r="W23">
+        <v>11.885999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>46183</v>
+        <v>46181</v>
       </c>
       <c r="B24">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C24">
         <v>81</v>
@@ -2079,26 +2111,26 @@
       <c r="E24" t="s">
         <v>27</v>
       </c>
-      <c r="F24">
-        <v>7468</v>
+      <c r="F24" t="s">
+        <v>30</v>
       </c>
       <c r="G24">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="H24">
         <v>0</v>
       </c>
       <c r="I24">
-        <v>11322</v>
+        <v>277</v>
       </c>
       <c r="J24">
-        <v>189</v>
+        <v>2</v>
       </c>
       <c r="K24">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="L24">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M24">
         <v>0</v>
@@ -2107,104 +2139,110 @@
         <v>0</v>
       </c>
       <c r="O24" s="4">
-        <v>6.8287037037037036E-4</v>
+        <v>1.5972222222222223E-3</v>
       </c>
       <c r="P24" t="s">
         <v>24</v>
       </c>
       <c r="Q24" s="5">
-        <v>1.67E-2</v>
-      </c>
-      <c r="R24" s="5">
-        <v>1.121</v>
-      </c>
-      <c r="S24" s="5">
-        <v>5.6599999999999998E-2</v>
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" t="s">
+        <v>25</v>
       </c>
       <c r="T24">
-        <v>200</v>
-      </c>
-      <c r="U24" s="3">
-        <v>1</v>
-      </c>
-      <c r="V24" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="U24" t="s">
+        <v>25</v>
+      </c>
+      <c r="V24" s="5">
+        <v>1</v>
+      </c>
+      <c r="W24">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>46183</v>
+        <v>46181</v>
       </c>
       <c r="B25">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C25">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D25">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E25" t="s">
-        <v>26</v>
-      </c>
-      <c r="F25">
-        <v>15993</v>
+        <v>27</v>
+      </c>
+      <c r="F25" t="s">
+        <v>30</v>
       </c>
       <c r="G25">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I25">
-        <v>4604</v>
+        <v>1171</v>
       </c>
       <c r="J25">
-        <v>139</v>
+        <v>9</v>
       </c>
       <c r="K25">
-        <v>104</v>
+        <v>2</v>
       </c>
       <c r="L25">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N25">
         <v>0</v>
       </c>
       <c r="O25" s="4">
-        <v>3.7037037037037035E-4</v>
-      </c>
-      <c r="P25" t="s">
-        <v>24</v>
+        <v>1.5046296296296296E-3</v>
+      </c>
+      <c r="P25" s="4">
+        <v>5.6712962962962967E-4</v>
       </c>
       <c r="Q25" s="5">
-        <v>3.0200000000000001E-2</v>
+        <v>7.7000000000000002E-3</v>
       </c>
       <c r="R25" s="5">
-        <v>0.74819999999999998</v>
-      </c>
-      <c r="S25" s="5">
-        <v>6.7299999999999999E-2</v>
+        <v>0.22220000000000001</v>
+      </c>
+      <c r="S25" s="3">
+        <v>1</v>
       </c>
       <c r="T25">
-        <v>97</v>
-      </c>
-      <c r="U25" s="3">
-        <v>1</v>
-      </c>
-      <c r="V25" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
+        <v>-2</v>
+      </c>
+      <c r="U25" t="s">
+        <v>25</v>
+      </c>
+      <c r="V25" s="5">
+        <v>1</v>
+      </c>
+      <c r="W25">
+        <v>0.79800000000000004</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>46183</v>
+        <v>46181</v>
       </c>
       <c r="B26">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C26">
         <v>81</v>
@@ -2215,132 +2253,135 @@
       <c r="E26" t="s">
         <v>27</v>
       </c>
-      <c r="F26">
-        <v>7468</v>
+      <c r="F26" t="s">
+        <v>30</v>
       </c>
       <c r="G26">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H26">
         <v>5</v>
       </c>
       <c r="I26">
-        <v>7174</v>
+        <v>20275</v>
       </c>
       <c r="J26">
-        <v>91</v>
+        <v>241</v>
       </c>
       <c r="K26">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="L26">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="M26">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="N26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" s="4">
-        <v>9.0277777777777774E-4</v>
+        <v>9.7222222222222219E-4</v>
       </c>
       <c r="P26" s="4">
-        <v>1.1111111111111111E-3</v>
+        <v>1.736111111111111E-3</v>
       </c>
       <c r="Q26" s="5">
-        <v>1.2699999999999999E-2</v>
+        <v>1.1900000000000001E-2</v>
       </c>
       <c r="R26" s="5">
-        <v>0.32969999999999999</v>
-      </c>
-      <c r="S26" s="5">
-        <v>0.36670000000000003</v>
+        <v>0.18260000000000001</v>
+      </c>
+      <c r="S26" s="3">
+        <v>1</v>
       </c>
       <c r="T26">
-        <v>1</v>
-      </c>
-      <c r="U26" s="5">
-        <v>5.2600000000000001E-2</v>
+        <v>-25</v>
+      </c>
+      <c r="U26" t="s">
+        <v>25</v>
       </c>
       <c r="V26" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+        <v>0.87880000000000003</v>
+      </c>
+      <c r="W26">
+        <v>34.314</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <v>46183</v>
+        <v>46181</v>
       </c>
       <c r="B27">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C27">
         <v>84</v>
       </c>
       <c r="D27">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="E27" t="s">
         <v>26</v>
       </c>
-      <c r="F27">
-        <v>15993</v>
+      <c r="F27" t="s">
+        <v>30</v>
       </c>
       <c r="G27">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H27">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I27">
-        <v>7018</v>
+        <v>4199</v>
       </c>
       <c r="J27">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="K27">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="L27">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="M27">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="N27">
         <v>0</v>
       </c>
       <c r="O27" s="4">
-        <v>4.3981481481481481E-4</v>
+        <v>2.8935185185185184E-4</v>
       </c>
       <c r="P27" s="4">
-        <v>6.018518518518519E-4</v>
+        <v>5.6712962962962967E-4</v>
       </c>
       <c r="Q27" s="5">
-        <v>2.6100000000000002E-2</v>
+        <v>3.8800000000000001E-2</v>
       </c>
       <c r="R27" s="5">
-        <v>0.25679999999999997</v>
-      </c>
-      <c r="S27" s="5">
-        <v>0.10639999999999999</v>
+        <v>0.36199999999999999</v>
+      </c>
+      <c r="S27" s="3">
+        <v>1</v>
       </c>
       <c r="T27">
-        <v>1</v>
-      </c>
-      <c r="U27" s="5">
-        <v>2.3800000000000002E-2</v>
-      </c>
-      <c r="V27" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
+        <v>-33</v>
+      </c>
+      <c r="U27" t="s">
+        <v>25</v>
+      </c>
+      <c r="W27">
+        <v>16.956</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>46183</v>
+        <v>46181</v>
       </c>
       <c r="B28">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C28">
         <v>81</v>
@@ -2351,132 +2392,135 @@
       <c r="E28" t="s">
         <v>27</v>
       </c>
-      <c r="F28">
-        <v>7468</v>
+      <c r="F28" t="s">
+        <v>30</v>
       </c>
       <c r="G28">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H28">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I28">
-        <v>14655</v>
+        <v>14008</v>
       </c>
       <c r="J28">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="K28">
-        <v>3436</v>
+        <v>43</v>
       </c>
       <c r="L28">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="M28">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O28" s="4">
-        <v>9.837962962962962E-4</v>
+        <v>8.564814814814815E-4</v>
       </c>
       <c r="P28" s="4">
-        <v>1.5740740740740741E-3</v>
+        <v>1.4583333333333334E-3</v>
       </c>
       <c r="Q28" s="5">
-        <v>1.0999999999999999E-2</v>
+        <v>1.3299999999999999E-2</v>
       </c>
       <c r="R28" s="5">
-        <v>21.34</v>
-      </c>
-      <c r="S28" s="5">
-        <v>4.8999999999999998E-3</v>
+        <v>0.23119999999999999</v>
+      </c>
+      <c r="S28" s="3">
+        <v>1</v>
       </c>
       <c r="T28">
-        <v>3400</v>
-      </c>
-      <c r="U28" s="5">
-        <v>0.99439999999999995</v>
+        <v>-21</v>
+      </c>
+      <c r="U28" t="s">
+        <v>25</v>
       </c>
       <c r="V28" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+        <v>0.6774</v>
+      </c>
+      <c r="W28">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>46183</v>
+        <v>46181</v>
       </c>
       <c r="B29">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C29">
         <v>84</v>
       </c>
       <c r="D29">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="E29" t="s">
         <v>26</v>
       </c>
-      <c r="F29">
-        <v>15993</v>
+      <c r="F29" t="s">
+        <v>30</v>
       </c>
       <c r="G29">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="H29">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I29">
-        <v>5338</v>
+        <v>9091</v>
       </c>
       <c r="J29">
-        <v>127</v>
+        <v>285</v>
       </c>
       <c r="K29">
-        <v>1262</v>
+        <v>83</v>
       </c>
       <c r="L29">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="M29">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N29">
         <v>0</v>
       </c>
       <c r="O29" s="4">
-        <v>4.5138888888888887E-4</v>
+        <v>3.5879629629629629E-4</v>
       </c>
       <c r="P29" s="4">
-        <v>6.5972222222222224E-4</v>
+        <v>9.9537037037037042E-4</v>
       </c>
       <c r="Q29" s="5">
-        <v>2.3800000000000002E-2</v>
+        <v>3.1300000000000001E-2</v>
       </c>
       <c r="R29" s="5">
-        <v>9.9369999999999994</v>
-      </c>
-      <c r="S29" s="5">
-        <v>7.1000000000000004E-3</v>
+        <v>0.29120000000000001</v>
+      </c>
+      <c r="S29" s="3">
+        <v>1</v>
       </c>
       <c r="T29">
-        <v>1228</v>
-      </c>
-      <c r="U29" s="3">
-        <v>0.98</v>
-      </c>
-      <c r="V29" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
+        <v>-33</v>
+      </c>
+      <c r="U29" t="s">
+        <v>25</v>
+      </c>
+      <c r="W29">
+        <v>7.8479999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>46183</v>
+        <v>46181</v>
       </c>
       <c r="B30">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C30">
         <v>81</v>
@@ -2487,76 +2531,76 @@
       <c r="E30" t="s">
         <v>27</v>
       </c>
-      <c r="F30">
-        <v>7468</v>
+      <c r="F30" t="s">
+        <v>30</v>
       </c>
       <c r="G30">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H30">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I30">
-        <v>16328</v>
+        <v>361</v>
       </c>
       <c r="J30">
-        <v>181</v>
+        <v>3</v>
       </c>
       <c r="K30">
-        <v>3683</v>
+        <v>1</v>
       </c>
       <c r="L30">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="M30">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="N30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O30" s="4">
-        <v>9.7222222222222219E-4</v>
+        <v>1.3773148148148147E-3</v>
       </c>
       <c r="P30" s="4">
-        <v>1.2962962962962963E-3</v>
+        <v>7.6388888888888893E-4</v>
       </c>
       <c r="Q30" s="5">
-        <v>1.11E-2</v>
+        <v>8.3000000000000001E-3</v>
       </c>
       <c r="R30" s="5">
-        <v>20.34</v>
-      </c>
-      <c r="S30" s="5">
-        <v>4.8999999999999998E-3</v>
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="S30" s="3">
+        <v>1</v>
       </c>
       <c r="T30">
-        <v>3641</v>
-      </c>
-      <c r="U30" s="5">
-        <v>0.99350000000000005</v>
+        <v>-1</v>
+      </c>
+      <c r="U30" t="s">
+        <v>25</v>
       </c>
       <c r="V30" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <v>46183</v>
+        <v>46181</v>
       </c>
       <c r="B31">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C31">
         <v>84</v>
       </c>
       <c r="D31">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="E31" t="s">
         <v>26</v>
       </c>
-      <c r="F31">
-        <v>15993</v>
+      <c r="F31" t="s">
+        <v>30</v>
       </c>
       <c r="G31">
         <v>25</v>
@@ -2565,54 +2609,51 @@
         <v>1</v>
       </c>
       <c r="I31">
-        <v>2369</v>
+        <v>3492</v>
       </c>
       <c r="J31">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="K31">
-        <v>521</v>
+        <v>32</v>
       </c>
       <c r="L31">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="M31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N31">
         <v>0</v>
       </c>
       <c r="O31" s="4">
-        <v>4.9768518518518521E-4</v>
+        <v>4.2824074074074075E-4</v>
       </c>
       <c r="P31" s="4">
-        <v>7.291666666666667E-4</v>
+        <v>2.1990740740740742E-3</v>
       </c>
       <c r="Q31" s="5">
-        <v>2.1999999999999999E-2</v>
+        <v>2.69E-2</v>
       </c>
       <c r="R31" s="5">
-        <v>10.01</v>
-      </c>
-      <c r="S31" s="5">
-        <v>3.8E-3</v>
+        <v>0.34039999999999998</v>
+      </c>
+      <c r="S31" s="3">
+        <v>1</v>
       </c>
       <c r="T31">
-        <v>516</v>
-      </c>
-      <c r="U31" s="5">
-        <v>0.99419999999999997</v>
-      </c>
-      <c r="V31" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
+        <v>-4</v>
+      </c>
+      <c r="U31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B32">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C32">
         <v>81</v>
@@ -2623,132 +2664,132 @@
       <c r="E32" t="s">
         <v>27</v>
       </c>
-      <c r="F32">
-        <v>7468</v>
+      <c r="F32" t="s">
+        <v>30</v>
       </c>
       <c r="G32">
         <v>25</v>
       </c>
       <c r="H32">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I32">
-        <v>17098</v>
+        <v>18719</v>
       </c>
       <c r="J32">
-        <v>157</v>
+        <v>232</v>
       </c>
       <c r="K32">
-        <v>3426</v>
+        <v>35</v>
       </c>
       <c r="L32">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="M32">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" s="4">
-        <v>1.1805555555555556E-3</v>
+        <v>8.9120370370370373E-4</v>
       </c>
       <c r="P32" s="4">
-        <v>1.5625000000000001E-3</v>
+        <v>1.2037037037037038E-3</v>
       </c>
       <c r="Q32" s="5">
-        <v>9.1999999999999998E-3</v>
+        <v>1.24E-2</v>
       </c>
       <c r="R32" s="5">
-        <v>21.82</v>
-      </c>
-      <c r="S32" s="5">
-        <v>6.4000000000000003E-3</v>
+        <v>0.15090000000000001</v>
+      </c>
+      <c r="S32" s="3">
+        <v>1</v>
       </c>
       <c r="T32">
-        <v>3387</v>
-      </c>
-      <c r="U32" s="5">
-        <v>0.995</v>
+        <v>-18</v>
+      </c>
+      <c r="U32" t="s">
+        <v>25</v>
       </c>
       <c r="V32" s="5">
-        <v>1</v>
+        <v>0.95240000000000002</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B33">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C33">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D33">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E33" t="s">
+        <v>27</v>
+      </c>
+      <c r="F33" t="s">
+        <v>30</v>
+      </c>
+      <c r="G33">
+        <v>25</v>
+      </c>
+      <c r="H33">
+        <v>9</v>
+      </c>
+      <c r="I33">
+        <v>20163</v>
+      </c>
+      <c r="J33">
+        <v>250</v>
+      </c>
+      <c r="K33">
+        <v>53</v>
+      </c>
+      <c r="L33">
+        <v>53</v>
+      </c>
+      <c r="M33">
         <v>26</v>
       </c>
-      <c r="F33">
-        <v>15993</v>
-      </c>
-      <c r="G33">
-        <v>25</v>
-      </c>
-      <c r="H33">
-        <v>0</v>
-      </c>
-      <c r="I33">
-        <v>2068</v>
-      </c>
-      <c r="J33">
-        <v>49</v>
-      </c>
-      <c r="K33">
-        <v>441</v>
-      </c>
-      <c r="L33">
-        <v>5</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
       <c r="N33">
         <v>0</v>
       </c>
       <c r="O33" s="4">
-        <v>4.5138888888888887E-4</v>
-      </c>
-      <c r="P33" t="s">
-        <v>24</v>
+        <v>8.9120370370370373E-4</v>
+      </c>
+      <c r="P33" s="4">
+        <v>9.3749999999999997E-4</v>
       </c>
       <c r="Q33" s="5">
-        <v>2.3699999999999999E-2</v>
-      </c>
-      <c r="R33" s="3">
-        <v>9</v>
-      </c>
-      <c r="S33" s="5">
-        <v>1.1299999999999999E-2</v>
+        <v>1.24E-2</v>
+      </c>
+      <c r="R33" s="5">
+        <v>0.21199999999999999</v>
+      </c>
+      <c r="S33" s="3">
+        <v>1</v>
       </c>
       <c r="T33">
-        <v>436</v>
-      </c>
-      <c r="U33" s="3">
-        <v>1</v>
+        <v>-26</v>
+      </c>
+      <c r="U33" t="s">
+        <v>25</v>
       </c>
       <c r="V33" s="5">
-        <v>0.72729999999999995</v>
+        <v>0.85289999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B34">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C34">
         <v>81</v>
@@ -2759,53 +2800,53 @@
       <c r="E34" t="s">
         <v>27</v>
       </c>
-      <c r="F34">
-        <v>7468</v>
+      <c r="F34" t="s">
+        <v>30</v>
       </c>
       <c r="G34">
         <v>25</v>
       </c>
       <c r="H34">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I34">
-        <v>18676</v>
+        <v>12067</v>
       </c>
       <c r="J34">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="K34">
-        <v>2905</v>
+        <v>17</v>
       </c>
       <c r="L34">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="M34">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="N34">
         <v>0</v>
       </c>
       <c r="O34" s="4">
-        <v>1.2962962962962963E-3</v>
+        <v>1.1226851851851851E-3</v>
       </c>
       <c r="P34" s="4">
-        <v>1.0532407407407407E-3</v>
-      </c>
-      <c r="Q34" s="5">
-        <v>8.3999999999999995E-3</v>
+        <v>1.7824074074074075E-3</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0.01</v>
       </c>
       <c r="R34" s="5">
-        <v>18.5</v>
-      </c>
-      <c r="S34" s="5">
-        <v>7.1999999999999998E-3</v>
+        <v>0.14050000000000001</v>
+      </c>
+      <c r="S34" s="3">
+        <v>1</v>
       </c>
       <c r="T34">
-        <v>2865</v>
-      </c>
-      <c r="U34" s="5">
-        <v>0.99339999999999995</v>
+        <v>-13</v>
+      </c>
+      <c r="U34" t="s">
+        <v>25</v>
       </c>
       <c r="V34" s="5">
         <v>1</v>
@@ -2813,78 +2854,75 @@
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B35">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C35">
         <v>84</v>
       </c>
       <c r="D35">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="E35" t="s">
         <v>26</v>
       </c>
-      <c r="F35">
-        <v>15993</v>
+      <c r="F35" t="s">
+        <v>30</v>
       </c>
       <c r="G35">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I35">
-        <v>922</v>
+        <v>8477</v>
       </c>
       <c r="J35">
-        <v>16</v>
+        <v>315</v>
       </c>
       <c r="K35">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="L35">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="N35">
         <v>0</v>
       </c>
       <c r="O35" s="4">
-        <v>6.2500000000000001E-4</v>
-      </c>
-      <c r="P35" t="s">
-        <v>24</v>
+        <v>3.0092592592592595E-4</v>
+      </c>
+      <c r="P35" s="4">
+        <v>6.3657407407407413E-4</v>
       </c>
       <c r="Q35" s="5">
-        <v>1.7399999999999999E-2</v>
+        <v>3.7199999999999997E-2</v>
       </c>
       <c r="R35" s="5">
-        <v>8.5619999999999994</v>
-      </c>
-      <c r="S35" s="5">
-        <v>7.3000000000000001E-3</v>
+        <v>0.254</v>
+      </c>
+      <c r="S35" s="3">
+        <v>1</v>
       </c>
       <c r="T35">
-        <v>136</v>
-      </c>
-      <c r="U35" s="3">
-        <v>1</v>
-      </c>
-      <c r="V35" s="5">
-        <v>0.33329999999999999</v>
+        <v>-58</v>
+      </c>
+      <c r="U35" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B36">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C36">
         <v>81</v>
@@ -2895,132 +2933,129 @@
       <c r="E36" t="s">
         <v>27</v>
       </c>
-      <c r="F36">
-        <v>7468</v>
+      <c r="F36" t="s">
+        <v>30</v>
       </c>
       <c r="G36">
         <v>25</v>
       </c>
       <c r="H36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I36">
-        <v>18370</v>
+        <v>9021</v>
       </c>
       <c r="J36">
-        <v>182</v>
+        <v>85</v>
       </c>
       <c r="K36">
-        <v>1112</v>
+        <v>17</v>
       </c>
       <c r="L36">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="M36">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O36" s="4">
-        <v>1.1342592592592593E-3</v>
+        <v>1.1574074074074073E-3</v>
       </c>
       <c r="P36" s="4">
-        <v>1.1111111111111111E-3</v>
+        <v>1.4004629629629629E-3</v>
       </c>
       <c r="Q36" s="5">
-        <v>9.9000000000000008E-3</v>
-      </c>
-      <c r="R36" s="5">
-        <v>6.109</v>
-      </c>
-      <c r="S36" s="5">
-        <v>9.9000000000000008E-3</v>
+        <v>9.4000000000000004E-3</v>
+      </c>
+      <c r="R36" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="S36" s="3">
+        <v>1</v>
       </c>
       <c r="T36">
-        <v>1086</v>
-      </c>
-      <c r="U36" s="5">
-        <v>0.98640000000000005</v>
+        <v>-10</v>
+      </c>
+      <c r="U36" t="s">
+        <v>25</v>
       </c>
       <c r="V36" s="5">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B37">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C37">
         <v>84</v>
       </c>
       <c r="D37">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="E37" t="s">
         <v>26</v>
       </c>
-      <c r="F37">
-        <v>15993</v>
+      <c r="F37" t="s">
+        <v>30</v>
       </c>
       <c r="G37">
         <v>25</v>
       </c>
       <c r="H37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I37">
-        <v>2302</v>
+        <v>6627</v>
       </c>
       <c r="J37">
-        <v>94</v>
+        <v>232</v>
       </c>
       <c r="K37">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="L37">
+        <v>50</v>
+      </c>
+      <c r="M37">
         <v>4</v>
       </c>
-      <c r="M37">
-        <v>15</v>
-      </c>
       <c r="N37">
         <v>0</v>
       </c>
       <c r="O37" s="4">
-        <v>2.7777777777777778E-4</v>
+        <v>3.2407407407407406E-4</v>
       </c>
       <c r="P37" s="4">
-        <v>8.4490740740740739E-4</v>
+        <v>7.6388888888888893E-4</v>
       </c>
       <c r="Q37" s="5">
-        <v>4.0800000000000003E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="R37" s="5">
-        <v>1.595</v>
-      </c>
-      <c r="S37" s="5">
-        <v>2.6700000000000002E-2</v>
+        <v>0.2155</v>
+      </c>
+      <c r="S37" s="3">
+        <v>1</v>
       </c>
       <c r="T37">
-        <v>131</v>
-      </c>
-      <c r="U37" s="5">
-        <v>0.89729999999999999</v>
-      </c>
-      <c r="V37" s="5">
-        <v>0.88239999999999996</v>
+        <v>-4</v>
+      </c>
+      <c r="U37" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B38">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C38">
         <v>81</v>
@@ -3031,53 +3066,53 @@
       <c r="E38" t="s">
         <v>27</v>
       </c>
-      <c r="F38">
-        <v>7468</v>
+      <c r="F38" t="s">
+        <v>30</v>
       </c>
       <c r="G38">
         <v>25</v>
       </c>
       <c r="H38">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I38">
-        <v>14762</v>
+        <v>14219</v>
       </c>
       <c r="J38">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K38">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="L38">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="M38">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="N38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" s="4">
-        <v>9.837962962962962E-4</v>
+        <v>8.4490740740740739E-4</v>
       </c>
       <c r="P38" s="4">
-        <v>1.4930555555555556E-3</v>
+        <v>1.736111111111111E-3</v>
       </c>
       <c r="Q38" s="5">
-        <v>1.1599999999999999E-2</v>
+        <v>1.2800000000000001E-2</v>
       </c>
       <c r="R38" s="5">
-        <v>0.18709999999999999</v>
-      </c>
-      <c r="S38" s="5">
-        <v>0.40629999999999999</v>
+        <v>0.1429</v>
+      </c>
+      <c r="S38" s="3">
+        <v>1</v>
       </c>
       <c r="T38">
-        <v>1</v>
-      </c>
-      <c r="U38" s="5">
-        <v>5.2600000000000001E-2</v>
+        <v>-14</v>
+      </c>
+      <c r="U38" t="s">
+        <v>25</v>
       </c>
       <c r="V38" s="5">
         <v>1</v>
@@ -3085,43 +3120,43 @@
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B39">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C39">
         <v>84</v>
       </c>
       <c r="D39">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="E39" t="s">
         <v>26</v>
       </c>
-      <c r="F39">
-        <v>15993</v>
+      <c r="F39" t="s">
+        <v>30</v>
       </c>
       <c r="G39">
         <v>25</v>
       </c>
       <c r="H39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I39">
-        <v>5623</v>
+        <v>4319</v>
       </c>
       <c r="J39">
-        <v>163</v>
+        <v>123</v>
       </c>
       <c r="K39">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="L39">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="M39">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="N39">
         <v>0</v>
@@ -3130,33 +3165,30 @@
         <v>3.9351851851851852E-4</v>
       </c>
       <c r="P39" s="4">
-        <v>4.1666666666666669E-4</v>
+        <v>5.3240740740740744E-4</v>
       </c>
       <c r="Q39" s="5">
-        <v>2.9000000000000001E-2</v>
+        <v>2.8500000000000001E-2</v>
       </c>
       <c r="R39" s="5">
-        <v>0.22700000000000001</v>
-      </c>
-      <c r="S39" s="5">
-        <v>0.18920000000000001</v>
+        <v>0.24390000000000001</v>
+      </c>
+      <c r="S39" s="3">
+        <v>1</v>
       </c>
       <c r="T39">
-        <v>0</v>
-      </c>
-      <c r="U39" s="3">
-        <v>0</v>
-      </c>
-      <c r="V39" s="5">
-        <v>1</v>
+        <v>-11</v>
+      </c>
+      <c r="U39" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B40">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C40">
         <v>81</v>
@@ -3167,53 +3199,53 @@
       <c r="E40" t="s">
         <v>27</v>
       </c>
-      <c r="F40">
-        <v>7468</v>
+      <c r="F40" t="s">
+        <v>30</v>
       </c>
       <c r="G40">
         <v>25</v>
       </c>
       <c r="H40">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I40">
-        <v>16376</v>
+        <v>6219</v>
       </c>
       <c r="J40">
-        <v>157</v>
+        <v>72</v>
       </c>
       <c r="K40">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="L40">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="M40">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N40">
         <v>0</v>
       </c>
       <c r="O40" s="4">
-        <v>1.1921296296296296E-3</v>
+        <v>9.1435185185185185E-4</v>
       </c>
       <c r="P40" s="4">
-        <v>3.2407407407407406E-4</v>
+        <v>9.0277777777777774E-4</v>
       </c>
       <c r="Q40" s="5">
-        <v>9.5999999999999992E-3</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="R40" s="5">
-        <v>0.36309999999999998</v>
-      </c>
-      <c r="S40" s="5">
-        <v>0.52629999999999999</v>
+        <v>0.16669999999999999</v>
+      </c>
+      <c r="S40" s="3">
+        <v>1</v>
       </c>
       <c r="T40">
-        <v>16</v>
-      </c>
-      <c r="U40" s="5">
-        <v>0.59260000000000002</v>
+        <v>-7</v>
+      </c>
+      <c r="U40" t="s">
+        <v>25</v>
       </c>
       <c r="V40" s="5">
         <v>1</v>
@@ -3221,78 +3253,75 @@
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B41">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C41">
         <v>84</v>
       </c>
       <c r="D41">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="E41" t="s">
         <v>26</v>
       </c>
-      <c r="F41">
-        <v>15993</v>
+      <c r="F41" t="s">
+        <v>30</v>
       </c>
       <c r="G41">
         <v>25</v>
       </c>
       <c r="H41">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I41">
-        <v>8943</v>
+        <v>3712</v>
       </c>
       <c r="J41">
-        <v>253</v>
+        <v>87</v>
       </c>
       <c r="K41">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="L41">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="M41">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O41" s="4">
-        <v>4.0509259259259258E-4</v>
+        <v>4.7453703703703704E-4</v>
       </c>
       <c r="P41" s="4">
-        <v>4.5138888888888887E-4</v>
+        <v>1.3310185185185185E-3</v>
       </c>
       <c r="Q41" s="5">
-        <v>2.8299999999999999E-2</v>
+        <v>2.3400000000000001E-2</v>
       </c>
       <c r="R41" s="5">
-        <v>0.2964</v>
-      </c>
-      <c r="S41" s="5">
-        <v>0.33329999999999999</v>
+        <v>0.19539999999999999</v>
+      </c>
+      <c r="S41" s="3">
+        <v>1</v>
       </c>
       <c r="T41">
-        <v>10</v>
-      </c>
-      <c r="U41" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="V41" s="5">
-        <v>0.95240000000000002</v>
+        <v>-11</v>
+      </c>
+      <c r="U41" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B42">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C42">
         <v>81</v>
@@ -3303,53 +3332,53 @@
       <c r="E42" t="s">
         <v>27</v>
       </c>
-      <c r="F42">
-        <v>7468</v>
+      <c r="F42" t="s">
+        <v>30</v>
       </c>
       <c r="G42">
         <v>25</v>
       </c>
       <c r="H42">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I42">
-        <v>17303</v>
+        <v>11882</v>
       </c>
       <c r="J42">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="K42">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L42">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="M42">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="N42">
         <v>0</v>
       </c>
       <c r="O42" s="4">
-        <v>1.7476851851851852E-3</v>
+        <v>7.9861111111111116E-4</v>
       </c>
       <c r="P42" s="4">
-        <v>7.291666666666667E-4</v>
+        <v>1.9791666666666668E-3</v>
       </c>
       <c r="Q42" s="5">
-        <v>6.6E-3</v>
+        <v>1.29E-2</v>
       </c>
       <c r="R42" s="5">
-        <v>0.31580000000000003</v>
-      </c>
-      <c r="S42" s="5">
-        <v>0.52780000000000005</v>
+        <v>0.1895</v>
+      </c>
+      <c r="S42" s="3">
+        <v>1</v>
       </c>
       <c r="T42">
-        <v>6</v>
-      </c>
-      <c r="U42" s="5">
-        <v>0.35289999999999999</v>
+        <v>-16</v>
+      </c>
+      <c r="U42" t="s">
+        <v>25</v>
       </c>
       <c r="V42" s="5">
         <v>1</v>
@@ -3357,22 +3386,22 @@
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B43">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C43">
         <v>84</v>
       </c>
       <c r="D43">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="E43" t="s">
         <v>26</v>
       </c>
-      <c r="F43">
-        <v>15993</v>
+      <c r="F43" t="s">
+        <v>30</v>
       </c>
       <c r="G43">
         <v>25</v>
@@ -3381,54 +3410,51 @@
         <v>2</v>
       </c>
       <c r="I43">
-        <v>6584</v>
+        <v>3434</v>
       </c>
       <c r="J43">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="K43">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L43">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="M43">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N43">
         <v>0</v>
       </c>
       <c r="O43" s="4">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="P43" s="4">
         <v>4.7453703703703704E-4</v>
       </c>
-      <c r="P43" s="4">
-        <v>6.134259259259259E-4</v>
-      </c>
       <c r="Q43" s="5">
-        <v>2.4E-2</v>
+        <v>3.7900000000000003E-2</v>
       </c>
       <c r="R43" s="5">
-        <v>0.24679999999999999</v>
-      </c>
-      <c r="S43" s="5">
-        <v>0.28210000000000002</v>
+        <v>0.2923</v>
+      </c>
+      <c r="S43" s="3">
+        <v>1</v>
       </c>
       <c r="T43">
-        <v>15</v>
-      </c>
-      <c r="U43" s="5">
-        <v>0.53569999999999995</v>
-      </c>
-      <c r="V43" s="5">
-        <v>0.79410000000000003</v>
+        <v>-17</v>
+      </c>
+      <c r="U43" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B44">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C44">
         <v>81</v>
@@ -3439,132 +3465,129 @@
       <c r="E44" t="s">
         <v>27</v>
       </c>
-      <c r="F44">
-        <v>7468</v>
+      <c r="F44" t="s">
+        <v>30</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I44">
-        <v>133</v>
+        <v>16923</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>262</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M44">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="N44">
         <v>0</v>
       </c>
-      <c r="O44" t="s">
-        <v>24</v>
-      </c>
-      <c r="P44" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
-      <c r="R44" t="s">
-        <v>25</v>
-      </c>
-      <c r="S44" t="s">
-        <v>25</v>
+      <c r="O44" s="4">
+        <v>6.7129629629629625E-4</v>
+      </c>
+      <c r="P44" s="4">
+        <v>1.4467592592592592E-3</v>
+      </c>
+      <c r="Q44" s="5">
+        <v>1.55E-2</v>
+      </c>
+      <c r="R44" s="5">
+        <v>0.1565</v>
+      </c>
+      <c r="S44" s="3">
+        <v>1</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>-29</v>
       </c>
       <c r="U44" t="s">
         <v>25</v>
       </c>
-      <c r="V44" t="s">
-        <v>25</v>
+      <c r="V44" s="5">
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B45">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C45">
         <v>84</v>
       </c>
       <c r="D45">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="E45" t="s">
         <v>26</v>
       </c>
-      <c r="F45">
-        <v>15993</v>
+      <c r="F45" t="s">
+        <v>30</v>
       </c>
       <c r="G45">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I45">
-        <v>18</v>
+        <v>3916</v>
       </c>
       <c r="J45">
-        <v>1</v>
+        <v>121</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M45">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N45">
         <v>0</v>
       </c>
       <c r="O45" s="4">
-        <v>2.0833333333333335E-4</v>
-      </c>
-      <c r="P45" t="s">
-        <v>24</v>
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="P45" s="4">
+        <v>5.0925925925925921E-4</v>
       </c>
       <c r="Q45" s="5">
-        <v>5.5599999999999997E-2</v>
-      </c>
-      <c r="R45" s="3">
-        <v>0</v>
-      </c>
-      <c r="S45" t="s">
-        <v>25</v>
+        <v>3.09E-2</v>
+      </c>
+      <c r="R45" s="5">
+        <v>0.20660000000000001</v>
+      </c>
+      <c r="S45" s="3">
+        <v>1</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="U45" t="s">
-        <v>25</v>
-      </c>
-      <c r="V45" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="B46">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C46">
         <v>81</v>
@@ -3575,132 +3598,129 @@
       <c r="E46" t="s">
         <v>27</v>
       </c>
-      <c r="F46">
-        <v>7407</v>
+      <c r="F46" t="s">
+        <v>30</v>
       </c>
       <c r="G46">
         <v>25</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I46">
-        <v>17156</v>
+        <v>17295</v>
       </c>
       <c r="J46">
-        <v>138</v>
+        <v>282</v>
       </c>
       <c r="K46">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="L46">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="M46">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="N46">
         <v>0</v>
       </c>
       <c r="O46" s="4">
-        <v>1.4236111111111112E-3</v>
-      </c>
-      <c r="P46" t="s">
-        <v>24</v>
+        <v>6.5972222222222224E-4</v>
+      </c>
+      <c r="P46" s="4">
+        <v>9.1435185185185185E-4</v>
       </c>
       <c r="Q46" s="5">
-        <v>8.0000000000000002E-3</v>
+        <v>1.6299999999999999E-2</v>
       </c>
       <c r="R46" s="5">
-        <v>0.28989999999999999</v>
+        <v>0.15959999999999999</v>
       </c>
       <c r="S46" s="3">
-        <v>0.45</v>
+        <v>1</v>
       </c>
       <c r="T46">
-        <v>22</v>
-      </c>
-      <c r="U46" s="3">
-        <v>1</v>
-      </c>
-      <c r="V46" t="s">
-        <v>25</v>
+        <v>-27</v>
+      </c>
+      <c r="U46" t="s">
+        <v>25</v>
+      </c>
+      <c r="V46" s="5">
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="B47">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C47">
         <v>84</v>
       </c>
       <c r="D47">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="E47" t="s">
         <v>26</v>
       </c>
-      <c r="F47">
-        <v>36058</v>
+      <c r="F47" t="s">
+        <v>30</v>
       </c>
       <c r="G47">
         <v>25</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I47">
-        <v>7848</v>
+        <v>5345</v>
       </c>
       <c r="J47">
-        <v>143</v>
+        <v>192</v>
       </c>
       <c r="K47">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L47">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="M47">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="N47">
         <v>0</v>
       </c>
       <c r="O47" s="4">
-        <v>6.2500000000000001E-4</v>
-      </c>
-      <c r="P47" t="s">
-        <v>24</v>
+        <v>3.0092592592592595E-4</v>
+      </c>
+      <c r="P47" s="4">
+        <v>4.0509259259259258E-4</v>
       </c>
       <c r="Q47" s="5">
-        <v>1.8200000000000001E-2</v>
+        <v>3.5900000000000001E-2</v>
       </c>
       <c r="R47" s="5">
-        <v>0.2238</v>
-      </c>
-      <c r="S47" s="5">
-        <v>0.28129999999999999</v>
+        <v>0.20830000000000001</v>
+      </c>
+      <c r="S47" s="3">
+        <v>1</v>
       </c>
       <c r="T47">
-        <v>23</v>
-      </c>
-      <c r="U47" s="3">
-        <v>1</v>
-      </c>
-      <c r="V47" t="s">
+        <v>-28</v>
+      </c>
+      <c r="U47" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="B48">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C48">
         <v>81</v>
@@ -3711,53 +3731,53 @@
       <c r="E48" t="s">
         <v>27</v>
       </c>
-      <c r="F48">
-        <v>7407</v>
+      <c r="F48" t="s">
+        <v>30</v>
       </c>
       <c r="G48">
         <v>25</v>
       </c>
       <c r="H48">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I48">
-        <v>17669</v>
+        <v>24262</v>
       </c>
       <c r="J48">
-        <v>163</v>
+        <v>261</v>
       </c>
       <c r="K48">
-        <v>1068</v>
+        <v>59</v>
       </c>
       <c r="L48">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="M48">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O48" s="4">
-        <v>1.2268518518518518E-3</v>
-      </c>
-      <c r="P48" s="4">
-        <v>1.5740740740740741E-3</v>
+        <v>1.0532407407407407E-3</v>
+      </c>
+      <c r="P48" t="s">
+        <v>24</v>
       </c>
       <c r="Q48" s="5">
-        <v>9.1999999999999998E-3</v>
+        <v>1.0800000000000001E-2</v>
       </c>
       <c r="R48" s="5">
-        <v>6.5519999999999996</v>
-      </c>
-      <c r="S48" s="5">
-        <v>2.9000000000000001E-2</v>
+        <v>0.2261</v>
+      </c>
+      <c r="S48" s="3">
+        <v>1</v>
       </c>
       <c r="T48">
-        <v>1017</v>
-      </c>
-      <c r="U48" s="5">
-        <v>0.98070000000000002</v>
+        <v>0</v>
+      </c>
+      <c r="U48" t="s">
+        <v>25</v>
       </c>
       <c r="V48" s="5">
         <v>1</v>
@@ -3765,78 +3785,75 @@
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="B49">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C49">
         <v>84</v>
       </c>
       <c r="D49">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="E49" t="s">
         <v>26</v>
       </c>
-      <c r="F49">
-        <v>36058</v>
+      <c r="F49" t="s">
+        <v>30</v>
       </c>
       <c r="G49">
         <v>25</v>
       </c>
       <c r="H49">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I49">
-        <v>6190</v>
+        <v>8288</v>
       </c>
       <c r="J49">
-        <v>93</v>
+        <v>240</v>
       </c>
       <c r="K49">
-        <v>280</v>
+        <v>53</v>
       </c>
       <c r="L49">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="M49">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N49">
         <v>0</v>
       </c>
       <c r="O49" s="4">
-        <v>7.5231481481481482E-4</v>
-      </c>
-      <c r="P49" s="4">
-        <v>2.7777777777777778E-4</v>
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="P49" t="s">
+        <v>24</v>
       </c>
       <c r="Q49" s="5">
-        <v>1.4999999999999999E-2</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="R49" s="5">
-        <v>3.01</v>
-      </c>
-      <c r="S49" s="5">
-        <v>3.2099999999999997E-2</v>
+        <v>0.2208</v>
+      </c>
+      <c r="S49" s="3">
+        <v>1</v>
       </c>
       <c r="T49">
-        <v>257</v>
-      </c>
-      <c r="U49" s="5">
-        <v>0.94830000000000003</v>
-      </c>
-      <c r="V49" s="5">
-        <v>0.86360000000000003</v>
+        <v>0</v>
+      </c>
+      <c r="U49" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="B50">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C50">
         <v>81</v>
@@ -3847,97 +3864,97 @@
       <c r="E50" t="s">
         <v>27</v>
       </c>
-      <c r="F50">
-        <v>7407</v>
+      <c r="F50" t="s">
+        <v>30</v>
       </c>
       <c r="G50">
         <v>25</v>
       </c>
       <c r="H50">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I50">
-        <v>21673</v>
+        <v>28325</v>
       </c>
       <c r="J50">
-        <v>165</v>
+        <v>277</v>
       </c>
       <c r="K50">
-        <v>1685</v>
+        <v>38</v>
       </c>
       <c r="L50">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="M50">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N50">
         <v>0</v>
       </c>
       <c r="O50" s="4">
-        <v>1.4699074074074074E-3</v>
-      </c>
-      <c r="P50" s="4">
-        <v>1.1921296296296296E-3</v>
+        <v>1.1458333333333333E-3</v>
+      </c>
+      <c r="P50" t="s">
+        <v>24</v>
       </c>
       <c r="Q50" s="5">
-        <v>7.6E-3</v>
+        <v>9.7999999999999997E-3</v>
       </c>
       <c r="R50" s="5">
-        <v>10.210000000000001</v>
-      </c>
-      <c r="S50" s="5">
-        <v>1.3599999999999999E-2</v>
+        <v>0.13719999999999999</v>
+      </c>
+      <c r="S50" s="3">
+        <v>1</v>
       </c>
       <c r="T50">
-        <v>1637</v>
-      </c>
-      <c r="U50" s="5">
-        <v>0.98499999999999999</v>
-      </c>
-      <c r="V50" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U50" t="s">
+        <v>25</v>
+      </c>
+      <c r="V50" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="B51">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C51">
         <v>84</v>
       </c>
       <c r="D51">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="E51" t="s">
         <v>26</v>
       </c>
-      <c r="F51">
-        <v>36058</v>
+      <c r="F51" t="s">
+        <v>30</v>
       </c>
       <c r="G51">
         <v>25</v>
       </c>
       <c r="H51">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I51">
-        <v>2538</v>
+        <v>10294</v>
       </c>
       <c r="J51">
-        <v>75</v>
+        <v>298</v>
       </c>
       <c r="K51">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="L51">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="M51">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N51">
         <v>0</v>
@@ -3945,34 +3962,31 @@
       <c r="O51" s="4">
         <v>3.8194444444444446E-4</v>
       </c>
-      <c r="P51" s="4">
-        <v>4.861111111111111E-4</v>
+      <c r="P51" t="s">
+        <v>24</v>
       </c>
       <c r="Q51" s="5">
-        <v>2.9600000000000001E-2</v>
+        <v>2.8899999999999999E-2</v>
       </c>
       <c r="R51" s="5">
-        <v>1.0129999999999999</v>
-      </c>
-      <c r="S51" s="5">
-        <v>5.2600000000000001E-2</v>
+        <v>0.21809999999999999</v>
+      </c>
+      <c r="S51" s="3">
+        <v>1</v>
       </c>
       <c r="T51">
-        <v>64</v>
-      </c>
-      <c r="U51" s="5">
-        <v>0.88890000000000002</v>
-      </c>
-      <c r="V51" s="5">
-        <v>0.90910000000000002</v>
+        <v>0</v>
+      </c>
+      <c r="U51" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="B52">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C52">
         <v>81</v>
@@ -3983,132 +3997,126 @@
       <c r="E52" t="s">
         <v>27</v>
       </c>
-      <c r="F52">
-        <v>7407</v>
+      <c r="F52" t="s">
+        <v>30</v>
       </c>
       <c r="G52">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H52">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I52">
-        <v>17931</v>
+        <v>246</v>
       </c>
       <c r="J52">
-        <v>141</v>
+        <v>1</v>
       </c>
       <c r="K52">
-        <v>2061</v>
+        <v>0</v>
       </c>
       <c r="L52">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="M52">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O52" s="4">
-        <v>1.4120370370370369E-3</v>
-      </c>
-      <c r="P52" s="4">
-        <v>1.4120370370370369E-3</v>
+        <v>2.8240740740740739E-3</v>
+      </c>
+      <c r="P52" t="s">
+        <v>24</v>
       </c>
       <c r="Q52" s="5">
-        <v>7.9000000000000008E-3</v>
-      </c>
-      <c r="R52" s="5">
-        <v>14.61</v>
-      </c>
-      <c r="S52" s="5">
-        <v>1.3599999999999999E-2</v>
+        <v>4.1000000000000003E-3</v>
+      </c>
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" t="s">
+        <v>25</v>
       </c>
       <c r="T52">
-        <v>2018</v>
-      </c>
-      <c r="U52" s="5">
-        <v>0.99260000000000004</v>
-      </c>
-      <c r="V52" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U52" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="B53">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C53">
         <v>84</v>
       </c>
       <c r="D53">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="E53" t="s">
         <v>26</v>
       </c>
-      <c r="F53">
-        <v>36058</v>
+      <c r="F53" t="s">
+        <v>30</v>
       </c>
       <c r="G53">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>165</v>
+      </c>
+      <c r="J53">
         <v>3</v>
       </c>
-      <c r="I53">
-        <v>2818</v>
-      </c>
-      <c r="J53">
-        <v>119</v>
-      </c>
       <c r="K53">
-        <v>231</v>
+        <v>0</v>
       </c>
       <c r="L53">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M53">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="N53">
         <v>0</v>
       </c>
       <c r="O53" s="4">
-        <v>2.6620370370370372E-4</v>
-      </c>
-      <c r="P53" s="4">
-        <v>1.5162037037037036E-3</v>
+        <v>6.2500000000000001E-4</v>
+      </c>
+      <c r="P53" t="s">
+        <v>24</v>
       </c>
       <c r="Q53" s="5">
-        <v>4.2200000000000001E-2</v>
-      </c>
-      <c r="R53" s="5">
-        <v>1.9410000000000001</v>
-      </c>
-      <c r="S53" s="5">
-        <v>1.7299999999999999E-2</v>
+        <v>1.8200000000000001E-2</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" t="s">
+        <v>25</v>
       </c>
       <c r="T53">
-        <v>210</v>
-      </c>
-      <c r="U53" s="5">
-        <v>0.92510000000000003</v>
-      </c>
-      <c r="V53" s="5">
-        <v>0.95450000000000002</v>
+        <v>0</v>
+      </c>
+      <c r="U53" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="B54">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C54">
         <v>81</v>
@@ -4119,132 +4127,129 @@
       <c r="E54" t="s">
         <v>27</v>
       </c>
-      <c r="F54">
-        <v>7407</v>
+      <c r="F54" t="s">
+        <v>30</v>
       </c>
       <c r="G54">
         <v>25</v>
       </c>
       <c r="H54">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I54">
-        <v>31421</v>
+        <v>11322</v>
       </c>
       <c r="J54">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="K54">
-        <v>4079</v>
+        <v>35</v>
       </c>
       <c r="L54">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="M54">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N54">
         <v>0</v>
       </c>
       <c r="O54" s="4">
-        <v>1.6666666666666668E-3</v>
-      </c>
-      <c r="P54" s="4">
-        <v>1.2152777777777778E-3</v>
+        <v>6.8287037037037036E-4</v>
+      </c>
+      <c r="P54" t="s">
+        <v>24</v>
       </c>
       <c r="Q54" s="5">
-        <v>6.7000000000000002E-3</v>
+        <v>1.67E-2</v>
       </c>
       <c r="R54" s="5">
-        <v>19.510000000000002</v>
-      </c>
-      <c r="S54" s="5">
-        <v>6.4000000000000003E-3</v>
+        <v>0.1852</v>
+      </c>
+      <c r="S54" s="3">
+        <v>1</v>
       </c>
       <c r="T54">
-        <v>4037</v>
-      </c>
-      <c r="U54" s="5">
-        <v>0.99609999999999999</v>
-      </c>
-      <c r="V54" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U54" t="s">
+        <v>25</v>
+      </c>
+      <c r="V54" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="B55">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C55">
         <v>84</v>
       </c>
       <c r="D55">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="E55" t="s">
         <v>26</v>
       </c>
-      <c r="F55">
-        <v>36058</v>
+      <c r="F55" t="s">
+        <v>30</v>
       </c>
       <c r="G55">
         <v>25</v>
       </c>
       <c r="H55">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I55">
-        <v>1295</v>
+        <v>4604</v>
       </c>
       <c r="J55">
-        <v>51</v>
+        <v>139</v>
       </c>
       <c r="K55">
-        <v>208</v>
+        <v>33</v>
       </c>
       <c r="L55">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="M55">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N55">
         <v>0</v>
       </c>
       <c r="O55" s="4">
-        <v>2.7777777777777778E-4</v>
-      </c>
-      <c r="P55" s="4">
-        <v>7.8703703703703705E-4</v>
+        <v>3.7037037037037035E-4</v>
+      </c>
+      <c r="P55" t="s">
+        <v>24</v>
       </c>
       <c r="Q55" s="5">
-        <v>3.9399999999999998E-2</v>
+        <v>3.0200000000000001E-2</v>
       </c>
       <c r="R55" s="5">
-        <v>4.0780000000000003</v>
-      </c>
-      <c r="S55" s="5">
-        <v>1.44E-2</v>
+        <v>0.2374</v>
+      </c>
+      <c r="S55" s="3">
+        <v>1</v>
       </c>
       <c r="T55">
-        <v>193</v>
-      </c>
-      <c r="U55" s="5">
-        <v>0.9415</v>
-      </c>
-      <c r="V55" s="5">
-        <v>0.95</v>
+        <v>0</v>
+      </c>
+      <c r="U55" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="B56">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C56">
         <v>81</v>
@@ -4255,53 +4260,53 @@
       <c r="E56" t="s">
         <v>27</v>
       </c>
-      <c r="F56">
-        <v>7407</v>
+      <c r="F56" t="s">
+        <v>30</v>
       </c>
       <c r="G56">
         <v>25</v>
       </c>
       <c r="H56">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I56">
-        <v>32181</v>
+        <v>7174</v>
       </c>
       <c r="J56">
-        <v>227</v>
+        <v>91</v>
       </c>
       <c r="K56">
-        <v>4284</v>
+        <v>26</v>
       </c>
       <c r="L56">
         <v>26</v>
       </c>
       <c r="M56">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O56" s="4">
-        <v>1.5393518518518519E-3</v>
+        <v>9.0277777777777774E-4</v>
       </c>
       <c r="P56" s="4">
-        <v>1.5740740740740741E-3</v>
+        <v>1.1111111111111111E-3</v>
       </c>
       <c r="Q56" s="5">
-        <v>7.1000000000000004E-3</v>
+        <v>1.2699999999999999E-2</v>
       </c>
       <c r="R56" s="5">
-        <v>18.87</v>
-      </c>
-      <c r="S56" s="5">
-        <v>6.1000000000000004E-3</v>
+        <v>0.28570000000000001</v>
+      </c>
+      <c r="S56" s="3">
+        <v>1</v>
       </c>
       <c r="T56">
-        <v>4237</v>
-      </c>
-      <c r="U56" s="5">
-        <v>0.99509999999999998</v>
+        <v>-18</v>
+      </c>
+      <c r="U56" t="s">
+        <v>25</v>
       </c>
       <c r="V56" s="5">
         <v>1</v>
@@ -4309,78 +4314,75 @@
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="B57">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C57">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D57">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>27</v>
-      </c>
-      <c r="F57">
-        <v>7407</v>
+        <v>26</v>
+      </c>
+      <c r="F57" t="s">
+        <v>30</v>
       </c>
       <c r="G57">
         <v>25</v>
       </c>
       <c r="H57">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I57">
-        <v>12598</v>
+        <v>7018</v>
       </c>
       <c r="J57">
-        <v>72</v>
+        <v>183</v>
       </c>
       <c r="K57">
-        <v>1575</v>
+        <v>44</v>
       </c>
       <c r="L57">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="M57">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="N57">
         <v>0</v>
       </c>
       <c r="O57" s="4">
-        <v>1.9560185185185184E-3</v>
+        <v>4.3981481481481481E-4</v>
       </c>
       <c r="P57" s="4">
-        <v>2.0833333333333335E-4</v>
+        <v>6.018518518518519E-4</v>
       </c>
       <c r="Q57" s="5">
-        <v>5.7000000000000002E-3</v>
+        <v>2.6100000000000002E-2</v>
       </c>
       <c r="R57" s="5">
-        <v>21.87</v>
-      </c>
-      <c r="S57" s="5">
-        <v>8.3000000000000001E-3</v>
+        <v>0.2404</v>
+      </c>
+      <c r="S57" s="3">
+        <v>1</v>
       </c>
       <c r="T57">
-        <v>1555</v>
-      </c>
-      <c r="U57" s="5">
-        <v>0.99550000000000005</v>
-      </c>
-      <c r="V57" s="5">
-        <v>1</v>
+        <v>-41</v>
+      </c>
+      <c r="U57" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="B58">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C58">
         <v>81</v>
@@ -4391,53 +4393,53 @@
       <c r="E58" t="s">
         <v>27</v>
       </c>
-      <c r="F58">
-        <v>7407</v>
+      <c r="F58" t="s">
+        <v>30</v>
       </c>
       <c r="G58">
         <v>25</v>
       </c>
       <c r="H58">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I58">
-        <v>19843</v>
+        <v>14655</v>
       </c>
       <c r="J58">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="K58">
-        <v>1634</v>
+        <v>33</v>
       </c>
       <c r="L58">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="M58">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O58" s="4">
-        <v>1.5625000000000001E-3</v>
+        <v>9.837962962962962E-4</v>
       </c>
       <c r="P58" s="4">
-        <v>9.3749999999999997E-4</v>
+        <v>1.5740740740740741E-3</v>
       </c>
       <c r="Q58" s="5">
-        <v>7.1000000000000004E-3</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="R58" s="5">
-        <v>11.67</v>
-      </c>
-      <c r="S58" s="5">
-        <v>9.7999999999999997E-3</v>
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="S58" s="3">
+        <v>1</v>
       </c>
       <c r="T58">
-        <v>1608</v>
-      </c>
-      <c r="U58" s="5">
-        <v>0.99380000000000002</v>
+        <v>-19</v>
+      </c>
+      <c r="U58" t="s">
+        <v>25</v>
       </c>
       <c r="V58" s="5">
         <v>1</v>
@@ -4445,22 +4447,22 @@
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="B59">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C59">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D59">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>27</v>
-      </c>
-      <c r="F59">
-        <v>7407</v>
+        <v>26</v>
+      </c>
+      <c r="F59" t="s">
+        <v>30</v>
       </c>
       <c r="G59">
         <v>25</v>
@@ -4469,54 +4471,51 @@
         <v>8</v>
       </c>
       <c r="I59">
-        <v>31658</v>
+        <v>5338</v>
       </c>
       <c r="J59">
-        <v>240</v>
+        <v>127</v>
       </c>
       <c r="K59">
-        <v>1300</v>
+        <v>34</v>
       </c>
       <c r="L59">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="M59">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="N59">
         <v>0</v>
       </c>
       <c r="O59" s="4">
-        <v>1.4930555555555556E-3</v>
+        <v>4.5138888888888887E-4</v>
       </c>
       <c r="P59" s="4">
-        <v>1.0648148148148149E-3</v>
+        <v>6.5972222222222224E-4</v>
       </c>
       <c r="Q59" s="5">
-        <v>7.6E-3</v>
+        <v>2.3800000000000002E-2</v>
       </c>
       <c r="R59" s="5">
-        <v>5.4160000000000004</v>
-      </c>
-      <c r="S59" s="5">
-        <v>4.3799999999999999E-2</v>
+        <v>0.26769999999999999</v>
+      </c>
+      <c r="S59" s="3">
+        <v>1</v>
       </c>
       <c r="T59">
-        <v>1227</v>
-      </c>
-      <c r="U59" s="5">
-        <v>0.98709999999999998</v>
-      </c>
-      <c r="V59" s="5">
-        <v>1</v>
+        <v>-25</v>
+      </c>
+      <c r="U59" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="B60">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C60">
         <v>81</v>
@@ -4527,132 +4526,129 @@
       <c r="E60" t="s">
         <v>27</v>
       </c>
-      <c r="F60">
-        <v>7407</v>
+      <c r="F60" t="s">
+        <v>30</v>
       </c>
       <c r="G60">
         <v>25</v>
       </c>
       <c r="H60">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I60">
-        <v>28922</v>
+        <v>16328</v>
       </c>
       <c r="J60">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="K60">
-        <v>1897</v>
+        <v>40</v>
       </c>
       <c r="L60">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="M60">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O60" s="4">
-        <v>2.3495370370370371E-3</v>
+        <v>9.7222222222222219E-4</v>
       </c>
       <c r="P60" s="4">
-        <v>1.5856481481481481E-3</v>
+        <v>1.2962962962962963E-3</v>
       </c>
       <c r="Q60" s="5">
-        <v>4.7999999999999996E-3</v>
+        <v>1.11E-2</v>
       </c>
       <c r="R60" s="5">
-        <v>13.64</v>
-      </c>
-      <c r="S60" s="5">
-        <v>1.6299999999999999E-2</v>
+        <v>0.221</v>
+      </c>
+      <c r="S60" s="3">
+        <v>1</v>
       </c>
       <c r="T60">
-        <v>1856</v>
-      </c>
-      <c r="U60" s="5">
-        <v>0.99460000000000004</v>
+        <v>-24</v>
+      </c>
+      <c r="U60" t="s">
+        <v>25</v>
       </c>
       <c r="V60" s="5">
-        <v>0.92310000000000003</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="B61">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C61">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D61">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>27</v>
-      </c>
-      <c r="F61">
-        <v>7407</v>
+        <v>26</v>
+      </c>
+      <c r="F61" t="s">
+        <v>30</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61">
-        <v>278</v>
+        <v>2369</v>
       </c>
       <c r="J61">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="K61">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="L61">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M61">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N61">
         <v>0</v>
       </c>
-      <c r="O61" t="s">
-        <v>24</v>
-      </c>
-      <c r="P61" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" t="s">
-        <v>25</v>
+      <c r="O61" s="4">
+        <v>4.9768518518518521E-4</v>
+      </c>
+      <c r="P61" s="4">
+        <v>7.291666666666667E-4</v>
+      </c>
+      <c r="Q61" s="5">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="R61" s="5">
+        <v>0.15379999999999999</v>
       </c>
       <c r="S61" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61">
-        <v>73</v>
-      </c>
-      <c r="U61" s="3">
-        <v>1</v>
-      </c>
-      <c r="V61" t="s">
+        <v>-3</v>
+      </c>
+      <c r="U61" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
-        <v>46185</v>
+        <v>46183</v>
       </c>
       <c r="B62">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C62">
         <v>81</v>
@@ -4663,53 +4659,53 @@
       <c r="E62" t="s">
         <v>27</v>
       </c>
-      <c r="F62">
-        <v>7442</v>
+      <c r="F62" t="s">
+        <v>30</v>
       </c>
       <c r="G62">
         <v>25</v>
       </c>
       <c r="H62">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I62">
-        <v>18853</v>
+        <v>17098</v>
       </c>
       <c r="J62">
-        <v>112</v>
+        <v>157</v>
       </c>
       <c r="K62">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="L62">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="M62">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="N62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O62" s="4">
-        <v>1.8634259259259259E-3</v>
+        <v>1.1805555555555556E-3</v>
       </c>
       <c r="P62" s="4">
-        <v>1.4467592592592592E-3</v>
+        <v>1.5625000000000001E-3</v>
       </c>
       <c r="Q62" s="5">
-        <v>5.8999999999999999E-3</v>
-      </c>
-      <c r="R62" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="S62" s="5">
-        <v>0.71430000000000005</v>
+        <v>9.1999999999999998E-3</v>
+      </c>
+      <c r="R62" s="5">
+        <v>0.24199999999999999</v>
+      </c>
+      <c r="S62" s="3">
+        <v>1</v>
       </c>
       <c r="T62">
-        <v>1</v>
-      </c>
-      <c r="U62" s="5">
-        <v>0.125</v>
+        <v>-17</v>
+      </c>
+      <c r="U62" t="s">
+        <v>25</v>
       </c>
       <c r="V62" s="5">
         <v>1</v>
@@ -4717,78 +4713,75 @@
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
-        <v>46185</v>
+        <v>46183</v>
       </c>
       <c r="B63">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C63">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D63">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>27</v>
-      </c>
-      <c r="F63">
-        <v>7442</v>
+        <v>26</v>
+      </c>
+      <c r="F63" t="s">
+        <v>30</v>
       </c>
       <c r="G63">
         <v>25</v>
       </c>
       <c r="H63">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I63">
-        <v>31100</v>
+        <v>2068</v>
       </c>
       <c r="J63">
-        <v>234</v>
+        <v>49</v>
       </c>
       <c r="K63">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="L63">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="M63">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N63">
         <v>0</v>
       </c>
       <c r="O63" s="4">
-        <v>1.4699074074074074E-3</v>
-      </c>
-      <c r="P63" s="4">
-        <v>6.7129629629629625E-4</v>
+        <v>4.5138888888888887E-4</v>
+      </c>
+      <c r="P63" t="s">
+        <v>24</v>
       </c>
       <c r="Q63" s="5">
-        <v>7.4999999999999997E-3</v>
+        <v>2.3699999999999999E-2</v>
       </c>
       <c r="R63" s="5">
-        <v>0.312</v>
-      </c>
-      <c r="S63" s="5">
-        <v>0.80820000000000003</v>
+        <v>0.26529999999999998</v>
+      </c>
+      <c r="S63" s="3">
+        <v>1</v>
       </c>
       <c r="T63">
         <v>0</v>
       </c>
-      <c r="U63" s="3">
-        <v>0</v>
-      </c>
-      <c r="V63" s="5">
-        <v>1</v>
+      <c r="U63" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
-        <v>46185</v>
+        <v>46183</v>
       </c>
       <c r="B64">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C64">
         <v>81</v>
@@ -4799,132 +4792,129 @@
       <c r="E64" t="s">
         <v>27</v>
       </c>
-      <c r="F64">
-        <v>7442</v>
+      <c r="F64" t="s">
+        <v>30</v>
       </c>
       <c r="G64">
         <v>25</v>
       </c>
       <c r="H64">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I64">
-        <v>29093</v>
+        <v>18676</v>
       </c>
       <c r="J64">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="K64">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="L64">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="M64">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="N64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64" s="4">
-        <v>2.3611111111111111E-3</v>
+        <v>1.2962962962962963E-3</v>
       </c>
       <c r="P64" s="4">
-        <v>1.2268518518518518E-3</v>
+        <v>1.0532407407407407E-3</v>
       </c>
       <c r="Q64" s="5">
-        <v>4.7000000000000002E-3</v>
+        <v>8.3999999999999995E-3</v>
       </c>
       <c r="R64" s="5">
-        <v>0.29709999999999998</v>
-      </c>
-      <c r="S64" s="5">
-        <v>0.70730000000000004</v>
+        <v>0.22289999999999999</v>
+      </c>
+      <c r="S64" s="3">
+        <v>1</v>
       </c>
       <c r="T64">
-        <v>0</v>
-      </c>
-      <c r="U64" s="3">
-        <v>0</v>
+        <v>-19</v>
+      </c>
+      <c r="U64" t="s">
+        <v>25</v>
       </c>
       <c r="V64" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
-        <v>46185</v>
+        <v>46183</v>
       </c>
       <c r="B65">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C65">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D65">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E65" t="s">
-        <v>27</v>
-      </c>
-      <c r="F65">
-        <v>7442</v>
+        <v>26</v>
+      </c>
+      <c r="F65" t="s">
+        <v>30</v>
       </c>
       <c r="G65">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H65">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I65">
-        <v>21877</v>
+        <v>922</v>
       </c>
       <c r="J65">
-        <v>107</v>
+        <v>16</v>
       </c>
       <c r="K65">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="L65">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="M65">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N65">
         <v>0</v>
       </c>
       <c r="O65" s="4">
-        <v>2.2916666666666667E-3</v>
-      </c>
-      <c r="P65" s="4">
-        <v>7.6388888888888893E-4</v>
+        <v>6.2500000000000001E-4</v>
+      </c>
+      <c r="P65" t="s">
+        <v>24</v>
       </c>
       <c r="Q65" s="5">
-        <v>4.8999999999999998E-3</v>
-      </c>
-      <c r="R65" s="5">
-        <v>0.28970000000000001</v>
-      </c>
-      <c r="S65" s="5">
-        <v>0.4839</v>
+        <v>1.7399999999999999E-2</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="S65" s="3">
+        <v>1</v>
       </c>
       <c r="T65">
         <v>0</v>
       </c>
-      <c r="U65" s="3">
-        <v>0</v>
-      </c>
-      <c r="V65" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="U65" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
-        <v>46185</v>
+        <v>46183</v>
       </c>
       <c r="B66">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C66">
         <v>81</v>
@@ -4935,8 +4925,8 @@
       <c r="E66" t="s">
         <v>27</v>
       </c>
-      <c r="F66">
-        <v>7442</v>
+      <c r="F66" t="s">
+        <v>30</v>
       </c>
       <c r="G66">
         <v>25</v>
@@ -4945,119 +4935,116 @@
         <v>5</v>
       </c>
       <c r="I66">
-        <v>14372</v>
+        <v>18370</v>
       </c>
       <c r="J66">
-        <v>85</v>
+        <v>182</v>
       </c>
       <c r="K66">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="L66">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="M66">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="N66">
         <v>0</v>
       </c>
       <c r="O66" s="4">
-        <v>1.9444444444444444E-3</v>
+        <v>1.1342592592592593E-3</v>
       </c>
       <c r="P66" s="4">
-        <v>1.4930555555555556E-3</v>
+        <v>1.1111111111111111E-3</v>
       </c>
       <c r="Q66" s="5">
-        <v>5.8999999999999999E-3</v>
+        <v>9.9000000000000008E-3</v>
       </c>
       <c r="R66" s="5">
-        <v>0.27060000000000001</v>
-      </c>
-      <c r="S66" s="5">
-        <v>0.69569999999999999</v>
+        <v>0.1593</v>
+      </c>
+      <c r="S66" s="3">
+        <v>1</v>
       </c>
       <c r="T66">
-        <v>0</v>
-      </c>
-      <c r="U66" s="3">
-        <v>0</v>
+        <v>-15</v>
+      </c>
+      <c r="U66" t="s">
+        <v>25</v>
       </c>
       <c r="V66" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.3">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
-        <v>46185</v>
+        <v>46183</v>
       </c>
       <c r="B67">
         <v>14</v>
       </c>
       <c r="C67">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D67">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>27</v>
-      </c>
-      <c r="F67">
-        <v>7442</v>
+        <v>26</v>
+      </c>
+      <c r="F67" t="s">
+        <v>30</v>
       </c>
       <c r="G67">
         <v>25</v>
       </c>
       <c r="H67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I67">
-        <v>16434</v>
+        <v>2302</v>
       </c>
       <c r="J67">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="K67">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L67">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="M67">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="N67">
         <v>0</v>
       </c>
       <c r="O67" s="4">
-        <v>1.4814814814814814E-3</v>
+        <v>2.7777777777777778E-4</v>
       </c>
       <c r="P67" s="4">
-        <v>8.1018518518518516E-4</v>
+        <v>8.4490740740740739E-4</v>
       </c>
       <c r="Q67" s="5">
-        <v>7.7000000000000002E-3</v>
+        <v>4.0800000000000003E-2</v>
       </c>
       <c r="R67" s="5">
-        <v>0.15079999999999999</v>
-      </c>
-      <c r="S67" s="5">
-        <v>0.73680000000000001</v>
+        <v>0.21279999999999999</v>
+      </c>
+      <c r="S67" s="3">
+        <v>1</v>
       </c>
       <c r="T67">
-        <v>0</v>
-      </c>
-      <c r="U67" s="3">
-        <v>0</v>
-      </c>
-      <c r="V67" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.3">
+        <v>-15</v>
+      </c>
+      <c r="U67" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
-        <v>46185</v>
+        <v>46183</v>
       </c>
       <c r="B68">
         <v>15</v>
@@ -5071,132 +5058,129 @@
       <c r="E68" t="s">
         <v>27</v>
       </c>
-      <c r="F68">
-        <v>7442</v>
+      <c r="F68" t="s">
+        <v>30</v>
       </c>
       <c r="G68">
         <v>25</v>
       </c>
       <c r="H68">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I68">
-        <v>16782</v>
+        <v>14762</v>
       </c>
       <c r="J68">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="K68">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="L68">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="M68">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O68" s="4">
-        <v>1.6666666666666668E-3</v>
+        <v>9.837962962962962E-4</v>
       </c>
       <c r="P68" s="4">
-        <v>1.8518518518518518E-4</v>
+        <v>1.4930555555555556E-3</v>
       </c>
       <c r="Q68" s="5">
-        <v>6.8999999999999999E-3</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="R68" s="5">
-        <v>0.16520000000000001</v>
-      </c>
-      <c r="S68" s="5">
-        <v>0.57889999999999997</v>
+        <v>0.1696</v>
+      </c>
+      <c r="S68" s="3">
+        <v>1</v>
       </c>
       <c r="T68">
-        <v>0</v>
-      </c>
-      <c r="U68" s="3">
-        <v>0</v>
+        <v>-18</v>
+      </c>
+      <c r="U68" t="s">
+        <v>25</v>
       </c>
       <c r="V68" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
-        <v>46185</v>
+        <v>46183</v>
       </c>
       <c r="B69">
+        <v>15</v>
+      </c>
+      <c r="C69">
+        <v>84</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69" t="s">
+        <v>26</v>
+      </c>
+      <c r="F69" t="s">
+        <v>30</v>
+      </c>
+      <c r="G69">
+        <v>25</v>
+      </c>
+      <c r="H69">
+        <v>4</v>
+      </c>
+      <c r="I69">
+        <v>5623</v>
+      </c>
+      <c r="J69">
+        <v>163</v>
+      </c>
+      <c r="K69">
+        <v>37</v>
+      </c>
+      <c r="L69">
+        <v>37</v>
+      </c>
+      <c r="M69">
+        <v>30</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69" s="4">
+        <v>3.9351851851851852E-4</v>
+      </c>
+      <c r="P69" s="4">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="Q69" s="5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="R69" s="5">
+        <v>0.22700000000000001</v>
+      </c>
+      <c r="S69" s="3">
+        <v>1</v>
+      </c>
+      <c r="T69">
+        <v>-30</v>
+      </c>
+      <c r="U69" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A70" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B70">
         <v>16</v>
-      </c>
-      <c r="C69">
-        <v>81</v>
-      </c>
-      <c r="D69">
-        <v>85</v>
-      </c>
-      <c r="E69" t="s">
-        <v>27</v>
-      </c>
-      <c r="F69">
-        <v>7442</v>
-      </c>
-      <c r="G69">
-        <v>25</v>
-      </c>
-      <c r="H69">
-        <v>5</v>
-      </c>
-      <c r="I69">
-        <v>15999</v>
-      </c>
-      <c r="J69">
-        <v>121</v>
-      </c>
-      <c r="K69">
-        <v>17</v>
-      </c>
-      <c r="L69">
-        <v>11</v>
-      </c>
-      <c r="M69">
-        <v>6</v>
-      </c>
-      <c r="N69">
-        <v>0</v>
-      </c>
-      <c r="O69" s="4">
-        <v>1.4930555555555556E-3</v>
-      </c>
-      <c r="P69" s="4">
-        <v>3.8194444444444446E-4</v>
-      </c>
-      <c r="Q69" s="5">
-        <v>7.6E-3</v>
-      </c>
-      <c r="R69" s="5">
-        <v>0.14050000000000001</v>
-      </c>
-      <c r="S69" s="5">
-        <v>0.64710000000000001</v>
-      </c>
-      <c r="T69">
-        <v>0</v>
-      </c>
-      <c r="U69" s="3">
-        <v>0</v>
-      </c>
-      <c r="V69" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A70" s="2">
-        <v>46185</v>
-      </c>
-      <c r="B70">
-        <v>17</v>
       </c>
       <c r="C70">
         <v>81</v>
@@ -5207,132 +5191,129 @@
       <c r="E70" t="s">
         <v>27</v>
       </c>
-      <c r="F70">
-        <v>7442</v>
+      <c r="F70" t="s">
+        <v>30</v>
       </c>
       <c r="G70">
         <v>25</v>
       </c>
       <c r="H70">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I70">
-        <v>22243</v>
+        <v>16376</v>
       </c>
       <c r="J70">
-        <v>197</v>
+        <v>157</v>
       </c>
       <c r="K70">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="L70">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="M70">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N70">
         <v>0</v>
       </c>
       <c r="O70" s="4">
-        <v>1.2847222222222223E-3</v>
+        <v>1.1921296296296296E-3</v>
       </c>
       <c r="P70" s="4">
-        <v>1.0995370370370371E-3</v>
+        <v>3.2407407407407406E-4</v>
       </c>
       <c r="Q70" s="5">
-        <v>8.8999999999999999E-3</v>
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="R70" s="5">
-        <v>0.2944</v>
-      </c>
-      <c r="S70" s="5">
-        <v>0.8276</v>
+        <v>0.2611</v>
+      </c>
+      <c r="S70" s="3">
+        <v>1</v>
       </c>
       <c r="T70">
-        <v>0</v>
-      </c>
-      <c r="U70" s="3">
-        <v>0</v>
+        <v>-11</v>
+      </c>
+      <c r="U70" t="s">
+        <v>25</v>
       </c>
       <c r="V70" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
-        <v>46185</v>
+        <v>46183</v>
       </c>
       <c r="B71">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C71">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D71">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E71" t="s">
-        <v>27</v>
-      </c>
-      <c r="F71">
-        <v>7442</v>
+        <v>26</v>
+      </c>
+      <c r="F71" t="s">
+        <v>30</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I71">
-        <v>94</v>
+        <v>8943</v>
       </c>
       <c r="J71">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="K71">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="L71">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M71">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="N71">
         <v>0</v>
       </c>
-      <c r="O71" t="s">
-        <v>24</v>
-      </c>
-      <c r="P71" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q71" s="3">
-        <v>0</v>
-      </c>
-      <c r="R71" t="s">
-        <v>25</v>
-      </c>
-      <c r="S71" t="s">
-        <v>25</v>
+      <c r="O71" s="4">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="P71" s="4">
+        <v>4.5138888888888887E-4</v>
+      </c>
+      <c r="Q71" s="5">
+        <v>2.8299999999999999E-2</v>
+      </c>
+      <c r="R71" s="5">
+        <v>0.25690000000000002</v>
+      </c>
+      <c r="S71" s="3">
+        <v>1</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="U71" t="s">
         <v>25</v>
       </c>
-      <c r="V71" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
-        <v>46188</v>
+        <v>46183</v>
       </c>
       <c r="B72">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C72">
         <v>81</v>
@@ -5343,138 +5324,129 @@
       <c r="E72" t="s">
         <v>27</v>
       </c>
-      <c r="F72">
-        <v>8976</v>
+      <c r="F72" t="s">
+        <v>30</v>
       </c>
       <c r="G72">
         <v>25</v>
       </c>
       <c r="H72">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I72">
-        <v>11497</v>
+        <v>17306</v>
       </c>
       <c r="J72">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="K72">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="L72">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="M72">
+        <v>11</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72" s="4">
+        <v>1.7013888888888888E-3</v>
+      </c>
+      <c r="P72" s="4">
+        <v>7.291666666666667E-4</v>
+      </c>
+      <c r="Q72" s="5">
+        <v>6.7999999999999996E-3</v>
+      </c>
+      <c r="R72" s="5">
+        <v>0.23930000000000001</v>
+      </c>
+      <c r="S72" s="3">
+        <v>1</v>
+      </c>
+      <c r="T72">
+        <v>-11</v>
+      </c>
+      <c r="U72" t="s">
+        <v>25</v>
+      </c>
+      <c r="V72" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A73" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B73">
+        <v>17</v>
+      </c>
+      <c r="C73">
+        <v>84</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73" t="s">
+        <v>26</v>
+      </c>
+      <c r="F73" t="s">
+        <v>30</v>
+      </c>
+      <c r="G73">
+        <v>25</v>
+      </c>
+      <c r="H73">
+        <v>2</v>
+      </c>
+      <c r="I73">
+        <v>6585</v>
+      </c>
+      <c r="J73">
+        <v>159</v>
+      </c>
+      <c r="K73">
+        <v>39</v>
+      </c>
+      <c r="L73">
+        <v>39</v>
+      </c>
+      <c r="M73">
         <v>13</v>
       </c>
-      <c r="N72">
-        <v>0</v>
-      </c>
-      <c r="O72" s="4">
-        <v>9.9537037037037042E-4</v>
-      </c>
-      <c r="P72" s="4">
-        <v>2.3379629629629631E-3</v>
-      </c>
-      <c r="Q72" s="5">
-        <v>1.15E-2</v>
-      </c>
-      <c r="R72" s="5">
-        <v>0.38640000000000002</v>
-      </c>
-      <c r="S72" s="5">
-        <v>0.74509999999999998</v>
-      </c>
-      <c r="T72">
-        <v>0</v>
-      </c>
-      <c r="U72" s="3">
-        <v>0</v>
-      </c>
-      <c r="V72" s="5">
-        <v>1</v>
-      </c>
-      <c r="W72">
-        <v>3.6659999999999999</v>
-      </c>
-    </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A73" s="2">
-        <v>46188</v>
-      </c>
-      <c r="B73">
-        <v>11</v>
-      </c>
-      <c r="C73">
-        <v>81</v>
-      </c>
-      <c r="D73">
-        <v>85</v>
-      </c>
-      <c r="E73" t="s">
-        <v>27</v>
-      </c>
-      <c r="F73">
-        <v>8976</v>
-      </c>
-      <c r="G73">
-        <v>25</v>
-      </c>
-      <c r="H73">
-        <v>8</v>
-      </c>
-      <c r="I73">
-        <v>30692</v>
-      </c>
-      <c r="J73">
-        <v>259</v>
-      </c>
-      <c r="K73">
-        <v>83</v>
-      </c>
-      <c r="L73">
-        <v>51</v>
-      </c>
-      <c r="M73">
-        <v>30</v>
-      </c>
       <c r="N73">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O73" s="4">
-        <v>1.3541666666666667E-3</v>
+        <v>4.7453703703703704E-4</v>
       </c>
       <c r="P73" s="4">
-        <v>1.8055555555555555E-3</v>
+        <v>6.134259259259259E-4</v>
       </c>
       <c r="Q73" s="5">
-        <v>8.3999999999999995E-3</v>
+        <v>2.41E-2</v>
       </c>
       <c r="R73" s="5">
-        <v>0.32050000000000001</v>
-      </c>
-      <c r="S73" s="5">
-        <v>0.61450000000000005</v>
+        <v>0.24529999999999999</v>
+      </c>
+      <c r="S73" s="3">
+        <v>1</v>
       </c>
       <c r="T73">
-        <v>2</v>
-      </c>
-      <c r="U73" s="5">
-        <v>6.25E-2</v>
-      </c>
-      <c r="V73" s="5">
-        <v>0.9677</v>
-      </c>
-      <c r="W73">
-        <v>34.128</v>
-      </c>
-    </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.3">
+        <v>-13</v>
+      </c>
+      <c r="U73" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
-        <v>46188</v>
+        <v>46183</v>
       </c>
       <c r="B74">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C74">
         <v>81</v>
@@ -5485,97 +5457,94 @@
       <c r="E74" t="s">
         <v>27</v>
       </c>
-      <c r="F74">
-        <v>8976</v>
+      <c r="F74" t="s">
+        <v>30</v>
       </c>
       <c r="G74">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I74">
-        <v>33207</v>
+        <v>133</v>
       </c>
       <c r="J74">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="K74">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="L74">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N74">
         <v>0</v>
       </c>
-      <c r="O74" s="4">
-        <v>1.5856481481481481E-3</v>
-      </c>
-      <c r="P74" s="4">
-        <v>2.8935185185185184E-4</v>
-      </c>
-      <c r="Q74" s="5">
-        <v>7.1999999999999998E-3</v>
-      </c>
-      <c r="R74" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="S74" s="5">
-        <v>0.98329999999999995</v>
+      <c r="O74" t="s">
+        <v>24</v>
+      </c>
+      <c r="P74" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" t="s">
+        <v>25</v>
+      </c>
+      <c r="S74" t="s">
+        <v>25</v>
       </c>
       <c r="T74">
         <v>0</v>
       </c>
-      <c r="U74" s="3">
-        <v>0</v>
-      </c>
-      <c r="V74" s="5">
-        <v>1</v>
-      </c>
-      <c r="W74">
-        <v>22.643999999999998</v>
-      </c>
-    </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="U74" t="s">
+        <v>25</v>
+      </c>
+      <c r="V74" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="75" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
-        <v>46188</v>
+        <v>46183</v>
       </c>
       <c r="B75">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C75">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D75">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>27</v>
-      </c>
-      <c r="F75">
-        <v>8976</v>
+        <v>26</v>
+      </c>
+      <c r="F75" t="s">
+        <v>30</v>
       </c>
       <c r="G75">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="H75">
         <v>0</v>
       </c>
       <c r="I75">
-        <v>23624</v>
+        <v>32</v>
       </c>
       <c r="J75">
-        <v>220</v>
+        <v>1</v>
       </c>
       <c r="K75">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L75">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="M75">
         <v>0</v>
@@ -5584,19 +5553,19 @@
         <v>0</v>
       </c>
       <c r="O75" s="4">
-        <v>1.2268518518518518E-3</v>
+        <v>3.7037037037037035E-4</v>
       </c>
       <c r="P75" t="s">
         <v>24</v>
       </c>
       <c r="Q75" s="5">
-        <v>9.2999999999999992E-3</v>
-      </c>
-      <c r="R75" s="5">
-        <v>0.15909999999999999</v>
-      </c>
-      <c r="S75" s="3">
-        <v>1</v>
+        <v>3.1300000000000001E-2</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" t="s">
+        <v>25</v>
       </c>
       <c r="T75">
         <v>0</v>
@@ -5604,19 +5573,13 @@
       <c r="U75" t="s">
         <v>25</v>
       </c>
-      <c r="V75" t="s">
-        <v>25</v>
-      </c>
-      <c r="W75">
-        <v>26.43</v>
-      </c>
-    </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
-        <v>46188</v>
+        <v>46184</v>
       </c>
       <c r="B76">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C76">
         <v>81</v>
@@ -5627,8 +5590,8 @@
       <c r="E76" t="s">
         <v>27</v>
       </c>
-      <c r="F76">
-        <v>8976</v>
+      <c r="F76" t="s">
+        <v>30</v>
       </c>
       <c r="G76">
         <v>25</v>
@@ -5637,16 +5600,16 @@
         <v>0</v>
       </c>
       <c r="I76">
-        <v>22591</v>
+        <v>17156</v>
       </c>
       <c r="J76">
-        <v>239</v>
+        <v>138</v>
       </c>
       <c r="K76">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L76">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M76">
         <v>0</v>
@@ -5655,16 +5618,16 @@
         <v>0</v>
       </c>
       <c r="O76" s="4">
-        <v>1.0763888888888889E-3</v>
+        <v>1.4236111111111112E-3</v>
       </c>
       <c r="P76" t="s">
         <v>24</v>
       </c>
       <c r="Q76" s="5">
-        <v>1.06E-2</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="R76" s="5">
-        <v>0.1172</v>
+        <v>0.21010000000000001</v>
       </c>
       <c r="S76" s="3">
         <v>1</v>
@@ -5678,28 +5641,25 @@
       <c r="V76" t="s">
         <v>25</v>
       </c>
-      <c r="W76">
-        <v>24.654</v>
-      </c>
-    </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
-        <v>46188</v>
+        <v>46184</v>
       </c>
       <c r="B77">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C77">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D77">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>27</v>
-      </c>
-      <c r="F77">
-        <v>8976</v>
+        <v>26</v>
+      </c>
+      <c r="F77" t="s">
+        <v>30</v>
       </c>
       <c r="G77">
         <v>25</v>
@@ -5708,16 +5668,16 @@
         <v>0</v>
       </c>
       <c r="I77">
-        <v>21702</v>
+        <v>7848</v>
       </c>
       <c r="J77">
-        <v>216</v>
+        <v>143</v>
       </c>
       <c r="K77">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="L77">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="M77">
         <v>0</v>
@@ -5726,16 +5686,16 @@
         <v>0</v>
       </c>
       <c r="O77" s="4">
-        <v>1.1458333333333333E-3</v>
+        <v>6.2500000000000001E-4</v>
       </c>
       <c r="P77" t="s">
         <v>24</v>
       </c>
-      <c r="Q77" s="3">
-        <v>0.01</v>
+      <c r="Q77" s="5">
+        <v>1.8200000000000001E-2</v>
       </c>
       <c r="R77" s="5">
-        <v>0.2361</v>
+        <v>0.20280000000000001</v>
       </c>
       <c r="S77" s="3">
         <v>1</v>
@@ -5746,19 +5706,13 @@
       <c r="U77" t="s">
         <v>25</v>
       </c>
-      <c r="V77" t="s">
-        <v>25</v>
-      </c>
-      <c r="W77">
-        <v>36.558</v>
-      </c>
-    </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
-        <v>46188</v>
+        <v>46184</v>
       </c>
       <c r="B78">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C78">
         <v>81</v>
@@ -5769,138 +5723,129 @@
       <c r="E78" t="s">
         <v>27</v>
       </c>
-      <c r="F78">
-        <v>8976</v>
+      <c r="F78" t="s">
+        <v>30</v>
       </c>
       <c r="G78">
         <v>25</v>
       </c>
       <c r="H78">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I78">
-        <v>46702</v>
+        <v>17669</v>
       </c>
       <c r="J78">
-        <v>487</v>
+        <v>163</v>
       </c>
       <c r="K78">
-        <v>145</v>
+        <v>48</v>
       </c>
       <c r="L78">
-        <v>145</v>
+        <v>48</v>
       </c>
       <c r="M78">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O78" s="4">
-        <v>1.0995370370370371E-3</v>
-      </c>
-      <c r="P78" t="s">
-        <v>24</v>
+        <v>1.2268518518518518E-3</v>
+      </c>
+      <c r="P78" s="4">
+        <v>1.5740740740740741E-3</v>
       </c>
       <c r="Q78" s="5">
-        <v>1.04E-2</v>
+        <v>9.1999999999999998E-3</v>
       </c>
       <c r="R78" s="5">
-        <v>0.29770000000000002</v>
+        <v>0.29449999999999998</v>
       </c>
       <c r="S78" s="3">
         <v>1</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="U78" t="s">
         <v>25</v>
       </c>
-      <c r="V78" t="s">
-        <v>25</v>
-      </c>
-      <c r="W78">
-        <v>50.658000000000001</v>
-      </c>
-    </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="V78" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
-        <v>46188</v>
+        <v>46184</v>
       </c>
       <c r="B79">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C79">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D79">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E79" t="s">
-        <v>27</v>
-      </c>
-      <c r="F79">
-        <v>8976</v>
+        <v>26</v>
+      </c>
+      <c r="F79" t="s">
+        <v>30</v>
       </c>
       <c r="G79">
         <v>25</v>
       </c>
       <c r="H79">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I79">
-        <v>31351</v>
+        <v>6190</v>
       </c>
       <c r="J79">
-        <v>262</v>
+        <v>93</v>
       </c>
       <c r="K79">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="L79">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="M79">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="N79">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O79" s="4">
-        <v>1.3773148148148147E-3</v>
+        <v>7.5231481481481482E-4</v>
       </c>
       <c r="P79" s="4">
-        <v>1.7013888888888888E-3</v>
+        <v>2.7777777777777778E-4</v>
       </c>
       <c r="Q79" s="5">
-        <v>8.3999999999999995E-3</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="R79" s="5">
-        <v>0.30149999999999999</v>
-      </c>
-      <c r="S79" s="5">
-        <v>0.46839999999999998</v>
+        <v>0.3226</v>
+      </c>
+      <c r="S79" s="3">
+        <v>1</v>
       </c>
       <c r="T79">
-        <v>13</v>
-      </c>
-      <c r="U79" s="5">
-        <v>0.3095</v>
-      </c>
-      <c r="V79" s="5">
-        <v>0.78569999999999995</v>
-      </c>
-      <c r="W79">
-        <v>22.295999999999999</v>
-      </c>
-    </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
+        <v>-14</v>
+      </c>
+      <c r="U79" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
-        <v>46188</v>
+        <v>46184</v>
       </c>
       <c r="B80">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C80">
         <v>81</v>
@@ -5911,52 +5856,2107 @@
       <c r="E80" t="s">
         <v>27</v>
       </c>
-      <c r="F80">
-        <v>8976</v>
+      <c r="F80" t="s">
+        <v>30</v>
       </c>
       <c r="G80">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H80">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I80">
+        <v>21673</v>
+      </c>
+      <c r="J80">
+        <v>165</v>
+      </c>
+      <c r="K80">
+        <v>48</v>
+      </c>
+      <c r="L80">
+        <v>48</v>
+      </c>
+      <c r="M80">
+        <v>25</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80" s="4">
+        <v>1.4699074074074074E-3</v>
+      </c>
+      <c r="P80" s="4">
+        <v>1.1921296296296296E-3</v>
+      </c>
+      <c r="Q80" s="5">
+        <v>7.6E-3</v>
+      </c>
+      <c r="R80" s="5">
+        <v>0.29089999999999999</v>
+      </c>
+      <c r="S80" s="3">
+        <v>1</v>
+      </c>
+      <c r="T80">
+        <v>-25</v>
+      </c>
+      <c r="U80" t="s">
+        <v>25</v>
+      </c>
+      <c r="V80" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A81" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B81">
+        <v>10</v>
+      </c>
+      <c r="C81">
+        <v>84</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+      <c r="E81" t="s">
+        <v>26</v>
+      </c>
+      <c r="F81" t="s">
+        <v>30</v>
+      </c>
+      <c r="G81">
+        <v>25</v>
+      </c>
+      <c r="H81">
+        <v>3</v>
+      </c>
+      <c r="I81">
+        <v>2538</v>
+      </c>
+      <c r="J81">
+        <v>75</v>
+      </c>
+      <c r="K81">
+        <v>15</v>
+      </c>
+      <c r="L81">
+        <v>15</v>
+      </c>
+      <c r="M81">
+        <v>8</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81" s="4">
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="P81" s="4">
+        <v>4.861111111111111E-4</v>
+      </c>
+      <c r="Q81" s="5">
+        <v>2.9600000000000001E-2</v>
+      </c>
+      <c r="R81" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="S81" s="3">
+        <v>1</v>
+      </c>
+      <c r="T81">
+        <v>-8</v>
+      </c>
+      <c r="U81" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="82" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A82" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B82">
+        <v>11</v>
+      </c>
+      <c r="C82">
+        <v>81</v>
+      </c>
+      <c r="D82">
+        <v>85</v>
+      </c>
+      <c r="E82" t="s">
+        <v>27</v>
+      </c>
+      <c r="F82" t="s">
+        <v>30</v>
+      </c>
+      <c r="G82">
+        <v>25</v>
+      </c>
+      <c r="H82">
+        <v>8</v>
+      </c>
+      <c r="I82">
+        <v>17931</v>
+      </c>
+      <c r="J82">
+        <v>141</v>
+      </c>
+      <c r="K82">
+        <v>40</v>
+      </c>
+      <c r="L82">
+        <v>40</v>
+      </c>
+      <c r="M82">
+        <v>15</v>
+      </c>
+      <c r="N82">
+        <v>1</v>
+      </c>
+      <c r="O82" s="4">
+        <v>1.4120370370370369E-3</v>
+      </c>
+      <c r="P82" s="4">
+        <v>1.4120370370370369E-3</v>
+      </c>
+      <c r="Q82" s="5">
+        <v>7.9000000000000008E-3</v>
+      </c>
+      <c r="R82" s="5">
+        <v>0.28370000000000001</v>
+      </c>
+      <c r="S82" s="3">
+        <v>1</v>
+      </c>
+      <c r="T82">
+        <v>-15</v>
+      </c>
+      <c r="U82" t="s">
+        <v>25</v>
+      </c>
+      <c r="V82" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A83" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B83">
+        <v>11</v>
+      </c>
+      <c r="C83">
+        <v>84</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+      <c r="E83" t="s">
+        <v>26</v>
+      </c>
+      <c r="F83" t="s">
+        <v>30</v>
+      </c>
+      <c r="G83">
+        <v>25</v>
+      </c>
+      <c r="H83">
+        <v>3</v>
+      </c>
+      <c r="I83">
+        <v>2818</v>
+      </c>
+      <c r="J83">
+        <v>119</v>
+      </c>
+      <c r="K83">
+        <v>25</v>
+      </c>
+      <c r="L83">
+        <v>25</v>
+      </c>
+      <c r="M83">
+        <v>17</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83" s="4">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="P83" s="4">
+        <v>1.5162037037037036E-3</v>
+      </c>
+      <c r="Q83" s="5">
+        <v>4.2200000000000001E-2</v>
+      </c>
+      <c r="R83" s="5">
+        <v>0.21010000000000001</v>
+      </c>
+      <c r="S83" s="3">
+        <v>1</v>
+      </c>
+      <c r="T83">
+        <v>-17</v>
+      </c>
+      <c r="U83" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A84" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B84">
+        <v>12</v>
+      </c>
+      <c r="C84">
+        <v>81</v>
+      </c>
+      <c r="D84">
+        <v>85</v>
+      </c>
+      <c r="E84" t="s">
+        <v>27</v>
+      </c>
+      <c r="F84" t="s">
+        <v>30</v>
+      </c>
+      <c r="G84">
+        <v>25</v>
+      </c>
+      <c r="H84">
+        <v>8</v>
+      </c>
+      <c r="I84">
+        <v>31421</v>
+      </c>
+      <c r="J84">
+        <v>209</v>
+      </c>
+      <c r="K84">
+        <v>39</v>
+      </c>
+      <c r="L84">
+        <v>39</v>
+      </c>
+      <c r="M84">
+        <v>16</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84" s="4">
+        <v>1.6666666666666668E-3</v>
+      </c>
+      <c r="P84" s="4">
+        <v>1.2152777777777778E-3</v>
+      </c>
+      <c r="Q84" s="5">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="R84" s="5">
+        <v>0.18659999999999999</v>
+      </c>
+      <c r="S84" s="3">
+        <v>1</v>
+      </c>
+      <c r="T84">
+        <v>-16</v>
+      </c>
+      <c r="U84" t="s">
+        <v>25</v>
+      </c>
+      <c r="V84" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A85" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B85">
+        <v>12</v>
+      </c>
+      <c r="C85">
+        <v>84</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="E85" t="s">
+        <v>26</v>
+      </c>
+      <c r="F85" t="s">
+        <v>30</v>
+      </c>
+      <c r="G85">
+        <v>25</v>
+      </c>
+      <c r="H85">
+        <v>3</v>
+      </c>
+      <c r="I85">
+        <v>1295</v>
+      </c>
+      <c r="J85">
+        <v>51</v>
+      </c>
+      <c r="K85">
+        <v>20</v>
+      </c>
+      <c r="L85">
+        <v>20</v>
+      </c>
+      <c r="M85">
+        <v>12</v>
+      </c>
+      <c r="N85">
+        <v>0</v>
+      </c>
+      <c r="O85" s="4">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="P85" s="4">
+        <v>7.8703703703703705E-4</v>
+      </c>
+      <c r="Q85" s="5">
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="R85" s="5">
+        <v>0.39219999999999999</v>
+      </c>
+      <c r="S85" s="3">
+        <v>1</v>
+      </c>
+      <c r="T85">
+        <v>-12</v>
+      </c>
+      <c r="U85" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A86" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B86">
+        <v>13</v>
+      </c>
+      <c r="C86">
+        <v>81</v>
+      </c>
+      <c r="D86">
+        <v>85</v>
+      </c>
+      <c r="E86" t="s">
+        <v>27</v>
+      </c>
+      <c r="F86" t="s">
+        <v>30</v>
+      </c>
+      <c r="G86">
+        <v>25</v>
+      </c>
+      <c r="H86">
+        <v>6</v>
+      </c>
+      <c r="I86">
+        <v>32181</v>
+      </c>
+      <c r="J86">
+        <v>227</v>
+      </c>
+      <c r="K86">
+        <v>44</v>
+      </c>
+      <c r="L86">
+        <v>44</v>
+      </c>
+      <c r="M86">
+        <v>21</v>
+      </c>
+      <c r="N86">
+        <v>0</v>
+      </c>
+      <c r="O86" s="4">
+        <v>1.5393518518518519E-3</v>
+      </c>
+      <c r="P86" s="4">
+        <v>1.5740740740740741E-3</v>
+      </c>
+      <c r="Q86" s="5">
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="R86" s="5">
+        <v>0.1938</v>
+      </c>
+      <c r="S86" s="3">
+        <v>1</v>
+      </c>
+      <c r="T86">
+        <v>-21</v>
+      </c>
+      <c r="U86" t="s">
+        <v>25</v>
+      </c>
+      <c r="V86" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A87" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B87">
+        <v>14</v>
+      </c>
+      <c r="C87">
+        <v>81</v>
+      </c>
+      <c r="D87">
+        <v>85</v>
+      </c>
+      <c r="E87" t="s">
+        <v>27</v>
+      </c>
+      <c r="F87" t="s">
+        <v>30</v>
+      </c>
+      <c r="G87">
+        <v>25</v>
+      </c>
+      <c r="H87">
+        <v>6</v>
+      </c>
+      <c r="I87">
+        <v>12598</v>
+      </c>
+      <c r="J87">
+        <v>72</v>
+      </c>
+      <c r="K87">
+        <v>18</v>
+      </c>
+      <c r="L87">
+        <v>18</v>
+      </c>
+      <c r="M87">
+        <v>7</v>
+      </c>
+      <c r="N87">
+        <v>0</v>
+      </c>
+      <c r="O87" s="4">
+        <v>1.9560185185185184E-3</v>
+      </c>
+      <c r="P87" s="4">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="Q87" s="5">
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="S87" s="3">
+        <v>1</v>
+      </c>
+      <c r="T87">
+        <v>-7</v>
+      </c>
+      <c r="U87" t="s">
+        <v>25</v>
+      </c>
+      <c r="V87" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A88" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B88">
+        <v>15</v>
+      </c>
+      <c r="C88">
+        <v>81</v>
+      </c>
+      <c r="D88">
+        <v>85</v>
+      </c>
+      <c r="E88" t="s">
+        <v>27</v>
+      </c>
+      <c r="F88" t="s">
+        <v>30</v>
+      </c>
+      <c r="G88">
+        <v>25</v>
+      </c>
+      <c r="H88">
+        <v>6</v>
+      </c>
+      <c r="I88">
+        <v>19843</v>
+      </c>
+      <c r="J88">
+        <v>140</v>
+      </c>
+      <c r="K88">
+        <v>25</v>
+      </c>
+      <c r="L88">
+        <v>25</v>
+      </c>
+      <c r="M88">
+        <v>10</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+      <c r="O88" s="4">
+        <v>1.5625000000000001E-3</v>
+      </c>
+      <c r="P88" s="4">
+        <v>9.3749999999999997E-4</v>
+      </c>
+      <c r="Q88" s="5">
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="R88" s="5">
+        <v>0.17860000000000001</v>
+      </c>
+      <c r="S88" s="3">
+        <v>1</v>
+      </c>
+      <c r="T88">
+        <v>-10</v>
+      </c>
+      <c r="U88" t="s">
+        <v>25</v>
+      </c>
+      <c r="V88" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A89" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B89">
+        <v>16</v>
+      </c>
+      <c r="C89">
+        <v>81</v>
+      </c>
+      <c r="D89">
+        <v>85</v>
+      </c>
+      <c r="E89" t="s">
+        <v>27</v>
+      </c>
+      <c r="F89" t="s">
+        <v>30</v>
+      </c>
+      <c r="G89">
+        <v>25</v>
+      </c>
+      <c r="H89">
+        <v>8</v>
+      </c>
+      <c r="I89">
+        <v>31658</v>
+      </c>
+      <c r="J89">
+        <v>240</v>
+      </c>
+      <c r="K89">
+        <v>72</v>
+      </c>
+      <c r="L89">
+        <v>72</v>
+      </c>
+      <c r="M89">
+        <v>16</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89" s="4">
+        <v>1.4930555555555556E-3</v>
+      </c>
+      <c r="P89" s="4">
+        <v>1.0648148148148149E-3</v>
+      </c>
+      <c r="Q89" s="5">
+        <v>7.6E-3</v>
+      </c>
+      <c r="R89" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="S89" s="3">
+        <v>1</v>
+      </c>
+      <c r="T89">
+        <v>-16</v>
+      </c>
+      <c r="U89" t="s">
+        <v>25</v>
+      </c>
+      <c r="V89" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A90" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B90">
+        <v>17</v>
+      </c>
+      <c r="C90">
+        <v>81</v>
+      </c>
+      <c r="D90">
+        <v>85</v>
+      </c>
+      <c r="E90" t="s">
+        <v>27</v>
+      </c>
+      <c r="F90" t="s">
+        <v>30</v>
+      </c>
+      <c r="G90">
+        <v>25</v>
+      </c>
+      <c r="H90">
+        <v>5</v>
+      </c>
+      <c r="I90">
+        <v>28923</v>
+      </c>
+      <c r="J90">
+        <v>140</v>
+      </c>
+      <c r="K90">
+        <v>41</v>
+      </c>
+      <c r="L90">
+        <v>41</v>
+      </c>
+      <c r="M90">
+        <v>10</v>
+      </c>
+      <c r="N90">
+        <v>0</v>
+      </c>
+      <c r="O90" s="4">
+        <v>2.3379629629629631E-3</v>
+      </c>
+      <c r="P90" s="4">
+        <v>1.5856481481481481E-3</v>
+      </c>
+      <c r="Q90" s="5">
+        <v>4.7999999999999996E-3</v>
+      </c>
+      <c r="R90" s="5">
+        <v>0.29289999999999999</v>
+      </c>
+      <c r="S90" s="3">
+        <v>1</v>
+      </c>
+      <c r="T90">
+        <v>-10</v>
+      </c>
+      <c r="U90" t="s">
+        <v>25</v>
+      </c>
+      <c r="V90" s="5">
+        <v>0.92310000000000003</v>
+      </c>
+    </row>
+    <row r="91" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A91" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B91">
+        <v>18</v>
+      </c>
+      <c r="C91">
+        <v>81</v>
+      </c>
+      <c r="D91">
+        <v>85</v>
+      </c>
+      <c r="E91" t="s">
+        <v>27</v>
+      </c>
+      <c r="F91" t="s">
+        <v>30</v>
+      </c>
+      <c r="G91">
+        <v>2</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91">
+        <v>285</v>
+      </c>
+      <c r="J91">
+        <v>2</v>
+      </c>
+      <c r="K91">
+        <v>0</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>0</v>
+      </c>
+      <c r="O91" s="4">
+        <v>1.6435185185185185E-3</v>
+      </c>
+      <c r="P91" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q91" s="5">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" t="s">
+        <v>25</v>
+      </c>
+      <c r="T91">
+        <v>0</v>
+      </c>
+      <c r="U91" t="s">
+        <v>25</v>
+      </c>
+      <c r="V91" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="92" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A92" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B92">
+        <v>9</v>
+      </c>
+      <c r="C92">
+        <v>81</v>
+      </c>
+      <c r="D92">
+        <v>85</v>
+      </c>
+      <c r="E92" t="s">
+        <v>27</v>
+      </c>
+      <c r="F92" t="s">
+        <v>30</v>
+      </c>
+      <c r="G92">
+        <v>25</v>
+      </c>
+      <c r="H92">
+        <v>5</v>
+      </c>
+      <c r="I92">
+        <v>18853</v>
+      </c>
+      <c r="J92">
+        <v>112</v>
+      </c>
+      <c r="K92">
+        <v>28</v>
+      </c>
+      <c r="L92">
+        <v>28</v>
+      </c>
+      <c r="M92">
+        <v>7</v>
+      </c>
+      <c r="N92">
+        <v>1</v>
+      </c>
+      <c r="O92" s="4">
+        <v>1.8634259259259259E-3</v>
+      </c>
+      <c r="P92" s="4">
+        <v>1.4467592592592592E-3</v>
+      </c>
+      <c r="Q92" s="5">
+        <v>5.8999999999999999E-3</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="S92" s="3">
+        <v>1</v>
+      </c>
+      <c r="T92">
+        <v>-7</v>
+      </c>
+      <c r="U92" t="s">
+        <v>25</v>
+      </c>
+      <c r="V92" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A93" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B93">
+        <v>10</v>
+      </c>
+      <c r="C93">
+        <v>81</v>
+      </c>
+      <c r="D93">
+        <v>85</v>
+      </c>
+      <c r="E93" t="s">
+        <v>27</v>
+      </c>
+      <c r="F93" t="s">
+        <v>30</v>
+      </c>
+      <c r="G93">
+        <v>25</v>
+      </c>
+      <c r="H93">
+        <v>5</v>
+      </c>
+      <c r="I93">
+        <v>31100</v>
+      </c>
+      <c r="J93">
+        <v>234</v>
+      </c>
+      <c r="K93">
         <v>70</v>
       </c>
-      <c r="J80">
-        <v>0</v>
-      </c>
-      <c r="K80">
-        <v>0</v>
-      </c>
-      <c r="L80">
-        <v>0</v>
-      </c>
-      <c r="M80">
-        <v>0</v>
-      </c>
-      <c r="N80">
-        <v>0</v>
-      </c>
-      <c r="O80" t="s">
+      <c r="L93">
+        <v>70</v>
+      </c>
+      <c r="M93">
+        <v>14</v>
+      </c>
+      <c r="N93">
+        <v>0</v>
+      </c>
+      <c r="O93" s="4">
+        <v>1.4699074074074074E-3</v>
+      </c>
+      <c r="P93" s="4">
+        <v>6.7129629629629625E-4</v>
+      </c>
+      <c r="Q93" s="5">
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="R93" s="5">
+        <v>0.29909999999999998</v>
+      </c>
+      <c r="S93" s="3">
+        <v>1</v>
+      </c>
+      <c r="T93">
+        <v>-14</v>
+      </c>
+      <c r="U93" t="s">
+        <v>25</v>
+      </c>
+      <c r="V93" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A94" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B94">
+        <v>11</v>
+      </c>
+      <c r="C94">
+        <v>81</v>
+      </c>
+      <c r="D94">
+        <v>85</v>
+      </c>
+      <c r="E94" t="s">
+        <v>27</v>
+      </c>
+      <c r="F94" t="s">
+        <v>30</v>
+      </c>
+      <c r="G94">
+        <v>25</v>
+      </c>
+      <c r="H94">
+        <v>8</v>
+      </c>
+      <c r="I94">
+        <v>29093</v>
+      </c>
+      <c r="J94">
+        <v>138</v>
+      </c>
+      <c r="K94">
+        <v>40</v>
+      </c>
+      <c r="L94">
+        <v>40</v>
+      </c>
+      <c r="M94">
+        <v>12</v>
+      </c>
+      <c r="N94">
+        <v>1</v>
+      </c>
+      <c r="O94" s="4">
+        <v>2.3611111111111111E-3</v>
+      </c>
+      <c r="P94" s="4">
+        <v>1.2268518518518518E-3</v>
+      </c>
+      <c r="Q94" s="5">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="R94" s="5">
+        <v>0.28989999999999999</v>
+      </c>
+      <c r="S94" s="3">
+        <v>1</v>
+      </c>
+      <c r="T94">
+        <v>-12</v>
+      </c>
+      <c r="U94" t="s">
+        <v>25</v>
+      </c>
+      <c r="V94" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A95" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B95">
+        <v>12</v>
+      </c>
+      <c r="C95">
+        <v>81</v>
+      </c>
+      <c r="D95">
+        <v>85</v>
+      </c>
+      <c r="E95" t="s">
+        <v>27</v>
+      </c>
+      <c r="F95" t="s">
+        <v>30</v>
+      </c>
+      <c r="G95">
+        <v>25</v>
+      </c>
+      <c r="H95">
+        <v>8</v>
+      </c>
+      <c r="I95">
+        <v>21877</v>
+      </c>
+      <c r="J95">
+        <v>107</v>
+      </c>
+      <c r="K95">
+        <v>30</v>
+      </c>
+      <c r="L95">
+        <v>30</v>
+      </c>
+      <c r="M95">
+        <v>16</v>
+      </c>
+      <c r="N95">
+        <v>0</v>
+      </c>
+      <c r="O95" s="4">
+        <v>2.2916666666666667E-3</v>
+      </c>
+      <c r="P95" s="4">
+        <v>7.6388888888888893E-4</v>
+      </c>
+      <c r="Q95" s="5">
+        <v>4.8999999999999998E-3</v>
+      </c>
+      <c r="R95" s="5">
+        <v>0.28039999999999998</v>
+      </c>
+      <c r="S95" s="3">
+        <v>1</v>
+      </c>
+      <c r="T95">
+        <v>-16</v>
+      </c>
+      <c r="U95" t="s">
+        <v>25</v>
+      </c>
+      <c r="V95" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A96" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B96">
+        <v>13</v>
+      </c>
+      <c r="C96">
+        <v>81</v>
+      </c>
+      <c r="D96">
+        <v>85</v>
+      </c>
+      <c r="E96" t="s">
+        <v>27</v>
+      </c>
+      <c r="F96" t="s">
+        <v>30</v>
+      </c>
+      <c r="G96">
+        <v>25</v>
+      </c>
+      <c r="H96">
+        <v>5</v>
+      </c>
+      <c r="I96">
+        <v>14372</v>
+      </c>
+      <c r="J96">
+        <v>85</v>
+      </c>
+      <c r="K96">
+        <v>22</v>
+      </c>
+      <c r="L96">
+        <v>22</v>
+      </c>
+      <c r="M96">
+        <v>7</v>
+      </c>
+      <c r="N96">
+        <v>0</v>
+      </c>
+      <c r="O96" s="4">
+        <v>1.9444444444444444E-3</v>
+      </c>
+      <c r="P96" s="4">
+        <v>1.4930555555555556E-3</v>
+      </c>
+      <c r="Q96" s="5">
+        <v>5.8999999999999999E-3</v>
+      </c>
+      <c r="R96" s="5">
+        <v>0.25879999999999997</v>
+      </c>
+      <c r="S96" s="3">
+        <v>1</v>
+      </c>
+      <c r="T96">
+        <v>-7</v>
+      </c>
+      <c r="U96" t="s">
+        <v>25</v>
+      </c>
+      <c r="V96" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A97" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B97">
+        <v>14</v>
+      </c>
+      <c r="C97">
+        <v>81</v>
+      </c>
+      <c r="D97">
+        <v>85</v>
+      </c>
+      <c r="E97" t="s">
+        <v>27</v>
+      </c>
+      <c r="F97" t="s">
+        <v>30</v>
+      </c>
+      <c r="G97">
+        <v>25</v>
+      </c>
+      <c r="H97">
+        <v>4</v>
+      </c>
+      <c r="I97">
+        <v>16434</v>
+      </c>
+      <c r="J97">
+        <v>126</v>
+      </c>
+      <c r="K97">
+        <v>18</v>
+      </c>
+      <c r="L97">
+        <v>18</v>
+      </c>
+      <c r="M97">
+        <v>5</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97" s="4">
+        <v>1.4814814814814814E-3</v>
+      </c>
+      <c r="P97" s="4">
+        <v>8.1018518518518516E-4</v>
+      </c>
+      <c r="Q97" s="5">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="R97" s="5">
+        <v>0.1429</v>
+      </c>
+      <c r="S97" s="3">
+        <v>1</v>
+      </c>
+      <c r="T97">
+        <v>-5</v>
+      </c>
+      <c r="U97" t="s">
+        <v>25</v>
+      </c>
+      <c r="V97" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A98" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B98">
+        <v>15</v>
+      </c>
+      <c r="C98">
+        <v>81</v>
+      </c>
+      <c r="D98">
+        <v>85</v>
+      </c>
+      <c r="E98" t="s">
+        <v>27</v>
+      </c>
+      <c r="F98" t="s">
+        <v>30</v>
+      </c>
+      <c r="G98">
+        <v>25</v>
+      </c>
+      <c r="H98">
+        <v>3</v>
+      </c>
+      <c r="I98">
+        <v>16782</v>
+      </c>
+      <c r="J98">
+        <v>115</v>
+      </c>
+      <c r="K98">
+        <v>18</v>
+      </c>
+      <c r="L98">
+        <v>18</v>
+      </c>
+      <c r="M98">
+        <v>8</v>
+      </c>
+      <c r="N98">
+        <v>0</v>
+      </c>
+      <c r="O98" s="4">
+        <v>1.6666666666666668E-3</v>
+      </c>
+      <c r="P98" s="4">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="Q98" s="5">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="R98" s="5">
+        <v>0.1565</v>
+      </c>
+      <c r="S98" s="3">
+        <v>1</v>
+      </c>
+      <c r="T98">
+        <v>-8</v>
+      </c>
+      <c r="U98" t="s">
+        <v>25</v>
+      </c>
+      <c r="V98" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A99" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B99">
+        <v>16</v>
+      </c>
+      <c r="C99">
+        <v>81</v>
+      </c>
+      <c r="D99">
+        <v>85</v>
+      </c>
+      <c r="E99" t="s">
+        <v>27</v>
+      </c>
+      <c r="F99" t="s">
+        <v>30</v>
+      </c>
+      <c r="G99">
+        <v>25</v>
+      </c>
+      <c r="H99">
+        <v>5</v>
+      </c>
+      <c r="I99">
+        <v>15999</v>
+      </c>
+      <c r="J99">
+        <v>121</v>
+      </c>
+      <c r="K99">
+        <v>17</v>
+      </c>
+      <c r="L99">
+        <v>17</v>
+      </c>
+      <c r="M99">
+        <v>6</v>
+      </c>
+      <c r="N99">
+        <v>0</v>
+      </c>
+      <c r="O99" s="4">
+        <v>1.4930555555555556E-3</v>
+      </c>
+      <c r="P99" s="4">
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="Q99" s="5">
+        <v>7.6E-3</v>
+      </c>
+      <c r="R99" s="5">
+        <v>0.14050000000000001</v>
+      </c>
+      <c r="S99" s="3">
+        <v>1</v>
+      </c>
+      <c r="T99">
+        <v>-6</v>
+      </c>
+      <c r="U99" t="s">
+        <v>25</v>
+      </c>
+      <c r="V99" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A100" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B100">
+        <v>17</v>
+      </c>
+      <c r="C100">
+        <v>81</v>
+      </c>
+      <c r="D100">
+        <v>85</v>
+      </c>
+      <c r="E100" t="s">
+        <v>27</v>
+      </c>
+      <c r="F100" t="s">
+        <v>30</v>
+      </c>
+      <c r="G100">
+        <v>25</v>
+      </c>
+      <c r="H100">
+        <v>6</v>
+      </c>
+      <c r="I100">
+        <v>22246</v>
+      </c>
+      <c r="J100">
+        <v>200</v>
+      </c>
+      <c r="K100">
+        <v>59</v>
+      </c>
+      <c r="L100">
+        <v>59</v>
+      </c>
+      <c r="M100">
+        <v>10</v>
+      </c>
+      <c r="N100">
+        <v>0</v>
+      </c>
+      <c r="O100" s="4">
+        <v>1.2731481481481483E-3</v>
+      </c>
+      <c r="P100" s="4">
+        <v>1.0995370370370371E-3</v>
+      </c>
+      <c r="Q100" s="5">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="R100" s="5">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="S100" s="3">
+        <v>1</v>
+      </c>
+      <c r="T100">
+        <v>-10</v>
+      </c>
+      <c r="U100" t="s">
+        <v>25</v>
+      </c>
+      <c r="V100" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A101" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B101">
+        <v>18</v>
+      </c>
+      <c r="C101">
+        <v>81</v>
+      </c>
+      <c r="D101">
+        <v>85</v>
+      </c>
+      <c r="E101" t="s">
+        <v>27</v>
+      </c>
+      <c r="F101" t="s">
+        <v>30</v>
+      </c>
+      <c r="G101">
+        <v>1</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+      <c r="I101">
+        <v>103</v>
+      </c>
+      <c r="J101">
+        <v>1</v>
+      </c>
+      <c r="K101">
+        <v>0</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101">
+        <v>0</v>
+      </c>
+      <c r="N101">
+        <v>0</v>
+      </c>
+      <c r="O101" s="4">
+        <v>1.1805555555555556E-3</v>
+      </c>
+      <c r="P101" t="s">
         <v>24</v>
       </c>
-      <c r="P80" t="s">
+      <c r="Q101" s="5">
+        <v>9.7000000000000003E-3</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" t="s">
+        <v>25</v>
+      </c>
+      <c r="T101">
+        <v>0</v>
+      </c>
+      <c r="U101" t="s">
+        <v>25</v>
+      </c>
+      <c r="V101" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="102" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A102" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B102">
+        <v>10</v>
+      </c>
+      <c r="C102">
+        <v>81</v>
+      </c>
+      <c r="D102">
+        <v>85</v>
+      </c>
+      <c r="E102" t="s">
+        <v>27</v>
+      </c>
+      <c r="F102" t="s">
+        <v>30</v>
+      </c>
+      <c r="G102">
+        <v>25</v>
+      </c>
+      <c r="H102">
+        <v>8</v>
+      </c>
+      <c r="I102">
+        <v>11497</v>
+      </c>
+      <c r="J102">
+        <v>132</v>
+      </c>
+      <c r="K102">
+        <v>50</v>
+      </c>
+      <c r="L102">
+        <v>50</v>
+      </c>
+      <c r="M102">
+        <v>13</v>
+      </c>
+      <c r="N102">
+        <v>0</v>
+      </c>
+      <c r="O102" s="4">
+        <v>9.9537037037037042E-4</v>
+      </c>
+      <c r="P102" s="4">
+        <v>2.3379629629629631E-3</v>
+      </c>
+      <c r="Q102" s="5">
+        <v>1.15E-2</v>
+      </c>
+      <c r="R102" s="5">
+        <v>0.37880000000000003</v>
+      </c>
+      <c r="S102" s="3">
+        <v>1</v>
+      </c>
+      <c r="T102">
+        <v>-13</v>
+      </c>
+      <c r="U102" t="s">
+        <v>25</v>
+      </c>
+      <c r="V102" s="5">
+        <v>1</v>
+      </c>
+      <c r="W102">
+        <v>3.6659999999999999</v>
+      </c>
+    </row>
+    <row r="103" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A103" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B103">
+        <v>11</v>
+      </c>
+      <c r="C103">
+        <v>81</v>
+      </c>
+      <c r="D103">
+        <v>85</v>
+      </c>
+      <c r="E103" t="s">
+        <v>27</v>
+      </c>
+      <c r="F103" t="s">
+        <v>30</v>
+      </c>
+      <c r="G103">
+        <v>25</v>
+      </c>
+      <c r="H103">
+        <v>8</v>
+      </c>
+      <c r="I103">
+        <v>30692</v>
+      </c>
+      <c r="J103">
+        <v>259</v>
+      </c>
+      <c r="K103">
+        <v>82</v>
+      </c>
+      <c r="L103">
+        <v>82</v>
+      </c>
+      <c r="M103">
+        <v>30</v>
+      </c>
+      <c r="N103">
+        <v>2</v>
+      </c>
+      <c r="O103" s="4">
+        <v>1.3541666666666667E-3</v>
+      </c>
+      <c r="P103" s="4">
+        <v>1.8055555555555555E-3</v>
+      </c>
+      <c r="Q103" s="5">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="R103" s="5">
+        <v>0.31659999999999999</v>
+      </c>
+      <c r="S103" s="3">
+        <v>1</v>
+      </c>
+      <c r="T103">
+        <v>-30</v>
+      </c>
+      <c r="U103" t="s">
+        <v>25</v>
+      </c>
+      <c r="V103" s="5">
+        <v>0.9677</v>
+      </c>
+      <c r="W103">
+        <v>34.128</v>
+      </c>
+    </row>
+    <row r="104" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A104" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B104">
+        <v>12</v>
+      </c>
+      <c r="C104">
+        <v>81</v>
+      </c>
+      <c r="D104">
+        <v>85</v>
+      </c>
+      <c r="E104" t="s">
+        <v>27</v>
+      </c>
+      <c r="F104" t="s">
+        <v>30</v>
+      </c>
+      <c r="G104">
+        <v>25</v>
+      </c>
+      <c r="H104">
+        <v>1</v>
+      </c>
+      <c r="I104">
+        <v>33207</v>
+      </c>
+      <c r="J104">
+        <v>240</v>
+      </c>
+      <c r="K104">
+        <v>60</v>
+      </c>
+      <c r="L104">
+        <v>60</v>
+      </c>
+      <c r="M104">
+        <v>1</v>
+      </c>
+      <c r="N104">
+        <v>0</v>
+      </c>
+      <c r="O104" s="4">
+        <v>1.5856481481481481E-3</v>
+      </c>
+      <c r="P104" s="4">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="Q104" s="5">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="R104" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="S104" s="3">
+        <v>1</v>
+      </c>
+      <c r="T104">
+        <v>-1</v>
+      </c>
+      <c r="U104" t="s">
+        <v>25</v>
+      </c>
+      <c r="V104" s="5">
+        <v>1</v>
+      </c>
+      <c r="W104">
+        <v>22.643999999999998</v>
+      </c>
+    </row>
+    <row r="105" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A105" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B105">
+        <v>13</v>
+      </c>
+      <c r="C105">
+        <v>81</v>
+      </c>
+      <c r="D105">
+        <v>85</v>
+      </c>
+      <c r="E105" t="s">
+        <v>27</v>
+      </c>
+      <c r="F105" t="s">
+        <v>30</v>
+      </c>
+      <c r="G105">
+        <v>44</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+      <c r="I105">
+        <v>23624</v>
+      </c>
+      <c r="J105">
+        <v>220</v>
+      </c>
+      <c r="K105">
+        <v>35</v>
+      </c>
+      <c r="L105">
+        <v>35</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105">
+        <v>0</v>
+      </c>
+      <c r="O105" s="4">
+        <v>1.2268518518518518E-3</v>
+      </c>
+      <c r="P105" t="s">
         <v>24</v>
       </c>
-      <c r="Q80" s="3">
-        <v>0</v>
-      </c>
-      <c r="R80" t="s">
-        <v>25</v>
-      </c>
-      <c r="S80" t="s">
-        <v>25</v>
-      </c>
-      <c r="T80">
-        <v>0</v>
-      </c>
-      <c r="U80" t="s">
+      <c r="Q105" s="5">
+        <v>9.2999999999999992E-3</v>
+      </c>
+      <c r="R105" s="5">
+        <v>0.15909999999999999</v>
+      </c>
+      <c r="S105" s="3">
+        <v>1</v>
+      </c>
+      <c r="T105">
+        <v>0</v>
+      </c>
+      <c r="U105" t="s">
+        <v>25</v>
+      </c>
+      <c r="V105" t="s">
+        <v>25</v>
+      </c>
+      <c r="W105">
+        <v>26.43</v>
+      </c>
+    </row>
+    <row r="106" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A106" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B106">
+        <v>14</v>
+      </c>
+      <c r="C106">
+        <v>81</v>
+      </c>
+      <c r="D106">
+        <v>85</v>
+      </c>
+      <c r="E106" t="s">
+        <v>27</v>
+      </c>
+      <c r="F106" t="s">
+        <v>30</v>
+      </c>
+      <c r="G106">
+        <v>25</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
+      </c>
+      <c r="I106">
+        <v>22591</v>
+      </c>
+      <c r="J106">
+        <v>239</v>
+      </c>
+      <c r="K106">
+        <v>28</v>
+      </c>
+      <c r="L106">
+        <v>28</v>
+      </c>
+      <c r="M106">
+        <v>0</v>
+      </c>
+      <c r="N106">
+        <v>0</v>
+      </c>
+      <c r="O106" s="4">
+        <v>1.0763888888888889E-3</v>
+      </c>
+      <c r="P106" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q106" s="5">
+        <v>1.06E-2</v>
+      </c>
+      <c r="R106" s="5">
+        <v>0.1172</v>
+      </c>
+      <c r="S106" s="3">
+        <v>1</v>
+      </c>
+      <c r="T106">
+        <v>0</v>
+      </c>
+      <c r="U106" t="s">
+        <v>25</v>
+      </c>
+      <c r="V106" t="s">
+        <v>25</v>
+      </c>
+      <c r="W106">
+        <v>24.654</v>
+      </c>
+    </row>
+    <row r="107" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A107" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B107">
+        <v>15</v>
+      </c>
+      <c r="C107">
+        <v>81</v>
+      </c>
+      <c r="D107">
+        <v>85</v>
+      </c>
+      <c r="E107" t="s">
+        <v>27</v>
+      </c>
+      <c r="F107" t="s">
+        <v>30</v>
+      </c>
+      <c r="G107">
+        <v>25</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
+      </c>
+      <c r="I107">
+        <v>21702</v>
+      </c>
+      <c r="J107">
+        <v>216</v>
+      </c>
+      <c r="K107">
+        <v>51</v>
+      </c>
+      <c r="L107">
+        <v>51</v>
+      </c>
+      <c r="M107">
+        <v>0</v>
+      </c>
+      <c r="N107">
+        <v>0</v>
+      </c>
+      <c r="O107" s="4">
+        <v>1.1458333333333333E-3</v>
+      </c>
+      <c r="P107" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q107" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="R107" s="5">
+        <v>0.2361</v>
+      </c>
+      <c r="S107" s="3">
+        <v>1</v>
+      </c>
+      <c r="T107">
+        <v>0</v>
+      </c>
+      <c r="U107" t="s">
+        <v>25</v>
+      </c>
+      <c r="V107" t="s">
+        <v>25</v>
+      </c>
+      <c r="W107">
+        <v>36.558</v>
+      </c>
+    </row>
+    <row r="108" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A108" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B108">
+        <v>16</v>
+      </c>
+      <c r="C108">
+        <v>81</v>
+      </c>
+      <c r="D108">
+        <v>85</v>
+      </c>
+      <c r="E108" t="s">
+        <v>27</v>
+      </c>
+      <c r="F108" t="s">
+        <v>30</v>
+      </c>
+      <c r="G108">
+        <v>25</v>
+      </c>
+      <c r="H108">
+        <v>0</v>
+      </c>
+      <c r="I108">
+        <v>46702</v>
+      </c>
+      <c r="J108">
+        <v>487</v>
+      </c>
+      <c r="K108">
+        <v>145</v>
+      </c>
+      <c r="L108">
+        <v>145</v>
+      </c>
+      <c r="M108">
+        <v>0</v>
+      </c>
+      <c r="N108">
+        <v>0</v>
+      </c>
+      <c r="O108" s="4">
+        <v>1.0995370370370371E-3</v>
+      </c>
+      <c r="P108" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q108" s="5">
+        <v>1.04E-2</v>
+      </c>
+      <c r="R108" s="5">
+        <v>0.29770000000000002</v>
+      </c>
+      <c r="S108" s="3">
+        <v>1</v>
+      </c>
+      <c r="T108">
+        <v>0</v>
+      </c>
+      <c r="U108" t="s">
+        <v>25</v>
+      </c>
+      <c r="V108" t="s">
+        <v>25</v>
+      </c>
+      <c r="W108">
+        <v>50.658000000000001</v>
+      </c>
+    </row>
+    <row r="109" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A109" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B109">
+        <v>17</v>
+      </c>
+      <c r="C109">
+        <v>81</v>
+      </c>
+      <c r="D109">
+        <v>85</v>
+      </c>
+      <c r="E109" t="s">
+        <v>27</v>
+      </c>
+      <c r="F109" t="s">
+        <v>30</v>
+      </c>
+      <c r="G109">
+        <v>25</v>
+      </c>
+      <c r="H109">
+        <v>5</v>
+      </c>
+      <c r="I109">
+        <v>31360</v>
+      </c>
+      <c r="J109">
+        <v>270</v>
+      </c>
+      <c r="K109">
+        <v>79</v>
+      </c>
+      <c r="L109">
+        <v>79</v>
+      </c>
+      <c r="M109">
+        <v>29</v>
+      </c>
+      <c r="N109">
+        <v>2</v>
+      </c>
+      <c r="O109" s="4">
+        <v>1.3310185185185185E-3</v>
+      </c>
+      <c r="P109" s="4">
+        <v>1.7013888888888888E-3</v>
+      </c>
+      <c r="Q109" s="5">
+        <v>8.6E-3</v>
+      </c>
+      <c r="R109" s="5">
+        <v>0.29260000000000003</v>
+      </c>
+      <c r="S109" s="3">
+        <v>1</v>
+      </c>
+      <c r="T109">
+        <v>-29</v>
+      </c>
+      <c r="U109" t="s">
+        <v>25</v>
+      </c>
+      <c r="V109" s="5">
+        <v>0.78569999999999995</v>
+      </c>
+      <c r="W109">
+        <v>22.295999999999999</v>
+      </c>
+    </row>
+    <row r="110" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A110" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B110">
+        <v>18</v>
+      </c>
+      <c r="C110">
+        <v>81</v>
+      </c>
+      <c r="D110">
+        <v>85</v>
+      </c>
+      <c r="E110" t="s">
+        <v>27</v>
+      </c>
+      <c r="F110" t="s">
+        <v>30</v>
+      </c>
+      <c r="G110">
+        <v>0</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+      <c r="I110">
+        <v>78</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>0</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="N110">
+        <v>0</v>
+      </c>
+      <c r="O110" t="s">
+        <v>24</v>
+      </c>
+      <c r="P110" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q110" s="3">
+        <v>0</v>
+      </c>
+      <c r="R110" t="s">
+        <v>25</v>
+      </c>
+      <c r="S110" t="s">
+        <v>25</v>
+      </c>
+      <c r="T110">
+        <v>0</v>
+      </c>
+      <c r="U110" t="s">
         <v>25</v>
       </c>
     </row>

--- a/data/base_creditas.xlsx
+++ b/data/base_creditas.xlsx
@@ -8,21 +8,37 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09AACF5-8504-4D54-8101-2FD8D426C7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64372A37-9E80-4B97-BE8A-49079493CD7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Funil_2" sheetId="2" r:id="rId2"/>
     <sheet name="Funil_3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Funil_3!$A$1:$T$49</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="31">
   <si>
     <t>Data</t>
   </si>
@@ -487,10 +503,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W110"/>
+  <dimension ref="A1:W128"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
@@ -7957,6 +7974,1281 @@
         <v>0</v>
       </c>
       <c r="U110" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="111" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A111" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B111">
+        <v>9</v>
+      </c>
+      <c r="C111">
+        <v>81</v>
+      </c>
+      <c r="D111">
+        <v>85</v>
+      </c>
+      <c r="E111" t="s">
+        <v>27</v>
+      </c>
+      <c r="F111">
+        <v>9736</v>
+      </c>
+      <c r="G111">
+        <v>25</v>
+      </c>
+      <c r="H111">
+        <v>7</v>
+      </c>
+      <c r="I111">
+        <v>23715</v>
+      </c>
+      <c r="J111">
+        <v>271</v>
+      </c>
+      <c r="K111">
+        <v>85</v>
+      </c>
+      <c r="L111">
+        <v>43</v>
+      </c>
+      <c r="M111">
+        <v>42</v>
+      </c>
+      <c r="N111">
+        <v>5</v>
+      </c>
+      <c r="O111" s="4">
+        <v>1.0069444444444444E-3</v>
+      </c>
+      <c r="P111" s="4">
+        <v>1.3194444444444445E-3</v>
+      </c>
+      <c r="Q111" s="5">
+        <v>1.14E-2</v>
+      </c>
+      <c r="R111" s="5">
+        <v>0.31369999999999998</v>
+      </c>
+      <c r="S111" s="5">
+        <v>0.50590000000000002</v>
+      </c>
+      <c r="T111">
+        <v>0</v>
+      </c>
+      <c r="U111" s="3">
+        <v>0</v>
+      </c>
+      <c r="V111" s="5">
+        <v>0.97440000000000004</v>
+      </c>
+      <c r="W111">
+        <v>47.375999999999998</v>
+      </c>
+    </row>
+    <row r="112" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A112" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B112">
+        <v>10</v>
+      </c>
+      <c r="C112">
+        <v>81</v>
+      </c>
+      <c r="D112">
+        <v>85</v>
+      </c>
+      <c r="E112" t="s">
+        <v>27</v>
+      </c>
+      <c r="F112">
+        <v>9736</v>
+      </c>
+      <c r="G112">
+        <v>25</v>
+      </c>
+      <c r="H112">
+        <v>11</v>
+      </c>
+      <c r="I112">
+        <v>35588</v>
+      </c>
+      <c r="J112">
+        <v>304</v>
+      </c>
+      <c r="K112">
+        <v>89</v>
+      </c>
+      <c r="L112">
+        <v>42</v>
+      </c>
+      <c r="M112">
+        <v>47</v>
+      </c>
+      <c r="N112">
+        <v>3</v>
+      </c>
+      <c r="O112" s="4">
+        <v>1.3425925925925925E-3</v>
+      </c>
+      <c r="P112" s="4">
+        <v>1.8634259259259259E-3</v>
+      </c>
+      <c r="Q112" s="5">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="R112" s="5">
+        <v>0.2928</v>
+      </c>
+      <c r="S112" s="5">
+        <v>0.47189999999999999</v>
+      </c>
+      <c r="T112">
+        <v>0</v>
+      </c>
+      <c r="U112" s="3">
+        <v>0</v>
+      </c>
+      <c r="V112" s="5">
+        <v>0.95920000000000005</v>
+      </c>
+      <c r="W112">
+        <v>44.16</v>
+      </c>
+    </row>
+    <row r="113" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A113" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B113">
+        <v>11</v>
+      </c>
+      <c r="C113">
+        <v>81</v>
+      </c>
+      <c r="D113">
+        <v>85</v>
+      </c>
+      <c r="E113" t="s">
+        <v>27</v>
+      </c>
+      <c r="F113">
+        <v>9736</v>
+      </c>
+      <c r="G113">
+        <v>25</v>
+      </c>
+      <c r="H113">
+        <v>11</v>
+      </c>
+      <c r="I113">
+        <v>32331</v>
+      </c>
+      <c r="J113">
+        <v>224</v>
+      </c>
+      <c r="K113">
+        <v>66</v>
+      </c>
+      <c r="L113">
+        <v>31</v>
+      </c>
+      <c r="M113">
+        <v>35</v>
+      </c>
+      <c r="N113">
+        <v>1</v>
+      </c>
+      <c r="O113" s="4">
+        <v>1.6550925925925926E-3</v>
+      </c>
+      <c r="P113" s="4">
+        <v>1.0300925925925926E-3</v>
+      </c>
+      <c r="Q113" s="5">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="R113" s="5">
+        <v>0.29459999999999997</v>
+      </c>
+      <c r="S113" s="5">
+        <v>0.46970000000000001</v>
+      </c>
+      <c r="T113">
+        <v>0</v>
+      </c>
+      <c r="U113" s="3">
+        <v>0</v>
+      </c>
+      <c r="V113" s="5">
+        <v>1</v>
+      </c>
+      <c r="W113">
+        <v>33.851999999999997</v>
+      </c>
+    </row>
+    <row r="114" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A114" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B114">
+        <v>11</v>
+      </c>
+      <c r="C114">
+        <v>84</v>
+      </c>
+      <c r="D114">
+        <v>86</v>
+      </c>
+      <c r="E114" t="s">
+        <v>26</v>
+      </c>
+      <c r="F114">
+        <v>35585</v>
+      </c>
+      <c r="G114">
+        <v>25</v>
+      </c>
+      <c r="H114">
+        <v>1</v>
+      </c>
+      <c r="I114">
+        <v>1173</v>
+      </c>
+      <c r="J114">
+        <v>33</v>
+      </c>
+      <c r="K114">
+        <v>14</v>
+      </c>
+      <c r="L114">
+        <v>11</v>
+      </c>
+      <c r="M114">
+        <v>2</v>
+      </c>
+      <c r="N114">
+        <v>0</v>
+      </c>
+      <c r="O114" s="4">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="P114" s="4">
+        <v>9.1435185185185185E-4</v>
+      </c>
+      <c r="Q114" s="5">
+        <v>2.81E-2</v>
+      </c>
+      <c r="R114" s="5">
+        <v>0.42420000000000002</v>
+      </c>
+      <c r="S114" s="5">
+        <v>0.78569999999999995</v>
+      </c>
+      <c r="T114">
+        <v>1</v>
+      </c>
+      <c r="U114" s="5">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="V114" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="W114">
+        <v>3.234</v>
+      </c>
+    </row>
+    <row r="115" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A115" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B115">
+        <v>12</v>
+      </c>
+      <c r="C115">
+        <v>81</v>
+      </c>
+      <c r="D115">
+        <v>85</v>
+      </c>
+      <c r="E115" t="s">
+        <v>27</v>
+      </c>
+      <c r="F115">
+        <v>9736</v>
+      </c>
+      <c r="G115">
+        <v>25</v>
+      </c>
+      <c r="H115">
+        <v>10</v>
+      </c>
+      <c r="I115">
+        <v>45775</v>
+      </c>
+      <c r="J115">
+        <v>534</v>
+      </c>
+      <c r="K115">
+        <v>118</v>
+      </c>
+      <c r="L115">
+        <v>52</v>
+      </c>
+      <c r="M115">
+        <v>63</v>
+      </c>
+      <c r="N115">
+        <v>0</v>
+      </c>
+      <c r="O115" s="4">
+        <v>9.837962962962962E-4</v>
+      </c>
+      <c r="P115" s="4">
+        <v>1.2268518518518518E-3</v>
+      </c>
+      <c r="Q115" s="5">
+        <v>1.17E-2</v>
+      </c>
+      <c r="R115" s="5">
+        <v>0.221</v>
+      </c>
+      <c r="S115" s="5">
+        <v>0.44069999999999998</v>
+      </c>
+      <c r="T115">
+        <v>3</v>
+      </c>
+      <c r="U115" s="5">
+        <v>4.5499999999999999E-2</v>
+      </c>
+      <c r="V115" s="5">
+        <v>1</v>
+      </c>
+      <c r="W115">
+        <v>88.8</v>
+      </c>
+    </row>
+    <row r="116" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A116" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B116">
+        <v>12</v>
+      </c>
+      <c r="C116">
+        <v>84</v>
+      </c>
+      <c r="D116">
+        <v>86</v>
+      </c>
+      <c r="E116" t="s">
+        <v>26</v>
+      </c>
+      <c r="F116">
+        <v>35585</v>
+      </c>
+      <c r="G116">
+        <v>25</v>
+      </c>
+      <c r="H116">
+        <v>1</v>
+      </c>
+      <c r="I116">
+        <v>2183</v>
+      </c>
+      <c r="J116">
+        <v>54</v>
+      </c>
+      <c r="K116">
+        <v>10</v>
+      </c>
+      <c r="L116">
+        <v>5</v>
+      </c>
+      <c r="M116">
+        <v>5</v>
+      </c>
+      <c r="N116">
+        <v>0</v>
+      </c>
+      <c r="O116" s="4">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="P116" s="4">
+        <v>5.0925925925925921E-4</v>
+      </c>
+      <c r="Q116" s="5">
+        <v>2.47E-2</v>
+      </c>
+      <c r="R116" s="5">
+        <v>0.1852</v>
+      </c>
+      <c r="S116" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="T116">
+        <v>0</v>
+      </c>
+      <c r="U116" s="3">
+        <v>0</v>
+      </c>
+      <c r="V116" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="W116">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="117" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A117" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B117">
+        <v>13</v>
+      </c>
+      <c r="C117">
+        <v>81</v>
+      </c>
+      <c r="D117">
+        <v>85</v>
+      </c>
+      <c r="E117" t="s">
+        <v>27</v>
+      </c>
+      <c r="F117">
+        <v>9736</v>
+      </c>
+      <c r="G117">
+        <v>25</v>
+      </c>
+      <c r="H117">
+        <v>8</v>
+      </c>
+      <c r="I117">
+        <v>42602</v>
+      </c>
+      <c r="J117">
+        <v>445</v>
+      </c>
+      <c r="K117">
+        <v>100</v>
+      </c>
+      <c r="L117">
+        <v>42</v>
+      </c>
+      <c r="M117">
+        <v>55</v>
+      </c>
+      <c r="N117">
+        <v>1</v>
+      </c>
+      <c r="O117" s="4">
+        <v>1.0995370370370371E-3</v>
+      </c>
+      <c r="P117" s="4">
+        <v>1.3773148148148147E-3</v>
+      </c>
+      <c r="Q117" s="5">
+        <v>1.04E-2</v>
+      </c>
+      <c r="R117" s="5">
+        <v>0.22470000000000001</v>
+      </c>
+      <c r="S117" s="3">
+        <v>0.42</v>
+      </c>
+      <c r="T117">
+        <v>3</v>
+      </c>
+      <c r="U117" s="5">
+        <v>5.1700000000000003E-2</v>
+      </c>
+      <c r="V117" s="5">
+        <v>0.89829999999999999</v>
+      </c>
+      <c r="W117">
+        <v>42.81</v>
+      </c>
+    </row>
+    <row r="118" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A118" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B118">
+        <v>13</v>
+      </c>
+      <c r="C118">
+        <v>84</v>
+      </c>
+      <c r="D118">
+        <v>86</v>
+      </c>
+      <c r="E118" t="s">
+        <v>26</v>
+      </c>
+      <c r="F118">
+        <v>35585</v>
+      </c>
+      <c r="G118">
+        <v>25</v>
+      </c>
+      <c r="H118">
+        <v>1</v>
+      </c>
+      <c r="I118">
+        <v>3237</v>
+      </c>
+      <c r="J118">
+        <v>49</v>
+      </c>
+      <c r="K118">
+        <v>12</v>
+      </c>
+      <c r="L118">
+        <v>5</v>
+      </c>
+      <c r="M118">
+        <v>7</v>
+      </c>
+      <c r="N118">
+        <v>0</v>
+      </c>
+      <c r="O118" s="4">
+        <v>7.5231481481481482E-4</v>
+      </c>
+      <c r="P118" s="4">
+        <v>8.2175925925925927E-4</v>
+      </c>
+      <c r="Q118" s="5">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="R118" s="5">
+        <v>0.24490000000000001</v>
+      </c>
+      <c r="S118" s="5">
+        <v>0.41670000000000001</v>
+      </c>
+      <c r="T118">
+        <v>0</v>
+      </c>
+      <c r="U118" s="3">
+        <v>0</v>
+      </c>
+      <c r="V118" s="5">
+        <v>0.88890000000000002</v>
+      </c>
+      <c r="W118">
+        <v>4.0259999999999998</v>
+      </c>
+    </row>
+    <row r="119" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A119" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B119">
+        <v>14</v>
+      </c>
+      <c r="C119">
+        <v>81</v>
+      </c>
+      <c r="D119">
+        <v>85</v>
+      </c>
+      <c r="E119" t="s">
+        <v>27</v>
+      </c>
+      <c r="F119">
+        <v>9736</v>
+      </c>
+      <c r="G119">
+        <v>25</v>
+      </c>
+      <c r="H119">
+        <v>9</v>
+      </c>
+      <c r="I119">
+        <v>26039</v>
+      </c>
+      <c r="J119">
+        <v>181</v>
+      </c>
+      <c r="K119">
+        <v>32</v>
+      </c>
+      <c r="L119">
+        <v>17</v>
+      </c>
+      <c r="M119">
+        <v>15</v>
+      </c>
+      <c r="N119">
+        <v>0</v>
+      </c>
+      <c r="O119" s="4">
+        <v>1.6319444444444445E-3</v>
+      </c>
+      <c r="P119" s="4">
+        <v>8.9120370370370373E-4</v>
+      </c>
+      <c r="Q119" s="5">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="R119" s="5">
+        <v>0.17680000000000001</v>
+      </c>
+      <c r="S119" s="5">
+        <v>0.53129999999999999</v>
+      </c>
+      <c r="T119">
+        <v>0</v>
+      </c>
+      <c r="U119" s="3">
+        <v>0</v>
+      </c>
+      <c r="V119" s="5">
+        <v>1</v>
+      </c>
+      <c r="W119">
+        <v>21.515999999999998</v>
+      </c>
+    </row>
+    <row r="120" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A120" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B120">
+        <v>14</v>
+      </c>
+      <c r="C120">
+        <v>84</v>
+      </c>
+      <c r="D120">
+        <v>86</v>
+      </c>
+      <c r="E120" t="s">
+        <v>26</v>
+      </c>
+      <c r="F120">
+        <v>35585</v>
+      </c>
+      <c r="G120">
+        <v>25</v>
+      </c>
+      <c r="H120">
+        <v>4</v>
+      </c>
+      <c r="I120">
+        <v>3765</v>
+      </c>
+      <c r="J120">
+        <v>67</v>
+      </c>
+      <c r="K120">
+        <v>12</v>
+      </c>
+      <c r="L120">
+        <v>5</v>
+      </c>
+      <c r="M120">
+        <v>7</v>
+      </c>
+      <c r="N120">
+        <v>0</v>
+      </c>
+      <c r="O120" s="4">
+        <v>6.3657407407407413E-4</v>
+      </c>
+      <c r="P120" s="4">
+        <v>7.5231481481481482E-4</v>
+      </c>
+      <c r="Q120" s="5">
+        <v>1.78E-2</v>
+      </c>
+      <c r="R120" s="5">
+        <v>0.17910000000000001</v>
+      </c>
+      <c r="S120" s="5">
+        <v>0.41670000000000001</v>
+      </c>
+      <c r="T120">
+        <v>0</v>
+      </c>
+      <c r="U120" s="3">
+        <v>0</v>
+      </c>
+      <c r="V120" s="5">
+        <v>1</v>
+      </c>
+      <c r="W120">
+        <v>5.5739999999999998</v>
+      </c>
+    </row>
+    <row r="121" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A121" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B121">
+        <v>15</v>
+      </c>
+      <c r="C121">
+        <v>81</v>
+      </c>
+      <c r="D121">
+        <v>85</v>
+      </c>
+      <c r="E121" t="s">
+        <v>27</v>
+      </c>
+      <c r="F121">
+        <v>9736</v>
+      </c>
+      <c r="G121">
+        <v>25</v>
+      </c>
+      <c r="H121">
+        <v>10</v>
+      </c>
+      <c r="I121">
+        <v>49318</v>
+      </c>
+      <c r="J121">
+        <v>599</v>
+      </c>
+      <c r="K121">
+        <v>128</v>
+      </c>
+      <c r="L121">
+        <v>55</v>
+      </c>
+      <c r="M121">
+        <v>71</v>
+      </c>
+      <c r="N121">
+        <v>4</v>
+      </c>
+      <c r="O121" s="4">
+        <v>9.3749999999999997E-4</v>
+      </c>
+      <c r="P121" s="4">
+        <v>1.0185185185185184E-3</v>
+      </c>
+      <c r="Q121" s="5">
+        <v>1.21E-2</v>
+      </c>
+      <c r="R121" s="5">
+        <v>0.2137</v>
+      </c>
+      <c r="S121" s="5">
+        <v>0.42970000000000003</v>
+      </c>
+      <c r="T121">
+        <v>2</v>
+      </c>
+      <c r="U121" s="5">
+        <v>2.7400000000000001E-2</v>
+      </c>
+      <c r="V121" s="5">
+        <v>1</v>
+      </c>
+      <c r="W121">
+        <v>86.34</v>
+      </c>
+    </row>
+    <row r="122" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A122" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B122">
+        <v>15</v>
+      </c>
+      <c r="C122">
+        <v>84</v>
+      </c>
+      <c r="D122">
+        <v>86</v>
+      </c>
+      <c r="E122" t="s">
+        <v>26</v>
+      </c>
+      <c r="F122">
+        <v>35585</v>
+      </c>
+      <c r="G122">
+        <v>25</v>
+      </c>
+      <c r="H122">
+        <v>4</v>
+      </c>
+      <c r="I122">
+        <v>3187</v>
+      </c>
+      <c r="J122">
+        <v>71</v>
+      </c>
+      <c r="K122">
+        <v>23</v>
+      </c>
+      <c r="L122">
+        <v>8</v>
+      </c>
+      <c r="M122">
+        <v>15</v>
+      </c>
+      <c r="N122">
+        <v>0</v>
+      </c>
+      <c r="O122" s="4">
+        <v>5.0925925925925921E-4</v>
+      </c>
+      <c r="P122" s="4">
+        <v>6.4814814814814813E-4</v>
+      </c>
+      <c r="Q122" s="5">
+        <v>2.23E-2</v>
+      </c>
+      <c r="R122" s="5">
+        <v>0.32390000000000002</v>
+      </c>
+      <c r="S122" s="5">
+        <v>0.3478</v>
+      </c>
+      <c r="T122">
+        <v>0</v>
+      </c>
+      <c r="U122" s="3">
+        <v>0</v>
+      </c>
+      <c r="V122" s="5">
+        <v>1</v>
+      </c>
+      <c r="W122">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A123" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B123">
+        <v>16</v>
+      </c>
+      <c r="C123">
+        <v>81</v>
+      </c>
+      <c r="D123">
+        <v>85</v>
+      </c>
+      <c r="E123" t="s">
+        <v>27</v>
+      </c>
+      <c r="F123">
+        <v>9736</v>
+      </c>
+      <c r="G123">
+        <v>25</v>
+      </c>
+      <c r="H123">
+        <v>7</v>
+      </c>
+      <c r="I123">
+        <v>36538</v>
+      </c>
+      <c r="J123">
+        <v>412</v>
+      </c>
+      <c r="K123">
+        <v>116</v>
+      </c>
+      <c r="L123">
+        <v>63</v>
+      </c>
+      <c r="M123">
+        <v>52</v>
+      </c>
+      <c r="N123">
+        <v>0</v>
+      </c>
+      <c r="O123" s="4">
+        <v>1.0069444444444444E-3</v>
+      </c>
+      <c r="P123" s="4">
+        <v>1.0416666666666667E-3</v>
+      </c>
+      <c r="Q123" s="5">
+        <v>1.1299999999999999E-2</v>
+      </c>
+      <c r="R123" s="5">
+        <v>0.28160000000000002</v>
+      </c>
+      <c r="S123" s="5">
+        <v>0.54310000000000003</v>
+      </c>
+      <c r="T123">
+        <v>1</v>
+      </c>
+      <c r="U123" s="5">
+        <v>1.89E-2</v>
+      </c>
+      <c r="V123" s="5">
+        <v>1</v>
+      </c>
+      <c r="W123">
+        <v>50.195999999999998</v>
+      </c>
+    </row>
+    <row r="124" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A124" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B124">
+        <v>16</v>
+      </c>
+      <c r="C124">
+        <v>84</v>
+      </c>
+      <c r="D124">
+        <v>86</v>
+      </c>
+      <c r="E124" t="s">
+        <v>26</v>
+      </c>
+      <c r="F124">
+        <v>35585</v>
+      </c>
+      <c r="G124">
+        <v>25</v>
+      </c>
+      <c r="H124">
+        <v>3</v>
+      </c>
+      <c r="I124">
+        <v>2942</v>
+      </c>
+      <c r="J124">
+        <v>88</v>
+      </c>
+      <c r="K124">
+        <v>17</v>
+      </c>
+      <c r="L124">
+        <v>3</v>
+      </c>
+      <c r="M124">
+        <v>14</v>
+      </c>
+      <c r="N124">
+        <v>1</v>
+      </c>
+      <c r="O124" s="4">
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="P124" s="4">
+        <v>4.2824074074074075E-4</v>
+      </c>
+      <c r="Q124" s="5">
+        <v>2.9899999999999999E-2</v>
+      </c>
+      <c r="R124" s="5">
+        <v>0.19320000000000001</v>
+      </c>
+      <c r="S124" s="5">
+        <v>0.17649999999999999</v>
+      </c>
+      <c r="T124">
+        <v>0</v>
+      </c>
+      <c r="U124" s="3">
+        <v>0</v>
+      </c>
+      <c r="V124" s="5">
+        <v>1</v>
+      </c>
+      <c r="W124">
+        <v>7.008</v>
+      </c>
+    </row>
+    <row r="125" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A125" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B125">
+        <v>17</v>
+      </c>
+      <c r="C125">
+        <v>81</v>
+      </c>
+      <c r="D125">
+        <v>85</v>
+      </c>
+      <c r="E125" t="s">
+        <v>27</v>
+      </c>
+      <c r="F125">
+        <v>9736</v>
+      </c>
+      <c r="G125">
+        <v>25</v>
+      </c>
+      <c r="H125">
+        <v>4</v>
+      </c>
+      <c r="I125">
+        <v>25875</v>
+      </c>
+      <c r="J125">
+        <v>186</v>
+      </c>
+      <c r="K125">
+        <v>57</v>
+      </c>
+      <c r="L125">
+        <v>30</v>
+      </c>
+      <c r="M125">
+        <v>24</v>
+      </c>
+      <c r="N125">
+        <v>0</v>
+      </c>
+      <c r="O125" s="4">
+        <v>1.5972222222222223E-3</v>
+      </c>
+      <c r="P125" s="4">
+        <v>6.018518518518519E-4</v>
+      </c>
+      <c r="Q125" s="5">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="R125" s="5">
+        <v>0.30649999999999999</v>
+      </c>
+      <c r="S125" s="5">
+        <v>0.52629999999999999</v>
+      </c>
+      <c r="T125">
+        <v>3</v>
+      </c>
+      <c r="U125" s="5">
+        <v>0.1111</v>
+      </c>
+      <c r="V125" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="W125">
+        <v>19.074000000000002</v>
+      </c>
+    </row>
+    <row r="126" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A126" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B126">
+        <v>17</v>
+      </c>
+      <c r="C126">
+        <v>84</v>
+      </c>
+      <c r="D126">
+        <v>86</v>
+      </c>
+      <c r="E126" t="s">
+        <v>26</v>
+      </c>
+      <c r="F126">
+        <v>35585</v>
+      </c>
+      <c r="G126">
+        <v>11</v>
+      </c>
+      <c r="H126">
+        <v>2</v>
+      </c>
+      <c r="I126">
+        <v>485</v>
+      </c>
+      <c r="J126">
+        <v>11</v>
+      </c>
+      <c r="K126">
+        <v>3</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126">
+        <v>3</v>
+      </c>
+      <c r="N126">
+        <v>0</v>
+      </c>
+      <c r="O126" s="4">
+        <v>5.0925925925925921E-4</v>
+      </c>
+      <c r="P126" s="4">
+        <v>3.7037037037037035E-4</v>
+      </c>
+      <c r="Q126" s="5">
+        <v>2.2700000000000001E-2</v>
+      </c>
+      <c r="R126" s="5">
+        <v>0.2727</v>
+      </c>
+      <c r="S126" s="3">
+        <v>0</v>
+      </c>
+      <c r="T126">
+        <v>0</v>
+      </c>
+      <c r="U126" s="3">
+        <v>0</v>
+      </c>
+      <c r="V126" s="5">
+        <v>1</v>
+      </c>
+      <c r="W126">
+        <v>1.452</v>
+      </c>
+    </row>
+    <row r="127" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A127" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B127">
+        <v>18</v>
+      </c>
+      <c r="C127">
+        <v>81</v>
+      </c>
+      <c r="D127">
+        <v>85</v>
+      </c>
+      <c r="E127" t="s">
+        <v>27</v>
+      </c>
+      <c r="F127">
+        <v>9736</v>
+      </c>
+      <c r="G127">
+        <v>1</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+      <c r="I127">
+        <v>196</v>
+      </c>
+      <c r="J127">
+        <v>1</v>
+      </c>
+      <c r="K127">
+        <v>1</v>
+      </c>
+      <c r="L127">
+        <v>1</v>
+      </c>
+      <c r="M127">
+        <v>0</v>
+      </c>
+      <c r="N127">
+        <v>0</v>
+      </c>
+      <c r="O127" s="4">
+        <v>2.2569444444444442E-3</v>
+      </c>
+      <c r="P127" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q127" s="5">
+        <v>5.1000000000000004E-3</v>
+      </c>
+      <c r="R127" s="3">
+        <v>1</v>
+      </c>
+      <c r="S127" s="3">
+        <v>1</v>
+      </c>
+      <c r="T127">
+        <v>0</v>
+      </c>
+      <c r="U127" t="s">
+        <v>25</v>
+      </c>
+      <c r="V127" t="s">
+        <v>25</v>
+      </c>
+      <c r="W127">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="128" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A128" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B128">
+        <v>18</v>
+      </c>
+      <c r="C128">
+        <v>84</v>
+      </c>
+      <c r="D128">
+        <v>86</v>
+      </c>
+      <c r="E128" t="s">
+        <v>26</v>
+      </c>
+      <c r="F128">
+        <v>35585</v>
+      </c>
+      <c r="G128">
+        <v>0</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+      <c r="I128">
+        <v>5</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+      <c r="K128">
+        <v>0</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128">
+        <v>0</v>
+      </c>
+      <c r="N128">
+        <v>0</v>
+      </c>
+      <c r="O128" t="s">
+        <v>24</v>
+      </c>
+      <c r="P128" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q128" s="3">
+        <v>0</v>
+      </c>
+      <c r="R128" t="s">
+        <v>25</v>
+      </c>
+      <c r="S128" t="s">
+        <v>25</v>
+      </c>
+      <c r="T128">
+        <v>0</v>
+      </c>
+      <c r="U128" t="s">
+        <v>25</v>
+      </c>
+      <c r="V128" t="s">
         <v>25</v>
       </c>
     </row>
@@ -7980,7 +9272,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.88671875" customWidth="1"/>
     <col min="4" max="4" width="3.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.33203125" bestFit="1" customWidth="1"/>

--- a/data/base_creditas.xlsx
+++ b/data/base_creditas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D468CE10-89A6-4972-BDED-7B61EC740751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71455D80-0F10-49F7-8E2C-CFA20B8868FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="30">
   <si>
     <t>Data</t>
   </si>
@@ -500,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W148"/>
+  <dimension ref="A1:W198"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -10695,6 +10695,3547 @@
       </c>
       <c r="W148">
         <v>0.03</v>
+      </c>
+    </row>
+    <row r="149" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A149" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B149">
+        <v>9</v>
+      </c>
+      <c r="C149">
+        <v>81</v>
+      </c>
+      <c r="D149">
+        <v>85</v>
+      </c>
+      <c r="E149" t="s">
+        <v>26</v>
+      </c>
+      <c r="F149">
+        <v>6296</v>
+      </c>
+      <c r="G149">
+        <v>23</v>
+      </c>
+      <c r="H149">
+        <v>0</v>
+      </c>
+      <c r="I149">
+        <v>1154</v>
+      </c>
+      <c r="J149">
+        <v>23</v>
+      </c>
+      <c r="K149">
+        <v>10</v>
+      </c>
+      <c r="L149">
+        <v>0</v>
+      </c>
+      <c r="M149">
+        <v>0</v>
+      </c>
+      <c r="N149">
+        <v>0</v>
+      </c>
+      <c r="O149" s="4">
+        <v>5.7870370370370367E-4</v>
+      </c>
+      <c r="P149" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q149" s="5">
+        <v>1.9900000000000001E-2</v>
+      </c>
+      <c r="R149" s="5">
+        <v>0.43480000000000002</v>
+      </c>
+      <c r="S149" s="3">
+        <v>0</v>
+      </c>
+      <c r="T149">
+        <v>10</v>
+      </c>
+      <c r="U149" s="3">
+        <v>1</v>
+      </c>
+      <c r="V149" t="s">
+        <v>24</v>
+      </c>
+      <c r="W149">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="150" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A150" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B150">
+        <v>11</v>
+      </c>
+      <c r="C150">
+        <v>81</v>
+      </c>
+      <c r="D150">
+        <v>85</v>
+      </c>
+      <c r="E150" t="s">
+        <v>26</v>
+      </c>
+      <c r="F150">
+        <v>6296</v>
+      </c>
+      <c r="G150">
+        <v>25</v>
+      </c>
+      <c r="H150">
+        <v>7</v>
+      </c>
+      <c r="I150">
+        <v>15340</v>
+      </c>
+      <c r="J150">
+        <v>194</v>
+      </c>
+      <c r="K150">
+        <v>60</v>
+      </c>
+      <c r="L150">
+        <v>8</v>
+      </c>
+      <c r="M150">
+        <v>43</v>
+      </c>
+      <c r="N150">
+        <v>0</v>
+      </c>
+      <c r="O150" s="4">
+        <v>9.0277777777777774E-4</v>
+      </c>
+      <c r="P150" s="4">
+        <v>1.0185185185185184E-3</v>
+      </c>
+      <c r="Q150" s="5">
+        <v>1.26E-2</v>
+      </c>
+      <c r="R150" s="5">
+        <v>0.30930000000000002</v>
+      </c>
+      <c r="S150" s="5">
+        <v>0.1333</v>
+      </c>
+      <c r="T150">
+        <v>9</v>
+      </c>
+      <c r="U150" s="5">
+        <v>0.1731</v>
+      </c>
+      <c r="V150" s="5">
+        <v>0.71150000000000002</v>
+      </c>
+      <c r="W150">
+        <v>41.328000000000003</v>
+      </c>
+    </row>
+    <row r="151" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A151" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B151">
+        <v>12</v>
+      </c>
+      <c r="C151">
+        <v>81</v>
+      </c>
+      <c r="D151">
+        <v>85</v>
+      </c>
+      <c r="E151" t="s">
+        <v>26</v>
+      </c>
+      <c r="F151">
+        <v>6296</v>
+      </c>
+      <c r="G151">
+        <v>25</v>
+      </c>
+      <c r="H151">
+        <v>3</v>
+      </c>
+      <c r="I151">
+        <v>13755</v>
+      </c>
+      <c r="J151">
+        <v>106</v>
+      </c>
+      <c r="K151">
+        <v>28</v>
+      </c>
+      <c r="L151">
+        <v>4</v>
+      </c>
+      <c r="M151">
+        <v>19</v>
+      </c>
+      <c r="N151">
+        <v>2</v>
+      </c>
+      <c r="O151" s="4">
+        <v>1.4930555555555556E-3</v>
+      </c>
+      <c r="P151" s="4">
+        <v>9.1435185185185185E-4</v>
+      </c>
+      <c r="Q151" s="5">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="R151" s="5">
+        <v>0.26419999999999999</v>
+      </c>
+      <c r="S151" s="5">
+        <v>0.1429</v>
+      </c>
+      <c r="T151">
+        <v>5</v>
+      </c>
+      <c r="U151" s="5">
+        <v>0.20830000000000001</v>
+      </c>
+      <c r="V151" s="5">
+        <v>0.72</v>
+      </c>
+      <c r="W151">
+        <v>12.054</v>
+      </c>
+    </row>
+    <row r="152" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A152" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B152">
+        <v>13</v>
+      </c>
+      <c r="C152">
+        <v>81</v>
+      </c>
+      <c r="D152">
+        <v>85</v>
+      </c>
+      <c r="E152" t="s">
+        <v>26</v>
+      </c>
+      <c r="F152">
+        <v>6296</v>
+      </c>
+      <c r="G152">
+        <v>25</v>
+      </c>
+      <c r="H152">
+        <v>2</v>
+      </c>
+      <c r="I152">
+        <v>10249</v>
+      </c>
+      <c r="J152">
+        <v>69</v>
+      </c>
+      <c r="K152">
+        <v>27</v>
+      </c>
+      <c r="L152">
+        <v>5</v>
+      </c>
+      <c r="M152">
+        <v>7</v>
+      </c>
+      <c r="N152">
+        <v>0</v>
+      </c>
+      <c r="O152" s="4">
+        <v>1.712962962962963E-3</v>
+      </c>
+      <c r="P152" s="4">
+        <v>1.5972222222222223E-3</v>
+      </c>
+      <c r="Q152" s="5">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="R152" s="5">
+        <v>0.39129999999999998</v>
+      </c>
+      <c r="S152" s="5">
+        <v>0.1852</v>
+      </c>
+      <c r="T152">
+        <v>15</v>
+      </c>
+      <c r="U152" s="5">
+        <v>0.68179999999999996</v>
+      </c>
+      <c r="V152" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="W152">
+        <v>7.5720000000000001</v>
+      </c>
+    </row>
+    <row r="153" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A153" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B153">
+        <v>14</v>
+      </c>
+      <c r="C153">
+        <v>81</v>
+      </c>
+      <c r="D153">
+        <v>85</v>
+      </c>
+      <c r="E153" t="s">
+        <v>26</v>
+      </c>
+      <c r="F153">
+        <v>6296</v>
+      </c>
+      <c r="G153">
+        <v>25</v>
+      </c>
+      <c r="H153">
+        <v>3</v>
+      </c>
+      <c r="I153">
+        <v>3450</v>
+      </c>
+      <c r="J153">
+        <v>51</v>
+      </c>
+      <c r="K153">
+        <v>16</v>
+      </c>
+      <c r="L153">
+        <v>1</v>
+      </c>
+      <c r="M153">
+        <v>14</v>
+      </c>
+      <c r="N153">
+        <v>0</v>
+      </c>
+      <c r="O153" s="4">
+        <v>7.7546296296296293E-4</v>
+      </c>
+      <c r="P153" s="4">
+        <v>2.2569444444444442E-3</v>
+      </c>
+      <c r="Q153" s="5">
+        <v>1.4800000000000001E-2</v>
+      </c>
+      <c r="R153" s="5">
+        <v>0.31369999999999998</v>
+      </c>
+      <c r="S153" s="5">
+        <v>6.25E-2</v>
+      </c>
+      <c r="T153">
+        <v>1</v>
+      </c>
+      <c r="U153" s="5">
+        <v>6.6699999999999995E-2</v>
+      </c>
+      <c r="V153" s="5">
+        <v>0.70589999999999997</v>
+      </c>
+      <c r="W153">
+        <v>17.202000000000002</v>
+      </c>
+    </row>
+    <row r="154" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A154" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B154">
+        <v>15</v>
+      </c>
+      <c r="C154">
+        <v>81</v>
+      </c>
+      <c r="D154">
+        <v>85</v>
+      </c>
+      <c r="E154" t="s">
+        <v>26</v>
+      </c>
+      <c r="F154">
+        <v>6296</v>
+      </c>
+      <c r="G154">
+        <v>25</v>
+      </c>
+      <c r="H154">
+        <v>5</v>
+      </c>
+      <c r="I154">
+        <v>4341</v>
+      </c>
+      <c r="J154">
+        <v>61</v>
+      </c>
+      <c r="K154">
+        <v>13</v>
+      </c>
+      <c r="L154">
+        <v>0</v>
+      </c>
+      <c r="M154">
+        <v>13</v>
+      </c>
+      <c r="N154">
+        <v>0</v>
+      </c>
+      <c r="O154" s="4">
+        <v>8.2175925925925927E-4</v>
+      </c>
+      <c r="P154" s="4">
+        <v>1.0185185185185184E-3</v>
+      </c>
+      <c r="Q154" s="5">
+        <v>1.41E-2</v>
+      </c>
+      <c r="R154" s="5">
+        <v>0.21310000000000001</v>
+      </c>
+      <c r="S154" s="3">
+        <v>0</v>
+      </c>
+      <c r="T154">
+        <v>0</v>
+      </c>
+      <c r="U154" s="3">
+        <v>0</v>
+      </c>
+      <c r="V154" s="5">
+        <v>0.92310000000000003</v>
+      </c>
+      <c r="W154">
+        <v>14.43</v>
+      </c>
+    </row>
+    <row r="155" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A155" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B155">
+        <v>16</v>
+      </c>
+      <c r="C155">
+        <v>81</v>
+      </c>
+      <c r="D155">
+        <v>85</v>
+      </c>
+      <c r="E155" t="s">
+        <v>26</v>
+      </c>
+      <c r="F155">
+        <v>6296</v>
+      </c>
+      <c r="G155">
+        <v>25</v>
+      </c>
+      <c r="H155">
+        <v>5</v>
+      </c>
+      <c r="I155">
+        <v>15744</v>
+      </c>
+      <c r="J155">
+        <v>76</v>
+      </c>
+      <c r="K155">
+        <v>16</v>
+      </c>
+      <c r="L155">
+        <v>2</v>
+      </c>
+      <c r="M155">
+        <v>14</v>
+      </c>
+      <c r="N155">
+        <v>0</v>
+      </c>
+      <c r="O155" s="4">
+        <v>2.3842592592592591E-3</v>
+      </c>
+      <c r="P155" s="4">
+        <v>1.3425925925925925E-3</v>
+      </c>
+      <c r="Q155" s="5">
+        <v>4.7999999999999996E-3</v>
+      </c>
+      <c r="R155" s="5">
+        <v>0.21049999999999999</v>
+      </c>
+      <c r="S155" s="5">
+        <v>0.125</v>
+      </c>
+      <c r="T155">
+        <v>0</v>
+      </c>
+      <c r="U155" s="3">
+        <v>0</v>
+      </c>
+      <c r="V155" s="5">
+        <v>0.64290000000000003</v>
+      </c>
+      <c r="W155">
+        <v>19.77</v>
+      </c>
+    </row>
+    <row r="156" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A156" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B156">
+        <v>17</v>
+      </c>
+      <c r="C156">
+        <v>81</v>
+      </c>
+      <c r="D156">
+        <v>85</v>
+      </c>
+      <c r="E156" t="s">
+        <v>26</v>
+      </c>
+      <c r="F156">
+        <v>6296</v>
+      </c>
+      <c r="G156">
+        <v>25</v>
+      </c>
+      <c r="H156">
+        <v>4</v>
+      </c>
+      <c r="I156">
+        <v>17046</v>
+      </c>
+      <c r="J156">
+        <v>93</v>
+      </c>
+      <c r="K156">
+        <v>21</v>
+      </c>
+      <c r="L156">
+        <v>4</v>
+      </c>
+      <c r="M156">
+        <v>14</v>
+      </c>
+      <c r="N156">
+        <v>0</v>
+      </c>
+      <c r="O156" s="4">
+        <v>2.1180555555555558E-3</v>
+      </c>
+      <c r="P156" s="4">
+        <v>1.1689814814814816E-3</v>
+      </c>
+      <c r="Q156" s="5">
+        <v>5.4999999999999997E-3</v>
+      </c>
+      <c r="R156" s="5">
+        <v>0.2258</v>
+      </c>
+      <c r="S156" s="5">
+        <v>0.1905</v>
+      </c>
+      <c r="T156">
+        <v>3</v>
+      </c>
+      <c r="U156" s="5">
+        <v>0.17649999999999999</v>
+      </c>
+      <c r="V156" s="5">
+        <v>0.73329999999999995</v>
+      </c>
+      <c r="W156">
+        <v>18.600000000000001</v>
+      </c>
+    </row>
+    <row r="157" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A157" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B157">
+        <v>18</v>
+      </c>
+      <c r="C157">
+        <v>81</v>
+      </c>
+      <c r="D157">
+        <v>85</v>
+      </c>
+      <c r="E157" t="s">
+        <v>26</v>
+      </c>
+      <c r="F157">
+        <v>6296</v>
+      </c>
+      <c r="G157">
+        <v>0</v>
+      </c>
+      <c r="H157">
+        <v>0</v>
+      </c>
+      <c r="I157">
+        <v>125</v>
+      </c>
+      <c r="J157">
+        <v>0</v>
+      </c>
+      <c r="K157">
+        <v>0</v>
+      </c>
+      <c r="L157">
+        <v>0</v>
+      </c>
+      <c r="M157">
+        <v>0</v>
+      </c>
+      <c r="N157">
+        <v>0</v>
+      </c>
+      <c r="O157" t="s">
+        <v>23</v>
+      </c>
+      <c r="P157" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q157" s="3">
+        <v>0</v>
+      </c>
+      <c r="R157" t="s">
+        <v>24</v>
+      </c>
+      <c r="S157" t="s">
+        <v>24</v>
+      </c>
+      <c r="T157">
+        <v>0</v>
+      </c>
+      <c r="U157" t="s">
+        <v>24</v>
+      </c>
+      <c r="V157" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A158" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B158">
+        <v>9</v>
+      </c>
+      <c r="C158">
+        <v>81</v>
+      </c>
+      <c r="D158">
+        <v>85</v>
+      </c>
+      <c r="E158" t="s">
+        <v>26</v>
+      </c>
+      <c r="F158">
+        <v>10273</v>
+      </c>
+      <c r="G158">
+        <v>25</v>
+      </c>
+      <c r="H158">
+        <v>5</v>
+      </c>
+      <c r="I158">
+        <v>11546</v>
+      </c>
+      <c r="J158">
+        <v>140</v>
+      </c>
+      <c r="K158">
+        <v>33</v>
+      </c>
+      <c r="L158">
+        <v>11</v>
+      </c>
+      <c r="M158">
+        <v>11</v>
+      </c>
+      <c r="N158">
+        <v>0</v>
+      </c>
+      <c r="O158" s="4">
+        <v>9.4907407407407408E-4</v>
+      </c>
+      <c r="P158" s="4">
+        <v>3.2407407407407406E-4</v>
+      </c>
+      <c r="Q158" s="5">
+        <v>1.21E-2</v>
+      </c>
+      <c r="R158" s="5">
+        <v>0.23569999999999999</v>
+      </c>
+      <c r="S158" s="5">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="T158">
+        <v>11</v>
+      </c>
+      <c r="U158" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V158" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="W158">
+        <v>34.590000000000003</v>
+      </c>
+    </row>
+    <row r="159" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A159" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B159">
+        <v>10</v>
+      </c>
+      <c r="C159">
+        <v>81</v>
+      </c>
+      <c r="D159">
+        <v>85</v>
+      </c>
+      <c r="E159" t="s">
+        <v>26</v>
+      </c>
+      <c r="F159">
+        <v>10273</v>
+      </c>
+      <c r="G159">
+        <v>25</v>
+      </c>
+      <c r="H159">
+        <v>8</v>
+      </c>
+      <c r="I159">
+        <v>37400</v>
+      </c>
+      <c r="J159">
+        <v>247</v>
+      </c>
+      <c r="K159">
+        <v>77</v>
+      </c>
+      <c r="L159">
+        <v>42</v>
+      </c>
+      <c r="M159">
+        <v>29</v>
+      </c>
+      <c r="N159">
+        <v>0</v>
+      </c>
+      <c r="O159" s="4">
+        <v>1.7476851851851852E-3</v>
+      </c>
+      <c r="P159" s="4">
+        <v>1.8981481481481482E-3</v>
+      </c>
+      <c r="Q159" s="5">
+        <v>6.6E-3</v>
+      </c>
+      <c r="R159" s="5">
+        <v>0.31169999999999998</v>
+      </c>
+      <c r="S159" s="5">
+        <v>0.54549999999999998</v>
+      </c>
+      <c r="T159">
+        <v>6</v>
+      </c>
+      <c r="U159" s="5">
+        <v>0.1714</v>
+      </c>
+      <c r="V159" s="5">
+        <v>0.76470000000000005</v>
+      </c>
+      <c r="W159">
+        <v>51.036000000000001</v>
+      </c>
+    </row>
+    <row r="160" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A160" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B160">
+        <v>11</v>
+      </c>
+      <c r="C160">
+        <v>81</v>
+      </c>
+      <c r="D160">
+        <v>85</v>
+      </c>
+      <c r="E160" t="s">
+        <v>26</v>
+      </c>
+      <c r="F160">
+        <v>10273</v>
+      </c>
+      <c r="G160">
+        <v>25</v>
+      </c>
+      <c r="H160">
+        <v>10</v>
+      </c>
+      <c r="I160">
+        <v>39400</v>
+      </c>
+      <c r="J160">
+        <v>279</v>
+      </c>
+      <c r="K160">
+        <v>62</v>
+      </c>
+      <c r="L160">
+        <v>30</v>
+      </c>
+      <c r="M160">
+        <v>32</v>
+      </c>
+      <c r="N160">
+        <v>0</v>
+      </c>
+      <c r="O160" s="4">
+        <v>1.6203703703703703E-3</v>
+      </c>
+      <c r="P160" s="4">
+        <v>5.9027777777777778E-4</v>
+      </c>
+      <c r="Q160" s="5">
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="R160" s="5">
+        <v>0.22220000000000001</v>
+      </c>
+      <c r="S160" s="5">
+        <v>0.4839</v>
+      </c>
+      <c r="T160">
+        <v>0</v>
+      </c>
+      <c r="U160" s="3">
+        <v>0</v>
+      </c>
+      <c r="V160" s="5">
+        <v>1</v>
+      </c>
+      <c r="W160">
+        <v>34.014000000000003</v>
+      </c>
+    </row>
+    <row r="161" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A161" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B161">
+        <v>12</v>
+      </c>
+      <c r="C161">
+        <v>81</v>
+      </c>
+      <c r="D161">
+        <v>85</v>
+      </c>
+      <c r="E161" t="s">
+        <v>26</v>
+      </c>
+      <c r="F161">
+        <v>10273</v>
+      </c>
+      <c r="G161">
+        <v>25</v>
+      </c>
+      <c r="H161">
+        <v>12</v>
+      </c>
+      <c r="I161">
+        <v>28100</v>
+      </c>
+      <c r="J161">
+        <v>246</v>
+      </c>
+      <c r="K161">
+        <v>64</v>
+      </c>
+      <c r="L161">
+        <v>26</v>
+      </c>
+      <c r="M161">
+        <v>38</v>
+      </c>
+      <c r="N161">
+        <v>1</v>
+      </c>
+      <c r="O161" s="4">
+        <v>1.3194444444444445E-3</v>
+      </c>
+      <c r="P161" s="4">
+        <v>1.6550925925925926E-3</v>
+      </c>
+      <c r="Q161" s="5">
+        <v>8.8000000000000005E-3</v>
+      </c>
+      <c r="R161" s="5">
+        <v>0.26019999999999999</v>
+      </c>
+      <c r="S161" s="5">
+        <v>0.40629999999999999</v>
+      </c>
+      <c r="T161">
+        <v>0</v>
+      </c>
+      <c r="U161" s="3">
+        <v>0</v>
+      </c>
+      <c r="V161" s="5">
+        <v>1</v>
+      </c>
+      <c r="W161">
+        <v>37.728000000000002</v>
+      </c>
+    </row>
+    <row r="162" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A162" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B162">
+        <v>13</v>
+      </c>
+      <c r="C162">
+        <v>81</v>
+      </c>
+      <c r="D162">
+        <v>85</v>
+      </c>
+      <c r="E162" t="s">
+        <v>26</v>
+      </c>
+      <c r="F162">
+        <v>10273</v>
+      </c>
+      <c r="G162">
+        <v>25</v>
+      </c>
+      <c r="H162">
+        <v>8</v>
+      </c>
+      <c r="I162">
+        <v>12290</v>
+      </c>
+      <c r="J162">
+        <v>174</v>
+      </c>
+      <c r="K162">
+        <v>45</v>
+      </c>
+      <c r="L162">
+        <v>20</v>
+      </c>
+      <c r="M162">
+        <v>25</v>
+      </c>
+      <c r="N162">
+        <v>1</v>
+      </c>
+      <c r="O162" s="4">
+        <v>8.1018518518518516E-4</v>
+      </c>
+      <c r="P162" s="4">
+        <v>1.4814814814814814E-3</v>
+      </c>
+      <c r="Q162" s="5">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="R162" s="5">
+        <v>0.2586</v>
+      </c>
+      <c r="S162" s="5">
+        <v>0.44440000000000002</v>
+      </c>
+      <c r="T162">
+        <v>0</v>
+      </c>
+      <c r="U162" s="3">
+        <v>0</v>
+      </c>
+      <c r="V162" s="5">
+        <v>0.96150000000000002</v>
+      </c>
+      <c r="W162">
+        <v>27.713999999999999</v>
+      </c>
+    </row>
+    <row r="163" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A163" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B163">
+        <v>13</v>
+      </c>
+      <c r="C163">
+        <v>84</v>
+      </c>
+      <c r="D163">
+        <v>86</v>
+      </c>
+      <c r="E163" t="s">
+        <v>25</v>
+      </c>
+      <c r="F163">
+        <v>29563</v>
+      </c>
+      <c r="G163">
+        <v>10</v>
+      </c>
+      <c r="H163">
+        <v>1</v>
+      </c>
+      <c r="I163">
+        <v>201</v>
+      </c>
+      <c r="J163">
+        <v>10</v>
+      </c>
+      <c r="K163">
+        <v>2</v>
+      </c>
+      <c r="L163">
+        <v>1</v>
+      </c>
+      <c r="M163">
+        <v>1</v>
+      </c>
+      <c r="N163">
+        <v>0</v>
+      </c>
+      <c r="O163" s="4">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="P163" s="4">
+        <v>4.7453703703703704E-4</v>
+      </c>
+      <c r="Q163" s="5">
+        <v>4.9799999999999997E-2</v>
+      </c>
+      <c r="R163" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="S163" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="T163">
+        <v>0</v>
+      </c>
+      <c r="U163" s="3">
+        <v>0</v>
+      </c>
+      <c r="V163" s="5">
+        <v>0</v>
+      </c>
+      <c r="W163">
+        <v>0.88200000000000001</v>
+      </c>
+    </row>
+    <row r="164" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A164" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B164">
+        <v>14</v>
+      </c>
+      <c r="C164">
+        <v>81</v>
+      </c>
+      <c r="D164">
+        <v>85</v>
+      </c>
+      <c r="E164" t="s">
+        <v>26</v>
+      </c>
+      <c r="F164">
+        <v>10273</v>
+      </c>
+      <c r="G164">
+        <v>25</v>
+      </c>
+      <c r="H164">
+        <v>7</v>
+      </c>
+      <c r="I164">
+        <v>4902</v>
+      </c>
+      <c r="J164">
+        <v>91</v>
+      </c>
+      <c r="K164">
+        <v>16</v>
+      </c>
+      <c r="L164">
+        <v>4</v>
+      </c>
+      <c r="M164">
+        <v>11</v>
+      </c>
+      <c r="N164">
+        <v>0</v>
+      </c>
+      <c r="O164" s="4">
+        <v>6.134259259259259E-4</v>
+      </c>
+      <c r="P164" s="4">
+        <v>1.5393518518518519E-3</v>
+      </c>
+      <c r="Q164" s="5">
+        <v>1.8599999999999998E-2</v>
+      </c>
+      <c r="R164" s="5">
+        <v>0.17580000000000001</v>
+      </c>
+      <c r="S164" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="T164">
+        <v>1</v>
+      </c>
+      <c r="U164" s="5">
+        <v>8.3299999999999999E-2</v>
+      </c>
+      <c r="V164" s="5">
+        <v>0.85709999999999997</v>
+      </c>
+      <c r="W164">
+        <v>9.0660000000000007</v>
+      </c>
+    </row>
+    <row r="165" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A165" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B165">
+        <v>14</v>
+      </c>
+      <c r="C165">
+        <v>84</v>
+      </c>
+      <c r="D165">
+        <v>86</v>
+      </c>
+      <c r="E165" t="s">
+        <v>25</v>
+      </c>
+      <c r="F165">
+        <v>29563</v>
+      </c>
+      <c r="G165">
+        <v>25</v>
+      </c>
+      <c r="H165">
+        <v>2</v>
+      </c>
+      <c r="I165">
+        <v>12861</v>
+      </c>
+      <c r="J165">
+        <v>202</v>
+      </c>
+      <c r="K165">
+        <v>47</v>
+      </c>
+      <c r="L165">
+        <v>17</v>
+      </c>
+      <c r="M165">
+        <v>27</v>
+      </c>
+      <c r="N165">
+        <v>1</v>
+      </c>
+      <c r="O165" s="4">
+        <v>7.291666666666667E-4</v>
+      </c>
+      <c r="P165" s="4">
+        <v>4.9768518518518521E-4</v>
+      </c>
+      <c r="Q165" s="5">
+        <v>1.5699999999999999E-2</v>
+      </c>
+      <c r="R165" s="5">
+        <v>0.23269999999999999</v>
+      </c>
+      <c r="S165" s="5">
+        <v>0.36170000000000002</v>
+      </c>
+      <c r="T165">
+        <v>3</v>
+      </c>
+      <c r="U165" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="V165" s="5">
+        <v>0.60609999999999997</v>
+      </c>
+      <c r="W165">
+        <v>24.731999999999999</v>
+      </c>
+    </row>
+    <row r="166" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A166" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B166">
+        <v>15</v>
+      </c>
+      <c r="C166">
+        <v>81</v>
+      </c>
+      <c r="D166">
+        <v>85</v>
+      </c>
+      <c r="E166" t="s">
+        <v>26</v>
+      </c>
+      <c r="F166">
+        <v>10273</v>
+      </c>
+      <c r="G166">
+        <v>25</v>
+      </c>
+      <c r="H166">
+        <v>0</v>
+      </c>
+      <c r="I166">
+        <v>2338</v>
+      </c>
+      <c r="J166">
+        <v>27</v>
+      </c>
+      <c r="K166">
+        <v>2</v>
+      </c>
+      <c r="L166">
+        <v>2</v>
+      </c>
+      <c r="M166">
+        <v>0</v>
+      </c>
+      <c r="N166">
+        <v>0</v>
+      </c>
+      <c r="O166" s="4">
+        <v>9.9537037037037042E-4</v>
+      </c>
+      <c r="P166" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q166" s="5">
+        <v>1.15E-2</v>
+      </c>
+      <c r="R166" s="5">
+        <v>7.4099999999999999E-2</v>
+      </c>
+      <c r="S166" s="3">
+        <v>1</v>
+      </c>
+      <c r="T166">
+        <v>0</v>
+      </c>
+      <c r="U166" t="s">
+        <v>24</v>
+      </c>
+      <c r="V166" t="s">
+        <v>24</v>
+      </c>
+      <c r="W166">
+        <v>7.1459999999999999</v>
+      </c>
+    </row>
+    <row r="167" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A167" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B167">
+        <v>15</v>
+      </c>
+      <c r="C167">
+        <v>84</v>
+      </c>
+      <c r="D167">
+        <v>86</v>
+      </c>
+      <c r="E167" t="s">
+        <v>25</v>
+      </c>
+      <c r="F167">
+        <v>29563</v>
+      </c>
+      <c r="G167">
+        <v>25</v>
+      </c>
+      <c r="H167">
+        <v>2</v>
+      </c>
+      <c r="I167">
+        <v>16078</v>
+      </c>
+      <c r="J167">
+        <v>161</v>
+      </c>
+      <c r="K167">
+        <v>48</v>
+      </c>
+      <c r="L167">
+        <v>29</v>
+      </c>
+      <c r="M167">
+        <v>19</v>
+      </c>
+      <c r="N167">
+        <v>0</v>
+      </c>
+      <c r="O167" s="4">
+        <v>1.1458333333333333E-3</v>
+      </c>
+      <c r="P167" s="4">
+        <v>4.861111111111111E-4</v>
+      </c>
+      <c r="Q167" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="R167" s="5">
+        <v>0.29809999999999998</v>
+      </c>
+      <c r="S167" s="5">
+        <v>0.60419999999999996</v>
+      </c>
+      <c r="T167">
+        <v>0</v>
+      </c>
+      <c r="U167" s="3">
+        <v>0</v>
+      </c>
+      <c r="V167" s="5">
+        <v>0.44740000000000002</v>
+      </c>
+      <c r="W167">
+        <v>17.190000000000001</v>
+      </c>
+    </row>
+    <row r="168" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A168" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B168">
+        <v>16</v>
+      </c>
+      <c r="C168">
+        <v>81</v>
+      </c>
+      <c r="D168">
+        <v>85</v>
+      </c>
+      <c r="E168" t="s">
+        <v>26</v>
+      </c>
+      <c r="F168">
+        <v>10273</v>
+      </c>
+      <c r="G168">
+        <v>25</v>
+      </c>
+      <c r="H168">
+        <v>6</v>
+      </c>
+      <c r="I168">
+        <v>7276</v>
+      </c>
+      <c r="J168">
+        <v>123</v>
+      </c>
+      <c r="K168">
+        <v>17</v>
+      </c>
+      <c r="L168">
+        <v>6</v>
+      </c>
+      <c r="M168">
+        <v>10</v>
+      </c>
+      <c r="N168">
+        <v>0</v>
+      </c>
+      <c r="O168" s="4">
+        <v>6.7129629629629625E-4</v>
+      </c>
+      <c r="P168" s="4">
+        <v>4.5138888888888887E-4</v>
+      </c>
+      <c r="Q168" s="5">
+        <v>1.6899999999999998E-2</v>
+      </c>
+      <c r="R168" s="5">
+        <v>0.13819999999999999</v>
+      </c>
+      <c r="S168" s="5">
+        <v>0.35289999999999999</v>
+      </c>
+      <c r="T168">
+        <v>1</v>
+      </c>
+      <c r="U168" s="5">
+        <v>9.0899999999999995E-2</v>
+      </c>
+      <c r="V168" s="5">
+        <v>0.81820000000000004</v>
+      </c>
+      <c r="W168">
+        <v>17.574000000000002</v>
+      </c>
+    </row>
+    <row r="169" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A169" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B169">
+        <v>16</v>
+      </c>
+      <c r="C169">
+        <v>84</v>
+      </c>
+      <c r="D169">
+        <v>86</v>
+      </c>
+      <c r="E169" t="s">
+        <v>25</v>
+      </c>
+      <c r="F169">
+        <v>29563</v>
+      </c>
+      <c r="G169">
+        <v>25</v>
+      </c>
+      <c r="H169">
+        <v>2</v>
+      </c>
+      <c r="I169">
+        <v>16063</v>
+      </c>
+      <c r="J169">
+        <v>204</v>
+      </c>
+      <c r="K169">
+        <v>63</v>
+      </c>
+      <c r="L169">
+        <v>25</v>
+      </c>
+      <c r="M169">
+        <v>38</v>
+      </c>
+      <c r="N169">
+        <v>1</v>
+      </c>
+      <c r="O169" s="4">
+        <v>9.0277777777777774E-4</v>
+      </c>
+      <c r="P169" s="4">
+        <v>6.7129629629629625E-4</v>
+      </c>
+      <c r="Q169" s="5">
+        <v>1.2699999999999999E-2</v>
+      </c>
+      <c r="R169" s="5">
+        <v>0.30880000000000002</v>
+      </c>
+      <c r="S169" s="5">
+        <v>0.39679999999999999</v>
+      </c>
+      <c r="T169">
+        <v>0</v>
+      </c>
+      <c r="U169" s="3">
+        <v>0</v>
+      </c>
+      <c r="V169" s="5">
+        <v>0.51849999999999996</v>
+      </c>
+      <c r="W169">
+        <v>18.276</v>
+      </c>
+    </row>
+    <row r="170" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A170" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B170">
+        <v>17</v>
+      </c>
+      <c r="C170">
+        <v>81</v>
+      </c>
+      <c r="D170">
+        <v>85</v>
+      </c>
+      <c r="E170" t="s">
+        <v>26</v>
+      </c>
+      <c r="F170">
+        <v>10273</v>
+      </c>
+      <c r="G170">
+        <v>8</v>
+      </c>
+      <c r="H170">
+        <v>0</v>
+      </c>
+      <c r="I170">
+        <v>1769</v>
+      </c>
+      <c r="J170">
+        <v>8</v>
+      </c>
+      <c r="K170">
+        <v>0</v>
+      </c>
+      <c r="L170">
+        <v>0</v>
+      </c>
+      <c r="M170">
+        <v>0</v>
+      </c>
+      <c r="N170">
+        <v>0</v>
+      </c>
+      <c r="O170" s="4">
+        <v>2.5578703703703705E-3</v>
+      </c>
+      <c r="P170" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q170" s="5">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="R170" s="3">
+        <v>0</v>
+      </c>
+      <c r="S170" t="s">
+        <v>24</v>
+      </c>
+      <c r="T170">
+        <v>0</v>
+      </c>
+      <c r="U170" t="s">
+        <v>24</v>
+      </c>
+      <c r="V170" t="s">
+        <v>24</v>
+      </c>
+      <c r="W170">
+        <v>3.5819999999999999</v>
+      </c>
+    </row>
+    <row r="171" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A171" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B171">
+        <v>17</v>
+      </c>
+      <c r="C171">
+        <v>84</v>
+      </c>
+      <c r="D171">
+        <v>86</v>
+      </c>
+      <c r="E171" t="s">
+        <v>25</v>
+      </c>
+      <c r="F171">
+        <v>29563</v>
+      </c>
+      <c r="G171">
+        <v>24</v>
+      </c>
+      <c r="H171">
+        <v>2</v>
+      </c>
+      <c r="I171">
+        <v>1021</v>
+      </c>
+      <c r="J171">
+        <v>25</v>
+      </c>
+      <c r="K171">
+        <v>5</v>
+      </c>
+      <c r="L171">
+        <v>1</v>
+      </c>
+      <c r="M171">
+        <v>4</v>
+      </c>
+      <c r="N171">
+        <v>0</v>
+      </c>
+      <c r="O171" s="4">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="P171" s="4">
+        <v>5.6712962962962967E-4</v>
+      </c>
+      <c r="Q171" s="5">
+        <v>2.4500000000000001E-2</v>
+      </c>
+      <c r="R171" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="S171" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="T171">
+        <v>0</v>
+      </c>
+      <c r="U171" s="3">
+        <v>0</v>
+      </c>
+      <c r="V171" s="5">
+        <v>1</v>
+      </c>
+      <c r="W171">
+        <v>2.802</v>
+      </c>
+    </row>
+    <row r="172" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A172" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B172">
+        <v>18</v>
+      </c>
+      <c r="C172">
+        <v>81</v>
+      </c>
+      <c r="D172">
+        <v>85</v>
+      </c>
+      <c r="E172" t="s">
+        <v>26</v>
+      </c>
+      <c r="F172">
+        <v>10273</v>
+      </c>
+      <c r="G172">
+        <v>1</v>
+      </c>
+      <c r="H172">
+        <v>0</v>
+      </c>
+      <c r="I172">
+        <v>301</v>
+      </c>
+      <c r="J172">
+        <v>1</v>
+      </c>
+      <c r="K172">
+        <v>1</v>
+      </c>
+      <c r="L172">
+        <v>1</v>
+      </c>
+      <c r="M172">
+        <v>0</v>
+      </c>
+      <c r="N172">
+        <v>0</v>
+      </c>
+      <c r="O172" s="4">
+        <v>2.7546296296296294E-3</v>
+      </c>
+      <c r="P172" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q172" s="5">
+        <v>3.3E-3</v>
+      </c>
+      <c r="R172" s="3">
+        <v>1</v>
+      </c>
+      <c r="S172" s="3">
+        <v>1</v>
+      </c>
+      <c r="T172">
+        <v>0</v>
+      </c>
+      <c r="U172" t="s">
+        <v>24</v>
+      </c>
+      <c r="V172" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="173" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A173" s="2">
+        <v>46197</v>
+      </c>
+      <c r="B173">
+        <v>9</v>
+      </c>
+      <c r="C173">
+        <v>81</v>
+      </c>
+      <c r="D173">
+        <v>85</v>
+      </c>
+      <c r="E173" t="s">
+        <v>26</v>
+      </c>
+      <c r="F173">
+        <v>13133</v>
+      </c>
+      <c r="G173">
+        <v>25</v>
+      </c>
+      <c r="H173">
+        <v>7</v>
+      </c>
+      <c r="I173">
+        <v>39259</v>
+      </c>
+      <c r="J173">
+        <v>449</v>
+      </c>
+      <c r="K173">
+        <v>120</v>
+      </c>
+      <c r="L173">
+        <v>68</v>
+      </c>
+      <c r="M173">
+        <v>43</v>
+      </c>
+      <c r="N173">
+        <v>1</v>
+      </c>
+      <c r="O173" s="4">
+        <v>1.0069444444444444E-3</v>
+      </c>
+      <c r="P173" s="4">
+        <v>2.1759259259259258E-3</v>
+      </c>
+      <c r="Q173" s="5">
+        <v>1.14E-2</v>
+      </c>
+      <c r="R173" s="5">
+        <v>0.26729999999999998</v>
+      </c>
+      <c r="S173" s="5">
+        <v>0.56669999999999998</v>
+      </c>
+      <c r="T173">
+        <v>9</v>
+      </c>
+      <c r="U173" s="5">
+        <v>0.1731</v>
+      </c>
+      <c r="V173" s="5">
+        <v>0.77549999999999997</v>
+      </c>
+      <c r="W173">
+        <v>115.176</v>
+      </c>
+    </row>
+    <row r="174" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A174" s="2">
+        <v>46197</v>
+      </c>
+      <c r="B174">
+        <v>10</v>
+      </c>
+      <c r="C174">
+        <v>81</v>
+      </c>
+      <c r="D174">
+        <v>85</v>
+      </c>
+      <c r="E174" t="s">
+        <v>26</v>
+      </c>
+      <c r="F174">
+        <v>13133</v>
+      </c>
+      <c r="G174">
+        <v>25</v>
+      </c>
+      <c r="H174">
+        <v>9</v>
+      </c>
+      <c r="I174">
+        <v>49673</v>
+      </c>
+      <c r="J174">
+        <v>488</v>
+      </c>
+      <c r="K174">
+        <v>111</v>
+      </c>
+      <c r="L174">
+        <v>58</v>
+      </c>
+      <c r="M174">
+        <v>49</v>
+      </c>
+      <c r="N174">
+        <v>1</v>
+      </c>
+      <c r="O174" s="4">
+        <v>1.1689814814814816E-3</v>
+      </c>
+      <c r="P174" s="4">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="Q174" s="5">
+        <v>9.7999999999999997E-3</v>
+      </c>
+      <c r="R174" s="5">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="S174" s="5">
+        <v>0.52249999999999996</v>
+      </c>
+      <c r="T174">
+        <v>4</v>
+      </c>
+      <c r="U174" s="5">
+        <v>7.5499999999999998E-2</v>
+      </c>
+      <c r="V174" s="5">
+        <v>0.79630000000000001</v>
+      </c>
+      <c r="W174">
+        <v>54.893999999999998</v>
+      </c>
+    </row>
+    <row r="175" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A175" s="2">
+        <v>46197</v>
+      </c>
+      <c r="B175">
+        <v>11</v>
+      </c>
+      <c r="C175">
+        <v>81</v>
+      </c>
+      <c r="D175">
+        <v>85</v>
+      </c>
+      <c r="E175" t="s">
+        <v>26</v>
+      </c>
+      <c r="F175">
+        <v>13133</v>
+      </c>
+      <c r="G175">
+        <v>25</v>
+      </c>
+      <c r="H175">
+        <v>12</v>
+      </c>
+      <c r="I175">
+        <v>20164</v>
+      </c>
+      <c r="J175">
+        <v>181</v>
+      </c>
+      <c r="K175">
+        <v>49</v>
+      </c>
+      <c r="L175">
+        <v>28</v>
+      </c>
+      <c r="M175">
+        <v>21</v>
+      </c>
+      <c r="N175">
+        <v>0</v>
+      </c>
+      <c r="O175" s="4">
+        <v>1.2847222222222223E-3</v>
+      </c>
+      <c r="P175" s="4">
+        <v>1.4351851851851852E-3</v>
+      </c>
+      <c r="Q175" s="5">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="R175" s="5">
+        <v>0.2707</v>
+      </c>
+      <c r="S175" s="5">
+        <v>0.57140000000000002</v>
+      </c>
+      <c r="T175">
+        <v>0</v>
+      </c>
+      <c r="U175" s="3">
+        <v>0</v>
+      </c>
+      <c r="V175" s="5">
+        <v>1</v>
+      </c>
+      <c r="W175">
+        <v>15.282</v>
+      </c>
+    </row>
+    <row r="176" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A176" s="2">
+        <v>46197</v>
+      </c>
+      <c r="B176">
+        <v>12</v>
+      </c>
+      <c r="C176">
+        <v>81</v>
+      </c>
+      <c r="D176">
+        <v>85</v>
+      </c>
+      <c r="E176" t="s">
+        <v>26</v>
+      </c>
+      <c r="F176">
+        <v>13133</v>
+      </c>
+      <c r="G176">
+        <v>25</v>
+      </c>
+      <c r="H176">
+        <v>10</v>
+      </c>
+      <c r="I176">
+        <v>5656</v>
+      </c>
+      <c r="J176">
+        <v>111</v>
+      </c>
+      <c r="K176">
+        <v>36</v>
+      </c>
+      <c r="L176">
+        <v>19</v>
+      </c>
+      <c r="M176">
+        <v>17</v>
+      </c>
+      <c r="N176">
+        <v>0</v>
+      </c>
+      <c r="O176" s="4">
+        <v>5.7870370370370367E-4</v>
+      </c>
+      <c r="P176" s="4">
+        <v>1.0416666666666667E-3</v>
+      </c>
+      <c r="Q176" s="5">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="R176" s="5">
+        <v>0.32429999999999998</v>
+      </c>
+      <c r="S176" s="5">
+        <v>0.52780000000000005</v>
+      </c>
+      <c r="T176">
+        <v>0</v>
+      </c>
+      <c r="U176" s="3">
+        <v>0</v>
+      </c>
+      <c r="V176" s="5">
+        <v>1</v>
+      </c>
+      <c r="W176">
+        <v>24.318000000000001</v>
+      </c>
+    </row>
+    <row r="177" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A177" s="2">
+        <v>46197</v>
+      </c>
+      <c r="B177">
+        <v>13</v>
+      </c>
+      <c r="C177">
+        <v>81</v>
+      </c>
+      <c r="D177">
+        <v>85</v>
+      </c>
+      <c r="E177" t="s">
+        <v>26</v>
+      </c>
+      <c r="F177">
+        <v>13133</v>
+      </c>
+      <c r="G177">
+        <v>25</v>
+      </c>
+      <c r="H177">
+        <v>7</v>
+      </c>
+      <c r="I177">
+        <v>6821</v>
+      </c>
+      <c r="J177">
+        <v>108</v>
+      </c>
+      <c r="K177">
+        <v>30</v>
+      </c>
+      <c r="L177">
+        <v>13</v>
+      </c>
+      <c r="M177">
+        <v>17</v>
+      </c>
+      <c r="N177">
+        <v>2</v>
+      </c>
+      <c r="O177" s="4">
+        <v>7.1759259259259259E-4</v>
+      </c>
+      <c r="P177" s="4">
+        <v>1.2847222222222223E-3</v>
+      </c>
+      <c r="Q177" s="5">
+        <v>1.5800000000000002E-2</v>
+      </c>
+      <c r="R177" s="5">
+        <v>0.27779999999999999</v>
+      </c>
+      <c r="S177" s="5">
+        <v>0.43330000000000002</v>
+      </c>
+      <c r="T177">
+        <v>0</v>
+      </c>
+      <c r="U177" s="3">
+        <v>0</v>
+      </c>
+      <c r="V177" s="5">
+        <v>0.88239999999999996</v>
+      </c>
+      <c r="W177">
+        <v>20.466000000000001</v>
+      </c>
+    </row>
+    <row r="178" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A178" s="2">
+        <v>46197</v>
+      </c>
+      <c r="B178">
+        <v>14</v>
+      </c>
+      <c r="C178">
+        <v>81</v>
+      </c>
+      <c r="D178">
+        <v>85</v>
+      </c>
+      <c r="E178" t="s">
+        <v>26</v>
+      </c>
+      <c r="F178">
+        <v>13133</v>
+      </c>
+      <c r="G178">
+        <v>25</v>
+      </c>
+      <c r="H178">
+        <v>4</v>
+      </c>
+      <c r="I178">
+        <v>11468</v>
+      </c>
+      <c r="J178">
+        <v>97</v>
+      </c>
+      <c r="K178">
+        <v>15</v>
+      </c>
+      <c r="L178">
+        <v>6</v>
+      </c>
+      <c r="M178">
+        <v>8</v>
+      </c>
+      <c r="N178">
+        <v>0</v>
+      </c>
+      <c r="O178" s="4">
+        <v>1.3657407407407407E-3</v>
+      </c>
+      <c r="P178" s="4">
+        <v>1.3194444444444445E-3</v>
+      </c>
+      <c r="Q178" s="5">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="R178" s="5">
+        <v>0.15459999999999999</v>
+      </c>
+      <c r="S178" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="T178">
+        <v>1</v>
+      </c>
+      <c r="U178" s="5">
+        <v>0.1111</v>
+      </c>
+      <c r="V178" s="5">
+        <v>0.77780000000000005</v>
+      </c>
+      <c r="W178">
+        <v>9.6300000000000008</v>
+      </c>
+    </row>
+    <row r="179" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A179" s="2">
+        <v>46197</v>
+      </c>
+      <c r="B179">
+        <v>15</v>
+      </c>
+      <c r="C179">
+        <v>81</v>
+      </c>
+      <c r="D179">
+        <v>85</v>
+      </c>
+      <c r="E179" t="s">
+        <v>26</v>
+      </c>
+      <c r="F179">
+        <v>13133</v>
+      </c>
+      <c r="G179">
+        <v>25</v>
+      </c>
+      <c r="H179">
+        <v>7</v>
+      </c>
+      <c r="I179">
+        <v>14474</v>
+      </c>
+      <c r="J179">
+        <v>191</v>
+      </c>
+      <c r="K179">
+        <v>29</v>
+      </c>
+      <c r="L179">
+        <v>17</v>
+      </c>
+      <c r="M179">
+        <v>12</v>
+      </c>
+      <c r="N179">
+        <v>0</v>
+      </c>
+      <c r="O179" s="4">
+        <v>8.6805555555555551E-4</v>
+      </c>
+      <c r="P179" s="4">
+        <v>7.6388888888888893E-4</v>
+      </c>
+      <c r="Q179" s="5">
+        <v>1.32E-2</v>
+      </c>
+      <c r="R179" s="5">
+        <v>0.15179999999999999</v>
+      </c>
+      <c r="S179" s="5">
+        <v>0.58620000000000005</v>
+      </c>
+      <c r="T179">
+        <v>0</v>
+      </c>
+      <c r="U179" s="3">
+        <v>0</v>
+      </c>
+      <c r="V179" s="5">
+        <v>1</v>
+      </c>
+      <c r="W179">
+        <v>30.617999999999999</v>
+      </c>
+    </row>
+    <row r="180" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A180" s="2">
+        <v>46197</v>
+      </c>
+      <c r="B180">
+        <v>16</v>
+      </c>
+      <c r="C180">
+        <v>81</v>
+      </c>
+      <c r="D180">
+        <v>85</v>
+      </c>
+      <c r="E180" t="s">
+        <v>26</v>
+      </c>
+      <c r="F180">
+        <v>13133</v>
+      </c>
+      <c r="G180">
+        <v>25</v>
+      </c>
+      <c r="H180">
+        <v>5</v>
+      </c>
+      <c r="I180">
+        <v>10739</v>
+      </c>
+      <c r="J180">
+        <v>83</v>
+      </c>
+      <c r="K180">
+        <v>14</v>
+      </c>
+      <c r="L180">
+        <v>8</v>
+      </c>
+      <c r="M180">
+        <v>6</v>
+      </c>
+      <c r="N180">
+        <v>0</v>
+      </c>
+      <c r="O180" s="4">
+        <v>1.4814814814814814E-3</v>
+      </c>
+      <c r="P180" s="4">
+        <v>1.0648148148148149E-3</v>
+      </c>
+      <c r="Q180" s="5">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="R180" s="5">
+        <v>0.16869999999999999</v>
+      </c>
+      <c r="S180" s="5">
+        <v>0.57140000000000002</v>
+      </c>
+      <c r="T180">
+        <v>0</v>
+      </c>
+      <c r="U180" s="3">
+        <v>0</v>
+      </c>
+      <c r="V180" s="5">
+        <v>1</v>
+      </c>
+      <c r="W180">
+        <v>12.69</v>
+      </c>
+    </row>
+    <row r="181" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A181" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B181">
+        <v>9</v>
+      </c>
+      <c r="C181">
+        <v>81</v>
+      </c>
+      <c r="D181">
+        <v>85</v>
+      </c>
+      <c r="E181" t="s">
+        <v>26</v>
+      </c>
+      <c r="F181">
+        <v>10141</v>
+      </c>
+      <c r="G181">
+        <v>4</v>
+      </c>
+      <c r="H181">
+        <v>0</v>
+      </c>
+      <c r="I181">
+        <v>21046</v>
+      </c>
+      <c r="J181">
+        <v>4</v>
+      </c>
+      <c r="K181">
+        <v>0</v>
+      </c>
+      <c r="L181">
+        <v>0</v>
+      </c>
+      <c r="M181">
+        <v>0</v>
+      </c>
+      <c r="N181">
+        <v>0</v>
+      </c>
+      <c r="O181" s="4">
+        <v>1.9131944444444444E-2</v>
+      </c>
+      <c r="P181" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q181" s="5">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="R181" s="3">
+        <v>0</v>
+      </c>
+      <c r="S181" t="s">
+        <v>24</v>
+      </c>
+      <c r="T181">
+        <v>0</v>
+      </c>
+      <c r="U181" t="s">
+        <v>24</v>
+      </c>
+      <c r="V181" t="s">
+        <v>24</v>
+      </c>
+      <c r="W181">
+        <v>257.94</v>
+      </c>
+    </row>
+    <row r="182" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A182" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B182">
+        <v>10</v>
+      </c>
+      <c r="C182">
+        <v>81</v>
+      </c>
+      <c r="D182">
+        <v>85</v>
+      </c>
+      <c r="E182" t="s">
+        <v>26</v>
+      </c>
+      <c r="F182">
+        <v>10141</v>
+      </c>
+      <c r="G182">
+        <v>50</v>
+      </c>
+      <c r="H182">
+        <v>7</v>
+      </c>
+      <c r="I182">
+        <v>19394</v>
+      </c>
+      <c r="J182">
+        <v>74</v>
+      </c>
+      <c r="K182">
+        <v>20</v>
+      </c>
+      <c r="L182">
+        <v>10</v>
+      </c>
+      <c r="M182">
+        <v>10</v>
+      </c>
+      <c r="N182">
+        <v>2</v>
+      </c>
+      <c r="O182" s="4">
+        <v>2.9976851851851853E-3</v>
+      </c>
+      <c r="P182" s="4">
+        <v>1.8518518518518519E-3</v>
+      </c>
+      <c r="Q182" s="5">
+        <v>3.8E-3</v>
+      </c>
+      <c r="R182" s="5">
+        <v>0.27029999999999998</v>
+      </c>
+      <c r="S182" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="T182">
+        <v>0</v>
+      </c>
+      <c r="U182" s="3">
+        <v>0</v>
+      </c>
+      <c r="V182" s="5">
+        <v>1</v>
+      </c>
+      <c r="W182">
+        <v>144.87</v>
+      </c>
+    </row>
+    <row r="183" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A183" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B183">
+        <v>11</v>
+      </c>
+      <c r="C183">
+        <v>81</v>
+      </c>
+      <c r="D183">
+        <v>85</v>
+      </c>
+      <c r="E183" t="s">
+        <v>26</v>
+      </c>
+      <c r="F183">
+        <v>10141</v>
+      </c>
+      <c r="G183">
+        <v>50</v>
+      </c>
+      <c r="H183">
+        <v>11</v>
+      </c>
+      <c r="I183">
+        <v>34690</v>
+      </c>
+      <c r="J183">
+        <v>349</v>
+      </c>
+      <c r="K183">
+        <v>115</v>
+      </c>
+      <c r="L183">
+        <v>61</v>
+      </c>
+      <c r="M183">
+        <v>54</v>
+      </c>
+      <c r="N183">
+        <v>1</v>
+      </c>
+      <c r="O183" s="4">
+        <v>1.1458333333333333E-3</v>
+      </c>
+      <c r="P183" s="4">
+        <v>1.3773148148148147E-3</v>
+      </c>
+      <c r="Q183" s="5">
+        <v>1.01E-2</v>
+      </c>
+      <c r="R183" s="5">
+        <v>0.32950000000000002</v>
+      </c>
+      <c r="S183" s="5">
+        <v>0.53039999999999998</v>
+      </c>
+      <c r="T183">
+        <v>0</v>
+      </c>
+      <c r="U183" s="3">
+        <v>0</v>
+      </c>
+      <c r="V183" s="5">
+        <v>1</v>
+      </c>
+      <c r="W183">
+        <v>69.510000000000005</v>
+      </c>
+    </row>
+    <row r="184" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A184" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B184">
+        <v>12</v>
+      </c>
+      <c r="C184">
+        <v>81</v>
+      </c>
+      <c r="D184">
+        <v>85</v>
+      </c>
+      <c r="E184" t="s">
+        <v>26</v>
+      </c>
+      <c r="F184">
+        <v>10141</v>
+      </c>
+      <c r="G184">
+        <v>50</v>
+      </c>
+      <c r="H184">
+        <v>12</v>
+      </c>
+      <c r="I184">
+        <v>38305</v>
+      </c>
+      <c r="J184">
+        <v>288</v>
+      </c>
+      <c r="K184">
+        <v>73</v>
+      </c>
+      <c r="L184">
+        <v>34</v>
+      </c>
+      <c r="M184">
+        <v>39</v>
+      </c>
+      <c r="N184">
+        <v>0</v>
+      </c>
+      <c r="O184" s="4">
+        <v>1.5277777777777779E-3</v>
+      </c>
+      <c r="P184" s="4">
+        <v>1.4467592592592592E-3</v>
+      </c>
+      <c r="Q184" s="5">
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="R184" s="5">
+        <v>0.2535</v>
+      </c>
+      <c r="S184" s="5">
+        <v>0.46579999999999999</v>
+      </c>
+      <c r="T184">
+        <v>0</v>
+      </c>
+      <c r="U184" s="3">
+        <v>0</v>
+      </c>
+      <c r="V184" s="5">
+        <v>1</v>
+      </c>
+      <c r="W184">
+        <v>29.55</v>
+      </c>
+    </row>
+    <row r="185" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A185" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B185">
+        <v>13</v>
+      </c>
+      <c r="C185">
+        <v>81</v>
+      </c>
+      <c r="D185">
+        <v>85</v>
+      </c>
+      <c r="E185" t="s">
+        <v>26</v>
+      </c>
+      <c r="F185">
+        <v>10141</v>
+      </c>
+      <c r="G185">
+        <v>50</v>
+      </c>
+      <c r="H185">
+        <v>6</v>
+      </c>
+      <c r="I185">
+        <v>29239</v>
+      </c>
+      <c r="J185">
+        <v>207</v>
+      </c>
+      <c r="K185">
+        <v>54</v>
+      </c>
+      <c r="L185">
+        <v>25</v>
+      </c>
+      <c r="M185">
+        <v>14</v>
+      </c>
+      <c r="N185">
+        <v>0</v>
+      </c>
+      <c r="O185" s="4">
+        <v>1.6319444444444445E-3</v>
+      </c>
+      <c r="P185" s="4">
+        <v>1.5509259259259259E-3</v>
+      </c>
+      <c r="Q185" s="5">
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="R185" s="5">
+        <v>0.26090000000000002</v>
+      </c>
+      <c r="S185" s="5">
+        <v>0.46300000000000002</v>
+      </c>
+      <c r="T185">
+        <v>15</v>
+      </c>
+      <c r="U185" s="5">
+        <v>0.51719999999999999</v>
+      </c>
+      <c r="V185" s="5">
+        <v>0.57140000000000002</v>
+      </c>
+      <c r="W185">
+        <v>20.952000000000002</v>
+      </c>
+    </row>
+    <row r="186" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A186" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B186">
+        <v>14</v>
+      </c>
+      <c r="C186">
+        <v>81</v>
+      </c>
+      <c r="D186">
+        <v>85</v>
+      </c>
+      <c r="E186" t="s">
+        <v>26</v>
+      </c>
+      <c r="F186">
+        <v>10141</v>
+      </c>
+      <c r="G186">
+        <v>50</v>
+      </c>
+      <c r="H186">
+        <v>5</v>
+      </c>
+      <c r="I186">
+        <v>12359</v>
+      </c>
+      <c r="J186">
+        <v>191</v>
+      </c>
+      <c r="K186">
+        <v>37</v>
+      </c>
+      <c r="L186">
+        <v>14</v>
+      </c>
+      <c r="M186">
+        <v>17</v>
+      </c>
+      <c r="N186">
+        <v>1</v>
+      </c>
+      <c r="O186" s="4">
+        <v>7.407407407407407E-4</v>
+      </c>
+      <c r="P186" s="4">
+        <v>1.0648148148148149E-3</v>
+      </c>
+      <c r="Q186" s="5">
+        <v>1.55E-2</v>
+      </c>
+      <c r="R186" s="5">
+        <v>0.19370000000000001</v>
+      </c>
+      <c r="S186" s="5">
+        <v>0.37840000000000001</v>
+      </c>
+      <c r="T186">
+        <v>6</v>
+      </c>
+      <c r="U186" s="5">
+        <v>0.26090000000000002</v>
+      </c>
+      <c r="V186" s="5">
+        <v>0.53849999999999998</v>
+      </c>
+      <c r="W186">
+        <v>38.688000000000002</v>
+      </c>
+    </row>
+    <row r="187" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A187" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B187">
+        <v>15</v>
+      </c>
+      <c r="C187">
+        <v>81</v>
+      </c>
+      <c r="D187">
+        <v>85</v>
+      </c>
+      <c r="E187" t="s">
+        <v>26</v>
+      </c>
+      <c r="F187">
+        <v>10141</v>
+      </c>
+      <c r="G187">
+        <v>50</v>
+      </c>
+      <c r="H187">
+        <v>5</v>
+      </c>
+      <c r="I187">
+        <v>9569</v>
+      </c>
+      <c r="J187">
+        <v>120</v>
+      </c>
+      <c r="K187">
+        <v>40</v>
+      </c>
+      <c r="L187">
+        <v>27</v>
+      </c>
+      <c r="M187">
+        <v>10</v>
+      </c>
+      <c r="N187">
+        <v>0</v>
+      </c>
+      <c r="O187" s="4">
+        <v>9.1435185185185185E-4</v>
+      </c>
+      <c r="P187" s="4">
+        <v>1.25E-3</v>
+      </c>
+      <c r="Q187" s="5">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="R187" s="5">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="S187" s="5">
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="T187">
+        <v>3</v>
+      </c>
+      <c r="U187" s="5">
+        <v>0.23080000000000001</v>
+      </c>
+      <c r="V187" s="5">
+        <v>1</v>
+      </c>
+      <c r="W187">
+        <v>19.332000000000001</v>
+      </c>
+    </row>
+    <row r="188" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A188" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B188">
+        <v>16</v>
+      </c>
+      <c r="C188">
+        <v>81</v>
+      </c>
+      <c r="D188">
+        <v>85</v>
+      </c>
+      <c r="E188" t="s">
+        <v>26</v>
+      </c>
+      <c r="F188">
+        <v>10141</v>
+      </c>
+      <c r="G188">
+        <v>50</v>
+      </c>
+      <c r="H188">
+        <v>7</v>
+      </c>
+      <c r="I188">
+        <v>12597</v>
+      </c>
+      <c r="J188">
+        <v>142</v>
+      </c>
+      <c r="K188">
+        <v>49</v>
+      </c>
+      <c r="L188">
+        <v>29</v>
+      </c>
+      <c r="M188">
+        <v>17</v>
+      </c>
+      <c r="N188">
+        <v>0</v>
+      </c>
+      <c r="O188" s="4">
+        <v>1.0069444444444444E-3</v>
+      </c>
+      <c r="P188" s="4">
+        <v>1.0763888888888889E-3</v>
+      </c>
+      <c r="Q188" s="5">
+        <v>1.1299999999999999E-2</v>
+      </c>
+      <c r="R188" s="5">
+        <v>0.34510000000000002</v>
+      </c>
+      <c r="S188" s="5">
+        <v>0.59179999999999999</v>
+      </c>
+      <c r="T188">
+        <v>3</v>
+      </c>
+      <c r="U188" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="V188" s="5">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="W188">
+        <v>28.038</v>
+      </c>
+    </row>
+    <row r="189" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A189" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B189">
+        <v>17</v>
+      </c>
+      <c r="C189">
+        <v>81</v>
+      </c>
+      <c r="D189">
+        <v>85</v>
+      </c>
+      <c r="E189" t="s">
+        <v>26</v>
+      </c>
+      <c r="F189">
+        <v>10141</v>
+      </c>
+      <c r="G189">
+        <v>50</v>
+      </c>
+      <c r="H189">
+        <v>5</v>
+      </c>
+      <c r="I189">
+        <v>17041</v>
+      </c>
+      <c r="J189">
+        <v>129</v>
+      </c>
+      <c r="K189">
+        <v>32</v>
+      </c>
+      <c r="L189">
+        <v>17</v>
+      </c>
+      <c r="M189">
+        <v>15</v>
+      </c>
+      <c r="N189">
+        <v>0</v>
+      </c>
+      <c r="O189" s="4">
+        <v>1.5162037037037036E-3</v>
+      </c>
+      <c r="P189" s="4">
+        <v>8.564814814814815E-4</v>
+      </c>
+      <c r="Q189" s="5">
+        <v>7.6E-3</v>
+      </c>
+      <c r="R189" s="5">
+        <v>0.24809999999999999</v>
+      </c>
+      <c r="S189" s="5">
+        <v>0.53129999999999999</v>
+      </c>
+      <c r="T189">
+        <v>0</v>
+      </c>
+      <c r="U189" s="3">
+        <v>0</v>
+      </c>
+      <c r="V189" s="5">
+        <v>0.9375</v>
+      </c>
+      <c r="W189">
+        <v>21.846</v>
+      </c>
+    </row>
+    <row r="190" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A190" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B190">
+        <v>18</v>
+      </c>
+      <c r="C190">
+        <v>81</v>
+      </c>
+      <c r="D190">
+        <v>85</v>
+      </c>
+      <c r="E190" t="s">
+        <v>26</v>
+      </c>
+      <c r="F190">
+        <v>10141</v>
+      </c>
+      <c r="G190">
+        <v>0</v>
+      </c>
+      <c r="H190">
+        <v>0</v>
+      </c>
+      <c r="I190">
+        <v>26</v>
+      </c>
+      <c r="J190">
+        <v>0</v>
+      </c>
+      <c r="K190">
+        <v>0</v>
+      </c>
+      <c r="L190">
+        <v>0</v>
+      </c>
+      <c r="M190">
+        <v>0</v>
+      </c>
+      <c r="N190">
+        <v>0</v>
+      </c>
+      <c r="O190" t="s">
+        <v>23</v>
+      </c>
+      <c r="P190" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q190" s="3">
+        <v>0</v>
+      </c>
+      <c r="R190" t="s">
+        <v>24</v>
+      </c>
+      <c r="S190" t="s">
+        <v>24</v>
+      </c>
+      <c r="T190">
+        <v>0</v>
+      </c>
+      <c r="U190" t="s">
+        <v>24</v>
+      </c>
+      <c r="V190" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="191" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A191" s="2">
+        <v>46199</v>
+      </c>
+      <c r="B191">
+        <v>9</v>
+      </c>
+      <c r="C191">
+        <v>81</v>
+      </c>
+      <c r="D191">
+        <v>85</v>
+      </c>
+      <c r="E191" t="s">
+        <v>26</v>
+      </c>
+      <c r="F191">
+        <v>10023</v>
+      </c>
+      <c r="G191">
+        <v>50</v>
+      </c>
+      <c r="H191">
+        <v>7</v>
+      </c>
+      <c r="I191">
+        <v>37184</v>
+      </c>
+      <c r="J191">
+        <v>312</v>
+      </c>
+      <c r="K191">
+        <v>39</v>
+      </c>
+      <c r="L191">
+        <v>0</v>
+      </c>
+      <c r="M191">
+        <v>35</v>
+      </c>
+      <c r="N191">
+        <v>2</v>
+      </c>
+      <c r="O191" s="4">
+        <v>1.3773148148148147E-3</v>
+      </c>
+      <c r="P191" s="4">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="Q191" s="5">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="R191" s="5">
+        <v>0.125</v>
+      </c>
+      <c r="S191" s="3">
+        <v>0</v>
+      </c>
+      <c r="T191">
+        <v>4</v>
+      </c>
+      <c r="U191" s="5">
+        <v>0.1026</v>
+      </c>
+      <c r="V191" s="5">
+        <v>0.63890000000000002</v>
+      </c>
+      <c r="W191">
+        <v>93.683999999999997</v>
+      </c>
+    </row>
+    <row r="192" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A192" s="2">
+        <v>46199</v>
+      </c>
+      <c r="B192">
+        <v>10</v>
+      </c>
+      <c r="C192">
+        <v>81</v>
+      </c>
+      <c r="D192">
+        <v>85</v>
+      </c>
+      <c r="E192" t="s">
+        <v>26</v>
+      </c>
+      <c r="F192">
+        <v>10023</v>
+      </c>
+      <c r="G192">
+        <v>50</v>
+      </c>
+      <c r="H192">
+        <v>9</v>
+      </c>
+      <c r="I192">
+        <v>33856</v>
+      </c>
+      <c r="J192">
+        <v>188</v>
+      </c>
+      <c r="K192">
+        <v>21</v>
+      </c>
+      <c r="L192">
+        <v>0</v>
+      </c>
+      <c r="M192">
+        <v>21</v>
+      </c>
+      <c r="N192">
+        <v>1</v>
+      </c>
+      <c r="O192" s="4">
+        <v>2.0717592592592593E-3</v>
+      </c>
+      <c r="P192" s="4">
+        <v>1.3773148148148147E-3</v>
+      </c>
+      <c r="Q192" s="5">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="R192" s="5">
+        <v>0.11169999999999999</v>
+      </c>
+      <c r="S192" s="3">
+        <v>0</v>
+      </c>
+      <c r="T192">
+        <v>0</v>
+      </c>
+      <c r="U192" s="3">
+        <v>0</v>
+      </c>
+      <c r="V192" s="5">
+        <v>1</v>
+      </c>
+      <c r="W192">
+        <v>27.24</v>
+      </c>
+    </row>
+    <row r="193" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A193" s="2">
+        <v>46199</v>
+      </c>
+      <c r="B193">
+        <v>11</v>
+      </c>
+      <c r="C193">
+        <v>81</v>
+      </c>
+      <c r="D193">
+        <v>85</v>
+      </c>
+      <c r="E193" t="s">
+        <v>26</v>
+      </c>
+      <c r="F193">
+        <v>10023</v>
+      </c>
+      <c r="G193">
+        <v>50</v>
+      </c>
+      <c r="H193">
+        <v>11</v>
+      </c>
+      <c r="I193">
+        <v>39018</v>
+      </c>
+      <c r="J193">
+        <v>292</v>
+      </c>
+      <c r="K193">
+        <v>32</v>
+      </c>
+      <c r="L193">
+        <v>0</v>
+      </c>
+      <c r="M193">
+        <v>32</v>
+      </c>
+      <c r="N193">
+        <v>3</v>
+      </c>
+      <c r="O193" s="4">
+        <v>1.5393518518518519E-3</v>
+      </c>
+      <c r="P193" s="4">
+        <v>1.7824074074074075E-3</v>
+      </c>
+      <c r="Q193" s="5">
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="R193" s="5">
+        <v>0.1096</v>
+      </c>
+      <c r="S193" s="3">
+        <v>0</v>
+      </c>
+      <c r="T193">
+        <v>0</v>
+      </c>
+      <c r="U193" s="3">
+        <v>0</v>
+      </c>
+      <c r="V193" s="5">
+        <v>1</v>
+      </c>
+      <c r="W193">
+        <v>35.154000000000003</v>
+      </c>
+    </row>
+    <row r="194" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A194" s="2">
+        <v>46199</v>
+      </c>
+      <c r="B194">
+        <v>12</v>
+      </c>
+      <c r="C194">
+        <v>81</v>
+      </c>
+      <c r="D194">
+        <v>85</v>
+      </c>
+      <c r="E194" t="s">
+        <v>26</v>
+      </c>
+      <c r="F194">
+        <v>10023</v>
+      </c>
+      <c r="G194">
+        <v>50</v>
+      </c>
+      <c r="H194">
+        <v>7</v>
+      </c>
+      <c r="I194">
+        <v>11449</v>
+      </c>
+      <c r="J194">
+        <v>81</v>
+      </c>
+      <c r="K194">
+        <v>9</v>
+      </c>
+      <c r="L194">
+        <v>0</v>
+      </c>
+      <c r="M194">
+        <v>9</v>
+      </c>
+      <c r="N194">
+        <v>0</v>
+      </c>
+      <c r="O194" s="4">
+        <v>1.6319444444444445E-3</v>
+      </c>
+      <c r="P194" s="4">
+        <v>5.6712962962962967E-4</v>
+      </c>
+      <c r="Q194" s="5">
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="R194" s="5">
+        <v>0.1111</v>
+      </c>
+      <c r="S194" s="3">
+        <v>0</v>
+      </c>
+      <c r="T194">
+        <v>0</v>
+      </c>
+      <c r="U194" s="3">
+        <v>0</v>
+      </c>
+      <c r="V194" s="5">
+        <v>1</v>
+      </c>
+      <c r="W194">
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="195" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A195" s="2">
+        <v>46199</v>
+      </c>
+      <c r="B195">
+        <v>13</v>
+      </c>
+      <c r="C195">
+        <v>81</v>
+      </c>
+      <c r="D195">
+        <v>85</v>
+      </c>
+      <c r="E195" t="s">
+        <v>26</v>
+      </c>
+      <c r="F195">
+        <v>10023</v>
+      </c>
+      <c r="G195">
+        <v>50</v>
+      </c>
+      <c r="H195">
+        <v>3</v>
+      </c>
+      <c r="I195">
+        <v>10326</v>
+      </c>
+      <c r="J195">
+        <v>124</v>
+      </c>
+      <c r="K195">
+        <v>19</v>
+      </c>
+      <c r="L195">
+        <v>0</v>
+      </c>
+      <c r="M195">
+        <v>4</v>
+      </c>
+      <c r="N195">
+        <v>0</v>
+      </c>
+      <c r="O195" s="4">
+        <v>9.6064814814814819E-4</v>
+      </c>
+      <c r="P195" s="4">
+        <v>2.638888888888889E-3</v>
+      </c>
+      <c r="Q195" s="5">
+        <v>1.2E-2</v>
+      </c>
+      <c r="R195" s="5">
+        <v>0.1532</v>
+      </c>
+      <c r="S195" s="3">
+        <v>0</v>
+      </c>
+      <c r="T195">
+        <v>15</v>
+      </c>
+      <c r="U195" s="5">
+        <v>0.78949999999999998</v>
+      </c>
+      <c r="V195" s="5">
+        <v>0.1053</v>
+      </c>
+      <c r="W195">
+        <v>31.193999999999999</v>
+      </c>
+    </row>
+    <row r="196" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A196" s="2">
+        <v>46199</v>
+      </c>
+      <c r="B196">
+        <v>14</v>
+      </c>
+      <c r="C196">
+        <v>81</v>
+      </c>
+      <c r="D196">
+        <v>85</v>
+      </c>
+      <c r="E196" t="s">
+        <v>26</v>
+      </c>
+      <c r="F196">
+        <v>10023</v>
+      </c>
+      <c r="G196">
+        <v>50</v>
+      </c>
+      <c r="H196">
+        <v>5</v>
+      </c>
+      <c r="I196">
+        <v>16318</v>
+      </c>
+      <c r="J196">
+        <v>128</v>
+      </c>
+      <c r="K196">
+        <v>9</v>
+      </c>
+      <c r="L196">
+        <v>0</v>
+      </c>
+      <c r="M196">
+        <v>9</v>
+      </c>
+      <c r="N196">
+        <v>0</v>
+      </c>
+      <c r="O196" s="4">
+        <v>1.4699074074074074E-3</v>
+      </c>
+      <c r="P196" s="4">
+        <v>9.3749999999999997E-4</v>
+      </c>
+      <c r="Q196" s="5">
+        <v>7.7999999999999996E-3</v>
+      </c>
+      <c r="R196" s="5">
+        <v>7.0300000000000001E-2</v>
+      </c>
+      <c r="S196" s="3">
+        <v>0</v>
+      </c>
+      <c r="T196">
+        <v>0</v>
+      </c>
+      <c r="U196" s="3">
+        <v>0</v>
+      </c>
+      <c r="V196" s="5">
+        <v>0.88890000000000002</v>
+      </c>
+      <c r="W196">
+        <v>17.861999999999998</v>
+      </c>
+    </row>
+    <row r="197" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A197" s="2">
+        <v>46199</v>
+      </c>
+      <c r="B197">
+        <v>15</v>
+      </c>
+      <c r="C197">
+        <v>81</v>
+      </c>
+      <c r="D197">
+        <v>85</v>
+      </c>
+      <c r="E197" t="s">
+        <v>26</v>
+      </c>
+      <c r="F197">
+        <v>10023</v>
+      </c>
+      <c r="G197">
+        <v>50</v>
+      </c>
+      <c r="H197">
+        <v>4</v>
+      </c>
+      <c r="I197">
+        <v>21089</v>
+      </c>
+      <c r="J197">
+        <v>233</v>
+      </c>
+      <c r="K197">
+        <v>19</v>
+      </c>
+      <c r="L197">
+        <v>0</v>
+      </c>
+      <c r="M197">
+        <v>19</v>
+      </c>
+      <c r="N197">
+        <v>0</v>
+      </c>
+      <c r="O197" s="4">
+        <v>1.0416666666666667E-3</v>
+      </c>
+      <c r="P197" s="4">
+        <v>9.4907407407407408E-4</v>
+      </c>
+      <c r="Q197" s="5">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="R197" s="5">
+        <v>8.1500000000000003E-2</v>
+      </c>
+      <c r="S197" s="3">
+        <v>0</v>
+      </c>
+      <c r="T197">
+        <v>0</v>
+      </c>
+      <c r="U197" s="3">
+        <v>0</v>
+      </c>
+      <c r="V197" s="5">
+        <v>1</v>
+      </c>
+      <c r="W197">
+        <v>27.06</v>
+      </c>
+    </row>
+    <row r="198" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A198" s="2">
+        <v>46199</v>
+      </c>
+      <c r="B198">
+        <v>15</v>
+      </c>
+      <c r="C198">
+        <v>84</v>
+      </c>
+      <c r="D198">
+        <v>86</v>
+      </c>
+      <c r="E198" t="s">
+        <v>25</v>
+      </c>
+      <c r="F198">
+        <v>31375</v>
+      </c>
+      <c r="G198">
+        <v>40</v>
+      </c>
+      <c r="H198">
+        <v>3</v>
+      </c>
+      <c r="I198">
+        <v>3452</v>
+      </c>
+      <c r="J198">
+        <v>92</v>
+      </c>
+      <c r="K198">
+        <v>20</v>
+      </c>
+      <c r="L198">
+        <v>0</v>
+      </c>
+      <c r="M198">
+        <v>19</v>
+      </c>
+      <c r="N198">
+        <v>1</v>
+      </c>
+      <c r="O198" s="4">
+        <v>4.2824074074074075E-4</v>
+      </c>
+      <c r="P198" s="4">
+        <v>5.3240740740740744E-4</v>
+      </c>
+      <c r="Q198" s="5">
+        <v>2.6700000000000002E-2</v>
+      </c>
+      <c r="R198" s="5">
+        <v>0.21740000000000001</v>
+      </c>
+      <c r="S198" s="3">
+        <v>0</v>
+      </c>
+      <c r="T198">
+        <v>1</v>
+      </c>
+      <c r="U198" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="V198" s="5">
+        <v>0.92310000000000003</v>
+      </c>
+      <c r="W198">
+        <v>14.628</v>
       </c>
     </row>
   </sheetData>
